--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>编号</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>手枪1</t>
+  </si>
+  <si>
+    <t>刀2</t>
   </si>
 </sst>
 </file>
@@ -355,12 +358,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1566,16 +1569,36 @@
       <c r="P10" s="3"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G11" s="3">
+        <v>15</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>100</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>编号</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>名称</t>
+  </si>
+  <si>
+    <t>价格</t>
   </si>
   <si>
     <t>攻击间隔</t>
@@ -133,6 +136,9 @@
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>value</t>
   </si>
   <si>
     <t>attackInterval</t>
@@ -1176,15 +1182,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P608"/>
+  <dimension ref="A1:Q608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="12" width="25.125" style="2" customWidth="1"/>
-    <col min="13" max="16" width="25.125" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="1" max="13" width="25.125" style="2" customWidth="1"/>
+    <col min="14" max="17" width="25.125" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:16">
+    <row r="1" ht="16.5" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1221,84 +1227,93 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:16">
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:16">
+        <v>24</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:17">
       <c r="A3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:16">
+        <v>27</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:17">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1309,34 +1324,37 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F4" s="3">
         <v>0.5</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>2000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>10</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
       </c>
       <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
         <v>100</v>
       </c>
-      <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:16">
+      <c r="Q4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:17">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1347,34 +1365,37 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F5" s="3">
         <v>0.15</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>2000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>3</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>0.9</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>30</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>600</v>
       </c>
-      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:16">
+      <c r="Q5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:17">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1385,34 +1406,37 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F6" s="3">
         <v>0.05</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>2000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>4</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>0.9</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>25</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>600</v>
       </c>
-      <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:16">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:17">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1423,34 +1447,37 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F7" s="3">
         <v>0.2</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>2000</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>5</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>0.6</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>75</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>600</v>
       </c>
-      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:16">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:17">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1461,36 +1488,39 @@
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>0.9</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8</v>
       </c>
-      <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:16">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:17">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1501,36 +1531,39 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>0.8</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
+      <c r="L9" s="3"/>
+      <c r="M9" s="3">
         <v>1</v>
       </c>
-      <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:16">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:17">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1541,34 +1574,37 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F10" s="3">
         <v>0.2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>0.9</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:16">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:17">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1579,34 +1615,37 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F11" s="3">
         <v>0.2</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>2000</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>15</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
       </c>
       <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3">
         <v>100</v>
       </c>
-      <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:17">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1623,8 +1662,9 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:16">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:17">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1641,8 +1681,9 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:16">
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:17">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1659,8 +1700,9 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:16">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:17">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1677,8 +1719,9 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1691,8 +1734,9 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1705,8 +1749,9 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1719,8 +1764,9 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1733,8 +1779,9 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1747,8 +1794,9 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1761,8 +1809,9 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1775,8 +1824,9 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1789,8 +1839,9 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1803,8 +1854,9 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1817,8 +1869,9 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1831,8 +1884,9 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1845,8 +1899,9 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="M27" s="5"/>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1859,8 +1914,9 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="M28" s="5"/>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1873,8 +1929,9 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="M29" s="5"/>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1887,8 +1944,9 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="M30" s="5"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1901,8 +1959,9 @@
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1915,8 +1974,9 @@
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" s="5"/>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1929,8 +1989,9 @@
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="5"/>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -1943,8 +2004,9 @@
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" s="5"/>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -1957,8 +2019,9 @@
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" s="5"/>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -1971,8 +2034,9 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="M36" s="5"/>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -1985,8 +2049,9 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" s="5"/>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -1999,8 +2064,9 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" s="5"/>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2013,8 +2079,9 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="M39" s="5"/>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2027,8 +2094,9 @@
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="5"/>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2041,8 +2109,9 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="M41" s="5"/>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2055,8 +2124,9 @@
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="M42" s="5"/>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2069,8 +2139,9 @@
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="M43" s="5"/>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2083,8 +2154,9 @@
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="M44" s="5"/>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2097,8 +2169,9 @@
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="M45" s="5"/>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2111,8 +2184,9 @@
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="M46" s="5"/>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2125,8 +2199,9 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="M47" s="5"/>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2139,8 +2214,9 @@
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="M48" s="5"/>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2153,8 +2229,9 @@
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="M49" s="5"/>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2167,8 +2244,9 @@
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="M50" s="5"/>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2181,8 +2259,9 @@
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="M51" s="5"/>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2195,8 +2274,9 @@
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="M52" s="5"/>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2209,8 +2289,9 @@
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="M53" s="5"/>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2223,8 +2304,9 @@
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="M54" s="5"/>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2237,8 +2319,9 @@
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="M55" s="5"/>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2251,8 +2334,9 @@
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="M56" s="5"/>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2265,8 +2349,9 @@
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="M57" s="5"/>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2279,8 +2364,9 @@
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="M58" s="5"/>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2293,8 +2379,9 @@
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="M59" s="5"/>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2307,8 +2394,9 @@
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="M60" s="5"/>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2321,8 +2409,9 @@
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="M61" s="5"/>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2335,8 +2424,9 @@
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="M62" s="5"/>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2349,8 +2439,9 @@
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="M63" s="5"/>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2363,8 +2454,9 @@
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="M64" s="5"/>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2377,8 +2469,9 @@
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="M65" s="5"/>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2391,8 +2484,9 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="M66" s="5"/>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2405,8 +2499,9 @@
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="M67" s="5"/>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2419,8 +2514,9 @@
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="M68" s="5"/>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2433,8 +2529,9 @@
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="M69" s="5"/>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2447,8 +2544,9 @@
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
-    </row>
-    <row r="71" spans="1:12">
+      <c r="M70" s="5"/>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2461,8 +2559,9 @@
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
-    </row>
-    <row r="72" spans="1:12">
+      <c r="M71" s="5"/>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2475,8 +2574,9 @@
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="M72" s="5"/>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2489,8 +2589,9 @@
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
-    </row>
-    <row r="74" spans="1:12">
+      <c r="M73" s="5"/>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2503,8 +2604,9 @@
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
-    </row>
-    <row r="75" spans="1:12">
+      <c r="M74" s="5"/>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2517,8 +2619,9 @@
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
-    </row>
-    <row r="76" spans="1:12">
+      <c r="M75" s="5"/>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -2531,8 +2634,9 @@
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
-    </row>
-    <row r="77" spans="1:12">
+      <c r="M76" s="5"/>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2545,8 +2649,9 @@
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
-    </row>
-    <row r="78" spans="1:12">
+      <c r="M77" s="5"/>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -2559,8 +2664,9 @@
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
-    </row>
-    <row r="79" spans="1:12">
+      <c r="M78" s="5"/>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2573,8 +2679,9 @@
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
-    </row>
-    <row r="80" spans="1:12">
+      <c r="M79" s="5"/>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2587,8 +2694,9 @@
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
-    </row>
-    <row r="81" spans="1:12">
+      <c r="M80" s="5"/>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2601,8 +2709,9 @@
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
-    </row>
-    <row r="82" spans="1:12">
+      <c r="M81" s="5"/>
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -2615,8 +2724,9 @@
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
       <c r="L82" s="5"/>
-    </row>
-    <row r="83" spans="1:12">
+      <c r="M82" s="5"/>
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2629,8 +2739,9 @@
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
-    </row>
-    <row r="84" spans="1:12">
+      <c r="M83" s="5"/>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -2643,8 +2754,9 @@
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
       <c r="L84" s="5"/>
-    </row>
-    <row r="85" spans="1:12">
+      <c r="M84" s="5"/>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -2657,8 +2769,9 @@
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
       <c r="L85" s="5"/>
-    </row>
-    <row r="86" spans="1:12">
+      <c r="M85" s="5"/>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -2671,8 +2784,9 @@
       <c r="J86" s="5"/>
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
-    </row>
-    <row r="87" spans="1:12">
+      <c r="M86" s="5"/>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -2685,8 +2799,9 @@
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
-    </row>
-    <row r="88" spans="1:12">
+      <c r="M87" s="5"/>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -2699,8 +2814,9 @@
       <c r="J88" s="5"/>
       <c r="K88" s="5"/>
       <c r="L88" s="5"/>
-    </row>
-    <row r="89" spans="1:12">
+      <c r="M88" s="5"/>
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -2713,8 +2829,9 @@
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
-    </row>
-    <row r="90" spans="1:12">
+      <c r="M89" s="5"/>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -2727,8 +2844,9 @@
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
-    </row>
-    <row r="91" spans="1:12">
+      <c r="M90" s="5"/>
+    </row>
+    <row r="91" spans="1:13">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -2741,8 +2859,9 @@
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
-    </row>
-    <row r="92" spans="1:12">
+      <c r="M91" s="5"/>
+    </row>
+    <row r="92" spans="1:13">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -2755,8 +2874,9 @@
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
       <c r="L92" s="5"/>
-    </row>
-    <row r="93" spans="1:12">
+      <c r="M92" s="5"/>
+    </row>
+    <row r="93" spans="1:13">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2769,8 +2889,9 @@
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
       <c r="L93" s="5"/>
-    </row>
-    <row r="94" spans="1:12">
+      <c r="M93" s="5"/>
+    </row>
+    <row r="94" spans="1:13">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -2783,8 +2904,9 @@
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
       <c r="L94" s="5"/>
-    </row>
-    <row r="95" spans="1:12">
+      <c r="M94" s="5"/>
+    </row>
+    <row r="95" spans="1:13">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -2797,8 +2919,9 @@
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
       <c r="L95" s="5"/>
-    </row>
-    <row r="96" spans="1:12">
+      <c r="M95" s="5"/>
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -2811,8 +2934,9 @@
       <c r="J96" s="5"/>
       <c r="K96" s="5"/>
       <c r="L96" s="5"/>
-    </row>
-    <row r="97" spans="1:12">
+      <c r="M96" s="5"/>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -2825,8 +2949,9 @@
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
       <c r="L97" s="5"/>
-    </row>
-    <row r="98" spans="1:12">
+      <c r="M97" s="5"/>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -2839,8 +2964,9 @@
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
       <c r="L98" s="5"/>
-    </row>
-    <row r="99" spans="1:12">
+      <c r="M98" s="5"/>
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -2853,8 +2979,9 @@
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
-    </row>
-    <row r="100" spans="1:12">
+      <c r="M99" s="5"/>
+    </row>
+    <row r="100" spans="1:13">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -2867,8 +2994,9 @@
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
-    </row>
-    <row r="101" spans="1:12">
+      <c r="M100" s="5"/>
+    </row>
+    <row r="101" spans="1:13">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -2881,8 +3009,9 @@
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
-    </row>
-    <row r="102" spans="1:12">
+      <c r="M101" s="5"/>
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -2895,8 +3024,9 @@
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
       <c r="L102" s="5"/>
-    </row>
-    <row r="103" spans="1:12">
+      <c r="M102" s="5"/>
+    </row>
+    <row r="103" spans="1:13">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -2909,8 +3039,9 @@
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
       <c r="L103" s="5"/>
-    </row>
-    <row r="104" spans="1:12">
+      <c r="M103" s="5"/>
+    </row>
+    <row r="104" spans="1:13">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -2923,8 +3054,9 @@
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
-    </row>
-    <row r="105" spans="1:12">
+      <c r="M104" s="5"/>
+    </row>
+    <row r="105" spans="1:13">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -2937,8 +3069,9 @@
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
       <c r="L105" s="5"/>
-    </row>
-    <row r="106" spans="1:12">
+      <c r="M105" s="5"/>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -2951,8 +3084,9 @@
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
       <c r="L106" s="5"/>
-    </row>
-    <row r="107" spans="1:12">
+      <c r="M106" s="5"/>
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -2965,8 +3099,9 @@
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
       <c r="L107" s="5"/>
-    </row>
-    <row r="108" spans="1:12">
+      <c r="M107" s="5"/>
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -2979,8 +3114,9 @@
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
       <c r="L108" s="5"/>
-    </row>
-    <row r="109" spans="1:12">
+      <c r="M108" s="5"/>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -2993,8 +3129,9 @@
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
       <c r="L109" s="5"/>
-    </row>
-    <row r="110" spans="1:12">
+      <c r="M109" s="5"/>
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3007,8 +3144,9 @@
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
-    </row>
-    <row r="111" spans="1:12">
+      <c r="M110" s="5"/>
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3021,8 +3159,9 @@
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
       <c r="L111" s="5"/>
-    </row>
-    <row r="112" spans="1:12">
+      <c r="M111" s="5"/>
+    </row>
+    <row r="112" spans="1:13">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3035,8 +3174,9 @@
       <c r="J112" s="5"/>
       <c r="K112" s="5"/>
       <c r="L112" s="5"/>
-    </row>
-    <row r="113" spans="1:12">
+      <c r="M112" s="5"/>
+    </row>
+    <row r="113" spans="1:13">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3049,8 +3189,9 @@
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
-    </row>
-    <row r="114" spans="1:12">
+      <c r="M113" s="5"/>
+    </row>
+    <row r="114" spans="1:13">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -3063,8 +3204,9 @@
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
       <c r="L114" s="5"/>
-    </row>
-    <row r="115" spans="1:12">
+      <c r="M114" s="5"/>
+    </row>
+    <row r="115" spans="1:13">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3077,8 +3219,9 @@
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
       <c r="L115" s="5"/>
-    </row>
-    <row r="116" spans="1:12">
+      <c r="M115" s="5"/>
+    </row>
+    <row r="116" spans="1:13">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3091,8 +3234,9 @@
       <c r="J116" s="5"/>
       <c r="K116" s="5"/>
       <c r="L116" s="5"/>
-    </row>
-    <row r="117" spans="1:12">
+      <c r="M116" s="5"/>
+    </row>
+    <row r="117" spans="1:13">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -3105,8 +3249,9 @@
       <c r="J117" s="5"/>
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
-    </row>
-    <row r="118" spans="1:12">
+      <c r="M117" s="5"/>
+    </row>
+    <row r="118" spans="1:13">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -3119,8 +3264,9 @@
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
       <c r="L118" s="5"/>
-    </row>
-    <row r="119" spans="1:12">
+      <c r="M118" s="5"/>
+    </row>
+    <row r="119" spans="1:13">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -3133,8 +3279,9 @@
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
-    </row>
-    <row r="120" spans="1:12">
+      <c r="M119" s="5"/>
+    </row>
+    <row r="120" spans="1:13">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -3147,8 +3294,9 @@
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
       <c r="L120" s="5"/>
-    </row>
-    <row r="121" spans="1:12">
+      <c r="M120" s="5"/>
+    </row>
+    <row r="121" spans="1:13">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -3161,8 +3309,9 @@
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
       <c r="L121" s="5"/>
-    </row>
-    <row r="122" spans="1:12">
+      <c r="M121" s="5"/>
+    </row>
+    <row r="122" spans="1:13">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -3175,8 +3324,9 @@
       <c r="J122" s="5"/>
       <c r="K122" s="5"/>
       <c r="L122" s="5"/>
-    </row>
-    <row r="123" spans="1:12">
+      <c r="M122" s="5"/>
+    </row>
+    <row r="123" spans="1:13">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -3189,8 +3339,9 @@
       <c r="J123" s="5"/>
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
-    </row>
-    <row r="124" spans="1:12">
+      <c r="M123" s="5"/>
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -3203,8 +3354,9 @@
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
-    </row>
-    <row r="125" spans="1:12">
+      <c r="M124" s="5"/>
+    </row>
+    <row r="125" spans="1:13">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -3217,8 +3369,9 @@
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
       <c r="L125" s="5"/>
-    </row>
-    <row r="126" spans="1:12">
+      <c r="M125" s="5"/>
+    </row>
+    <row r="126" spans="1:13">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -3231,8 +3384,9 @@
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
       <c r="L126" s="5"/>
-    </row>
-    <row r="127" spans="1:12">
+      <c r="M126" s="5"/>
+    </row>
+    <row r="127" spans="1:13">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -3245,8 +3399,9 @@
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
       <c r="L127" s="5"/>
-    </row>
-    <row r="128" spans="1:12">
+      <c r="M127" s="5"/>
+    </row>
+    <row r="128" spans="1:13">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3259,8 +3414,9 @@
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
       <c r="L128" s="5"/>
-    </row>
-    <row r="129" spans="1:12">
+      <c r="M128" s="5"/>
+    </row>
+    <row r="129" spans="1:13">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -3273,8 +3429,9 @@
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
       <c r="L129" s="5"/>
-    </row>
-    <row r="130" spans="1:12">
+      <c r="M129" s="5"/>
+    </row>
+    <row r="130" spans="1:13">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -3287,8 +3444,9 @@
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
       <c r="L130" s="5"/>
-    </row>
-    <row r="131" spans="1:12">
+      <c r="M130" s="5"/>
+    </row>
+    <row r="131" spans="1:13">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -3301,8 +3459,9 @@
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
       <c r="L131" s="5"/>
-    </row>
-    <row r="132" spans="1:12">
+      <c r="M131" s="5"/>
+    </row>
+    <row r="132" spans="1:13">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -3315,8 +3474,9 @@
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
-    </row>
-    <row r="133" spans="1:12">
+      <c r="M132" s="5"/>
+    </row>
+    <row r="133" spans="1:13">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -3329,8 +3489,9 @@
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
       <c r="L133" s="5"/>
-    </row>
-    <row r="134" spans="1:12">
+      <c r="M133" s="5"/>
+    </row>
+    <row r="134" spans="1:13">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -3343,8 +3504,9 @@
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
-    </row>
-    <row r="135" spans="1:12">
+      <c r="M134" s="5"/>
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -3357,8 +3519,9 @@
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
       <c r="L135" s="5"/>
-    </row>
-    <row r="136" spans="1:12">
+      <c r="M135" s="5"/>
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -3371,8 +3534,9 @@
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
-    </row>
-    <row r="137" spans="1:12">
+      <c r="M136" s="5"/>
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -3385,8 +3549,9 @@
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
-    </row>
-    <row r="138" spans="1:12">
+      <c r="M137" s="5"/>
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -3399,8 +3564,9 @@
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
       <c r="L138" s="5"/>
-    </row>
-    <row r="139" spans="1:12">
+      <c r="M138" s="5"/>
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -3413,8 +3579,9 @@
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
       <c r="L139" s="5"/>
-    </row>
-    <row r="140" spans="1:12">
+      <c r="M139" s="5"/>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -3427,8 +3594,9 @@
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
       <c r="L140" s="5"/>
-    </row>
-    <row r="141" spans="1:12">
+      <c r="M140" s="5"/>
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -3441,8 +3609,9 @@
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
       <c r="L141" s="5"/>
-    </row>
-    <row r="142" spans="1:12">
+      <c r="M141" s="5"/>
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -3455,8 +3624,9 @@
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
       <c r="L142" s="5"/>
-    </row>
-    <row r="143" spans="1:12">
+      <c r="M142" s="5"/>
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -3469,8 +3639,9 @@
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
       <c r="L143" s="5"/>
-    </row>
-    <row r="144" spans="1:12">
+      <c r="M143" s="5"/>
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -3483,8 +3654,9 @@
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
       <c r="L144" s="5"/>
-    </row>
-    <row r="145" spans="1:12">
+      <c r="M144" s="5"/>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -3497,8 +3669,9 @@
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
-    </row>
-    <row r="146" spans="1:12">
+      <c r="M145" s="5"/>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -3511,8 +3684,9 @@
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
-    </row>
-    <row r="147" spans="1:12">
+      <c r="M146" s="5"/>
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -3525,8 +3699,9 @@
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
-    </row>
-    <row r="148" spans="1:12">
+      <c r="M147" s="5"/>
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -3539,8 +3714,9 @@
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
-    </row>
-    <row r="149" spans="1:12">
+      <c r="M148" s="5"/>
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -3553,8 +3729,9 @@
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
-    </row>
-    <row r="150" spans="1:12">
+      <c r="M149" s="5"/>
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -3567,8 +3744,9 @@
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
-    </row>
-    <row r="151" spans="1:12">
+      <c r="M150" s="5"/>
+    </row>
+    <row r="151" spans="1:13">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -3581,8 +3759,9 @@
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
-    </row>
-    <row r="152" spans="1:12">
+      <c r="M151" s="5"/>
+    </row>
+    <row r="152" spans="1:13">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -3595,8 +3774,9 @@
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
-    </row>
-    <row r="153" spans="1:12">
+      <c r="M152" s="5"/>
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -3609,8 +3789,9 @@
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
-    </row>
-    <row r="154" spans="1:12">
+      <c r="M153" s="5"/>
+    </row>
+    <row r="154" spans="1:13">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -3623,8 +3804,9 @@
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
-    </row>
-    <row r="155" spans="1:12">
+      <c r="M154" s="5"/>
+    </row>
+    <row r="155" spans="1:13">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -3637,8 +3819,9 @@
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
-    </row>
-    <row r="156" spans="1:12">
+      <c r="M155" s="5"/>
+    </row>
+    <row r="156" spans="1:13">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -3651,8 +3834,9 @@
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
-    </row>
-    <row r="157" spans="1:12">
+      <c r="M156" s="5"/>
+    </row>
+    <row r="157" spans="1:13">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -3665,8 +3849,9 @@
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
-    </row>
-    <row r="158" spans="1:12">
+      <c r="M157" s="5"/>
+    </row>
+    <row r="158" spans="1:13">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -3679,8 +3864,9 @@
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
-    </row>
-    <row r="159" spans="1:12">
+      <c r="M158" s="5"/>
+    </row>
+    <row r="159" spans="1:13">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -3693,8 +3879,9 @@
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
-    </row>
-    <row r="160" spans="1:12">
+      <c r="M159" s="5"/>
+    </row>
+    <row r="160" spans="1:13">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -3707,8 +3894,9 @@
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
-    </row>
-    <row r="161" spans="1:12">
+      <c r="M160" s="5"/>
+    </row>
+    <row r="161" spans="1:13">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -3721,8 +3909,9 @@
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
-    </row>
-    <row r="162" spans="1:12">
+      <c r="M161" s="5"/>
+    </row>
+    <row r="162" spans="1:13">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -3735,8 +3924,9 @@
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
       <c r="L162" s="5"/>
-    </row>
-    <row r="163" spans="1:12">
+      <c r="M162" s="5"/>
+    </row>
+    <row r="163" spans="1:13">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -3749,8 +3939,9 @@
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
       <c r="L163" s="5"/>
-    </row>
-    <row r="164" spans="1:12">
+      <c r="M163" s="5"/>
+    </row>
+    <row r="164" spans="1:13">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -3763,8 +3954,9 @@
       <c r="J164" s="5"/>
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
-    </row>
-    <row r="165" spans="1:12">
+      <c r="M164" s="5"/>
+    </row>
+    <row r="165" spans="1:13">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -3777,8 +3969,9 @@
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
       <c r="L165" s="5"/>
-    </row>
-    <row r="166" spans="1:12">
+      <c r="M165" s="5"/>
+    </row>
+    <row r="166" spans="1:13">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -3791,8 +3984,9 @@
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
-    </row>
-    <row r="167" spans="1:12">
+      <c r="M166" s="5"/>
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -3805,8 +3999,9 @@
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
-    </row>
-    <row r="168" spans="1:12">
+      <c r="M167" s="5"/>
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -3819,8 +4014,9 @@
       <c r="J168" s="5"/>
       <c r="K168" s="5"/>
       <c r="L168" s="5"/>
-    </row>
-    <row r="169" spans="1:12">
+      <c r="M168" s="5"/>
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -3833,8 +4029,9 @@
       <c r="J169" s="5"/>
       <c r="K169" s="5"/>
       <c r="L169" s="5"/>
-    </row>
-    <row r="170" spans="1:12">
+      <c r="M169" s="5"/>
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -3847,8 +4044,9 @@
       <c r="J170" s="5"/>
       <c r="K170" s="5"/>
       <c r="L170" s="5"/>
-    </row>
-    <row r="171" spans="1:12">
+      <c r="M170" s="5"/>
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -3861,8 +4059,9 @@
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
       <c r="L171" s="5"/>
-    </row>
-    <row r="172" spans="1:12">
+      <c r="M171" s="5"/>
+    </row>
+    <row r="172" spans="1:13">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -3875,8 +4074,9 @@
       <c r="J172" s="5"/>
       <c r="K172" s="5"/>
       <c r="L172" s="5"/>
-    </row>
-    <row r="173" spans="1:12">
+      <c r="M172" s="5"/>
+    </row>
+    <row r="173" spans="1:13">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -3889,8 +4089,9 @@
       <c r="J173" s="5"/>
       <c r="K173" s="5"/>
       <c r="L173" s="5"/>
-    </row>
-    <row r="174" spans="1:12">
+      <c r="M173" s="5"/>
+    </row>
+    <row r="174" spans="1:13">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -3903,8 +4104,9 @@
       <c r="J174" s="5"/>
       <c r="K174" s="5"/>
       <c r="L174" s="5"/>
-    </row>
-    <row r="175" spans="1:12">
+      <c r="M174" s="5"/>
+    </row>
+    <row r="175" spans="1:13">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -3917,8 +4119,9 @@
       <c r="J175" s="5"/>
       <c r="K175" s="5"/>
       <c r="L175" s="5"/>
-    </row>
-    <row r="176" spans="1:12">
+      <c r="M175" s="5"/>
+    </row>
+    <row r="176" spans="1:13">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -3931,8 +4134,9 @@
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
       <c r="L176" s="5"/>
-    </row>
-    <row r="177" spans="1:12">
+      <c r="M176" s="5"/>
+    </row>
+    <row r="177" spans="1:13">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -3945,8 +4149,9 @@
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
       <c r="L177" s="5"/>
-    </row>
-    <row r="178" spans="1:12">
+      <c r="M177" s="5"/>
+    </row>
+    <row r="178" spans="1:13">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -3959,8 +4164,9 @@
       <c r="J178" s="5"/>
       <c r="K178" s="5"/>
       <c r="L178" s="5"/>
-    </row>
-    <row r="179" spans="1:12">
+      <c r="M178" s="5"/>
+    </row>
+    <row r="179" spans="1:13">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -3973,8 +4179,9 @@
       <c r="J179" s="5"/>
       <c r="K179" s="5"/>
       <c r="L179" s="5"/>
-    </row>
-    <row r="180" spans="1:12">
+      <c r="M179" s="5"/>
+    </row>
+    <row r="180" spans="1:13">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -3987,8 +4194,9 @@
       <c r="J180" s="5"/>
       <c r="K180" s="5"/>
       <c r="L180" s="5"/>
-    </row>
-    <row r="181" spans="1:12">
+      <c r="M180" s="5"/>
+    </row>
+    <row r="181" spans="1:13">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -4001,8 +4209,9 @@
       <c r="J181" s="5"/>
       <c r="K181" s="5"/>
       <c r="L181" s="5"/>
-    </row>
-    <row r="182" spans="1:12">
+      <c r="M181" s="5"/>
+    </row>
+    <row r="182" spans="1:13">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -4015,8 +4224,9 @@
       <c r="J182" s="5"/>
       <c r="K182" s="5"/>
       <c r="L182" s="5"/>
-    </row>
-    <row r="183" spans="1:12">
+      <c r="M182" s="5"/>
+    </row>
+    <row r="183" spans="1:13">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -4029,8 +4239,9 @@
       <c r="J183" s="5"/>
       <c r="K183" s="5"/>
       <c r="L183" s="5"/>
-    </row>
-    <row r="184" spans="1:12">
+      <c r="M183" s="5"/>
+    </row>
+    <row r="184" spans="1:13">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -4043,8 +4254,9 @@
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
       <c r="L184" s="5"/>
-    </row>
-    <row r="185" spans="1:12">
+      <c r="M184" s="5"/>
+    </row>
+    <row r="185" spans="1:13">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -4057,8 +4269,9 @@
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
       <c r="L185" s="5"/>
-    </row>
-    <row r="186" spans="1:12">
+      <c r="M185" s="5"/>
+    </row>
+    <row r="186" spans="1:13">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -4071,8 +4284,9 @@
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
       <c r="L186" s="5"/>
-    </row>
-    <row r="187" spans="1:12">
+      <c r="M186" s="5"/>
+    </row>
+    <row r="187" spans="1:13">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -4085,8 +4299,9 @@
       <c r="J187" s="5"/>
       <c r="K187" s="5"/>
       <c r="L187" s="5"/>
-    </row>
-    <row r="188" spans="1:12">
+      <c r="M187" s="5"/>
+    </row>
+    <row r="188" spans="1:13">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -4099,8 +4314,9 @@
       <c r="J188" s="5"/>
       <c r="K188" s="5"/>
       <c r="L188" s="5"/>
-    </row>
-    <row r="189" spans="1:12">
+      <c r="M188" s="5"/>
+    </row>
+    <row r="189" spans="1:13">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -4113,8 +4329,9 @@
       <c r="J189" s="5"/>
       <c r="K189" s="5"/>
       <c r="L189" s="5"/>
-    </row>
-    <row r="190" spans="1:12">
+      <c r="M189" s="5"/>
+    </row>
+    <row r="190" spans="1:13">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -4127,8 +4344,9 @@
       <c r="J190" s="5"/>
       <c r="K190" s="5"/>
       <c r="L190" s="5"/>
-    </row>
-    <row r="191" spans="1:12">
+      <c r="M190" s="5"/>
+    </row>
+    <row r="191" spans="1:13">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -4141,8 +4359,9 @@
       <c r="J191" s="5"/>
       <c r="K191" s="5"/>
       <c r="L191" s="5"/>
-    </row>
-    <row r="192" spans="1:12">
+      <c r="M191" s="5"/>
+    </row>
+    <row r="192" spans="1:13">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -4155,8 +4374,9 @@
       <c r="J192" s="5"/>
       <c r="K192" s="5"/>
       <c r="L192" s="5"/>
-    </row>
-    <row r="193" spans="1:12">
+      <c r="M192" s="5"/>
+    </row>
+    <row r="193" spans="1:13">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -4169,8 +4389,9 @@
       <c r="J193" s="5"/>
       <c r="K193" s="5"/>
       <c r="L193" s="5"/>
-    </row>
-    <row r="194" spans="1:12">
+      <c r="M193" s="5"/>
+    </row>
+    <row r="194" spans="1:13">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -4183,8 +4404,9 @@
       <c r="J194" s="5"/>
       <c r="K194" s="5"/>
       <c r="L194" s="5"/>
-    </row>
-    <row r="195" spans="1:12">
+      <c r="M194" s="5"/>
+    </row>
+    <row r="195" spans="1:13">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -4197,8 +4419,9 @@
       <c r="J195" s="5"/>
       <c r="K195" s="5"/>
       <c r="L195" s="5"/>
-    </row>
-    <row r="196" spans="1:12">
+      <c r="M195" s="5"/>
+    </row>
+    <row r="196" spans="1:13">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -4211,8 +4434,9 @@
       <c r="J196" s="5"/>
       <c r="K196" s="5"/>
       <c r="L196" s="5"/>
-    </row>
-    <row r="197" spans="1:12">
+      <c r="M196" s="5"/>
+    </row>
+    <row r="197" spans="1:13">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -4225,8 +4449,9 @@
       <c r="J197" s="5"/>
       <c r="K197" s="5"/>
       <c r="L197" s="5"/>
-    </row>
-    <row r="198" spans="1:12">
+      <c r="M197" s="5"/>
+    </row>
+    <row r="198" spans="1:13">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -4239,8 +4464,9 @@
       <c r="J198" s="5"/>
       <c r="K198" s="5"/>
       <c r="L198" s="5"/>
-    </row>
-    <row r="199" spans="1:12">
+      <c r="M198" s="5"/>
+    </row>
+    <row r="199" spans="1:13">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -4253,8 +4479,9 @@
       <c r="J199" s="5"/>
       <c r="K199" s="5"/>
       <c r="L199" s="5"/>
-    </row>
-    <row r="200" spans="1:12">
+      <c r="M199" s="5"/>
+    </row>
+    <row r="200" spans="1:13">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -4267,8 +4494,9 @@
       <c r="J200" s="5"/>
       <c r="K200" s="5"/>
       <c r="L200" s="5"/>
-    </row>
-    <row r="201" spans="1:12">
+      <c r="M200" s="5"/>
+    </row>
+    <row r="201" spans="1:13">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -4281,8 +4509,9 @@
       <c r="J201" s="5"/>
       <c r="K201" s="5"/>
       <c r="L201" s="5"/>
-    </row>
-    <row r="202" spans="1:12">
+      <c r="M201" s="5"/>
+    </row>
+    <row r="202" spans="1:13">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -4295,8 +4524,9 @@
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
       <c r="L202" s="5"/>
-    </row>
-    <row r="203" spans="1:12">
+      <c r="M202" s="5"/>
+    </row>
+    <row r="203" spans="1:13">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -4309,8 +4539,9 @@
       <c r="J203" s="5"/>
       <c r="K203" s="5"/>
       <c r="L203" s="5"/>
-    </row>
-    <row r="204" spans="1:12">
+      <c r="M203" s="5"/>
+    </row>
+    <row r="204" spans="1:13">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -4323,8 +4554,9 @@
       <c r="J204" s="5"/>
       <c r="K204" s="5"/>
       <c r="L204" s="5"/>
-    </row>
-    <row r="205" spans="1:12">
+      <c r="M204" s="5"/>
+    </row>
+    <row r="205" spans="1:13">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -4337,8 +4569,9 @@
       <c r="J205" s="5"/>
       <c r="K205" s="5"/>
       <c r="L205" s="5"/>
-    </row>
-    <row r="206" spans="1:12">
+      <c r="M205" s="5"/>
+    </row>
+    <row r="206" spans="1:13">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -4351,8 +4584,9 @@
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
       <c r="L206" s="5"/>
-    </row>
-    <row r="207" spans="1:12">
+      <c r="M206" s="5"/>
+    </row>
+    <row r="207" spans="1:13">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -4365,8 +4599,9 @@
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
       <c r="L207" s="5"/>
-    </row>
-    <row r="208" spans="1:12">
+      <c r="M207" s="5"/>
+    </row>
+    <row r="208" spans="1:13">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -4379,8 +4614,9 @@
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
       <c r="L208" s="5"/>
-    </row>
-    <row r="209" spans="1:12">
+      <c r="M208" s="5"/>
+    </row>
+    <row r="209" spans="1:13">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -4393,8 +4629,9 @@
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
       <c r="L209" s="5"/>
-    </row>
-    <row r="210" spans="1:12">
+      <c r="M209" s="5"/>
+    </row>
+    <row r="210" spans="1:13">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -4407,8 +4644,9 @@
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
       <c r="L210" s="5"/>
-    </row>
-    <row r="211" spans="1:12">
+      <c r="M210" s="5"/>
+    </row>
+    <row r="211" spans="1:13">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -4421,8 +4659,9 @@
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
       <c r="L211" s="5"/>
-    </row>
-    <row r="212" spans="1:12">
+      <c r="M211" s="5"/>
+    </row>
+    <row r="212" spans="1:13">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -4435,8 +4674,9 @@
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
       <c r="L212" s="5"/>
-    </row>
-    <row r="213" spans="1:12">
+      <c r="M212" s="5"/>
+    </row>
+    <row r="213" spans="1:13">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -4449,8 +4689,9 @@
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
       <c r="L213" s="5"/>
-    </row>
-    <row r="214" spans="1:12">
+      <c r="M213" s="5"/>
+    </row>
+    <row r="214" spans="1:13">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -4463,8 +4704,9 @@
       <c r="J214" s="5"/>
       <c r="K214" s="5"/>
       <c r="L214" s="5"/>
-    </row>
-    <row r="215" spans="1:12">
+      <c r="M214" s="5"/>
+    </row>
+    <row r="215" spans="1:13">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -4477,8 +4719,9 @@
       <c r="J215" s="5"/>
       <c r="K215" s="5"/>
       <c r="L215" s="5"/>
-    </row>
-    <row r="216" spans="1:12">
+      <c r="M215" s="5"/>
+    </row>
+    <row r="216" spans="1:13">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -4491,8 +4734,9 @@
       <c r="J216" s="5"/>
       <c r="K216" s="5"/>
       <c r="L216" s="5"/>
-    </row>
-    <row r="217" spans="1:12">
+      <c r="M216" s="5"/>
+    </row>
+    <row r="217" spans="1:13">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -4505,8 +4749,9 @@
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
       <c r="L217" s="5"/>
-    </row>
-    <row r="218" spans="1:12">
+      <c r="M217" s="5"/>
+    </row>
+    <row r="218" spans="1:13">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -4519,8 +4764,9 @@
       <c r="J218" s="5"/>
       <c r="K218" s="5"/>
       <c r="L218" s="5"/>
-    </row>
-    <row r="219" spans="1:12">
+      <c r="M218" s="5"/>
+    </row>
+    <row r="219" spans="1:13">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -4533,8 +4779,9 @@
       <c r="J219" s="5"/>
       <c r="K219" s="5"/>
       <c r="L219" s="5"/>
-    </row>
-    <row r="220" spans="1:12">
+      <c r="M219" s="5"/>
+    </row>
+    <row r="220" spans="1:13">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -4547,8 +4794,9 @@
       <c r="J220" s="5"/>
       <c r="K220" s="5"/>
       <c r="L220" s="5"/>
-    </row>
-    <row r="221" spans="1:12">
+      <c r="M220" s="5"/>
+    </row>
+    <row r="221" spans="1:13">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -4561,8 +4809,9 @@
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
       <c r="L221" s="5"/>
-    </row>
-    <row r="222" spans="1:12">
+      <c r="M221" s="5"/>
+    </row>
+    <row r="222" spans="1:13">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -4575,8 +4824,9 @@
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
       <c r="L222" s="5"/>
-    </row>
-    <row r="223" spans="1:12">
+      <c r="M222" s="5"/>
+    </row>
+    <row r="223" spans="1:13">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -4589,8 +4839,9 @@
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
       <c r="L223" s="5"/>
-    </row>
-    <row r="224" spans="1:12">
+      <c r="M223" s="5"/>
+    </row>
+    <row r="224" spans="1:13">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -4603,8 +4854,9 @@
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
       <c r="L224" s="5"/>
-    </row>
-    <row r="225" spans="1:12">
+      <c r="M224" s="5"/>
+    </row>
+    <row r="225" spans="1:13">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -4617,8 +4869,9 @@
       <c r="J225" s="5"/>
       <c r="K225" s="5"/>
       <c r="L225" s="5"/>
-    </row>
-    <row r="226" spans="1:12">
+      <c r="M225" s="5"/>
+    </row>
+    <row r="226" spans="1:13">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -4631,8 +4884,9 @@
       <c r="J226" s="5"/>
       <c r="K226" s="5"/>
       <c r="L226" s="5"/>
-    </row>
-    <row r="227" spans="1:12">
+      <c r="M226" s="5"/>
+    </row>
+    <row r="227" spans="1:13">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -4645,8 +4899,9 @@
       <c r="J227" s="5"/>
       <c r="K227" s="5"/>
       <c r="L227" s="5"/>
-    </row>
-    <row r="228" spans="1:12">
+      <c r="M227" s="5"/>
+    </row>
+    <row r="228" spans="1:13">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -4659,8 +4914,9 @@
       <c r="J228" s="5"/>
       <c r="K228" s="5"/>
       <c r="L228" s="5"/>
-    </row>
-    <row r="229" spans="1:12">
+      <c r="M228" s="5"/>
+    </row>
+    <row r="229" spans="1:13">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -4673,8 +4929,9 @@
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
       <c r="L229" s="5"/>
-    </row>
-    <row r="230" spans="1:12">
+      <c r="M229" s="5"/>
+    </row>
+    <row r="230" spans="1:13">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -4687,8 +4944,9 @@
       <c r="J230" s="5"/>
       <c r="K230" s="5"/>
       <c r="L230" s="5"/>
-    </row>
-    <row r="231" spans="1:12">
+      <c r="M230" s="5"/>
+    </row>
+    <row r="231" spans="1:13">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -4701,8 +4959,9 @@
       <c r="J231" s="5"/>
       <c r="K231" s="5"/>
       <c r="L231" s="5"/>
-    </row>
-    <row r="232" spans="1:12">
+      <c r="M231" s="5"/>
+    </row>
+    <row r="232" spans="1:13">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -4715,8 +4974,9 @@
       <c r="J232" s="5"/>
       <c r="K232" s="5"/>
       <c r="L232" s="5"/>
-    </row>
-    <row r="233" spans="1:12">
+      <c r="M232" s="5"/>
+    </row>
+    <row r="233" spans="1:13">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -4729,8 +4989,9 @@
       <c r="J233" s="5"/>
       <c r="K233" s="5"/>
       <c r="L233" s="5"/>
-    </row>
-    <row r="234" spans="1:12">
+      <c r="M233" s="5"/>
+    </row>
+    <row r="234" spans="1:13">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -4743,8 +5004,9 @@
       <c r="J234" s="5"/>
       <c r="K234" s="5"/>
       <c r="L234" s="5"/>
-    </row>
-    <row r="235" spans="1:12">
+      <c r="M234" s="5"/>
+    </row>
+    <row r="235" spans="1:13">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -4757,8 +5019,9 @@
       <c r="J235" s="5"/>
       <c r="K235" s="5"/>
       <c r="L235" s="5"/>
-    </row>
-    <row r="236" spans="1:12">
+      <c r="M235" s="5"/>
+    </row>
+    <row r="236" spans="1:13">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -4771,8 +5034,9 @@
       <c r="J236" s="5"/>
       <c r="K236" s="5"/>
       <c r="L236" s="5"/>
-    </row>
-    <row r="237" spans="1:12">
+      <c r="M236" s="5"/>
+    </row>
+    <row r="237" spans="1:13">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -4785,8 +5049,9 @@
       <c r="J237" s="5"/>
       <c r="K237" s="5"/>
       <c r="L237" s="5"/>
-    </row>
-    <row r="238" spans="1:12">
+      <c r="M237" s="5"/>
+    </row>
+    <row r="238" spans="1:13">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -4799,8 +5064,9 @@
       <c r="J238" s="5"/>
       <c r="K238" s="5"/>
       <c r="L238" s="5"/>
-    </row>
-    <row r="239" spans="1:12">
+      <c r="M238" s="5"/>
+    </row>
+    <row r="239" spans="1:13">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -4813,8 +5079,9 @@
       <c r="J239" s="5"/>
       <c r="K239" s="5"/>
       <c r="L239" s="5"/>
-    </row>
-    <row r="240" spans="1:12">
+      <c r="M239" s="5"/>
+    </row>
+    <row r="240" spans="1:13">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -4827,8 +5094,9 @@
       <c r="J240" s="5"/>
       <c r="K240" s="5"/>
       <c r="L240" s="5"/>
-    </row>
-    <row r="241" spans="1:12">
+      <c r="M240" s="5"/>
+    </row>
+    <row r="241" spans="1:13">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -4841,8 +5109,9 @@
       <c r="J241" s="5"/>
       <c r="K241" s="5"/>
       <c r="L241" s="5"/>
-    </row>
-    <row r="242" spans="1:12">
+      <c r="M241" s="5"/>
+    </row>
+    <row r="242" spans="1:13">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -4855,8 +5124,9 @@
       <c r="J242" s="5"/>
       <c r="K242" s="5"/>
       <c r="L242" s="5"/>
-    </row>
-    <row r="243" spans="1:12">
+      <c r="M242" s="5"/>
+    </row>
+    <row r="243" spans="1:13">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -4869,8 +5139,9 @@
       <c r="J243" s="5"/>
       <c r="K243" s="5"/>
       <c r="L243" s="5"/>
-    </row>
-    <row r="244" spans="1:12">
+      <c r="M243" s="5"/>
+    </row>
+    <row r="244" spans="1:13">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -4883,8 +5154,9 @@
       <c r="J244" s="5"/>
       <c r="K244" s="5"/>
       <c r="L244" s="5"/>
-    </row>
-    <row r="245" spans="1:12">
+      <c r="M244" s="5"/>
+    </row>
+    <row r="245" spans="1:13">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -4897,8 +5169,9 @@
       <c r="J245" s="5"/>
       <c r="K245" s="5"/>
       <c r="L245" s="5"/>
-    </row>
-    <row r="246" spans="1:12">
+      <c r="M245" s="5"/>
+    </row>
+    <row r="246" spans="1:13">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -4911,8 +5184,9 @@
       <c r="J246" s="5"/>
       <c r="K246" s="5"/>
       <c r="L246" s="5"/>
-    </row>
-    <row r="247" spans="1:12">
+      <c r="M246" s="5"/>
+    </row>
+    <row r="247" spans="1:13">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -4925,8 +5199,9 @@
       <c r="J247" s="5"/>
       <c r="K247" s="5"/>
       <c r="L247" s="5"/>
-    </row>
-    <row r="248" spans="1:12">
+      <c r="M247" s="5"/>
+    </row>
+    <row r="248" spans="1:13">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -4939,8 +5214,9 @@
       <c r="J248" s="5"/>
       <c r="K248" s="5"/>
       <c r="L248" s="5"/>
-    </row>
-    <row r="249" spans="1:12">
+      <c r="M248" s="5"/>
+    </row>
+    <row r="249" spans="1:13">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -4953,8 +5229,9 @@
       <c r="J249" s="5"/>
       <c r="K249" s="5"/>
       <c r="L249" s="5"/>
-    </row>
-    <row r="250" spans="1:12">
+      <c r="M249" s="5"/>
+    </row>
+    <row r="250" spans="1:13">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -4967,8 +5244,9 @@
       <c r="J250" s="5"/>
       <c r="K250" s="5"/>
       <c r="L250" s="5"/>
-    </row>
-    <row r="251" spans="1:12">
+      <c r="M250" s="5"/>
+    </row>
+    <row r="251" spans="1:13">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -4981,8 +5259,9 @@
       <c r="J251" s="5"/>
       <c r="K251" s="5"/>
       <c r="L251" s="5"/>
-    </row>
-    <row r="252" spans="1:12">
+      <c r="M251" s="5"/>
+    </row>
+    <row r="252" spans="1:13">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -4995,8 +5274,9 @@
       <c r="J252" s="5"/>
       <c r="K252" s="5"/>
       <c r="L252" s="5"/>
-    </row>
-    <row r="253" spans="1:12">
+      <c r="M252" s="5"/>
+    </row>
+    <row r="253" spans="1:13">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -5009,8 +5289,9 @@
       <c r="J253" s="5"/>
       <c r="K253" s="5"/>
       <c r="L253" s="5"/>
-    </row>
-    <row r="254" spans="1:12">
+      <c r="M253" s="5"/>
+    </row>
+    <row r="254" spans="1:13">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -5023,8 +5304,9 @@
       <c r="J254" s="5"/>
       <c r="K254" s="5"/>
       <c r="L254" s="5"/>
-    </row>
-    <row r="255" spans="1:12">
+      <c r="M254" s="5"/>
+    </row>
+    <row r="255" spans="1:13">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -5037,8 +5319,9 @@
       <c r="J255" s="5"/>
       <c r="K255" s="5"/>
       <c r="L255" s="5"/>
-    </row>
-    <row r="256" spans="1:12">
+      <c r="M255" s="5"/>
+    </row>
+    <row r="256" spans="1:13">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -5051,8 +5334,9 @@
       <c r="J256" s="5"/>
       <c r="K256" s="5"/>
       <c r="L256" s="5"/>
-    </row>
-    <row r="257" spans="1:12">
+      <c r="M256" s="5"/>
+    </row>
+    <row r="257" spans="1:13">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -5065,8 +5349,9 @@
       <c r="J257" s="5"/>
       <c r="K257" s="5"/>
       <c r="L257" s="5"/>
-    </row>
-    <row r="258" spans="1:12">
+      <c r="M257" s="5"/>
+    </row>
+    <row r="258" spans="1:13">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -5079,8 +5364,9 @@
       <c r="J258" s="5"/>
       <c r="K258" s="5"/>
       <c r="L258" s="5"/>
-    </row>
-    <row r="259" spans="1:12">
+      <c r="M258" s="5"/>
+    </row>
+    <row r="259" spans="1:13">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -5093,8 +5379,9 @@
       <c r="J259" s="5"/>
       <c r="K259" s="5"/>
       <c r="L259" s="5"/>
-    </row>
-    <row r="260" spans="1:12">
+      <c r="M259" s="5"/>
+    </row>
+    <row r="260" spans="1:13">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -5107,8 +5394,9 @@
       <c r="J260" s="5"/>
       <c r="K260" s="5"/>
       <c r="L260" s="5"/>
-    </row>
-    <row r="261" spans="1:12">
+      <c r="M260" s="5"/>
+    </row>
+    <row r="261" spans="1:13">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -5121,8 +5409,9 @@
       <c r="J261" s="5"/>
       <c r="K261" s="5"/>
       <c r="L261" s="5"/>
-    </row>
-    <row r="262" spans="1:12">
+      <c r="M261" s="5"/>
+    </row>
+    <row r="262" spans="1:13">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -5135,8 +5424,9 @@
       <c r="J262" s="5"/>
       <c r="K262" s="5"/>
       <c r="L262" s="5"/>
-    </row>
-    <row r="263" spans="1:12">
+      <c r="M262" s="5"/>
+    </row>
+    <row r="263" spans="1:13">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -5149,8 +5439,9 @@
       <c r="J263" s="5"/>
       <c r="K263" s="5"/>
       <c r="L263" s="5"/>
-    </row>
-    <row r="264" spans="1:12">
+      <c r="M263" s="5"/>
+    </row>
+    <row r="264" spans="1:13">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -5163,8 +5454,9 @@
       <c r="J264" s="5"/>
       <c r="K264" s="5"/>
       <c r="L264" s="5"/>
-    </row>
-    <row r="265" spans="1:12">
+      <c r="M264" s="5"/>
+    </row>
+    <row r="265" spans="1:13">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -5177,8 +5469,9 @@
       <c r="J265" s="5"/>
       <c r="K265" s="5"/>
       <c r="L265" s="5"/>
-    </row>
-    <row r="266" spans="1:12">
+      <c r="M265" s="5"/>
+    </row>
+    <row r="266" spans="1:13">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -5191,8 +5484,9 @@
       <c r="J266" s="5"/>
       <c r="K266" s="5"/>
       <c r="L266" s="5"/>
-    </row>
-    <row r="267" spans="1:12">
+      <c r="M266" s="5"/>
+    </row>
+    <row r="267" spans="1:13">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -5205,8 +5499,9 @@
       <c r="J267" s="5"/>
       <c r="K267" s="5"/>
       <c r="L267" s="5"/>
-    </row>
-    <row r="268" spans="1:12">
+      <c r="M267" s="5"/>
+    </row>
+    <row r="268" spans="1:13">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -5219,8 +5514,9 @@
       <c r="J268" s="5"/>
       <c r="K268" s="5"/>
       <c r="L268" s="5"/>
-    </row>
-    <row r="269" spans="1:12">
+      <c r="M268" s="5"/>
+    </row>
+    <row r="269" spans="1:13">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -5233,8 +5529,9 @@
       <c r="J269" s="5"/>
       <c r="K269" s="5"/>
       <c r="L269" s="5"/>
-    </row>
-    <row r="270" spans="1:12">
+      <c r="M269" s="5"/>
+    </row>
+    <row r="270" spans="1:13">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -5247,8 +5544,9 @@
       <c r="J270" s="5"/>
       <c r="K270" s="5"/>
       <c r="L270" s="5"/>
-    </row>
-    <row r="271" spans="1:12">
+      <c r="M270" s="5"/>
+    </row>
+    <row r="271" spans="1:13">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -5261,8 +5559,9 @@
       <c r="J271" s="5"/>
       <c r="K271" s="5"/>
       <c r="L271" s="5"/>
-    </row>
-    <row r="272" spans="1:12">
+      <c r="M271" s="5"/>
+    </row>
+    <row r="272" spans="1:13">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -5275,8 +5574,9 @@
       <c r="J272" s="5"/>
       <c r="K272" s="5"/>
       <c r="L272" s="5"/>
-    </row>
-    <row r="273" spans="1:12">
+      <c r="M272" s="5"/>
+    </row>
+    <row r="273" spans="1:13">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -5289,8 +5589,9 @@
       <c r="J273" s="5"/>
       <c r="K273" s="5"/>
       <c r="L273" s="5"/>
-    </row>
-    <row r="274" spans="1:12">
+      <c r="M273" s="5"/>
+    </row>
+    <row r="274" spans="1:13">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -5303,8 +5604,9 @@
       <c r="J274" s="5"/>
       <c r="K274" s="5"/>
       <c r="L274" s="5"/>
-    </row>
-    <row r="275" spans="1:12">
+      <c r="M274" s="5"/>
+    </row>
+    <row r="275" spans="1:13">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -5317,8 +5619,9 @@
       <c r="J275" s="5"/>
       <c r="K275" s="5"/>
       <c r="L275" s="5"/>
-    </row>
-    <row r="276" spans="1:12">
+      <c r="M275" s="5"/>
+    </row>
+    <row r="276" spans="1:13">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -5331,8 +5634,9 @@
       <c r="J276" s="5"/>
       <c r="K276" s="5"/>
       <c r="L276" s="5"/>
-    </row>
-    <row r="277" spans="1:12">
+      <c r="M276" s="5"/>
+    </row>
+    <row r="277" spans="1:13">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -5345,8 +5649,9 @@
       <c r="J277" s="5"/>
       <c r="K277" s="5"/>
       <c r="L277" s="5"/>
-    </row>
-    <row r="278" spans="1:12">
+      <c r="M277" s="5"/>
+    </row>
+    <row r="278" spans="1:13">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -5359,8 +5664,9 @@
       <c r="J278" s="5"/>
       <c r="K278" s="5"/>
       <c r="L278" s="5"/>
-    </row>
-    <row r="279" spans="1:12">
+      <c r="M278" s="5"/>
+    </row>
+    <row r="279" spans="1:13">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -5373,8 +5679,9 @@
       <c r="J279" s="5"/>
       <c r="K279" s="5"/>
       <c r="L279" s="5"/>
-    </row>
-    <row r="280" spans="1:12">
+      <c r="M279" s="5"/>
+    </row>
+    <row r="280" spans="1:13">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -5387,8 +5694,9 @@
       <c r="J280" s="5"/>
       <c r="K280" s="5"/>
       <c r="L280" s="5"/>
-    </row>
-    <row r="281" spans="1:12">
+      <c r="M280" s="5"/>
+    </row>
+    <row r="281" spans="1:13">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -5401,8 +5709,9 @@
       <c r="J281" s="5"/>
       <c r="K281" s="5"/>
       <c r="L281" s="5"/>
-    </row>
-    <row r="282" spans="1:12">
+      <c r="M281" s="5"/>
+    </row>
+    <row r="282" spans="1:13">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -5415,8 +5724,9 @@
       <c r="J282" s="5"/>
       <c r="K282" s="5"/>
       <c r="L282" s="5"/>
-    </row>
-    <row r="283" spans="1:12">
+      <c r="M282" s="5"/>
+    </row>
+    <row r="283" spans="1:13">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -5429,8 +5739,9 @@
       <c r="J283" s="5"/>
       <c r="K283" s="5"/>
       <c r="L283" s="5"/>
-    </row>
-    <row r="284" spans="1:12">
+      <c r="M283" s="5"/>
+    </row>
+    <row r="284" spans="1:13">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -5443,8 +5754,9 @@
       <c r="J284" s="5"/>
       <c r="K284" s="5"/>
       <c r="L284" s="5"/>
-    </row>
-    <row r="285" spans="1:12">
+      <c r="M284" s="5"/>
+    </row>
+    <row r="285" spans="1:13">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -5457,8 +5769,9 @@
       <c r="J285" s="5"/>
       <c r="K285" s="5"/>
       <c r="L285" s="5"/>
-    </row>
-    <row r="286" spans="1:12">
+      <c r="M285" s="5"/>
+    </row>
+    <row r="286" spans="1:13">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -5471,8 +5784,9 @@
       <c r="J286" s="5"/>
       <c r="K286" s="5"/>
       <c r="L286" s="5"/>
-    </row>
-    <row r="287" spans="1:12">
+      <c r="M286" s="5"/>
+    </row>
+    <row r="287" spans="1:13">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -5485,8 +5799,9 @@
       <c r="J287" s="5"/>
       <c r="K287" s="5"/>
       <c r="L287" s="5"/>
-    </row>
-    <row r="288" spans="1:12">
+      <c r="M287" s="5"/>
+    </row>
+    <row r="288" spans="1:13">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -5499,8 +5814,9 @@
       <c r="J288" s="5"/>
       <c r="K288" s="5"/>
       <c r="L288" s="5"/>
-    </row>
-    <row r="289" spans="1:12">
+      <c r="M288" s="5"/>
+    </row>
+    <row r="289" spans="1:13">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -5513,8 +5829,9 @@
       <c r="J289" s="5"/>
       <c r="K289" s="5"/>
       <c r="L289" s="5"/>
-    </row>
-    <row r="290" spans="1:12">
+      <c r="M289" s="5"/>
+    </row>
+    <row r="290" spans="1:13">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -5527,8 +5844,9 @@
       <c r="J290" s="5"/>
       <c r="K290" s="5"/>
       <c r="L290" s="5"/>
-    </row>
-    <row r="291" spans="1:12">
+      <c r="M290" s="5"/>
+    </row>
+    <row r="291" spans="1:13">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -5541,8 +5859,9 @@
       <c r="J291" s="5"/>
       <c r="K291" s="5"/>
       <c r="L291" s="5"/>
-    </row>
-    <row r="292" spans="1:12">
+      <c r="M291" s="5"/>
+    </row>
+    <row r="292" spans="1:13">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -5555,8 +5874,9 @@
       <c r="J292" s="5"/>
       <c r="K292" s="5"/>
       <c r="L292" s="5"/>
-    </row>
-    <row r="293" spans="1:12">
+      <c r="M292" s="5"/>
+    </row>
+    <row r="293" spans="1:13">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -5569,8 +5889,9 @@
       <c r="J293" s="5"/>
       <c r="K293" s="5"/>
       <c r="L293" s="5"/>
-    </row>
-    <row r="294" spans="1:12">
+      <c r="M293" s="5"/>
+    </row>
+    <row r="294" spans="1:13">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -5583,8 +5904,9 @@
       <c r="J294" s="5"/>
       <c r="K294" s="5"/>
       <c r="L294" s="5"/>
-    </row>
-    <row r="295" spans="1:12">
+      <c r="M294" s="5"/>
+    </row>
+    <row r="295" spans="1:13">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -5597,8 +5919,9 @@
       <c r="J295" s="5"/>
       <c r="K295" s="5"/>
       <c r="L295" s="5"/>
-    </row>
-    <row r="296" spans="1:12">
+      <c r="M295" s="5"/>
+    </row>
+    <row r="296" spans="1:13">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -5611,8 +5934,9 @@
       <c r="J296" s="5"/>
       <c r="K296" s="5"/>
       <c r="L296" s="5"/>
-    </row>
-    <row r="297" spans="1:12">
+      <c r="M296" s="5"/>
+    </row>
+    <row r="297" spans="1:13">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -5625,8 +5949,9 @@
       <c r="J297" s="5"/>
       <c r="K297" s="5"/>
       <c r="L297" s="5"/>
-    </row>
-    <row r="298" spans="1:12">
+      <c r="M297" s="5"/>
+    </row>
+    <row r="298" spans="1:13">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -5639,8 +5964,9 @@
       <c r="J298" s="5"/>
       <c r="K298" s="5"/>
       <c r="L298" s="5"/>
-    </row>
-    <row r="299" spans="1:12">
+      <c r="M298" s="5"/>
+    </row>
+    <row r="299" spans="1:13">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -5653,8 +5979,9 @@
       <c r="J299" s="5"/>
       <c r="K299" s="5"/>
       <c r="L299" s="5"/>
-    </row>
-    <row r="300" spans="1:12">
+      <c r="M299" s="5"/>
+    </row>
+    <row r="300" spans="1:13">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -5667,8 +5994,9 @@
       <c r="J300" s="5"/>
       <c r="K300" s="5"/>
       <c r="L300" s="5"/>
-    </row>
-    <row r="301" spans="1:12">
+      <c r="M300" s="5"/>
+    </row>
+    <row r="301" spans="1:13">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -5681,8 +6009,9 @@
       <c r="J301" s="5"/>
       <c r="K301" s="5"/>
       <c r="L301" s="5"/>
-    </row>
-    <row r="302" spans="1:12">
+      <c r="M301" s="5"/>
+    </row>
+    <row r="302" spans="1:13">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -5695,8 +6024,9 @@
       <c r="J302" s="5"/>
       <c r="K302" s="5"/>
       <c r="L302" s="5"/>
-    </row>
-    <row r="303" spans="1:12">
+      <c r="M302" s="5"/>
+    </row>
+    <row r="303" spans="1:13">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -5709,8 +6039,9 @@
       <c r="J303" s="5"/>
       <c r="K303" s="5"/>
       <c r="L303" s="5"/>
-    </row>
-    <row r="304" spans="1:12">
+      <c r="M303" s="5"/>
+    </row>
+    <row r="304" spans="1:13">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -5723,8 +6054,9 @@
       <c r="J304" s="5"/>
       <c r="K304" s="5"/>
       <c r="L304" s="5"/>
-    </row>
-    <row r="305" spans="1:12">
+      <c r="M304" s="5"/>
+    </row>
+    <row r="305" spans="1:13">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -5737,8 +6069,9 @@
       <c r="J305" s="5"/>
       <c r="K305" s="5"/>
       <c r="L305" s="5"/>
-    </row>
-    <row r="306" spans="1:12">
+      <c r="M305" s="5"/>
+    </row>
+    <row r="306" spans="1:13">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -5751,8 +6084,9 @@
       <c r="J306" s="5"/>
       <c r="K306" s="5"/>
       <c r="L306" s="5"/>
-    </row>
-    <row r="307" spans="1:12">
+      <c r="M306" s="5"/>
+    </row>
+    <row r="307" spans="1:13">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -5765,8 +6099,9 @@
       <c r="J307" s="5"/>
       <c r="K307" s="5"/>
       <c r="L307" s="5"/>
-    </row>
-    <row r="308" spans="1:12">
+      <c r="M307" s="5"/>
+    </row>
+    <row r="308" spans="1:13">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -5779,8 +6114,9 @@
       <c r="J308" s="5"/>
       <c r="K308" s="5"/>
       <c r="L308" s="5"/>
-    </row>
-    <row r="309" spans="1:12">
+      <c r="M308" s="5"/>
+    </row>
+    <row r="309" spans="1:13">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -5793,8 +6129,9 @@
       <c r="J309" s="5"/>
       <c r="K309" s="5"/>
       <c r="L309" s="5"/>
-    </row>
-    <row r="310" spans="1:12">
+      <c r="M309" s="5"/>
+    </row>
+    <row r="310" spans="1:13">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -5807,8 +6144,9 @@
       <c r="J310" s="5"/>
       <c r="K310" s="5"/>
       <c r="L310" s="5"/>
-    </row>
-    <row r="311" spans="1:12">
+      <c r="M310" s="5"/>
+    </row>
+    <row r="311" spans="1:13">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -5821,8 +6159,9 @@
       <c r="J311" s="5"/>
       <c r="K311" s="5"/>
       <c r="L311" s="5"/>
-    </row>
-    <row r="312" spans="1:12">
+      <c r="M311" s="5"/>
+    </row>
+    <row r="312" spans="1:13">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -5835,8 +6174,9 @@
       <c r="J312" s="5"/>
       <c r="K312" s="5"/>
       <c r="L312" s="5"/>
-    </row>
-    <row r="313" spans="1:12">
+      <c r="M312" s="5"/>
+    </row>
+    <row r="313" spans="1:13">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -5849,8 +6189,9 @@
       <c r="J313" s="5"/>
       <c r="K313" s="5"/>
       <c r="L313" s="5"/>
-    </row>
-    <row r="314" spans="1:12">
+      <c r="M313" s="5"/>
+    </row>
+    <row r="314" spans="1:13">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -5863,8 +6204,9 @@
       <c r="J314" s="5"/>
       <c r="K314" s="5"/>
       <c r="L314" s="5"/>
-    </row>
-    <row r="315" spans="1:12">
+      <c r="M314" s="5"/>
+    </row>
+    <row r="315" spans="1:13">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -5877,8 +6219,9 @@
       <c r="J315" s="5"/>
       <c r="K315" s="5"/>
       <c r="L315" s="5"/>
-    </row>
-    <row r="316" spans="1:12">
+      <c r="M315" s="5"/>
+    </row>
+    <row r="316" spans="1:13">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -5891,8 +6234,9 @@
       <c r="J316" s="5"/>
       <c r="K316" s="5"/>
       <c r="L316" s="5"/>
-    </row>
-    <row r="317" spans="1:12">
+      <c r="M316" s="5"/>
+    </row>
+    <row r="317" spans="1:13">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -5905,8 +6249,9 @@
       <c r="J317" s="5"/>
       <c r="K317" s="5"/>
       <c r="L317" s="5"/>
-    </row>
-    <row r="318" spans="1:12">
+      <c r="M317" s="5"/>
+    </row>
+    <row r="318" spans="1:13">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -5919,8 +6264,9 @@
       <c r="J318" s="5"/>
       <c r="K318" s="5"/>
       <c r="L318" s="5"/>
-    </row>
-    <row r="319" spans="1:12">
+      <c r="M318" s="5"/>
+    </row>
+    <row r="319" spans="1:13">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -5933,8 +6279,9 @@
       <c r="J319" s="5"/>
       <c r="K319" s="5"/>
       <c r="L319" s="5"/>
-    </row>
-    <row r="320" spans="1:12">
+      <c r="M319" s="5"/>
+    </row>
+    <row r="320" spans="1:13">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -5947,8 +6294,9 @@
       <c r="J320" s="5"/>
       <c r="K320" s="5"/>
       <c r="L320" s="5"/>
-    </row>
-    <row r="321" spans="1:12">
+      <c r="M320" s="5"/>
+    </row>
+    <row r="321" spans="1:13">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -5961,8 +6309,9 @@
       <c r="J321" s="5"/>
       <c r="K321" s="5"/>
       <c r="L321" s="5"/>
-    </row>
-    <row r="322" spans="1:12">
+      <c r="M321" s="5"/>
+    </row>
+    <row r="322" spans="1:13">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -5975,8 +6324,9 @@
       <c r="J322" s="5"/>
       <c r="K322" s="5"/>
       <c r="L322" s="5"/>
-    </row>
-    <row r="323" spans="1:12">
+      <c r="M322" s="5"/>
+    </row>
+    <row r="323" spans="1:13">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -5989,8 +6339,9 @@
       <c r="J323" s="5"/>
       <c r="K323" s="5"/>
       <c r="L323" s="5"/>
-    </row>
-    <row r="324" spans="1:12">
+      <c r="M323" s="5"/>
+    </row>
+    <row r="324" spans="1:13">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -6003,8 +6354,9 @@
       <c r="J324" s="5"/>
       <c r="K324" s="5"/>
       <c r="L324" s="5"/>
-    </row>
-    <row r="325" spans="1:12">
+      <c r="M324" s="5"/>
+    </row>
+    <row r="325" spans="1:13">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -6017,8 +6369,9 @@
       <c r="J325" s="5"/>
       <c r="K325" s="5"/>
       <c r="L325" s="5"/>
-    </row>
-    <row r="326" spans="1:12">
+      <c r="M325" s="5"/>
+    </row>
+    <row r="326" spans="1:13">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -6031,8 +6384,9 @@
       <c r="J326" s="5"/>
       <c r="K326" s="5"/>
       <c r="L326" s="5"/>
-    </row>
-    <row r="327" spans="1:12">
+      <c r="M326" s="5"/>
+    </row>
+    <row r="327" spans="1:13">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -6045,8 +6399,9 @@
       <c r="J327" s="5"/>
       <c r="K327" s="5"/>
       <c r="L327" s="5"/>
-    </row>
-    <row r="328" spans="1:12">
+      <c r="M327" s="5"/>
+    </row>
+    <row r="328" spans="1:13">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -6059,8 +6414,9 @@
       <c r="J328" s="5"/>
       <c r="K328" s="5"/>
       <c r="L328" s="5"/>
-    </row>
-    <row r="329" spans="1:12">
+      <c r="M328" s="5"/>
+    </row>
+    <row r="329" spans="1:13">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -6073,8 +6429,9 @@
       <c r="J329" s="5"/>
       <c r="K329" s="5"/>
       <c r="L329" s="5"/>
-    </row>
-    <row r="330" spans="1:12">
+      <c r="M329" s="5"/>
+    </row>
+    <row r="330" spans="1:13">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -6087,8 +6444,9 @@
       <c r="J330" s="5"/>
       <c r="K330" s="5"/>
       <c r="L330" s="5"/>
-    </row>
-    <row r="331" spans="1:12">
+      <c r="M330" s="5"/>
+    </row>
+    <row r="331" spans="1:13">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -6101,8 +6459,9 @@
       <c r="J331" s="5"/>
       <c r="K331" s="5"/>
       <c r="L331" s="5"/>
-    </row>
-    <row r="332" spans="1:12">
+      <c r="M331" s="5"/>
+    </row>
+    <row r="332" spans="1:13">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -6115,8 +6474,9 @@
       <c r="J332" s="5"/>
       <c r="K332" s="5"/>
       <c r="L332" s="5"/>
-    </row>
-    <row r="333" spans="1:12">
+      <c r="M332" s="5"/>
+    </row>
+    <row r="333" spans="1:13">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -6129,8 +6489,9 @@
       <c r="J333" s="5"/>
       <c r="K333" s="5"/>
       <c r="L333" s="5"/>
-    </row>
-    <row r="334" spans="1:12">
+      <c r="M333" s="5"/>
+    </row>
+    <row r="334" spans="1:13">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -6143,8 +6504,9 @@
       <c r="J334" s="5"/>
       <c r="K334" s="5"/>
       <c r="L334" s="5"/>
-    </row>
-    <row r="335" spans="1:12">
+      <c r="M334" s="5"/>
+    </row>
+    <row r="335" spans="1:13">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -6157,8 +6519,9 @@
       <c r="J335" s="5"/>
       <c r="K335" s="5"/>
       <c r="L335" s="5"/>
-    </row>
-    <row r="336" spans="1:12">
+      <c r="M335" s="5"/>
+    </row>
+    <row r="336" spans="1:13">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -6171,8 +6534,9 @@
       <c r="J336" s="5"/>
       <c r="K336" s="5"/>
       <c r="L336" s="5"/>
-    </row>
-    <row r="337" spans="1:12">
+      <c r="M336" s="5"/>
+    </row>
+    <row r="337" spans="1:13">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -6185,8 +6549,9 @@
       <c r="J337" s="5"/>
       <c r="K337" s="5"/>
       <c r="L337" s="5"/>
-    </row>
-    <row r="338" spans="1:12">
+      <c r="M337" s="5"/>
+    </row>
+    <row r="338" spans="1:13">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -6199,8 +6564,9 @@
       <c r="J338" s="5"/>
       <c r="K338" s="5"/>
       <c r="L338" s="5"/>
-    </row>
-    <row r="339" spans="1:12">
+      <c r="M338" s="5"/>
+    </row>
+    <row r="339" spans="1:13">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -6213,8 +6579,9 @@
       <c r="J339" s="5"/>
       <c r="K339" s="5"/>
       <c r="L339" s="5"/>
-    </row>
-    <row r="340" spans="1:12">
+      <c r="M339" s="5"/>
+    </row>
+    <row r="340" spans="1:13">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -6227,8 +6594,9 @@
       <c r="J340" s="5"/>
       <c r="K340" s="5"/>
       <c r="L340" s="5"/>
-    </row>
-    <row r="341" spans="1:12">
+      <c r="M340" s="5"/>
+    </row>
+    <row r="341" spans="1:13">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -6241,8 +6609,9 @@
       <c r="J341" s="5"/>
       <c r="K341" s="5"/>
       <c r="L341" s="5"/>
-    </row>
-    <row r="342" spans="1:12">
+      <c r="M341" s="5"/>
+    </row>
+    <row r="342" spans="1:13">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -6255,8 +6624,9 @@
       <c r="J342" s="5"/>
       <c r="K342" s="5"/>
       <c r="L342" s="5"/>
-    </row>
-    <row r="343" spans="1:12">
+      <c r="M342" s="5"/>
+    </row>
+    <row r="343" spans="1:13">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -6269,8 +6639,9 @@
       <c r="J343" s="5"/>
       <c r="K343" s="5"/>
       <c r="L343" s="5"/>
-    </row>
-    <row r="344" spans="1:12">
+      <c r="M343" s="5"/>
+    </row>
+    <row r="344" spans="1:13">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -6283,8 +6654,9 @@
       <c r="J344" s="5"/>
       <c r="K344" s="5"/>
       <c r="L344" s="5"/>
-    </row>
-    <row r="345" spans="1:12">
+      <c r="M344" s="5"/>
+    </row>
+    <row r="345" spans="1:13">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -6297,8 +6669,9 @@
       <c r="J345" s="5"/>
       <c r="K345" s="5"/>
       <c r="L345" s="5"/>
-    </row>
-    <row r="346" spans="1:12">
+      <c r="M345" s="5"/>
+    </row>
+    <row r="346" spans="1:13">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -6311,8 +6684,9 @@
       <c r="J346" s="5"/>
       <c r="K346" s="5"/>
       <c r="L346" s="5"/>
-    </row>
-    <row r="347" spans="1:12">
+      <c r="M346" s="5"/>
+    </row>
+    <row r="347" spans="1:13">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -6325,8 +6699,9 @@
       <c r="J347" s="5"/>
       <c r="K347" s="5"/>
       <c r="L347" s="5"/>
-    </row>
-    <row r="348" spans="1:12">
+      <c r="M347" s="5"/>
+    </row>
+    <row r="348" spans="1:13">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -6339,8 +6714,9 @@
       <c r="J348" s="5"/>
       <c r="K348" s="5"/>
       <c r="L348" s="5"/>
-    </row>
-    <row r="349" spans="1:12">
+      <c r="M348" s="5"/>
+    </row>
+    <row r="349" spans="1:13">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -6353,8 +6729,9 @@
       <c r="J349" s="5"/>
       <c r="K349" s="5"/>
       <c r="L349" s="5"/>
-    </row>
-    <row r="350" spans="1:12">
+      <c r="M349" s="5"/>
+    </row>
+    <row r="350" spans="1:13">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -6367,8 +6744,9 @@
       <c r="J350" s="5"/>
       <c r="K350" s="5"/>
       <c r="L350" s="5"/>
-    </row>
-    <row r="351" spans="1:12">
+      <c r="M350" s="5"/>
+    </row>
+    <row r="351" spans="1:13">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -6381,8 +6759,9 @@
       <c r="J351" s="5"/>
       <c r="K351" s="5"/>
       <c r="L351" s="5"/>
-    </row>
-    <row r="352" spans="1:12">
+      <c r="M351" s="5"/>
+    </row>
+    <row r="352" spans="1:13">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -6395,8 +6774,9 @@
       <c r="J352" s="5"/>
       <c r="K352" s="5"/>
       <c r="L352" s="5"/>
-    </row>
-    <row r="353" spans="1:12">
+      <c r="M352" s="5"/>
+    </row>
+    <row r="353" spans="1:13">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -6409,8 +6789,9 @@
       <c r="J353" s="5"/>
       <c r="K353" s="5"/>
       <c r="L353" s="5"/>
-    </row>
-    <row r="354" spans="1:12">
+      <c r="M353" s="5"/>
+    </row>
+    <row r="354" spans="1:13">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -6423,8 +6804,9 @@
       <c r="J354" s="5"/>
       <c r="K354" s="5"/>
       <c r="L354" s="5"/>
-    </row>
-    <row r="355" spans="1:12">
+      <c r="M354" s="5"/>
+    </row>
+    <row r="355" spans="1:13">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -6437,8 +6819,9 @@
       <c r="J355" s="5"/>
       <c r="K355" s="5"/>
       <c r="L355" s="5"/>
-    </row>
-    <row r="356" spans="1:12">
+      <c r="M355" s="5"/>
+    </row>
+    <row r="356" spans="1:13">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -6451,8 +6834,9 @@
       <c r="J356" s="5"/>
       <c r="K356" s="5"/>
       <c r="L356" s="5"/>
-    </row>
-    <row r="357" spans="1:12">
+      <c r="M356" s="5"/>
+    </row>
+    <row r="357" spans="1:13">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -6465,8 +6849,9 @@
       <c r="J357" s="5"/>
       <c r="K357" s="5"/>
       <c r="L357" s="5"/>
-    </row>
-    <row r="358" spans="1:12">
+      <c r="M357" s="5"/>
+    </row>
+    <row r="358" spans="1:13">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -6479,8 +6864,9 @@
       <c r="J358" s="5"/>
       <c r="K358" s="5"/>
       <c r="L358" s="5"/>
-    </row>
-    <row r="359" spans="1:12">
+      <c r="M358" s="5"/>
+    </row>
+    <row r="359" spans="1:13">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -6493,8 +6879,9 @@
       <c r="J359" s="5"/>
       <c r="K359" s="5"/>
       <c r="L359" s="5"/>
-    </row>
-    <row r="360" spans="1:12">
+      <c r="M359" s="5"/>
+    </row>
+    <row r="360" spans="1:13">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -6507,8 +6894,9 @@
       <c r="J360" s="5"/>
       <c r="K360" s="5"/>
       <c r="L360" s="5"/>
-    </row>
-    <row r="361" spans="1:12">
+      <c r="M360" s="5"/>
+    </row>
+    <row r="361" spans="1:13">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -6521,8 +6909,9 @@
       <c r="J361" s="5"/>
       <c r="K361" s="5"/>
       <c r="L361" s="5"/>
-    </row>
-    <row r="362" spans="1:12">
+      <c r="M361" s="5"/>
+    </row>
+    <row r="362" spans="1:13">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -6535,8 +6924,9 @@
       <c r="J362" s="5"/>
       <c r="K362" s="5"/>
       <c r="L362" s="5"/>
-    </row>
-    <row r="363" spans="1:12">
+      <c r="M362" s="5"/>
+    </row>
+    <row r="363" spans="1:13">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -6549,8 +6939,9 @@
       <c r="J363" s="5"/>
       <c r="K363" s="5"/>
       <c r="L363" s="5"/>
-    </row>
-    <row r="364" spans="1:12">
+      <c r="M363" s="5"/>
+    </row>
+    <row r="364" spans="1:13">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -6563,8 +6954,9 @@
       <c r="J364" s="5"/>
       <c r="K364" s="5"/>
       <c r="L364" s="5"/>
-    </row>
-    <row r="365" spans="1:12">
+      <c r="M364" s="5"/>
+    </row>
+    <row r="365" spans="1:13">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -6577,8 +6969,9 @@
       <c r="J365" s="5"/>
       <c r="K365" s="5"/>
       <c r="L365" s="5"/>
-    </row>
-    <row r="366" spans="1:12">
+      <c r="M365" s="5"/>
+    </row>
+    <row r="366" spans="1:13">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -6591,8 +6984,9 @@
       <c r="J366" s="5"/>
       <c r="K366" s="5"/>
       <c r="L366" s="5"/>
-    </row>
-    <row r="367" spans="1:12">
+      <c r="M366" s="5"/>
+    </row>
+    <row r="367" spans="1:13">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -6605,8 +6999,9 @@
       <c r="J367" s="5"/>
       <c r="K367" s="5"/>
       <c r="L367" s="5"/>
-    </row>
-    <row r="368" spans="1:12">
+      <c r="M367" s="5"/>
+    </row>
+    <row r="368" spans="1:13">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -6619,8 +7014,9 @@
       <c r="J368" s="5"/>
       <c r="K368" s="5"/>
       <c r="L368" s="5"/>
-    </row>
-    <row r="369" spans="1:12">
+      <c r="M368" s="5"/>
+    </row>
+    <row r="369" spans="1:13">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -6633,8 +7029,9 @@
       <c r="J369" s="5"/>
       <c r="K369" s="5"/>
       <c r="L369" s="5"/>
-    </row>
-    <row r="370" spans="1:12">
+      <c r="M369" s="5"/>
+    </row>
+    <row r="370" spans="1:13">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -6647,8 +7044,9 @@
       <c r="J370" s="5"/>
       <c r="K370" s="5"/>
       <c r="L370" s="5"/>
-    </row>
-    <row r="371" spans="1:12">
+      <c r="M370" s="5"/>
+    </row>
+    <row r="371" spans="1:13">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -6661,8 +7059,9 @@
       <c r="J371" s="5"/>
       <c r="K371" s="5"/>
       <c r="L371" s="5"/>
-    </row>
-    <row r="372" spans="1:12">
+      <c r="M371" s="5"/>
+    </row>
+    <row r="372" spans="1:13">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -6675,8 +7074,9 @@
       <c r="J372" s="5"/>
       <c r="K372" s="5"/>
       <c r="L372" s="5"/>
-    </row>
-    <row r="373" spans="1:12">
+      <c r="M372" s="5"/>
+    </row>
+    <row r="373" spans="1:13">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -6689,8 +7089,9 @@
       <c r="J373" s="5"/>
       <c r="K373" s="5"/>
       <c r="L373" s="5"/>
-    </row>
-    <row r="374" spans="1:12">
+      <c r="M373" s="5"/>
+    </row>
+    <row r="374" spans="1:13">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -6703,8 +7104,9 @@
       <c r="J374" s="5"/>
       <c r="K374" s="5"/>
       <c r="L374" s="5"/>
-    </row>
-    <row r="375" spans="1:12">
+      <c r="M374" s="5"/>
+    </row>
+    <row r="375" spans="1:13">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -6717,8 +7119,9 @@
       <c r="J375" s="5"/>
       <c r="K375" s="5"/>
       <c r="L375" s="5"/>
-    </row>
-    <row r="376" spans="1:12">
+      <c r="M375" s="5"/>
+    </row>
+    <row r="376" spans="1:13">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -6731,8 +7134,9 @@
       <c r="J376" s="5"/>
       <c r="K376" s="5"/>
       <c r="L376" s="5"/>
-    </row>
-    <row r="377" spans="1:12">
+      <c r="M376" s="5"/>
+    </row>
+    <row r="377" spans="1:13">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -6745,8 +7149,9 @@
       <c r="J377" s="5"/>
       <c r="K377" s="5"/>
       <c r="L377" s="5"/>
-    </row>
-    <row r="378" spans="1:12">
+      <c r="M377" s="5"/>
+    </row>
+    <row r="378" spans="1:13">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -6759,8 +7164,9 @@
       <c r="J378" s="5"/>
       <c r="K378" s="5"/>
       <c r="L378" s="5"/>
-    </row>
-    <row r="379" spans="1:12">
+      <c r="M378" s="5"/>
+    </row>
+    <row r="379" spans="1:13">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -6773,8 +7179,9 @@
       <c r="J379" s="5"/>
       <c r="K379" s="5"/>
       <c r="L379" s="5"/>
-    </row>
-    <row r="380" spans="1:12">
+      <c r="M379" s="5"/>
+    </row>
+    <row r="380" spans="1:13">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -6787,8 +7194,9 @@
       <c r="J380" s="5"/>
       <c r="K380" s="5"/>
       <c r="L380" s="5"/>
-    </row>
-    <row r="381" spans="1:12">
+      <c r="M380" s="5"/>
+    </row>
+    <row r="381" spans="1:13">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -6801,8 +7209,9 @@
       <c r="J381" s="5"/>
       <c r="K381" s="5"/>
       <c r="L381" s="5"/>
-    </row>
-    <row r="382" spans="1:12">
+      <c r="M381" s="5"/>
+    </row>
+    <row r="382" spans="1:13">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -6815,8 +7224,9 @@
       <c r="J382" s="5"/>
       <c r="K382" s="5"/>
       <c r="L382" s="5"/>
-    </row>
-    <row r="383" spans="1:12">
+      <c r="M382" s="5"/>
+    </row>
+    <row r="383" spans="1:13">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -6829,8 +7239,9 @@
       <c r="J383" s="5"/>
       <c r="K383" s="5"/>
       <c r="L383" s="5"/>
-    </row>
-    <row r="384" spans="1:12">
+      <c r="M383" s="5"/>
+    </row>
+    <row r="384" spans="1:13">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -6843,8 +7254,9 @@
       <c r="J384" s="5"/>
       <c r="K384" s="5"/>
       <c r="L384" s="5"/>
-    </row>
-    <row r="385" spans="1:12">
+      <c r="M384" s="5"/>
+    </row>
+    <row r="385" spans="1:13">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -6857,8 +7269,9 @@
       <c r="J385" s="5"/>
       <c r="K385" s="5"/>
       <c r="L385" s="5"/>
-    </row>
-    <row r="386" spans="1:12">
+      <c r="M385" s="5"/>
+    </row>
+    <row r="386" spans="1:13">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -6871,8 +7284,9 @@
       <c r="J386" s="5"/>
       <c r="K386" s="5"/>
       <c r="L386" s="5"/>
-    </row>
-    <row r="387" spans="1:12">
+      <c r="M386" s="5"/>
+    </row>
+    <row r="387" spans="1:13">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -6885,8 +7299,9 @@
       <c r="J387" s="5"/>
       <c r="K387" s="5"/>
       <c r="L387" s="5"/>
-    </row>
-    <row r="388" spans="1:12">
+      <c r="M387" s="5"/>
+    </row>
+    <row r="388" spans="1:13">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -6899,8 +7314,9 @@
       <c r="J388" s="5"/>
       <c r="K388" s="5"/>
       <c r="L388" s="5"/>
-    </row>
-    <row r="389" spans="1:12">
+      <c r="M388" s="5"/>
+    </row>
+    <row r="389" spans="1:13">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -6913,8 +7329,9 @@
       <c r="J389" s="5"/>
       <c r="K389" s="5"/>
       <c r="L389" s="5"/>
-    </row>
-    <row r="390" spans="1:12">
+      <c r="M389" s="5"/>
+    </row>
+    <row r="390" spans="1:13">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -6927,8 +7344,9 @@
       <c r="J390" s="5"/>
       <c r="K390" s="5"/>
       <c r="L390" s="5"/>
-    </row>
-    <row r="391" spans="1:12">
+      <c r="M390" s="5"/>
+    </row>
+    <row r="391" spans="1:13">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -6941,8 +7359,9 @@
       <c r="J391" s="5"/>
       <c r="K391" s="5"/>
       <c r="L391" s="5"/>
-    </row>
-    <row r="392" spans="1:12">
+      <c r="M391" s="5"/>
+    </row>
+    <row r="392" spans="1:13">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -6955,8 +7374,9 @@
       <c r="J392" s="5"/>
       <c r="K392" s="5"/>
       <c r="L392" s="5"/>
-    </row>
-    <row r="393" spans="1:12">
+      <c r="M392" s="5"/>
+    </row>
+    <row r="393" spans="1:13">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -6969,8 +7389,9 @@
       <c r="J393" s="5"/>
       <c r="K393" s="5"/>
       <c r="L393" s="5"/>
-    </row>
-    <row r="394" spans="1:12">
+      <c r="M393" s="5"/>
+    </row>
+    <row r="394" spans="1:13">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -6983,8 +7404,9 @@
       <c r="J394" s="5"/>
       <c r="K394" s="5"/>
       <c r="L394" s="5"/>
-    </row>
-    <row r="395" spans="1:12">
+      <c r="M394" s="5"/>
+    </row>
+    <row r="395" spans="1:13">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -6997,8 +7419,9 @@
       <c r="J395" s="5"/>
       <c r="K395" s="5"/>
       <c r="L395" s="5"/>
-    </row>
-    <row r="396" spans="1:12">
+      <c r="M395" s="5"/>
+    </row>
+    <row r="396" spans="1:13">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -7011,8 +7434,9 @@
       <c r="J396" s="5"/>
       <c r="K396" s="5"/>
       <c r="L396" s="5"/>
-    </row>
-    <row r="397" spans="1:12">
+      <c r="M396" s="5"/>
+    </row>
+    <row r="397" spans="1:13">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -7025,8 +7449,9 @@
       <c r="J397" s="5"/>
       <c r="K397" s="5"/>
       <c r="L397" s="5"/>
-    </row>
-    <row r="398" spans="1:12">
+      <c r="M397" s="5"/>
+    </row>
+    <row r="398" spans="1:13">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -7039,8 +7464,9 @@
       <c r="J398" s="5"/>
       <c r="K398" s="5"/>
       <c r="L398" s="5"/>
-    </row>
-    <row r="399" spans="1:12">
+      <c r="M398" s="5"/>
+    </row>
+    <row r="399" spans="1:13">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -7053,8 +7479,9 @@
       <c r="J399" s="5"/>
       <c r="K399" s="5"/>
       <c r="L399" s="5"/>
-    </row>
-    <row r="400" spans="1:12">
+      <c r="M399" s="5"/>
+    </row>
+    <row r="400" spans="1:13">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -7067,8 +7494,9 @@
       <c r="J400" s="5"/>
       <c r="K400" s="5"/>
       <c r="L400" s="5"/>
-    </row>
-    <row r="401" spans="1:12">
+      <c r="M400" s="5"/>
+    </row>
+    <row r="401" spans="1:13">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -7081,8 +7509,9 @@
       <c r="J401" s="5"/>
       <c r="K401" s="5"/>
       <c r="L401" s="5"/>
-    </row>
-    <row r="402" spans="1:12">
+      <c r="M401" s="5"/>
+    </row>
+    <row r="402" spans="1:13">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -7095,8 +7524,9 @@
       <c r="J402" s="5"/>
       <c r="K402" s="5"/>
       <c r="L402" s="5"/>
-    </row>
-    <row r="403" spans="1:12">
+      <c r="M402" s="5"/>
+    </row>
+    <row r="403" spans="1:13">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -7109,8 +7539,9 @@
       <c r="J403" s="5"/>
       <c r="K403" s="5"/>
       <c r="L403" s="5"/>
-    </row>
-    <row r="404" spans="1:12">
+      <c r="M403" s="5"/>
+    </row>
+    <row r="404" spans="1:13">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -7123,8 +7554,9 @@
       <c r="J404" s="5"/>
       <c r="K404" s="5"/>
       <c r="L404" s="5"/>
-    </row>
-    <row r="405" spans="1:12">
+      <c r="M404" s="5"/>
+    </row>
+    <row r="405" spans="1:13">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -7137,8 +7569,9 @@
       <c r="J405" s="5"/>
       <c r="K405" s="5"/>
       <c r="L405" s="5"/>
-    </row>
-    <row r="406" spans="1:12">
+      <c r="M405" s="5"/>
+    </row>
+    <row r="406" spans="1:13">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -7151,8 +7584,9 @@
       <c r="J406" s="5"/>
       <c r="K406" s="5"/>
       <c r="L406" s="5"/>
-    </row>
-    <row r="407" spans="1:12">
+      <c r="M406" s="5"/>
+    </row>
+    <row r="407" spans="1:13">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -7165,8 +7599,9 @@
       <c r="J407" s="5"/>
       <c r="K407" s="5"/>
       <c r="L407" s="5"/>
-    </row>
-    <row r="408" spans="1:12">
+      <c r="M407" s="5"/>
+    </row>
+    <row r="408" spans="1:13">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -7179,8 +7614,9 @@
       <c r="J408" s="5"/>
       <c r="K408" s="5"/>
       <c r="L408" s="5"/>
-    </row>
-    <row r="409" spans="1:12">
+      <c r="M408" s="5"/>
+    </row>
+    <row r="409" spans="1:13">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -7193,8 +7629,9 @@
       <c r="J409" s="5"/>
       <c r="K409" s="5"/>
       <c r="L409" s="5"/>
-    </row>
-    <row r="410" spans="1:12">
+      <c r="M409" s="5"/>
+    </row>
+    <row r="410" spans="1:13">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -7207,8 +7644,9 @@
       <c r="J410" s="5"/>
       <c r="K410" s="5"/>
       <c r="L410" s="5"/>
-    </row>
-    <row r="411" spans="1:12">
+      <c r="M410" s="5"/>
+    </row>
+    <row r="411" spans="1:13">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -7221,8 +7659,9 @@
       <c r="J411" s="5"/>
       <c r="K411" s="5"/>
       <c r="L411" s="5"/>
-    </row>
-    <row r="412" spans="1:12">
+      <c r="M411" s="5"/>
+    </row>
+    <row r="412" spans="1:13">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -7235,8 +7674,9 @@
       <c r="J412" s="5"/>
       <c r="K412" s="5"/>
       <c r="L412" s="5"/>
-    </row>
-    <row r="413" spans="1:12">
+      <c r="M412" s="5"/>
+    </row>
+    <row r="413" spans="1:13">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -7249,8 +7689,9 @@
       <c r="J413" s="5"/>
       <c r="K413" s="5"/>
       <c r="L413" s="5"/>
-    </row>
-    <row r="414" spans="1:12">
+      <c r="M413" s="5"/>
+    </row>
+    <row r="414" spans="1:13">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -7263,8 +7704,9 @@
       <c r="J414" s="5"/>
       <c r="K414" s="5"/>
       <c r="L414" s="5"/>
-    </row>
-    <row r="415" spans="1:12">
+      <c r="M414" s="5"/>
+    </row>
+    <row r="415" spans="1:13">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -7277,8 +7719,9 @@
       <c r="J415" s="5"/>
       <c r="K415" s="5"/>
       <c r="L415" s="5"/>
-    </row>
-    <row r="416" spans="1:12">
+      <c r="M415" s="5"/>
+    </row>
+    <row r="416" spans="1:13">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -7291,8 +7734,9 @@
       <c r="J416" s="5"/>
       <c r="K416" s="5"/>
       <c r="L416" s="5"/>
-    </row>
-    <row r="417" spans="1:12">
+      <c r="M416" s="5"/>
+    </row>
+    <row r="417" spans="1:13">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -7305,8 +7749,9 @@
       <c r="J417" s="5"/>
       <c r="K417" s="5"/>
       <c r="L417" s="5"/>
-    </row>
-    <row r="418" spans="1:12">
+      <c r="M417" s="5"/>
+    </row>
+    <row r="418" spans="1:13">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -7319,8 +7764,9 @@
       <c r="J418" s="5"/>
       <c r="K418" s="5"/>
       <c r="L418" s="5"/>
-    </row>
-    <row r="419" spans="1:12">
+      <c r="M418" s="5"/>
+    </row>
+    <row r="419" spans="1:13">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -7333,8 +7779,9 @@
       <c r="J419" s="5"/>
       <c r="K419" s="5"/>
       <c r="L419" s="5"/>
-    </row>
-    <row r="420" spans="1:12">
+      <c r="M419" s="5"/>
+    </row>
+    <row r="420" spans="1:13">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -7347,8 +7794,9 @@
       <c r="J420" s="5"/>
       <c r="K420" s="5"/>
       <c r="L420" s="5"/>
-    </row>
-    <row r="421" spans="1:12">
+      <c r="M420" s="5"/>
+    </row>
+    <row r="421" spans="1:13">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -7361,8 +7809,9 @@
       <c r="J421" s="5"/>
       <c r="K421" s="5"/>
       <c r="L421" s="5"/>
-    </row>
-    <row r="422" spans="1:12">
+      <c r="M421" s="5"/>
+    </row>
+    <row r="422" spans="1:13">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -7375,8 +7824,9 @@
       <c r="J422" s="5"/>
       <c r="K422" s="5"/>
       <c r="L422" s="5"/>
-    </row>
-    <row r="423" spans="1:12">
+      <c r="M422" s="5"/>
+    </row>
+    <row r="423" spans="1:13">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -7389,8 +7839,9 @@
       <c r="J423" s="5"/>
       <c r="K423" s="5"/>
       <c r="L423" s="5"/>
-    </row>
-    <row r="424" spans="1:12">
+      <c r="M423" s="5"/>
+    </row>
+    <row r="424" spans="1:13">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -7403,8 +7854,9 @@
       <c r="J424" s="5"/>
       <c r="K424" s="5"/>
       <c r="L424" s="5"/>
-    </row>
-    <row r="425" spans="1:12">
+      <c r="M424" s="5"/>
+    </row>
+    <row r="425" spans="1:13">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -7417,8 +7869,9 @@
       <c r="J425" s="5"/>
       <c r="K425" s="5"/>
       <c r="L425" s="5"/>
-    </row>
-    <row r="426" spans="1:12">
+      <c r="M425" s="5"/>
+    </row>
+    <row r="426" spans="1:13">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -7431,8 +7884,9 @@
       <c r="J426" s="5"/>
       <c r="K426" s="5"/>
       <c r="L426" s="5"/>
-    </row>
-    <row r="427" spans="1:12">
+      <c r="M426" s="5"/>
+    </row>
+    <row r="427" spans="1:13">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -7445,8 +7899,9 @@
       <c r="J427" s="5"/>
       <c r="K427" s="5"/>
       <c r="L427" s="5"/>
-    </row>
-    <row r="428" spans="1:12">
+      <c r="M427" s="5"/>
+    </row>
+    <row r="428" spans="1:13">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -7459,8 +7914,9 @@
       <c r="J428" s="5"/>
       <c r="K428" s="5"/>
       <c r="L428" s="5"/>
-    </row>
-    <row r="429" spans="1:12">
+      <c r="M428" s="5"/>
+    </row>
+    <row r="429" spans="1:13">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -7473,8 +7929,9 @@
       <c r="J429" s="5"/>
       <c r="K429" s="5"/>
       <c r="L429" s="5"/>
-    </row>
-    <row r="430" spans="1:12">
+      <c r="M429" s="5"/>
+    </row>
+    <row r="430" spans="1:13">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -7487,8 +7944,9 @@
       <c r="J430" s="5"/>
       <c r="K430" s="5"/>
       <c r="L430" s="5"/>
-    </row>
-    <row r="431" spans="1:12">
+      <c r="M430" s="5"/>
+    </row>
+    <row r="431" spans="1:13">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -7501,8 +7959,9 @@
       <c r="J431" s="5"/>
       <c r="K431" s="5"/>
       <c r="L431" s="5"/>
-    </row>
-    <row r="432" spans="1:12">
+      <c r="M431" s="5"/>
+    </row>
+    <row r="432" spans="1:13">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -7515,8 +7974,9 @@
       <c r="J432" s="5"/>
       <c r="K432" s="5"/>
       <c r="L432" s="5"/>
-    </row>
-    <row r="433" spans="1:12">
+      <c r="M432" s="5"/>
+    </row>
+    <row r="433" spans="1:13">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -7529,8 +7989,9 @@
       <c r="J433" s="5"/>
       <c r="K433" s="5"/>
       <c r="L433" s="5"/>
-    </row>
-    <row r="434" spans="1:12">
+      <c r="M433" s="5"/>
+    </row>
+    <row r="434" spans="1:13">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -7543,8 +8004,9 @@
       <c r="J434" s="5"/>
       <c r="K434" s="5"/>
       <c r="L434" s="5"/>
-    </row>
-    <row r="435" spans="1:12">
+      <c r="M434" s="5"/>
+    </row>
+    <row r="435" spans="1:13">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -7557,8 +8019,9 @@
       <c r="J435" s="5"/>
       <c r="K435" s="5"/>
       <c r="L435" s="5"/>
-    </row>
-    <row r="436" spans="1:12">
+      <c r="M435" s="5"/>
+    </row>
+    <row r="436" spans="1:13">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -7571,8 +8034,9 @@
       <c r="J436" s="5"/>
       <c r="K436" s="5"/>
       <c r="L436" s="5"/>
-    </row>
-    <row r="437" spans="1:12">
+      <c r="M436" s="5"/>
+    </row>
+    <row r="437" spans="1:13">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -7585,8 +8049,9 @@
       <c r="J437" s="5"/>
       <c r="K437" s="5"/>
       <c r="L437" s="5"/>
-    </row>
-    <row r="438" spans="1:12">
+      <c r="M437" s="5"/>
+    </row>
+    <row r="438" spans="1:13">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -7599,8 +8064,9 @@
       <c r="J438" s="5"/>
       <c r="K438" s="5"/>
       <c r="L438" s="5"/>
-    </row>
-    <row r="439" spans="1:12">
+      <c r="M438" s="5"/>
+    </row>
+    <row r="439" spans="1:13">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -7613,8 +8079,9 @@
       <c r="J439" s="5"/>
       <c r="K439" s="5"/>
       <c r="L439" s="5"/>
-    </row>
-    <row r="440" spans="1:12">
+      <c r="M439" s="5"/>
+    </row>
+    <row r="440" spans="1:13">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -7627,8 +8094,9 @@
       <c r="J440" s="5"/>
       <c r="K440" s="5"/>
       <c r="L440" s="5"/>
-    </row>
-    <row r="441" spans="1:12">
+      <c r="M440" s="5"/>
+    </row>
+    <row r="441" spans="1:13">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -7641,8 +8109,9 @@
       <c r="J441" s="5"/>
       <c r="K441" s="5"/>
       <c r="L441" s="5"/>
-    </row>
-    <row r="442" spans="1:12">
+      <c r="M441" s="5"/>
+    </row>
+    <row r="442" spans="1:13">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -7655,8 +8124,9 @@
       <c r="J442" s="5"/>
       <c r="K442" s="5"/>
       <c r="L442" s="5"/>
-    </row>
-    <row r="443" spans="1:12">
+      <c r="M442" s="5"/>
+    </row>
+    <row r="443" spans="1:13">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -7669,8 +8139,9 @@
       <c r="J443" s="5"/>
       <c r="K443" s="5"/>
       <c r="L443" s="5"/>
-    </row>
-    <row r="444" spans="1:12">
+      <c r="M443" s="5"/>
+    </row>
+    <row r="444" spans="1:13">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -7683,8 +8154,9 @@
       <c r="J444" s="5"/>
       <c r="K444" s="5"/>
       <c r="L444" s="5"/>
-    </row>
-    <row r="445" spans="1:12">
+      <c r="M444" s="5"/>
+    </row>
+    <row r="445" spans="1:13">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -7697,8 +8169,9 @@
       <c r="J445" s="5"/>
       <c r="K445" s="5"/>
       <c r="L445" s="5"/>
-    </row>
-    <row r="446" spans="1:12">
+      <c r="M445" s="5"/>
+    </row>
+    <row r="446" spans="1:13">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -7711,8 +8184,9 @@
       <c r="J446" s="5"/>
       <c r="K446" s="5"/>
       <c r="L446" s="5"/>
-    </row>
-    <row r="447" spans="1:12">
+      <c r="M446" s="5"/>
+    </row>
+    <row r="447" spans="1:13">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -7725,8 +8199,9 @@
       <c r="J447" s="5"/>
       <c r="K447" s="5"/>
       <c r="L447" s="5"/>
-    </row>
-    <row r="448" spans="1:12">
+      <c r="M447" s="5"/>
+    </row>
+    <row r="448" spans="1:13">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">
@@ -8210,7 +8685,7 @@
       <c r="A608" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F608" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -80,12 +80,84 @@
         </r>
       </text>
     </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0：普通
+1：超武</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0：绿
+1：蓝
+2：紫
+3：金
+4：红</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0：银币
+1：金币</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>编号</t>
   </si>
@@ -97,6 +169,15 @@
   </si>
   <si>
     <t>名称</t>
+  </si>
+  <si>
+    <t>种类</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>货币类型</t>
   </si>
   <si>
     <t>价格</t>
@@ -136,6 +217,15 @@
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>kinds</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>currencyType</t>
   </si>
   <si>
     <t>value</t>
@@ -1182,15 +1272,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q608"/>
+  <dimension ref="A1:T608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="13" width="25.125" style="2" customWidth="1"/>
-    <col min="14" max="17" width="25.125" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="1" max="16" width="25.125" style="2" customWidth="1"/>
+    <col min="17" max="20" width="25.125" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:17">
+    <row r="1" ht="16.5" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1230,90 +1320,117 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:17">
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:20">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:17">
+        <v>28</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:20">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:17">
+        <v>33</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:20">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1324,37 +1441,46 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
         <v>6000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="I4" s="3">
         <v>0.5</v>
       </c>
-      <c r="G4" s="3">
+      <c r="J4" s="3">
         <v>2000</v>
       </c>
-      <c r="H4" s="3">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="3">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="J4" s="3">
+      <c r="M4" s="3">
         <v>1</v>
       </c>
-      <c r="K4" s="3">
+      <c r="N4" s="3">
         <v>100</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:17">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:20">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1365,37 +1491,46 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
         <v>7000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="I5" s="3">
         <v>0.15</v>
       </c>
-      <c r="G5" s="3">
+      <c r="J5" s="3">
         <v>2000</v>
       </c>
-      <c r="H5" s="3">
+      <c r="K5" s="3">
         <v>3</v>
       </c>
-      <c r="I5" s="3">
+      <c r="L5" s="3">
         <v>0.9</v>
       </c>
-      <c r="J5" s="3">
+      <c r="M5" s="3">
         <v>30</v>
       </c>
-      <c r="K5" s="3">
+      <c r="N5" s="3">
         <v>600</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:17">
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:20">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1406,37 +1541,46 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
         <v>8000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="I6" s="3">
         <v>0.05</v>
       </c>
-      <c r="G6" s="3">
+      <c r="J6" s="3">
         <v>2000</v>
       </c>
-      <c r="H6" s="3">
+      <c r="K6" s="3">
         <v>4</v>
       </c>
-      <c r="I6" s="3">
+      <c r="L6" s="3">
         <v>0.9</v>
       </c>
-      <c r="J6" s="3">
+      <c r="M6" s="3">
         <v>25</v>
       </c>
-      <c r="K6" s="3">
+      <c r="N6" s="3">
         <v>600</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:17">
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:20">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1447,37 +1591,46 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
         <v>9000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="I7" s="3">
         <v>0.2</v>
       </c>
-      <c r="G7" s="3">
+      <c r="J7" s="3">
         <v>2000</v>
       </c>
-      <c r="H7" s="3">
+      <c r="K7" s="3">
         <v>5</v>
       </c>
-      <c r="I7" s="3">
+      <c r="L7" s="3">
         <v>0.6</v>
       </c>
-      <c r="J7" s="3">
+      <c r="M7" s="3">
         <v>75</v>
       </c>
-      <c r="K7" s="3">
+      <c r="N7" s="3">
         <v>600</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:17">
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:20">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1488,39 +1641,48 @@
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>10000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>6</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>0.9</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>8</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:17">
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:20">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1531,39 +1693,48 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
         <v>11000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="I9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>4000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3">
         <v>7</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>0.8</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>5</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3">
+      <c r="O9" s="3"/>
+      <c r="P9" s="3">
         <v>1</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:17">
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:20">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1574,37 +1745,46 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>0.2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>8</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>0.9</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>600</v>
       </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:17">
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:20">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1615,37 +1795,46 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
         <v>13000</v>
       </c>
-      <c r="F11" s="3">
+      <c r="I11" s="3">
         <v>0.2</v>
       </c>
-      <c r="G11" s="3">
+      <c r="J11" s="3">
         <v>2000</v>
       </c>
-      <c r="H11" s="3">
+      <c r="K11" s="3">
         <v>15</v>
       </c>
-      <c r="I11" s="3">
+      <c r="L11" s="3">
         <v>1</v>
       </c>
-      <c r="J11" s="3">
+      <c r="M11" s="3">
         <v>1</v>
       </c>
-      <c r="K11" s="3">
+      <c r="N11" s="3">
         <v>100</v>
       </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:17">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:20">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1663,8 +1852,11 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:17">
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:20">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1682,8 +1874,11 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:17">
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:20">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1701,8 +1896,11 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:17">
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:20">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1720,8 +1918,11 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1735,8 +1936,11 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1750,8 +1954,11 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1765,8 +1972,11 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1780,8 +1990,11 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1795,8 +2008,11 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1810,8 +2026,11 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1825,8 +2044,11 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1840,8 +2062,11 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1855,8 +2080,11 @@
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1870,8 +2098,11 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1885,8 +2116,11 @@
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1900,8 +2134,11 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1915,8 +2152,11 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1930,8 +2170,11 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1945,8 +2188,11 @@
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1960,8 +2206,11 @@
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1975,8 +2224,11 @@
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1990,8 +2242,11 @@
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2005,8 +2260,11 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2020,8 +2278,11 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2035,8 +2296,11 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2050,8 +2314,11 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2065,8 +2332,11 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2080,8 +2350,11 @@
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2095,8 +2368,11 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2110,8 +2386,11 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2125,8 +2404,11 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2140,8 +2422,11 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2155,8 +2440,11 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2170,8 +2458,11 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2185,8 +2476,11 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2200,8 +2494,11 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2215,8 +2512,11 @@
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2230,8 +2530,11 @@
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2245,8 +2548,11 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2260,8 +2566,11 @@
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2275,8 +2584,11 @@
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2290,8 +2602,11 @@
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2305,8 +2620,11 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2320,8 +2638,11 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2335,8 +2656,11 @@
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
-    </row>
-    <row r="57" spans="1:13">
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2350,8 +2674,11 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2365,8 +2692,11 @@
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
-    </row>
-    <row r="59" spans="1:13">
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2380,8 +2710,11 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
-    </row>
-    <row r="60" spans="1:13">
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2395,8 +2728,11 @@
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
-    </row>
-    <row r="61" spans="1:13">
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2410,8 +2746,11 @@
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
-    </row>
-    <row r="62" spans="1:13">
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2425,8 +2764,11 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
-    </row>
-    <row r="63" spans="1:13">
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2440,8 +2782,11 @@
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2455,8 +2800,11 @@
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2470,8 +2818,11 @@
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2485,8 +2836,11 @@
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2500,8 +2854,11 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2515,8 +2872,11 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2530,8 +2890,11 @@
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+    </row>
+    <row r="70" spans="1:16">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2545,8 +2908,11 @@
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2560,8 +2926,11 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2575,8 +2944,11 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2590,8 +2962,11 @@
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2605,8 +2980,11 @@
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2620,8 +2998,11 @@
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+    </row>
+    <row r="76" spans="1:16">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -2635,8 +3016,11 @@
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
-    </row>
-    <row r="77" spans="1:13">
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2650,8 +3034,11 @@
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
-    </row>
-    <row r="78" spans="1:13">
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -2665,8 +3052,11 @@
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
-    </row>
-    <row r="79" spans="1:13">
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2680,8 +3070,11 @@
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
       <c r="M79" s="5"/>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2695,8 +3088,11 @@
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+    </row>
+    <row r="81" spans="1:16">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2710,8 +3106,11 @@
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+    </row>
+    <row r="82" spans="1:16">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -2725,8 +3124,11 @@
       <c r="K82" s="5"/>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2740,8 +3142,11 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -2755,8 +3160,11 @@
       <c r="K84" s="5"/>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+    </row>
+    <row r="85" spans="1:16">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -2770,8 +3178,11 @@
       <c r="K85" s="5"/>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -2785,8 +3196,11 @@
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="5"/>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -2800,8 +3214,11 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
-    </row>
-    <row r="88" spans="1:13">
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5"/>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -2815,8 +3232,11 @@
       <c r="K88" s="5"/>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
-    </row>
-    <row r="89" spans="1:13">
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5"/>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -2830,8 +3250,11 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+    </row>
+    <row r="90" spans="1:16">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -2845,8 +3268,11 @@
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="N90" s="5"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="5"/>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -2860,8 +3286,11 @@
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -2875,8 +3304,11 @@
       <c r="K92" s="5"/>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2890,8 +3322,11 @@
       <c r="K93" s="5"/>
       <c r="L93" s="5"/>
       <c r="M93" s="5"/>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5"/>
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -2905,8 +3340,11 @@
       <c r="K94" s="5"/>
       <c r="L94" s="5"/>
       <c r="M94" s="5"/>
-    </row>
-    <row r="95" spans="1:13">
+      <c r="N94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="5"/>
+    </row>
+    <row r="95" spans="1:16">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -2920,8 +3358,11 @@
       <c r="K95" s="5"/>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
+      <c r="P95" s="5"/>
+    </row>
+    <row r="96" spans="1:16">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -2935,8 +3376,11 @@
       <c r="K96" s="5"/>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
-    </row>
-    <row r="97" spans="1:13">
+      <c r="N96" s="5"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="5"/>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -2950,8 +3394,11 @@
       <c r="K97" s="5"/>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
-    </row>
-    <row r="98" spans="1:13">
+      <c r="N97" s="5"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="5"/>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -2965,8 +3412,11 @@
       <c r="K98" s="5"/>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
-    </row>
-    <row r="99" spans="1:13">
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5"/>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -2980,8 +3430,11 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
-    </row>
-    <row r="100" spans="1:13">
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5"/>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -2995,8 +3448,11 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
-    </row>
-    <row r="101" spans="1:13">
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5"/>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -3010,8 +3466,11 @@
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
-    </row>
-    <row r="102" spans="1:13">
+      <c r="N101" s="5"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="5"/>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -3025,8 +3484,11 @@
       <c r="K102" s="5"/>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
-    </row>
-    <row r="103" spans="1:13">
+      <c r="N102" s="5"/>
+      <c r="O102" s="5"/>
+      <c r="P102" s="5"/>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -3040,8 +3502,11 @@
       <c r="K103" s="5"/>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
-    </row>
-    <row r="104" spans="1:13">
+      <c r="N103" s="5"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="5"/>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3055,8 +3520,11 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
-    </row>
-    <row r="105" spans="1:13">
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -3070,8 +3538,11 @@
       <c r="K105" s="5"/>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
-    </row>
-    <row r="106" spans="1:13">
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5"/>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3085,8 +3556,11 @@
       <c r="K106" s="5"/>
       <c r="L106" s="5"/>
       <c r="M106" s="5"/>
-    </row>
-    <row r="107" spans="1:13">
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+    </row>
+    <row r="107" spans="1:16">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -3100,8 +3574,11 @@
       <c r="K107" s="5"/>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
-    </row>
-    <row r="108" spans="1:13">
+      <c r="N107" s="5"/>
+      <c r="O107" s="5"/>
+      <c r="P107" s="5"/>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -3115,8 +3592,11 @@
       <c r="K108" s="5"/>
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
-    </row>
-    <row r="109" spans="1:13">
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="5"/>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -3130,8 +3610,11 @@
       <c r="K109" s="5"/>
       <c r="L109" s="5"/>
       <c r="M109" s="5"/>
-    </row>
-    <row r="110" spans="1:13">
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3145,8 +3628,11 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
-    </row>
-    <row r="111" spans="1:13">
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3160,8 +3646,11 @@
       <c r="K111" s="5"/>
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
-    </row>
-    <row r="112" spans="1:13">
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3175,8 +3664,11 @@
       <c r="K112" s="5"/>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
-    </row>
-    <row r="113" spans="1:13">
+      <c r="N112" s="5"/>
+      <c r="O112" s="5"/>
+      <c r="P112" s="5"/>
+    </row>
+    <row r="113" spans="1:16">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3190,8 +3682,11 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
-    </row>
-    <row r="114" spans="1:13">
+      <c r="N113" s="5"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="5"/>
+    </row>
+    <row r="114" spans="1:16">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -3205,8 +3700,11 @@
       <c r="K114" s="5"/>
       <c r="L114" s="5"/>
       <c r="M114" s="5"/>
-    </row>
-    <row r="115" spans="1:13">
+      <c r="N114" s="5"/>
+      <c r="O114" s="5"/>
+      <c r="P114" s="5"/>
+    </row>
+    <row r="115" spans="1:16">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3220,8 +3718,11 @@
       <c r="K115" s="5"/>
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
-    </row>
-    <row r="116" spans="1:13">
+      <c r="N115" s="5"/>
+      <c r="O115" s="5"/>
+      <c r="P115" s="5"/>
+    </row>
+    <row r="116" spans="1:16">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3235,8 +3736,11 @@
       <c r="K116" s="5"/>
       <c r="L116" s="5"/>
       <c r="M116" s="5"/>
-    </row>
-    <row r="117" spans="1:13">
+      <c r="N116" s="5"/>
+      <c r="O116" s="5"/>
+      <c r="P116" s="5"/>
+    </row>
+    <row r="117" spans="1:16">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -3250,8 +3754,11 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
-    </row>
-    <row r="118" spans="1:13">
+      <c r="N117" s="5"/>
+      <c r="O117" s="5"/>
+      <c r="P117" s="5"/>
+    </row>
+    <row r="118" spans="1:16">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -3265,8 +3772,11 @@
       <c r="K118" s="5"/>
       <c r="L118" s="5"/>
       <c r="M118" s="5"/>
-    </row>
-    <row r="119" spans="1:13">
+      <c r="N118" s="5"/>
+      <c r="O118" s="5"/>
+      <c r="P118" s="5"/>
+    </row>
+    <row r="119" spans="1:16">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -3280,8 +3790,11 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
-    </row>
-    <row r="120" spans="1:13">
+      <c r="N119" s="5"/>
+      <c r="O119" s="5"/>
+      <c r="P119" s="5"/>
+    </row>
+    <row r="120" spans="1:16">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -3295,8 +3808,11 @@
       <c r="K120" s="5"/>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
-    </row>
-    <row r="121" spans="1:13">
+      <c r="N120" s="5"/>
+      <c r="O120" s="5"/>
+      <c r="P120" s="5"/>
+    </row>
+    <row r="121" spans="1:16">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -3310,8 +3826,11 @@
       <c r="K121" s="5"/>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
-    </row>
-    <row r="122" spans="1:13">
+      <c r="N121" s="5"/>
+      <c r="O121" s="5"/>
+      <c r="P121" s="5"/>
+    </row>
+    <row r="122" spans="1:16">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -3325,8 +3844,11 @@
       <c r="K122" s="5"/>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
-    </row>
-    <row r="123" spans="1:13">
+      <c r="N122" s="5"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="5"/>
+    </row>
+    <row r="123" spans="1:16">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -3340,8 +3862,11 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
-    </row>
-    <row r="124" spans="1:13">
+      <c r="N123" s="5"/>
+      <c r="O123" s="5"/>
+      <c r="P123" s="5"/>
+    </row>
+    <row r="124" spans="1:16">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -3355,8 +3880,11 @@
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
-    </row>
-    <row r="125" spans="1:13">
+      <c r="N124" s="5"/>
+      <c r="O124" s="5"/>
+      <c r="P124" s="5"/>
+    </row>
+    <row r="125" spans="1:16">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -3370,8 +3898,11 @@
       <c r="K125" s="5"/>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
-    </row>
-    <row r="126" spans="1:13">
+      <c r="N125" s="5"/>
+      <c r="O125" s="5"/>
+      <c r="P125" s="5"/>
+    </row>
+    <row r="126" spans="1:16">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -3385,8 +3916,11 @@
       <c r="K126" s="5"/>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
-    </row>
-    <row r="127" spans="1:13">
+      <c r="N126" s="5"/>
+      <c r="O126" s="5"/>
+      <c r="P126" s="5"/>
+    </row>
+    <row r="127" spans="1:16">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -3400,8 +3934,11 @@
       <c r="K127" s="5"/>
       <c r="L127" s="5"/>
       <c r="M127" s="5"/>
-    </row>
-    <row r="128" spans="1:13">
+      <c r="N127" s="5"/>
+      <c r="O127" s="5"/>
+      <c r="P127" s="5"/>
+    </row>
+    <row r="128" spans="1:16">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3415,8 +3952,11 @@
       <c r="K128" s="5"/>
       <c r="L128" s="5"/>
       <c r="M128" s="5"/>
-    </row>
-    <row r="129" spans="1:13">
+      <c r="N128" s="5"/>
+      <c r="O128" s="5"/>
+      <c r="P128" s="5"/>
+    </row>
+    <row r="129" spans="1:16">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -3430,8 +3970,11 @@
       <c r="K129" s="5"/>
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
-    </row>
-    <row r="130" spans="1:13">
+      <c r="N129" s="5"/>
+      <c r="O129" s="5"/>
+      <c r="P129" s="5"/>
+    </row>
+    <row r="130" spans="1:16">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -3445,8 +3988,11 @@
       <c r="K130" s="5"/>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
-    </row>
-    <row r="131" spans="1:13">
+      <c r="N130" s="5"/>
+      <c r="O130" s="5"/>
+      <c r="P130" s="5"/>
+    </row>
+    <row r="131" spans="1:16">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -3460,8 +4006,11 @@
       <c r="K131" s="5"/>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
-    </row>
-    <row r="132" spans="1:13">
+      <c r="N131" s="5"/>
+      <c r="O131" s="5"/>
+      <c r="P131" s="5"/>
+    </row>
+    <row r="132" spans="1:16">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -3475,8 +4024,11 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-    </row>
-    <row r="133" spans="1:13">
+      <c r="N132" s="5"/>
+      <c r="O132" s="5"/>
+      <c r="P132" s="5"/>
+    </row>
+    <row r="133" spans="1:16">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -3490,8 +4042,11 @@
       <c r="K133" s="5"/>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-    </row>
-    <row r="134" spans="1:13">
+      <c r="N133" s="5"/>
+      <c r="O133" s="5"/>
+      <c r="P133" s="5"/>
+    </row>
+    <row r="134" spans="1:16">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -3505,8 +4060,11 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
-    </row>
-    <row r="135" spans="1:13">
+      <c r="N134" s="5"/>
+      <c r="O134" s="5"/>
+      <c r="P134" s="5"/>
+    </row>
+    <row r="135" spans="1:16">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -3520,8 +4078,11 @@
       <c r="K135" s="5"/>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
-    </row>
-    <row r="136" spans="1:13">
+      <c r="N135" s="5"/>
+      <c r="O135" s="5"/>
+      <c r="P135" s="5"/>
+    </row>
+    <row r="136" spans="1:16">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -3535,8 +4096,11 @@
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
-    </row>
-    <row r="137" spans="1:13">
+      <c r="N136" s="5"/>
+      <c r="O136" s="5"/>
+      <c r="P136" s="5"/>
+    </row>
+    <row r="137" spans="1:16">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -3550,8 +4114,11 @@
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
-    </row>
-    <row r="138" spans="1:13">
+      <c r="N137" s="5"/>
+      <c r="O137" s="5"/>
+      <c r="P137" s="5"/>
+    </row>
+    <row r="138" spans="1:16">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -3565,8 +4132,11 @@
       <c r="K138" s="5"/>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
-    </row>
-    <row r="139" spans="1:13">
+      <c r="N138" s="5"/>
+      <c r="O138" s="5"/>
+      <c r="P138" s="5"/>
+    </row>
+    <row r="139" spans="1:16">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -3580,8 +4150,11 @@
       <c r="K139" s="5"/>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
-    </row>
-    <row r="140" spans="1:13">
+      <c r="N139" s="5"/>
+      <c r="O139" s="5"/>
+      <c r="P139" s="5"/>
+    </row>
+    <row r="140" spans="1:16">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -3595,8 +4168,11 @@
       <c r="K140" s="5"/>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
-    </row>
-    <row r="141" spans="1:13">
+      <c r="N140" s="5"/>
+      <c r="O140" s="5"/>
+      <c r="P140" s="5"/>
+    </row>
+    <row r="141" spans="1:16">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -3610,8 +4186,11 @@
       <c r="K141" s="5"/>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
-    </row>
-    <row r="142" spans="1:13">
+      <c r="N141" s="5"/>
+      <c r="O141" s="5"/>
+      <c r="P141" s="5"/>
+    </row>
+    <row r="142" spans="1:16">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -3625,8 +4204,11 @@
       <c r="K142" s="5"/>
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
-    </row>
-    <row r="143" spans="1:13">
+      <c r="N142" s="5"/>
+      <c r="O142" s="5"/>
+      <c r="P142" s="5"/>
+    </row>
+    <row r="143" spans="1:16">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -3640,8 +4222,11 @@
       <c r="K143" s="5"/>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
-    </row>
-    <row r="144" spans="1:13">
+      <c r="N143" s="5"/>
+      <c r="O143" s="5"/>
+      <c r="P143" s="5"/>
+    </row>
+    <row r="144" spans="1:16">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -3655,8 +4240,11 @@
       <c r="K144" s="5"/>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
-    </row>
-    <row r="145" spans="1:13">
+      <c r="N144" s="5"/>
+      <c r="O144" s="5"/>
+      <c r="P144" s="5"/>
+    </row>
+    <row r="145" spans="1:16">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -3670,8 +4258,11 @@
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
-    </row>
-    <row r="146" spans="1:13">
+      <c r="N145" s="5"/>
+      <c r="O145" s="5"/>
+      <c r="P145" s="5"/>
+    </row>
+    <row r="146" spans="1:16">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -3685,8 +4276,11 @@
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
-    </row>
-    <row r="147" spans="1:13">
+      <c r="N146" s="5"/>
+      <c r="O146" s="5"/>
+      <c r="P146" s="5"/>
+    </row>
+    <row r="147" spans="1:16">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -3700,8 +4294,11 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
-    </row>
-    <row r="148" spans="1:13">
+      <c r="N147" s="5"/>
+      <c r="O147" s="5"/>
+      <c r="P147" s="5"/>
+    </row>
+    <row r="148" spans="1:16">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -3715,8 +4312,11 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
-    </row>
-    <row r="149" spans="1:13">
+      <c r="N148" s="5"/>
+      <c r="O148" s="5"/>
+      <c r="P148" s="5"/>
+    </row>
+    <row r="149" spans="1:16">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -3730,8 +4330,11 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="5"/>
-    </row>
-    <row r="150" spans="1:13">
+      <c r="N149" s="5"/>
+      <c r="O149" s="5"/>
+      <c r="P149" s="5"/>
+    </row>
+    <row r="150" spans="1:16">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -3745,8 +4348,11 @@
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
-    </row>
-    <row r="151" spans="1:13">
+      <c r="N150" s="5"/>
+      <c r="O150" s="5"/>
+      <c r="P150" s="5"/>
+    </row>
+    <row r="151" spans="1:16">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -3760,8 +4366,11 @@
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
-    </row>
-    <row r="152" spans="1:13">
+      <c r="N151" s="5"/>
+      <c r="O151" s="5"/>
+      <c r="P151" s="5"/>
+    </row>
+    <row r="152" spans="1:16">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -3775,8 +4384,11 @@
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
-    </row>
-    <row r="153" spans="1:13">
+      <c r="N152" s="5"/>
+      <c r="O152" s="5"/>
+      <c r="P152" s="5"/>
+    </row>
+    <row r="153" spans="1:16">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -3790,8 +4402,11 @@
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
-    </row>
-    <row r="154" spans="1:13">
+      <c r="N153" s="5"/>
+      <c r="O153" s="5"/>
+      <c r="P153" s="5"/>
+    </row>
+    <row r="154" spans="1:16">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -3805,8 +4420,11 @@
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-    </row>
-    <row r="155" spans="1:13">
+      <c r="N154" s="5"/>
+      <c r="O154" s="5"/>
+      <c r="P154" s="5"/>
+    </row>
+    <row r="155" spans="1:16">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -3820,8 +4438,11 @@
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
-    </row>
-    <row r="156" spans="1:13">
+      <c r="N155" s="5"/>
+      <c r="O155" s="5"/>
+      <c r="P155" s="5"/>
+    </row>
+    <row r="156" spans="1:16">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -3835,8 +4456,11 @@
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
-    </row>
-    <row r="157" spans="1:13">
+      <c r="N156" s="5"/>
+      <c r="O156" s="5"/>
+      <c r="P156" s="5"/>
+    </row>
+    <row r="157" spans="1:16">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -3850,8 +4474,11 @@
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
-    </row>
-    <row r="158" spans="1:13">
+      <c r="N157" s="5"/>
+      <c r="O157" s="5"/>
+      <c r="P157" s="5"/>
+    </row>
+    <row r="158" spans="1:16">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -3865,8 +4492,11 @@
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
-    </row>
-    <row r="159" spans="1:13">
+      <c r="N158" s="5"/>
+      <c r="O158" s="5"/>
+      <c r="P158" s="5"/>
+    </row>
+    <row r="159" spans="1:16">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -3880,8 +4510,11 @@
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
-    </row>
-    <row r="160" spans="1:13">
+      <c r="N159" s="5"/>
+      <c r="O159" s="5"/>
+      <c r="P159" s="5"/>
+    </row>
+    <row r="160" spans="1:16">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -3895,8 +4528,11 @@
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
-    </row>
-    <row r="161" spans="1:13">
+      <c r="N160" s="5"/>
+      <c r="O160" s="5"/>
+      <c r="P160" s="5"/>
+    </row>
+    <row r="161" spans="1:16">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -3910,8 +4546,11 @@
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
-    </row>
-    <row r="162" spans="1:13">
+      <c r="N161" s="5"/>
+      <c r="O161" s="5"/>
+      <c r="P161" s="5"/>
+    </row>
+    <row r="162" spans="1:16">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -3925,8 +4564,11 @@
       <c r="K162" s="5"/>
       <c r="L162" s="5"/>
       <c r="M162" s="5"/>
-    </row>
-    <row r="163" spans="1:13">
+      <c r="N162" s="5"/>
+      <c r="O162" s="5"/>
+      <c r="P162" s="5"/>
+    </row>
+    <row r="163" spans="1:16">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -3940,8 +4582,11 @@
       <c r="K163" s="5"/>
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
-    </row>
-    <row r="164" spans="1:13">
+      <c r="N163" s="5"/>
+      <c r="O163" s="5"/>
+      <c r="P163" s="5"/>
+    </row>
+    <row r="164" spans="1:16">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -3955,8 +4600,11 @@
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
-    </row>
-    <row r="165" spans="1:13">
+      <c r="N164" s="5"/>
+      <c r="O164" s="5"/>
+      <c r="P164" s="5"/>
+    </row>
+    <row r="165" spans="1:16">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -3970,8 +4618,11 @@
       <c r="K165" s="5"/>
       <c r="L165" s="5"/>
       <c r="M165" s="5"/>
-    </row>
-    <row r="166" spans="1:13">
+      <c r="N165" s="5"/>
+      <c r="O165" s="5"/>
+      <c r="P165" s="5"/>
+    </row>
+    <row r="166" spans="1:16">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -3985,8 +4636,11 @@
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
       <c r="M166" s="5"/>
-    </row>
-    <row r="167" spans="1:13">
+      <c r="N166" s="5"/>
+      <c r="O166" s="5"/>
+      <c r="P166" s="5"/>
+    </row>
+    <row r="167" spans="1:16">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -4000,8 +4654,11 @@
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
       <c r="M167" s="5"/>
-    </row>
-    <row r="168" spans="1:13">
+      <c r="N167" s="5"/>
+      <c r="O167" s="5"/>
+      <c r="P167" s="5"/>
+    </row>
+    <row r="168" spans="1:16">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -4015,8 +4672,11 @@
       <c r="K168" s="5"/>
       <c r="L168" s="5"/>
       <c r="M168" s="5"/>
-    </row>
-    <row r="169" spans="1:13">
+      <c r="N168" s="5"/>
+      <c r="O168" s="5"/>
+      <c r="P168" s="5"/>
+    </row>
+    <row r="169" spans="1:16">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -4030,8 +4690,11 @@
       <c r="K169" s="5"/>
       <c r="L169" s="5"/>
       <c r="M169" s="5"/>
-    </row>
-    <row r="170" spans="1:13">
+      <c r="N169" s="5"/>
+      <c r="O169" s="5"/>
+      <c r="P169" s="5"/>
+    </row>
+    <row r="170" spans="1:16">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -4045,8 +4708,11 @@
       <c r="K170" s="5"/>
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
-    </row>
-    <row r="171" spans="1:13">
+      <c r="N170" s="5"/>
+      <c r="O170" s="5"/>
+      <c r="P170" s="5"/>
+    </row>
+    <row r="171" spans="1:16">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -4060,8 +4726,11 @@
       <c r="K171" s="5"/>
       <c r="L171" s="5"/>
       <c r="M171" s="5"/>
-    </row>
-    <row r="172" spans="1:13">
+      <c r="N171" s="5"/>
+      <c r="O171" s="5"/>
+      <c r="P171" s="5"/>
+    </row>
+    <row r="172" spans="1:16">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -4075,8 +4744,11 @@
       <c r="K172" s="5"/>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
-    </row>
-    <row r="173" spans="1:13">
+      <c r="N172" s="5"/>
+      <c r="O172" s="5"/>
+      <c r="P172" s="5"/>
+    </row>
+    <row r="173" spans="1:16">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -4090,8 +4762,11 @@
       <c r="K173" s="5"/>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-    </row>
-    <row r="174" spans="1:13">
+      <c r="N173" s="5"/>
+      <c r="O173" s="5"/>
+      <c r="P173" s="5"/>
+    </row>
+    <row r="174" spans="1:16">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -4105,8 +4780,11 @@
       <c r="K174" s="5"/>
       <c r="L174" s="5"/>
       <c r="M174" s="5"/>
-    </row>
-    <row r="175" spans="1:13">
+      <c r="N174" s="5"/>
+      <c r="O174" s="5"/>
+      <c r="P174" s="5"/>
+    </row>
+    <row r="175" spans="1:16">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -4120,8 +4798,11 @@
       <c r="K175" s="5"/>
       <c r="L175" s="5"/>
       <c r="M175" s="5"/>
-    </row>
-    <row r="176" spans="1:13">
+      <c r="N175" s="5"/>
+      <c r="O175" s="5"/>
+      <c r="P175" s="5"/>
+    </row>
+    <row r="176" spans="1:16">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -4135,8 +4816,11 @@
       <c r="K176" s="5"/>
       <c r="L176" s="5"/>
       <c r="M176" s="5"/>
-    </row>
-    <row r="177" spans="1:13">
+      <c r="N176" s="5"/>
+      <c r="O176" s="5"/>
+      <c r="P176" s="5"/>
+    </row>
+    <row r="177" spans="1:16">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -4150,8 +4834,11 @@
       <c r="K177" s="5"/>
       <c r="L177" s="5"/>
       <c r="M177" s="5"/>
-    </row>
-    <row r="178" spans="1:13">
+      <c r="N177" s="5"/>
+      <c r="O177" s="5"/>
+      <c r="P177" s="5"/>
+    </row>
+    <row r="178" spans="1:16">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -4165,8 +4852,11 @@
       <c r="K178" s="5"/>
       <c r="L178" s="5"/>
       <c r="M178" s="5"/>
-    </row>
-    <row r="179" spans="1:13">
+      <c r="N178" s="5"/>
+      <c r="O178" s="5"/>
+      <c r="P178" s="5"/>
+    </row>
+    <row r="179" spans="1:16">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -4180,8 +4870,11 @@
       <c r="K179" s="5"/>
       <c r="L179" s="5"/>
       <c r="M179" s="5"/>
-    </row>
-    <row r="180" spans="1:13">
+      <c r="N179" s="5"/>
+      <c r="O179" s="5"/>
+      <c r="P179" s="5"/>
+    </row>
+    <row r="180" spans="1:16">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -4195,8 +4888,11 @@
       <c r="K180" s="5"/>
       <c r="L180" s="5"/>
       <c r="M180" s="5"/>
-    </row>
-    <row r="181" spans="1:13">
+      <c r="N180" s="5"/>
+      <c r="O180" s="5"/>
+      <c r="P180" s="5"/>
+    </row>
+    <row r="181" spans="1:16">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -4210,8 +4906,11 @@
       <c r="K181" s="5"/>
       <c r="L181" s="5"/>
       <c r="M181" s="5"/>
-    </row>
-    <row r="182" spans="1:13">
+      <c r="N181" s="5"/>
+      <c r="O181" s="5"/>
+      <c r="P181" s="5"/>
+    </row>
+    <row r="182" spans="1:16">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -4225,8 +4924,11 @@
       <c r="K182" s="5"/>
       <c r="L182" s="5"/>
       <c r="M182" s="5"/>
-    </row>
-    <row r="183" spans="1:13">
+      <c r="N182" s="5"/>
+      <c r="O182" s="5"/>
+      <c r="P182" s="5"/>
+    </row>
+    <row r="183" spans="1:16">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -4240,8 +4942,11 @@
       <c r="K183" s="5"/>
       <c r="L183" s="5"/>
       <c r="M183" s="5"/>
-    </row>
-    <row r="184" spans="1:13">
+      <c r="N183" s="5"/>
+      <c r="O183" s="5"/>
+      <c r="P183" s="5"/>
+    </row>
+    <row r="184" spans="1:16">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -4255,8 +4960,11 @@
       <c r="K184" s="5"/>
       <c r="L184" s="5"/>
       <c r="M184" s="5"/>
-    </row>
-    <row r="185" spans="1:13">
+      <c r="N184" s="5"/>
+      <c r="O184" s="5"/>
+      <c r="P184" s="5"/>
+    </row>
+    <row r="185" spans="1:16">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -4270,8 +4978,11 @@
       <c r="K185" s="5"/>
       <c r="L185" s="5"/>
       <c r="M185" s="5"/>
-    </row>
-    <row r="186" spans="1:13">
+      <c r="N185" s="5"/>
+      <c r="O185" s="5"/>
+      <c r="P185" s="5"/>
+    </row>
+    <row r="186" spans="1:16">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -4285,8 +4996,11 @@
       <c r="K186" s="5"/>
       <c r="L186" s="5"/>
       <c r="M186" s="5"/>
-    </row>
-    <row r="187" spans="1:13">
+      <c r="N186" s="5"/>
+      <c r="O186" s="5"/>
+      <c r="P186" s="5"/>
+    </row>
+    <row r="187" spans="1:16">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -4300,8 +5014,11 @@
       <c r="K187" s="5"/>
       <c r="L187" s="5"/>
       <c r="M187" s="5"/>
-    </row>
-    <row r="188" spans="1:13">
+      <c r="N187" s="5"/>
+      <c r="O187" s="5"/>
+      <c r="P187" s="5"/>
+    </row>
+    <row r="188" spans="1:16">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -4315,8 +5032,11 @@
       <c r="K188" s="5"/>
       <c r="L188" s="5"/>
       <c r="M188" s="5"/>
-    </row>
-    <row r="189" spans="1:13">
+      <c r="N188" s="5"/>
+      <c r="O188" s="5"/>
+      <c r="P188" s="5"/>
+    </row>
+    <row r="189" spans="1:16">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -4330,8 +5050,11 @@
       <c r="K189" s="5"/>
       <c r="L189" s="5"/>
       <c r="M189" s="5"/>
-    </row>
-    <row r="190" spans="1:13">
+      <c r="N189" s="5"/>
+      <c r="O189" s="5"/>
+      <c r="P189" s="5"/>
+    </row>
+    <row r="190" spans="1:16">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -4345,8 +5068,11 @@
       <c r="K190" s="5"/>
       <c r="L190" s="5"/>
       <c r="M190" s="5"/>
-    </row>
-    <row r="191" spans="1:13">
+      <c r="N190" s="5"/>
+      <c r="O190" s="5"/>
+      <c r="P190" s="5"/>
+    </row>
+    <row r="191" spans="1:16">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -4360,8 +5086,11 @@
       <c r="K191" s="5"/>
       <c r="L191" s="5"/>
       <c r="M191" s="5"/>
-    </row>
-    <row r="192" spans="1:13">
+      <c r="N191" s="5"/>
+      <c r="O191" s="5"/>
+      <c r="P191" s="5"/>
+    </row>
+    <row r="192" spans="1:16">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -4375,8 +5104,11 @@
       <c r="K192" s="5"/>
       <c r="L192" s="5"/>
       <c r="M192" s="5"/>
-    </row>
-    <row r="193" spans="1:13">
+      <c r="N192" s="5"/>
+      <c r="O192" s="5"/>
+      <c r="P192" s="5"/>
+    </row>
+    <row r="193" spans="1:16">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -4390,8 +5122,11 @@
       <c r="K193" s="5"/>
       <c r="L193" s="5"/>
       <c r="M193" s="5"/>
-    </row>
-    <row r="194" spans="1:13">
+      <c r="N193" s="5"/>
+      <c r="O193" s="5"/>
+      <c r="P193" s="5"/>
+    </row>
+    <row r="194" spans="1:16">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -4405,8 +5140,11 @@
       <c r="K194" s="5"/>
       <c r="L194" s="5"/>
       <c r="M194" s="5"/>
-    </row>
-    <row r="195" spans="1:13">
+      <c r="N194" s="5"/>
+      <c r="O194" s="5"/>
+      <c r="P194" s="5"/>
+    </row>
+    <row r="195" spans="1:16">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -4420,8 +5158,11 @@
       <c r="K195" s="5"/>
       <c r="L195" s="5"/>
       <c r="M195" s="5"/>
-    </row>
-    <row r="196" spans="1:13">
+      <c r="N195" s="5"/>
+      <c r="O195" s="5"/>
+      <c r="P195" s="5"/>
+    </row>
+    <row r="196" spans="1:16">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -4435,8 +5176,11 @@
       <c r="K196" s="5"/>
       <c r="L196" s="5"/>
       <c r="M196" s="5"/>
-    </row>
-    <row r="197" spans="1:13">
+      <c r="N196" s="5"/>
+      <c r="O196" s="5"/>
+      <c r="P196" s="5"/>
+    </row>
+    <row r="197" spans="1:16">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -4450,8 +5194,11 @@
       <c r="K197" s="5"/>
       <c r="L197" s="5"/>
       <c r="M197" s="5"/>
-    </row>
-    <row r="198" spans="1:13">
+      <c r="N197" s="5"/>
+      <c r="O197" s="5"/>
+      <c r="P197" s="5"/>
+    </row>
+    <row r="198" spans="1:16">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -4465,8 +5212,11 @@
       <c r="K198" s="5"/>
       <c r="L198" s="5"/>
       <c r="M198" s="5"/>
-    </row>
-    <row r="199" spans="1:13">
+      <c r="N198" s="5"/>
+      <c r="O198" s="5"/>
+      <c r="P198" s="5"/>
+    </row>
+    <row r="199" spans="1:16">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -4480,8 +5230,11 @@
       <c r="K199" s="5"/>
       <c r="L199" s="5"/>
       <c r="M199" s="5"/>
-    </row>
-    <row r="200" spans="1:13">
+      <c r="N199" s="5"/>
+      <c r="O199" s="5"/>
+      <c r="P199" s="5"/>
+    </row>
+    <row r="200" spans="1:16">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -4495,8 +5248,11 @@
       <c r="K200" s="5"/>
       <c r="L200" s="5"/>
       <c r="M200" s="5"/>
-    </row>
-    <row r="201" spans="1:13">
+      <c r="N200" s="5"/>
+      <c r="O200" s="5"/>
+      <c r="P200" s="5"/>
+    </row>
+    <row r="201" spans="1:16">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -4510,8 +5266,11 @@
       <c r="K201" s="5"/>
       <c r="L201" s="5"/>
       <c r="M201" s="5"/>
-    </row>
-    <row r="202" spans="1:13">
+      <c r="N201" s="5"/>
+      <c r="O201" s="5"/>
+      <c r="P201" s="5"/>
+    </row>
+    <row r="202" spans="1:16">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -4525,8 +5284,11 @@
       <c r="K202" s="5"/>
       <c r="L202" s="5"/>
       <c r="M202" s="5"/>
-    </row>
-    <row r="203" spans="1:13">
+      <c r="N202" s="5"/>
+      <c r="O202" s="5"/>
+      <c r="P202" s="5"/>
+    </row>
+    <row r="203" spans="1:16">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -4540,8 +5302,11 @@
       <c r="K203" s="5"/>
       <c r="L203" s="5"/>
       <c r="M203" s="5"/>
-    </row>
-    <row r="204" spans="1:13">
+      <c r="N203" s="5"/>
+      <c r="O203" s="5"/>
+      <c r="P203" s="5"/>
+    </row>
+    <row r="204" spans="1:16">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -4555,8 +5320,11 @@
       <c r="K204" s="5"/>
       <c r="L204" s="5"/>
       <c r="M204" s="5"/>
-    </row>
-    <row r="205" spans="1:13">
+      <c r="N204" s="5"/>
+      <c r="O204" s="5"/>
+      <c r="P204" s="5"/>
+    </row>
+    <row r="205" spans="1:16">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -4570,8 +5338,11 @@
       <c r="K205" s="5"/>
       <c r="L205" s="5"/>
       <c r="M205" s="5"/>
-    </row>
-    <row r="206" spans="1:13">
+      <c r="N205" s="5"/>
+      <c r="O205" s="5"/>
+      <c r="P205" s="5"/>
+    </row>
+    <row r="206" spans="1:16">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -4585,8 +5356,11 @@
       <c r="K206" s="5"/>
       <c r="L206" s="5"/>
       <c r="M206" s="5"/>
-    </row>
-    <row r="207" spans="1:13">
+      <c r="N206" s="5"/>
+      <c r="O206" s="5"/>
+      <c r="P206" s="5"/>
+    </row>
+    <row r="207" spans="1:16">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -4600,8 +5374,11 @@
       <c r="K207" s="5"/>
       <c r="L207" s="5"/>
       <c r="M207" s="5"/>
-    </row>
-    <row r="208" spans="1:13">
+      <c r="N207" s="5"/>
+      <c r="O207" s="5"/>
+      <c r="P207" s="5"/>
+    </row>
+    <row r="208" spans="1:16">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -4615,8 +5392,11 @@
       <c r="K208" s="5"/>
       <c r="L208" s="5"/>
       <c r="M208" s="5"/>
-    </row>
-    <row r="209" spans="1:13">
+      <c r="N208" s="5"/>
+      <c r="O208" s="5"/>
+      <c r="P208" s="5"/>
+    </row>
+    <row r="209" spans="1:16">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -4630,8 +5410,11 @@
       <c r="K209" s="5"/>
       <c r="L209" s="5"/>
       <c r="M209" s="5"/>
-    </row>
-    <row r="210" spans="1:13">
+      <c r="N209" s="5"/>
+      <c r="O209" s="5"/>
+      <c r="P209" s="5"/>
+    </row>
+    <row r="210" spans="1:16">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -4645,8 +5428,11 @@
       <c r="K210" s="5"/>
       <c r="L210" s="5"/>
       <c r="M210" s="5"/>
-    </row>
-    <row r="211" spans="1:13">
+      <c r="N210" s="5"/>
+      <c r="O210" s="5"/>
+      <c r="P210" s="5"/>
+    </row>
+    <row r="211" spans="1:16">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -4660,8 +5446,11 @@
       <c r="K211" s="5"/>
       <c r="L211" s="5"/>
       <c r="M211" s="5"/>
-    </row>
-    <row r="212" spans="1:13">
+      <c r="N211" s="5"/>
+      <c r="O211" s="5"/>
+      <c r="P211" s="5"/>
+    </row>
+    <row r="212" spans="1:16">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -4675,8 +5464,11 @@
       <c r="K212" s="5"/>
       <c r="L212" s="5"/>
       <c r="M212" s="5"/>
-    </row>
-    <row r="213" spans="1:13">
+      <c r="N212" s="5"/>
+      <c r="O212" s="5"/>
+      <c r="P212" s="5"/>
+    </row>
+    <row r="213" spans="1:16">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -4690,8 +5482,11 @@
       <c r="K213" s="5"/>
       <c r="L213" s="5"/>
       <c r="M213" s="5"/>
-    </row>
-    <row r="214" spans="1:13">
+      <c r="N213" s="5"/>
+      <c r="O213" s="5"/>
+      <c r="P213" s="5"/>
+    </row>
+    <row r="214" spans="1:16">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -4705,8 +5500,11 @@
       <c r="K214" s="5"/>
       <c r="L214" s="5"/>
       <c r="M214" s="5"/>
-    </row>
-    <row r="215" spans="1:13">
+      <c r="N214" s="5"/>
+      <c r="O214" s="5"/>
+      <c r="P214" s="5"/>
+    </row>
+    <row r="215" spans="1:16">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -4720,8 +5518,11 @@
       <c r="K215" s="5"/>
       <c r="L215" s="5"/>
       <c r="M215" s="5"/>
-    </row>
-    <row r="216" spans="1:13">
+      <c r="N215" s="5"/>
+      <c r="O215" s="5"/>
+      <c r="P215" s="5"/>
+    </row>
+    <row r="216" spans="1:16">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -4735,8 +5536,11 @@
       <c r="K216" s="5"/>
       <c r="L216" s="5"/>
       <c r="M216" s="5"/>
-    </row>
-    <row r="217" spans="1:13">
+      <c r="N216" s="5"/>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+    </row>
+    <row r="217" spans="1:16">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -4750,8 +5554,11 @@
       <c r="K217" s="5"/>
       <c r="L217" s="5"/>
       <c r="M217" s="5"/>
-    </row>
-    <row r="218" spans="1:13">
+      <c r="N217" s="5"/>
+      <c r="O217" s="5"/>
+      <c r="P217" s="5"/>
+    </row>
+    <row r="218" spans="1:16">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -4765,8 +5572,11 @@
       <c r="K218" s="5"/>
       <c r="L218" s="5"/>
       <c r="M218" s="5"/>
-    </row>
-    <row r="219" spans="1:13">
+      <c r="N218" s="5"/>
+      <c r="O218" s="5"/>
+      <c r="P218" s="5"/>
+    </row>
+    <row r="219" spans="1:16">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -4780,8 +5590,11 @@
       <c r="K219" s="5"/>
       <c r="L219" s="5"/>
       <c r="M219" s="5"/>
-    </row>
-    <row r="220" spans="1:13">
+      <c r="N219" s="5"/>
+      <c r="O219" s="5"/>
+      <c r="P219" s="5"/>
+    </row>
+    <row r="220" spans="1:16">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -4795,8 +5608,11 @@
       <c r="K220" s="5"/>
       <c r="L220" s="5"/>
       <c r="M220" s="5"/>
-    </row>
-    <row r="221" spans="1:13">
+      <c r="N220" s="5"/>
+      <c r="O220" s="5"/>
+      <c r="P220" s="5"/>
+    </row>
+    <row r="221" spans="1:16">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -4810,8 +5626,11 @@
       <c r="K221" s="5"/>
       <c r="L221" s="5"/>
       <c r="M221" s="5"/>
-    </row>
-    <row r="222" spans="1:13">
+      <c r="N221" s="5"/>
+      <c r="O221" s="5"/>
+      <c r="P221" s="5"/>
+    </row>
+    <row r="222" spans="1:16">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -4825,8 +5644,11 @@
       <c r="K222" s="5"/>
       <c r="L222" s="5"/>
       <c r="M222" s="5"/>
-    </row>
-    <row r="223" spans="1:13">
+      <c r="N222" s="5"/>
+      <c r="O222" s="5"/>
+      <c r="P222" s="5"/>
+    </row>
+    <row r="223" spans="1:16">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -4840,8 +5662,11 @@
       <c r="K223" s="5"/>
       <c r="L223" s="5"/>
       <c r="M223" s="5"/>
-    </row>
-    <row r="224" spans="1:13">
+      <c r="N223" s="5"/>
+      <c r="O223" s="5"/>
+      <c r="P223" s="5"/>
+    </row>
+    <row r="224" spans="1:16">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -4855,8 +5680,11 @@
       <c r="K224" s="5"/>
       <c r="L224" s="5"/>
       <c r="M224" s="5"/>
-    </row>
-    <row r="225" spans="1:13">
+      <c r="N224" s="5"/>
+      <c r="O224" s="5"/>
+      <c r="P224" s="5"/>
+    </row>
+    <row r="225" spans="1:16">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -4870,8 +5698,11 @@
       <c r="K225" s="5"/>
       <c r="L225" s="5"/>
       <c r="M225" s="5"/>
-    </row>
-    <row r="226" spans="1:13">
+      <c r="N225" s="5"/>
+      <c r="O225" s="5"/>
+      <c r="P225" s="5"/>
+    </row>
+    <row r="226" spans="1:16">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -4885,8 +5716,11 @@
       <c r="K226" s="5"/>
       <c r="L226" s="5"/>
       <c r="M226" s="5"/>
-    </row>
-    <row r="227" spans="1:13">
+      <c r="N226" s="5"/>
+      <c r="O226" s="5"/>
+      <c r="P226" s="5"/>
+    </row>
+    <row r="227" spans="1:16">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -4900,8 +5734,11 @@
       <c r="K227" s="5"/>
       <c r="L227" s="5"/>
       <c r="M227" s="5"/>
-    </row>
-    <row r="228" spans="1:13">
+      <c r="N227" s="5"/>
+      <c r="O227" s="5"/>
+      <c r="P227" s="5"/>
+    </row>
+    <row r="228" spans="1:16">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -4915,8 +5752,11 @@
       <c r="K228" s="5"/>
       <c r="L228" s="5"/>
       <c r="M228" s="5"/>
-    </row>
-    <row r="229" spans="1:13">
+      <c r="N228" s="5"/>
+      <c r="O228" s="5"/>
+      <c r="P228" s="5"/>
+    </row>
+    <row r="229" spans="1:16">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -4930,8 +5770,11 @@
       <c r="K229" s="5"/>
       <c r="L229" s="5"/>
       <c r="M229" s="5"/>
-    </row>
-    <row r="230" spans="1:13">
+      <c r="N229" s="5"/>
+      <c r="O229" s="5"/>
+      <c r="P229" s="5"/>
+    </row>
+    <row r="230" spans="1:16">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -4945,8 +5788,11 @@
       <c r="K230" s="5"/>
       <c r="L230" s="5"/>
       <c r="M230" s="5"/>
-    </row>
-    <row r="231" spans="1:13">
+      <c r="N230" s="5"/>
+      <c r="O230" s="5"/>
+      <c r="P230" s="5"/>
+    </row>
+    <row r="231" spans="1:16">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -4960,8 +5806,11 @@
       <c r="K231" s="5"/>
       <c r="L231" s="5"/>
       <c r="M231" s="5"/>
-    </row>
-    <row r="232" spans="1:13">
+      <c r="N231" s="5"/>
+      <c r="O231" s="5"/>
+      <c r="P231" s="5"/>
+    </row>
+    <row r="232" spans="1:16">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -4975,8 +5824,11 @@
       <c r="K232" s="5"/>
       <c r="L232" s="5"/>
       <c r="M232" s="5"/>
-    </row>
-    <row r="233" spans="1:13">
+      <c r="N232" s="5"/>
+      <c r="O232" s="5"/>
+      <c r="P232" s="5"/>
+    </row>
+    <row r="233" spans="1:16">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -4990,8 +5842,11 @@
       <c r="K233" s="5"/>
       <c r="L233" s="5"/>
       <c r="M233" s="5"/>
-    </row>
-    <row r="234" spans="1:13">
+      <c r="N233" s="5"/>
+      <c r="O233" s="5"/>
+      <c r="P233" s="5"/>
+    </row>
+    <row r="234" spans="1:16">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -5005,8 +5860,11 @@
       <c r="K234" s="5"/>
       <c r="L234" s="5"/>
       <c r="M234" s="5"/>
-    </row>
-    <row r="235" spans="1:13">
+      <c r="N234" s="5"/>
+      <c r="O234" s="5"/>
+      <c r="P234" s="5"/>
+    </row>
+    <row r="235" spans="1:16">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -5020,8 +5878,11 @@
       <c r="K235" s="5"/>
       <c r="L235" s="5"/>
       <c r="M235" s="5"/>
-    </row>
-    <row r="236" spans="1:13">
+      <c r="N235" s="5"/>
+      <c r="O235" s="5"/>
+      <c r="P235" s="5"/>
+    </row>
+    <row r="236" spans="1:16">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -5035,8 +5896,11 @@
       <c r="K236" s="5"/>
       <c r="L236" s="5"/>
       <c r="M236" s="5"/>
-    </row>
-    <row r="237" spans="1:13">
+      <c r="N236" s="5"/>
+      <c r="O236" s="5"/>
+      <c r="P236" s="5"/>
+    </row>
+    <row r="237" spans="1:16">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -5050,8 +5914,11 @@
       <c r="K237" s="5"/>
       <c r="L237" s="5"/>
       <c r="M237" s="5"/>
-    </row>
-    <row r="238" spans="1:13">
+      <c r="N237" s="5"/>
+      <c r="O237" s="5"/>
+      <c r="P237" s="5"/>
+    </row>
+    <row r="238" spans="1:16">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -5065,8 +5932,11 @@
       <c r="K238" s="5"/>
       <c r="L238" s="5"/>
       <c r="M238" s="5"/>
-    </row>
-    <row r="239" spans="1:13">
+      <c r="N238" s="5"/>
+      <c r="O238" s="5"/>
+      <c r="P238" s="5"/>
+    </row>
+    <row r="239" spans="1:16">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -5080,8 +5950,11 @@
       <c r="K239" s="5"/>
       <c r="L239" s="5"/>
       <c r="M239" s="5"/>
-    </row>
-    <row r="240" spans="1:13">
+      <c r="N239" s="5"/>
+      <c r="O239" s="5"/>
+      <c r="P239" s="5"/>
+    </row>
+    <row r="240" spans="1:16">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -5095,8 +5968,11 @@
       <c r="K240" s="5"/>
       <c r="L240" s="5"/>
       <c r="M240" s="5"/>
-    </row>
-    <row r="241" spans="1:13">
+      <c r="N240" s="5"/>
+      <c r="O240" s="5"/>
+      <c r="P240" s="5"/>
+    </row>
+    <row r="241" spans="1:16">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -5110,8 +5986,11 @@
       <c r="K241" s="5"/>
       <c r="L241" s="5"/>
       <c r="M241" s="5"/>
-    </row>
-    <row r="242" spans="1:13">
+      <c r="N241" s="5"/>
+      <c r="O241" s="5"/>
+      <c r="P241" s="5"/>
+    </row>
+    <row r="242" spans="1:16">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -5125,8 +6004,11 @@
       <c r="K242" s="5"/>
       <c r="L242" s="5"/>
       <c r="M242" s="5"/>
-    </row>
-    <row r="243" spans="1:13">
+      <c r="N242" s="5"/>
+      <c r="O242" s="5"/>
+      <c r="P242" s="5"/>
+    </row>
+    <row r="243" spans="1:16">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -5140,8 +6022,11 @@
       <c r="K243" s="5"/>
       <c r="L243" s="5"/>
       <c r="M243" s="5"/>
-    </row>
-    <row r="244" spans="1:13">
+      <c r="N243" s="5"/>
+      <c r="O243" s="5"/>
+      <c r="P243" s="5"/>
+    </row>
+    <row r="244" spans="1:16">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -5155,8 +6040,11 @@
       <c r="K244" s="5"/>
       <c r="L244" s="5"/>
       <c r="M244" s="5"/>
-    </row>
-    <row r="245" spans="1:13">
+      <c r="N244" s="5"/>
+      <c r="O244" s="5"/>
+      <c r="P244" s="5"/>
+    </row>
+    <row r="245" spans="1:16">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -5170,8 +6058,11 @@
       <c r="K245" s="5"/>
       <c r="L245" s="5"/>
       <c r="M245" s="5"/>
-    </row>
-    <row r="246" spans="1:13">
+      <c r="N245" s="5"/>
+      <c r="O245" s="5"/>
+      <c r="P245" s="5"/>
+    </row>
+    <row r="246" spans="1:16">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -5185,8 +6076,11 @@
       <c r="K246" s="5"/>
       <c r="L246" s="5"/>
       <c r="M246" s="5"/>
-    </row>
-    <row r="247" spans="1:13">
+      <c r="N246" s="5"/>
+      <c r="O246" s="5"/>
+      <c r="P246" s="5"/>
+    </row>
+    <row r="247" spans="1:16">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -5200,8 +6094,11 @@
       <c r="K247" s="5"/>
       <c r="L247" s="5"/>
       <c r="M247" s="5"/>
-    </row>
-    <row r="248" spans="1:13">
+      <c r="N247" s="5"/>
+      <c r="O247" s="5"/>
+      <c r="P247" s="5"/>
+    </row>
+    <row r="248" spans="1:16">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -5215,8 +6112,11 @@
       <c r="K248" s="5"/>
       <c r="L248" s="5"/>
       <c r="M248" s="5"/>
-    </row>
-    <row r="249" spans="1:13">
+      <c r="N248" s="5"/>
+      <c r="O248" s="5"/>
+      <c r="P248" s="5"/>
+    </row>
+    <row r="249" spans="1:16">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -5230,8 +6130,11 @@
       <c r="K249" s="5"/>
       <c r="L249" s="5"/>
       <c r="M249" s="5"/>
-    </row>
-    <row r="250" spans="1:13">
+      <c r="N249" s="5"/>
+      <c r="O249" s="5"/>
+      <c r="P249" s="5"/>
+    </row>
+    <row r="250" spans="1:16">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -5245,8 +6148,11 @@
       <c r="K250" s="5"/>
       <c r="L250" s="5"/>
       <c r="M250" s="5"/>
-    </row>
-    <row r="251" spans="1:13">
+      <c r="N250" s="5"/>
+      <c r="O250" s="5"/>
+      <c r="P250" s="5"/>
+    </row>
+    <row r="251" spans="1:16">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -5260,8 +6166,11 @@
       <c r="K251" s="5"/>
       <c r="L251" s="5"/>
       <c r="M251" s="5"/>
-    </row>
-    <row r="252" spans="1:13">
+      <c r="N251" s="5"/>
+      <c r="O251" s="5"/>
+      <c r="P251" s="5"/>
+    </row>
+    <row r="252" spans="1:16">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -5275,8 +6184,11 @@
       <c r="K252" s="5"/>
       <c r="L252" s="5"/>
       <c r="M252" s="5"/>
-    </row>
-    <row r="253" spans="1:13">
+      <c r="N252" s="5"/>
+      <c r="O252" s="5"/>
+      <c r="P252" s="5"/>
+    </row>
+    <row r="253" spans="1:16">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -5290,8 +6202,11 @@
       <c r="K253" s="5"/>
       <c r="L253" s="5"/>
       <c r="M253" s="5"/>
-    </row>
-    <row r="254" spans="1:13">
+      <c r="N253" s="5"/>
+      <c r="O253" s="5"/>
+      <c r="P253" s="5"/>
+    </row>
+    <row r="254" spans="1:16">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -5305,8 +6220,11 @@
       <c r="K254" s="5"/>
       <c r="L254" s="5"/>
       <c r="M254" s="5"/>
-    </row>
-    <row r="255" spans="1:13">
+      <c r="N254" s="5"/>
+      <c r="O254" s="5"/>
+      <c r="P254" s="5"/>
+    </row>
+    <row r="255" spans="1:16">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -5320,8 +6238,11 @@
       <c r="K255" s="5"/>
       <c r="L255" s="5"/>
       <c r="M255" s="5"/>
-    </row>
-    <row r="256" spans="1:13">
+      <c r="N255" s="5"/>
+      <c r="O255" s="5"/>
+      <c r="P255" s="5"/>
+    </row>
+    <row r="256" spans="1:16">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -5335,8 +6256,11 @@
       <c r="K256" s="5"/>
       <c r="L256" s="5"/>
       <c r="M256" s="5"/>
-    </row>
-    <row r="257" spans="1:13">
+      <c r="N256" s="5"/>
+      <c r="O256" s="5"/>
+      <c r="P256" s="5"/>
+    </row>
+    <row r="257" spans="1:16">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -5350,8 +6274,11 @@
       <c r="K257" s="5"/>
       <c r="L257" s="5"/>
       <c r="M257" s="5"/>
-    </row>
-    <row r="258" spans="1:13">
+      <c r="N257" s="5"/>
+      <c r="O257" s="5"/>
+      <c r="P257" s="5"/>
+    </row>
+    <row r="258" spans="1:16">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -5365,8 +6292,11 @@
       <c r="K258" s="5"/>
       <c r="L258" s="5"/>
       <c r="M258" s="5"/>
-    </row>
-    <row r="259" spans="1:13">
+      <c r="N258" s="5"/>
+      <c r="O258" s="5"/>
+      <c r="P258" s="5"/>
+    </row>
+    <row r="259" spans="1:16">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -5380,8 +6310,11 @@
       <c r="K259" s="5"/>
       <c r="L259" s="5"/>
       <c r="M259" s="5"/>
-    </row>
-    <row r="260" spans="1:13">
+      <c r="N259" s="5"/>
+      <c r="O259" s="5"/>
+      <c r="P259" s="5"/>
+    </row>
+    <row r="260" spans="1:16">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -5395,8 +6328,11 @@
       <c r="K260" s="5"/>
       <c r="L260" s="5"/>
       <c r="M260" s="5"/>
-    </row>
-    <row r="261" spans="1:13">
+      <c r="N260" s="5"/>
+      <c r="O260" s="5"/>
+      <c r="P260" s="5"/>
+    </row>
+    <row r="261" spans="1:16">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -5410,8 +6346,11 @@
       <c r="K261" s="5"/>
       <c r="L261" s="5"/>
       <c r="M261" s="5"/>
-    </row>
-    <row r="262" spans="1:13">
+      <c r="N261" s="5"/>
+      <c r="O261" s="5"/>
+      <c r="P261" s="5"/>
+    </row>
+    <row r="262" spans="1:16">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -5425,8 +6364,11 @@
       <c r="K262" s="5"/>
       <c r="L262" s="5"/>
       <c r="M262" s="5"/>
-    </row>
-    <row r="263" spans="1:13">
+      <c r="N262" s="5"/>
+      <c r="O262" s="5"/>
+      <c r="P262" s="5"/>
+    </row>
+    <row r="263" spans="1:16">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -5440,8 +6382,11 @@
       <c r="K263" s="5"/>
       <c r="L263" s="5"/>
       <c r="M263" s="5"/>
-    </row>
-    <row r="264" spans="1:13">
+      <c r="N263" s="5"/>
+      <c r="O263" s="5"/>
+      <c r="P263" s="5"/>
+    </row>
+    <row r="264" spans="1:16">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -5455,8 +6400,11 @@
       <c r="K264" s="5"/>
       <c r="L264" s="5"/>
       <c r="M264" s="5"/>
-    </row>
-    <row r="265" spans="1:13">
+      <c r="N264" s="5"/>
+      <c r="O264" s="5"/>
+      <c r="P264" s="5"/>
+    </row>
+    <row r="265" spans="1:16">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -5470,8 +6418,11 @@
       <c r="K265" s="5"/>
       <c r="L265" s="5"/>
       <c r="M265" s="5"/>
-    </row>
-    <row r="266" spans="1:13">
+      <c r="N265" s="5"/>
+      <c r="O265" s="5"/>
+      <c r="P265" s="5"/>
+    </row>
+    <row r="266" spans="1:16">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -5485,8 +6436,11 @@
       <c r="K266" s="5"/>
       <c r="L266" s="5"/>
       <c r="M266" s="5"/>
-    </row>
-    <row r="267" spans="1:13">
+      <c r="N266" s="5"/>
+      <c r="O266" s="5"/>
+      <c r="P266" s="5"/>
+    </row>
+    <row r="267" spans="1:16">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -5500,8 +6454,11 @@
       <c r="K267" s="5"/>
       <c r="L267" s="5"/>
       <c r="M267" s="5"/>
-    </row>
-    <row r="268" spans="1:13">
+      <c r="N267" s="5"/>
+      <c r="O267" s="5"/>
+      <c r="P267" s="5"/>
+    </row>
+    <row r="268" spans="1:16">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -5515,8 +6472,11 @@
       <c r="K268" s="5"/>
       <c r="L268" s="5"/>
       <c r="M268" s="5"/>
-    </row>
-    <row r="269" spans="1:13">
+      <c r="N268" s="5"/>
+      <c r="O268" s="5"/>
+      <c r="P268" s="5"/>
+    </row>
+    <row r="269" spans="1:16">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -5530,8 +6490,11 @@
       <c r="K269" s="5"/>
       <c r="L269" s="5"/>
       <c r="M269" s="5"/>
-    </row>
-    <row r="270" spans="1:13">
+      <c r="N269" s="5"/>
+      <c r="O269" s="5"/>
+      <c r="P269" s="5"/>
+    </row>
+    <row r="270" spans="1:16">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -5545,8 +6508,11 @@
       <c r="K270" s="5"/>
       <c r="L270" s="5"/>
       <c r="M270" s="5"/>
-    </row>
-    <row r="271" spans="1:13">
+      <c r="N270" s="5"/>
+      <c r="O270" s="5"/>
+      <c r="P270" s="5"/>
+    </row>
+    <row r="271" spans="1:16">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -5560,8 +6526,11 @@
       <c r="K271" s="5"/>
       <c r="L271" s="5"/>
       <c r="M271" s="5"/>
-    </row>
-    <row r="272" spans="1:13">
+      <c r="N271" s="5"/>
+      <c r="O271" s="5"/>
+      <c r="P271" s="5"/>
+    </row>
+    <row r="272" spans="1:16">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -5575,8 +6544,11 @@
       <c r="K272" s="5"/>
       <c r="L272" s="5"/>
       <c r="M272" s="5"/>
-    </row>
-    <row r="273" spans="1:13">
+      <c r="N272" s="5"/>
+      <c r="O272" s="5"/>
+      <c r="P272" s="5"/>
+    </row>
+    <row r="273" spans="1:16">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -5590,8 +6562,11 @@
       <c r="K273" s="5"/>
       <c r="L273" s="5"/>
       <c r="M273" s="5"/>
-    </row>
-    <row r="274" spans="1:13">
+      <c r="N273" s="5"/>
+      <c r="O273" s="5"/>
+      <c r="P273" s="5"/>
+    </row>
+    <row r="274" spans="1:16">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -5605,8 +6580,11 @@
       <c r="K274" s="5"/>
       <c r="L274" s="5"/>
       <c r="M274" s="5"/>
-    </row>
-    <row r="275" spans="1:13">
+      <c r="N274" s="5"/>
+      <c r="O274" s="5"/>
+      <c r="P274" s="5"/>
+    </row>
+    <row r="275" spans="1:16">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -5620,8 +6598,11 @@
       <c r="K275" s="5"/>
       <c r="L275" s="5"/>
       <c r="M275" s="5"/>
-    </row>
-    <row r="276" spans="1:13">
+      <c r="N275" s="5"/>
+      <c r="O275" s="5"/>
+      <c r="P275" s="5"/>
+    </row>
+    <row r="276" spans="1:16">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -5635,8 +6616,11 @@
       <c r="K276" s="5"/>
       <c r="L276" s="5"/>
       <c r="M276" s="5"/>
-    </row>
-    <row r="277" spans="1:13">
+      <c r="N276" s="5"/>
+      <c r="O276" s="5"/>
+      <c r="P276" s="5"/>
+    </row>
+    <row r="277" spans="1:16">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -5650,8 +6634,11 @@
       <c r="K277" s="5"/>
       <c r="L277" s="5"/>
       <c r="M277" s="5"/>
-    </row>
-    <row r="278" spans="1:13">
+      <c r="N277" s="5"/>
+      <c r="O277" s="5"/>
+      <c r="P277" s="5"/>
+    </row>
+    <row r="278" spans="1:16">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -5665,8 +6652,11 @@
       <c r="K278" s="5"/>
       <c r="L278" s="5"/>
       <c r="M278" s="5"/>
-    </row>
-    <row r="279" spans="1:13">
+      <c r="N278" s="5"/>
+      <c r="O278" s="5"/>
+      <c r="P278" s="5"/>
+    </row>
+    <row r="279" spans="1:16">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -5680,8 +6670,11 @@
       <c r="K279" s="5"/>
       <c r="L279" s="5"/>
       <c r="M279" s="5"/>
-    </row>
-    <row r="280" spans="1:13">
+      <c r="N279" s="5"/>
+      <c r="O279" s="5"/>
+      <c r="P279" s="5"/>
+    </row>
+    <row r="280" spans="1:16">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -5695,8 +6688,11 @@
       <c r="K280" s="5"/>
       <c r="L280" s="5"/>
       <c r="M280" s="5"/>
-    </row>
-    <row r="281" spans="1:13">
+      <c r="N280" s="5"/>
+      <c r="O280" s="5"/>
+      <c r="P280" s="5"/>
+    </row>
+    <row r="281" spans="1:16">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -5710,8 +6706,11 @@
       <c r="K281" s="5"/>
       <c r="L281" s="5"/>
       <c r="M281" s="5"/>
-    </row>
-    <row r="282" spans="1:13">
+      <c r="N281" s="5"/>
+      <c r="O281" s="5"/>
+      <c r="P281" s="5"/>
+    </row>
+    <row r="282" spans="1:16">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -5725,8 +6724,11 @@
       <c r="K282" s="5"/>
       <c r="L282" s="5"/>
       <c r="M282" s="5"/>
-    </row>
-    <row r="283" spans="1:13">
+      <c r="N282" s="5"/>
+      <c r="O282" s="5"/>
+      <c r="P282" s="5"/>
+    </row>
+    <row r="283" spans="1:16">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -5740,8 +6742,11 @@
       <c r="K283" s="5"/>
       <c r="L283" s="5"/>
       <c r="M283" s="5"/>
-    </row>
-    <row r="284" spans="1:13">
+      <c r="N283" s="5"/>
+      <c r="O283" s="5"/>
+      <c r="P283" s="5"/>
+    </row>
+    <row r="284" spans="1:16">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -5755,8 +6760,11 @@
       <c r="K284" s="5"/>
       <c r="L284" s="5"/>
       <c r="M284" s="5"/>
-    </row>
-    <row r="285" spans="1:13">
+      <c r="N284" s="5"/>
+      <c r="O284" s="5"/>
+      <c r="P284" s="5"/>
+    </row>
+    <row r="285" spans="1:16">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -5770,8 +6778,11 @@
       <c r="K285" s="5"/>
       <c r="L285" s="5"/>
       <c r="M285" s="5"/>
-    </row>
-    <row r="286" spans="1:13">
+      <c r="N285" s="5"/>
+      <c r="O285" s="5"/>
+      <c r="P285" s="5"/>
+    </row>
+    <row r="286" spans="1:16">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -5785,8 +6796,11 @@
       <c r="K286" s="5"/>
       <c r="L286" s="5"/>
       <c r="M286" s="5"/>
-    </row>
-    <row r="287" spans="1:13">
+      <c r="N286" s="5"/>
+      <c r="O286" s="5"/>
+      <c r="P286" s="5"/>
+    </row>
+    <row r="287" spans="1:16">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -5800,8 +6814,11 @@
       <c r="K287" s="5"/>
       <c r="L287" s="5"/>
       <c r="M287" s="5"/>
-    </row>
-    <row r="288" spans="1:13">
+      <c r="N287" s="5"/>
+      <c r="O287" s="5"/>
+      <c r="P287" s="5"/>
+    </row>
+    <row r="288" spans="1:16">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -5815,8 +6832,11 @@
       <c r="K288" s="5"/>
       <c r="L288" s="5"/>
       <c r="M288" s="5"/>
-    </row>
-    <row r="289" spans="1:13">
+      <c r="N288" s="5"/>
+      <c r="O288" s="5"/>
+      <c r="P288" s="5"/>
+    </row>
+    <row r="289" spans="1:16">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -5830,8 +6850,11 @@
       <c r="K289" s="5"/>
       <c r="L289" s="5"/>
       <c r="M289" s="5"/>
-    </row>
-    <row r="290" spans="1:13">
+      <c r="N289" s="5"/>
+      <c r="O289" s="5"/>
+      <c r="P289" s="5"/>
+    </row>
+    <row r="290" spans="1:16">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -5845,8 +6868,11 @@
       <c r="K290" s="5"/>
       <c r="L290" s="5"/>
       <c r="M290" s="5"/>
-    </row>
-    <row r="291" spans="1:13">
+      <c r="N290" s="5"/>
+      <c r="O290" s="5"/>
+      <c r="P290" s="5"/>
+    </row>
+    <row r="291" spans="1:16">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -5860,8 +6886,11 @@
       <c r="K291" s="5"/>
       <c r="L291" s="5"/>
       <c r="M291" s="5"/>
-    </row>
-    <row r="292" spans="1:13">
+      <c r="N291" s="5"/>
+      <c r="O291" s="5"/>
+      <c r="P291" s="5"/>
+    </row>
+    <row r="292" spans="1:16">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -5875,8 +6904,11 @@
       <c r="K292" s="5"/>
       <c r="L292" s="5"/>
       <c r="M292" s="5"/>
-    </row>
-    <row r="293" spans="1:13">
+      <c r="N292" s="5"/>
+      <c r="O292" s="5"/>
+      <c r="P292" s="5"/>
+    </row>
+    <row r="293" spans="1:16">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -5890,8 +6922,11 @@
       <c r="K293" s="5"/>
       <c r="L293" s="5"/>
       <c r="M293" s="5"/>
-    </row>
-    <row r="294" spans="1:13">
+      <c r="N293" s="5"/>
+      <c r="O293" s="5"/>
+      <c r="P293" s="5"/>
+    </row>
+    <row r="294" spans="1:16">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -5905,8 +6940,11 @@
       <c r="K294" s="5"/>
       <c r="L294" s="5"/>
       <c r="M294" s="5"/>
-    </row>
-    <row r="295" spans="1:13">
+      <c r="N294" s="5"/>
+      <c r="O294" s="5"/>
+      <c r="P294" s="5"/>
+    </row>
+    <row r="295" spans="1:16">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -5920,8 +6958,11 @@
       <c r="K295" s="5"/>
       <c r="L295" s="5"/>
       <c r="M295" s="5"/>
-    </row>
-    <row r="296" spans="1:13">
+      <c r="N295" s="5"/>
+      <c r="O295" s="5"/>
+      <c r="P295" s="5"/>
+    </row>
+    <row r="296" spans="1:16">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -5935,8 +6976,11 @@
       <c r="K296" s="5"/>
       <c r="L296" s="5"/>
       <c r="M296" s="5"/>
-    </row>
-    <row r="297" spans="1:13">
+      <c r="N296" s="5"/>
+      <c r="O296" s="5"/>
+      <c r="P296" s="5"/>
+    </row>
+    <row r="297" spans="1:16">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -5950,8 +6994,11 @@
       <c r="K297" s="5"/>
       <c r="L297" s="5"/>
       <c r="M297" s="5"/>
-    </row>
-    <row r="298" spans="1:13">
+      <c r="N297" s="5"/>
+      <c r="O297" s="5"/>
+      <c r="P297" s="5"/>
+    </row>
+    <row r="298" spans="1:16">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -5965,8 +7012,11 @@
       <c r="K298" s="5"/>
       <c r="L298" s="5"/>
       <c r="M298" s="5"/>
-    </row>
-    <row r="299" spans="1:13">
+      <c r="N298" s="5"/>
+      <c r="O298" s="5"/>
+      <c r="P298" s="5"/>
+    </row>
+    <row r="299" spans="1:16">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -5980,8 +7030,11 @@
       <c r="K299" s="5"/>
       <c r="L299" s="5"/>
       <c r="M299" s="5"/>
-    </row>
-    <row r="300" spans="1:13">
+      <c r="N299" s="5"/>
+      <c r="O299" s="5"/>
+      <c r="P299" s="5"/>
+    </row>
+    <row r="300" spans="1:16">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -5995,8 +7048,11 @@
       <c r="K300" s="5"/>
       <c r="L300" s="5"/>
       <c r="M300" s="5"/>
-    </row>
-    <row r="301" spans="1:13">
+      <c r="N300" s="5"/>
+      <c r="O300" s="5"/>
+      <c r="P300" s="5"/>
+    </row>
+    <row r="301" spans="1:16">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -6010,8 +7066,11 @@
       <c r="K301" s="5"/>
       <c r="L301" s="5"/>
       <c r="M301" s="5"/>
-    </row>
-    <row r="302" spans="1:13">
+      <c r="N301" s="5"/>
+      <c r="O301" s="5"/>
+      <c r="P301" s="5"/>
+    </row>
+    <row r="302" spans="1:16">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -6025,8 +7084,11 @@
       <c r="K302" s="5"/>
       <c r="L302" s="5"/>
       <c r="M302" s="5"/>
-    </row>
-    <row r="303" spans="1:13">
+      <c r="N302" s="5"/>
+      <c r="O302" s="5"/>
+      <c r="P302" s="5"/>
+    </row>
+    <row r="303" spans="1:16">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -6040,8 +7102,11 @@
       <c r="K303" s="5"/>
       <c r="L303" s="5"/>
       <c r="M303" s="5"/>
-    </row>
-    <row r="304" spans="1:13">
+      <c r="N303" s="5"/>
+      <c r="O303" s="5"/>
+      <c r="P303" s="5"/>
+    </row>
+    <row r="304" spans="1:16">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -6055,8 +7120,11 @@
       <c r="K304" s="5"/>
       <c r="L304" s="5"/>
       <c r="M304" s="5"/>
-    </row>
-    <row r="305" spans="1:13">
+      <c r="N304" s="5"/>
+      <c r="O304" s="5"/>
+      <c r="P304" s="5"/>
+    </row>
+    <row r="305" spans="1:16">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -6070,8 +7138,11 @@
       <c r="K305" s="5"/>
       <c r="L305" s="5"/>
       <c r="M305" s="5"/>
-    </row>
-    <row r="306" spans="1:13">
+      <c r="N305" s="5"/>
+      <c r="O305" s="5"/>
+      <c r="P305" s="5"/>
+    </row>
+    <row r="306" spans="1:16">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -6085,8 +7156,11 @@
       <c r="K306" s="5"/>
       <c r="L306" s="5"/>
       <c r="M306" s="5"/>
-    </row>
-    <row r="307" spans="1:13">
+      <c r="N306" s="5"/>
+      <c r="O306" s="5"/>
+      <c r="P306" s="5"/>
+    </row>
+    <row r="307" spans="1:16">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -6100,8 +7174,11 @@
       <c r="K307" s="5"/>
       <c r="L307" s="5"/>
       <c r="M307" s="5"/>
-    </row>
-    <row r="308" spans="1:13">
+      <c r="N307" s="5"/>
+      <c r="O307" s="5"/>
+      <c r="P307" s="5"/>
+    </row>
+    <row r="308" spans="1:16">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -6115,8 +7192,11 @@
       <c r="K308" s="5"/>
       <c r="L308" s="5"/>
       <c r="M308" s="5"/>
-    </row>
-    <row r="309" spans="1:13">
+      <c r="N308" s="5"/>
+      <c r="O308" s="5"/>
+      <c r="P308" s="5"/>
+    </row>
+    <row r="309" spans="1:16">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -6130,8 +7210,11 @@
       <c r="K309" s="5"/>
       <c r="L309" s="5"/>
       <c r="M309" s="5"/>
-    </row>
-    <row r="310" spans="1:13">
+      <c r="N309" s="5"/>
+      <c r="O309" s="5"/>
+      <c r="P309" s="5"/>
+    </row>
+    <row r="310" spans="1:16">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -6145,8 +7228,11 @@
       <c r="K310" s="5"/>
       <c r="L310" s="5"/>
       <c r="M310" s="5"/>
-    </row>
-    <row r="311" spans="1:13">
+      <c r="N310" s="5"/>
+      <c r="O310" s="5"/>
+      <c r="P310" s="5"/>
+    </row>
+    <row r="311" spans="1:16">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -6160,8 +7246,11 @@
       <c r="K311" s="5"/>
       <c r="L311" s="5"/>
       <c r="M311" s="5"/>
-    </row>
-    <row r="312" spans="1:13">
+      <c r="N311" s="5"/>
+      <c r="O311" s="5"/>
+      <c r="P311" s="5"/>
+    </row>
+    <row r="312" spans="1:16">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -6175,8 +7264,11 @@
       <c r="K312" s="5"/>
       <c r="L312" s="5"/>
       <c r="M312" s="5"/>
-    </row>
-    <row r="313" spans="1:13">
+      <c r="N312" s="5"/>
+      <c r="O312" s="5"/>
+      <c r="P312" s="5"/>
+    </row>
+    <row r="313" spans="1:16">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -6190,8 +7282,11 @@
       <c r="K313" s="5"/>
       <c r="L313" s="5"/>
       <c r="M313" s="5"/>
-    </row>
-    <row r="314" spans="1:13">
+      <c r="N313" s="5"/>
+      <c r="O313" s="5"/>
+      <c r="P313" s="5"/>
+    </row>
+    <row r="314" spans="1:16">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -6205,8 +7300,11 @@
       <c r="K314" s="5"/>
       <c r="L314" s="5"/>
       <c r="M314" s="5"/>
-    </row>
-    <row r="315" spans="1:13">
+      <c r="N314" s="5"/>
+      <c r="O314" s="5"/>
+      <c r="P314" s="5"/>
+    </row>
+    <row r="315" spans="1:16">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -6220,8 +7318,11 @@
       <c r="K315" s="5"/>
       <c r="L315" s="5"/>
       <c r="M315" s="5"/>
-    </row>
-    <row r="316" spans="1:13">
+      <c r="N315" s="5"/>
+      <c r="O315" s="5"/>
+      <c r="P315" s="5"/>
+    </row>
+    <row r="316" spans="1:16">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -6235,8 +7336,11 @@
       <c r="K316" s="5"/>
       <c r="L316" s="5"/>
       <c r="M316" s="5"/>
-    </row>
-    <row r="317" spans="1:13">
+      <c r="N316" s="5"/>
+      <c r="O316" s="5"/>
+      <c r="P316" s="5"/>
+    </row>
+    <row r="317" spans="1:16">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -6250,8 +7354,11 @@
       <c r="K317" s="5"/>
       <c r="L317" s="5"/>
       <c r="M317" s="5"/>
-    </row>
-    <row r="318" spans="1:13">
+      <c r="N317" s="5"/>
+      <c r="O317" s="5"/>
+      <c r="P317" s="5"/>
+    </row>
+    <row r="318" spans="1:16">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -6265,8 +7372,11 @@
       <c r="K318" s="5"/>
       <c r="L318" s="5"/>
       <c r="M318" s="5"/>
-    </row>
-    <row r="319" spans="1:13">
+      <c r="N318" s="5"/>
+      <c r="O318" s="5"/>
+      <c r="P318" s="5"/>
+    </row>
+    <row r="319" spans="1:16">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -6280,8 +7390,11 @@
       <c r="K319" s="5"/>
       <c r="L319" s="5"/>
       <c r="M319" s="5"/>
-    </row>
-    <row r="320" spans="1:13">
+      <c r="N319" s="5"/>
+      <c r="O319" s="5"/>
+      <c r="P319" s="5"/>
+    </row>
+    <row r="320" spans="1:16">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -6295,8 +7408,11 @@
       <c r="K320" s="5"/>
       <c r="L320" s="5"/>
       <c r="M320" s="5"/>
-    </row>
-    <row r="321" spans="1:13">
+      <c r="N320" s="5"/>
+      <c r="O320" s="5"/>
+      <c r="P320" s="5"/>
+    </row>
+    <row r="321" spans="1:16">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -6310,8 +7426,11 @@
       <c r="K321" s="5"/>
       <c r="L321" s="5"/>
       <c r="M321" s="5"/>
-    </row>
-    <row r="322" spans="1:13">
+      <c r="N321" s="5"/>
+      <c r="O321" s="5"/>
+      <c r="P321" s="5"/>
+    </row>
+    <row r="322" spans="1:16">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -6325,8 +7444,11 @@
       <c r="K322" s="5"/>
       <c r="L322" s="5"/>
       <c r="M322" s="5"/>
-    </row>
-    <row r="323" spans="1:13">
+      <c r="N322" s="5"/>
+      <c r="O322" s="5"/>
+      <c r="P322" s="5"/>
+    </row>
+    <row r="323" spans="1:16">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -6340,8 +7462,11 @@
       <c r="K323" s="5"/>
       <c r="L323" s="5"/>
       <c r="M323" s="5"/>
-    </row>
-    <row r="324" spans="1:13">
+      <c r="N323" s="5"/>
+      <c r="O323" s="5"/>
+      <c r="P323" s="5"/>
+    </row>
+    <row r="324" spans="1:16">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -6355,8 +7480,11 @@
       <c r="K324" s="5"/>
       <c r="L324" s="5"/>
       <c r="M324" s="5"/>
-    </row>
-    <row r="325" spans="1:13">
+      <c r="N324" s="5"/>
+      <c r="O324" s="5"/>
+      <c r="P324" s="5"/>
+    </row>
+    <row r="325" spans="1:16">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -6370,8 +7498,11 @@
       <c r="K325" s="5"/>
       <c r="L325" s="5"/>
       <c r="M325" s="5"/>
-    </row>
-    <row r="326" spans="1:13">
+      <c r="N325" s="5"/>
+      <c r="O325" s="5"/>
+      <c r="P325" s="5"/>
+    </row>
+    <row r="326" spans="1:16">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -6385,8 +7516,11 @@
       <c r="K326" s="5"/>
       <c r="L326" s="5"/>
       <c r="M326" s="5"/>
-    </row>
-    <row r="327" spans="1:13">
+      <c r="N326" s="5"/>
+      <c r="O326" s="5"/>
+      <c r="P326" s="5"/>
+    </row>
+    <row r="327" spans="1:16">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -6400,8 +7534,11 @@
       <c r="K327" s="5"/>
       <c r="L327" s="5"/>
       <c r="M327" s="5"/>
-    </row>
-    <row r="328" spans="1:13">
+      <c r="N327" s="5"/>
+      <c r="O327" s="5"/>
+      <c r="P327" s="5"/>
+    </row>
+    <row r="328" spans="1:16">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -6415,8 +7552,11 @@
       <c r="K328" s="5"/>
       <c r="L328" s="5"/>
       <c r="M328" s="5"/>
-    </row>
-    <row r="329" spans="1:13">
+      <c r="N328" s="5"/>
+      <c r="O328" s="5"/>
+      <c r="P328" s="5"/>
+    </row>
+    <row r="329" spans="1:16">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -6430,8 +7570,11 @@
       <c r="K329" s="5"/>
       <c r="L329" s="5"/>
       <c r="M329" s="5"/>
-    </row>
-    <row r="330" spans="1:13">
+      <c r="N329" s="5"/>
+      <c r="O329" s="5"/>
+      <c r="P329" s="5"/>
+    </row>
+    <row r="330" spans="1:16">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -6445,8 +7588,11 @@
       <c r="K330" s="5"/>
       <c r="L330" s="5"/>
       <c r="M330" s="5"/>
-    </row>
-    <row r="331" spans="1:13">
+      <c r="N330" s="5"/>
+      <c r="O330" s="5"/>
+      <c r="P330" s="5"/>
+    </row>
+    <row r="331" spans="1:16">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -6460,8 +7606,11 @@
       <c r="K331" s="5"/>
       <c r="L331" s="5"/>
       <c r="M331" s="5"/>
-    </row>
-    <row r="332" spans="1:13">
+      <c r="N331" s="5"/>
+      <c r="O331" s="5"/>
+      <c r="P331" s="5"/>
+    </row>
+    <row r="332" spans="1:16">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -6475,8 +7624,11 @@
       <c r="K332" s="5"/>
       <c r="L332" s="5"/>
       <c r="M332" s="5"/>
-    </row>
-    <row r="333" spans="1:13">
+      <c r="N332" s="5"/>
+      <c r="O332" s="5"/>
+      <c r="P332" s="5"/>
+    </row>
+    <row r="333" spans="1:16">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -6490,8 +7642,11 @@
       <c r="K333" s="5"/>
       <c r="L333" s="5"/>
       <c r="M333" s="5"/>
-    </row>
-    <row r="334" spans="1:13">
+      <c r="N333" s="5"/>
+      <c r="O333" s="5"/>
+      <c r="P333" s="5"/>
+    </row>
+    <row r="334" spans="1:16">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -6505,8 +7660,11 @@
       <c r="K334" s="5"/>
       <c r="L334" s="5"/>
       <c r="M334" s="5"/>
-    </row>
-    <row r="335" spans="1:13">
+      <c r="N334" s="5"/>
+      <c r="O334" s="5"/>
+      <c r="P334" s="5"/>
+    </row>
+    <row r="335" spans="1:16">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -6520,8 +7678,11 @@
       <c r="K335" s="5"/>
       <c r="L335" s="5"/>
       <c r="M335" s="5"/>
-    </row>
-    <row r="336" spans="1:13">
+      <c r="N335" s="5"/>
+      <c r="O335" s="5"/>
+      <c r="P335" s="5"/>
+    </row>
+    <row r="336" spans="1:16">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -6535,8 +7696,11 @@
       <c r="K336" s="5"/>
       <c r="L336" s="5"/>
       <c r="M336" s="5"/>
-    </row>
-    <row r="337" spans="1:13">
+      <c r="N336" s="5"/>
+      <c r="O336" s="5"/>
+      <c r="P336" s="5"/>
+    </row>
+    <row r="337" spans="1:16">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -6550,8 +7714,11 @@
       <c r="K337" s="5"/>
       <c r="L337" s="5"/>
       <c r="M337" s="5"/>
-    </row>
-    <row r="338" spans="1:13">
+      <c r="N337" s="5"/>
+      <c r="O337" s="5"/>
+      <c r="P337" s="5"/>
+    </row>
+    <row r="338" spans="1:16">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -6565,8 +7732,11 @@
       <c r="K338" s="5"/>
       <c r="L338" s="5"/>
       <c r="M338" s="5"/>
-    </row>
-    <row r="339" spans="1:13">
+      <c r="N338" s="5"/>
+      <c r="O338" s="5"/>
+      <c r="P338" s="5"/>
+    </row>
+    <row r="339" spans="1:16">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -6580,8 +7750,11 @@
       <c r="K339" s="5"/>
       <c r="L339" s="5"/>
       <c r="M339" s="5"/>
-    </row>
-    <row r="340" spans="1:13">
+      <c r="N339" s="5"/>
+      <c r="O339" s="5"/>
+      <c r="P339" s="5"/>
+    </row>
+    <row r="340" spans="1:16">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -6595,8 +7768,11 @@
       <c r="K340" s="5"/>
       <c r="L340" s="5"/>
       <c r="M340" s="5"/>
-    </row>
-    <row r="341" spans="1:13">
+      <c r="N340" s="5"/>
+      <c r="O340" s="5"/>
+      <c r="P340" s="5"/>
+    </row>
+    <row r="341" spans="1:16">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -6610,8 +7786,11 @@
       <c r="K341" s="5"/>
       <c r="L341" s="5"/>
       <c r="M341" s="5"/>
-    </row>
-    <row r="342" spans="1:13">
+      <c r="N341" s="5"/>
+      <c r="O341" s="5"/>
+      <c r="P341" s="5"/>
+    </row>
+    <row r="342" spans="1:16">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -6625,8 +7804,11 @@
       <c r="K342" s="5"/>
       <c r="L342" s="5"/>
       <c r="M342" s="5"/>
-    </row>
-    <row r="343" spans="1:13">
+      <c r="N342" s="5"/>
+      <c r="O342" s="5"/>
+      <c r="P342" s="5"/>
+    </row>
+    <row r="343" spans="1:16">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -6640,8 +7822,11 @@
       <c r="K343" s="5"/>
       <c r="L343" s="5"/>
       <c r="M343" s="5"/>
-    </row>
-    <row r="344" spans="1:13">
+      <c r="N343" s="5"/>
+      <c r="O343" s="5"/>
+      <c r="P343" s="5"/>
+    </row>
+    <row r="344" spans="1:16">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -6655,8 +7840,11 @@
       <c r="K344" s="5"/>
       <c r="L344" s="5"/>
       <c r="M344" s="5"/>
-    </row>
-    <row r="345" spans="1:13">
+      <c r="N344" s="5"/>
+      <c r="O344" s="5"/>
+      <c r="P344" s="5"/>
+    </row>
+    <row r="345" spans="1:16">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -6670,8 +7858,11 @@
       <c r="K345" s="5"/>
       <c r="L345" s="5"/>
       <c r="M345" s="5"/>
-    </row>
-    <row r="346" spans="1:13">
+      <c r="N345" s="5"/>
+      <c r="O345" s="5"/>
+      <c r="P345" s="5"/>
+    </row>
+    <row r="346" spans="1:16">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -6685,8 +7876,11 @@
       <c r="K346" s="5"/>
       <c r="L346" s="5"/>
       <c r="M346" s="5"/>
-    </row>
-    <row r="347" spans="1:13">
+      <c r="N346" s="5"/>
+      <c r="O346" s="5"/>
+      <c r="P346" s="5"/>
+    </row>
+    <row r="347" spans="1:16">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -6700,8 +7894,11 @@
       <c r="K347" s="5"/>
       <c r="L347" s="5"/>
       <c r="M347" s="5"/>
-    </row>
-    <row r="348" spans="1:13">
+      <c r="N347" s="5"/>
+      <c r="O347" s="5"/>
+      <c r="P347" s="5"/>
+    </row>
+    <row r="348" spans="1:16">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -6715,8 +7912,11 @@
       <c r="K348" s="5"/>
       <c r="L348" s="5"/>
       <c r="M348" s="5"/>
-    </row>
-    <row r="349" spans="1:13">
+      <c r="N348" s="5"/>
+      <c r="O348" s="5"/>
+      <c r="P348" s="5"/>
+    </row>
+    <row r="349" spans="1:16">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -6730,8 +7930,11 @@
       <c r="K349" s="5"/>
       <c r="L349" s="5"/>
       <c r="M349" s="5"/>
-    </row>
-    <row r="350" spans="1:13">
+      <c r="N349" s="5"/>
+      <c r="O349" s="5"/>
+      <c r="P349" s="5"/>
+    </row>
+    <row r="350" spans="1:16">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -6745,8 +7948,11 @@
       <c r="K350" s="5"/>
       <c r="L350" s="5"/>
       <c r="M350" s="5"/>
-    </row>
-    <row r="351" spans="1:13">
+      <c r="N350" s="5"/>
+      <c r="O350" s="5"/>
+      <c r="P350" s="5"/>
+    </row>
+    <row r="351" spans="1:16">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -6760,8 +7966,11 @@
       <c r="K351" s="5"/>
       <c r="L351" s="5"/>
       <c r="M351" s="5"/>
-    </row>
-    <row r="352" spans="1:13">
+      <c r="N351" s="5"/>
+      <c r="O351" s="5"/>
+      <c r="P351" s="5"/>
+    </row>
+    <row r="352" spans="1:16">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -6775,8 +7984,11 @@
       <c r="K352" s="5"/>
       <c r="L352" s="5"/>
       <c r="M352" s="5"/>
-    </row>
-    <row r="353" spans="1:13">
+      <c r="N352" s="5"/>
+      <c r="O352" s="5"/>
+      <c r="P352" s="5"/>
+    </row>
+    <row r="353" spans="1:16">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -6790,8 +8002,11 @@
       <c r="K353" s="5"/>
       <c r="L353" s="5"/>
       <c r="M353" s="5"/>
-    </row>
-    <row r="354" spans="1:13">
+      <c r="N353" s="5"/>
+      <c r="O353" s="5"/>
+      <c r="P353" s="5"/>
+    </row>
+    <row r="354" spans="1:16">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -6805,8 +8020,11 @@
       <c r="K354" s="5"/>
       <c r="L354" s="5"/>
       <c r="M354" s="5"/>
-    </row>
-    <row r="355" spans="1:13">
+      <c r="N354" s="5"/>
+      <c r="O354" s="5"/>
+      <c r="P354" s="5"/>
+    </row>
+    <row r="355" spans="1:16">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -6820,8 +8038,11 @@
       <c r="K355" s="5"/>
       <c r="L355" s="5"/>
       <c r="M355" s="5"/>
-    </row>
-    <row r="356" spans="1:13">
+      <c r="N355" s="5"/>
+      <c r="O355" s="5"/>
+      <c r="P355" s="5"/>
+    </row>
+    <row r="356" spans="1:16">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -6835,8 +8056,11 @@
       <c r="K356" s="5"/>
       <c r="L356" s="5"/>
       <c r="M356" s="5"/>
-    </row>
-    <row r="357" spans="1:13">
+      <c r="N356" s="5"/>
+      <c r="O356" s="5"/>
+      <c r="P356" s="5"/>
+    </row>
+    <row r="357" spans="1:16">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -6850,8 +8074,11 @@
       <c r="K357" s="5"/>
       <c r="L357" s="5"/>
       <c r="M357" s="5"/>
-    </row>
-    <row r="358" spans="1:13">
+      <c r="N357" s="5"/>
+      <c r="O357" s="5"/>
+      <c r="P357" s="5"/>
+    </row>
+    <row r="358" spans="1:16">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -6865,8 +8092,11 @@
       <c r="K358" s="5"/>
       <c r="L358" s="5"/>
       <c r="M358" s="5"/>
-    </row>
-    <row r="359" spans="1:13">
+      <c r="N358" s="5"/>
+      <c r="O358" s="5"/>
+      <c r="P358" s="5"/>
+    </row>
+    <row r="359" spans="1:16">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -6880,8 +8110,11 @@
       <c r="K359" s="5"/>
       <c r="L359" s="5"/>
       <c r="M359" s="5"/>
-    </row>
-    <row r="360" spans="1:13">
+      <c r="N359" s="5"/>
+      <c r="O359" s="5"/>
+      <c r="P359" s="5"/>
+    </row>
+    <row r="360" spans="1:16">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -6895,8 +8128,11 @@
       <c r="K360" s="5"/>
       <c r="L360" s="5"/>
       <c r="M360" s="5"/>
-    </row>
-    <row r="361" spans="1:13">
+      <c r="N360" s="5"/>
+      <c r="O360" s="5"/>
+      <c r="P360" s="5"/>
+    </row>
+    <row r="361" spans="1:16">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -6910,8 +8146,11 @@
       <c r="K361" s="5"/>
       <c r="L361" s="5"/>
       <c r="M361" s="5"/>
-    </row>
-    <row r="362" spans="1:13">
+      <c r="N361" s="5"/>
+      <c r="O361" s="5"/>
+      <c r="P361" s="5"/>
+    </row>
+    <row r="362" spans="1:16">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -6925,8 +8164,11 @@
       <c r="K362" s="5"/>
       <c r="L362" s="5"/>
       <c r="M362" s="5"/>
-    </row>
-    <row r="363" spans="1:13">
+      <c r="N362" s="5"/>
+      <c r="O362" s="5"/>
+      <c r="P362" s="5"/>
+    </row>
+    <row r="363" spans="1:16">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -6940,8 +8182,11 @@
       <c r="K363" s="5"/>
       <c r="L363" s="5"/>
       <c r="M363" s="5"/>
-    </row>
-    <row r="364" spans="1:13">
+      <c r="N363" s="5"/>
+      <c r="O363" s="5"/>
+      <c r="P363" s="5"/>
+    </row>
+    <row r="364" spans="1:16">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -6955,8 +8200,11 @@
       <c r="K364" s="5"/>
       <c r="L364" s="5"/>
       <c r="M364" s="5"/>
-    </row>
-    <row r="365" spans="1:13">
+      <c r="N364" s="5"/>
+      <c r="O364" s="5"/>
+      <c r="P364" s="5"/>
+    </row>
+    <row r="365" spans="1:16">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -6970,8 +8218,11 @@
       <c r="K365" s="5"/>
       <c r="L365" s="5"/>
       <c r="M365" s="5"/>
-    </row>
-    <row r="366" spans="1:13">
+      <c r="N365" s="5"/>
+      <c r="O365" s="5"/>
+      <c r="P365" s="5"/>
+    </row>
+    <row r="366" spans="1:16">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -6985,8 +8236,11 @@
       <c r="K366" s="5"/>
       <c r="L366" s="5"/>
       <c r="M366" s="5"/>
-    </row>
-    <row r="367" spans="1:13">
+      <c r="N366" s="5"/>
+      <c r="O366" s="5"/>
+      <c r="P366" s="5"/>
+    </row>
+    <row r="367" spans="1:16">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -7000,8 +8254,11 @@
       <c r="K367" s="5"/>
       <c r="L367" s="5"/>
       <c r="M367" s="5"/>
-    </row>
-    <row r="368" spans="1:13">
+      <c r="N367" s="5"/>
+      <c r="O367" s="5"/>
+      <c r="P367" s="5"/>
+    </row>
+    <row r="368" spans="1:16">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -7015,8 +8272,11 @@
       <c r="K368" s="5"/>
       <c r="L368" s="5"/>
       <c r="M368" s="5"/>
-    </row>
-    <row r="369" spans="1:13">
+      <c r="N368" s="5"/>
+      <c r="O368" s="5"/>
+      <c r="P368" s="5"/>
+    </row>
+    <row r="369" spans="1:16">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -7030,8 +8290,11 @@
       <c r="K369" s="5"/>
       <c r="L369" s="5"/>
       <c r="M369" s="5"/>
-    </row>
-    <row r="370" spans="1:13">
+      <c r="N369" s="5"/>
+      <c r="O369" s="5"/>
+      <c r="P369" s="5"/>
+    </row>
+    <row r="370" spans="1:16">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -7045,8 +8308,11 @@
       <c r="K370" s="5"/>
       <c r="L370" s="5"/>
       <c r="M370" s="5"/>
-    </row>
-    <row r="371" spans="1:13">
+      <c r="N370" s="5"/>
+      <c r="O370" s="5"/>
+      <c r="P370" s="5"/>
+    </row>
+    <row r="371" spans="1:16">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -7060,8 +8326,11 @@
       <c r="K371" s="5"/>
       <c r="L371" s="5"/>
       <c r="M371" s="5"/>
-    </row>
-    <row r="372" spans="1:13">
+      <c r="N371" s="5"/>
+      <c r="O371" s="5"/>
+      <c r="P371" s="5"/>
+    </row>
+    <row r="372" spans="1:16">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -7075,8 +8344,11 @@
       <c r="K372" s="5"/>
       <c r="L372" s="5"/>
       <c r="M372" s="5"/>
-    </row>
-    <row r="373" spans="1:13">
+      <c r="N372" s="5"/>
+      <c r="O372" s="5"/>
+      <c r="P372" s="5"/>
+    </row>
+    <row r="373" spans="1:16">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -7090,8 +8362,11 @@
       <c r="K373" s="5"/>
       <c r="L373" s="5"/>
       <c r="M373" s="5"/>
-    </row>
-    <row r="374" spans="1:13">
+      <c r="N373" s="5"/>
+      <c r="O373" s="5"/>
+      <c r="P373" s="5"/>
+    </row>
+    <row r="374" spans="1:16">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -7105,8 +8380,11 @@
       <c r="K374" s="5"/>
       <c r="L374" s="5"/>
       <c r="M374" s="5"/>
-    </row>
-    <row r="375" spans="1:13">
+      <c r="N374" s="5"/>
+      <c r="O374" s="5"/>
+      <c r="P374" s="5"/>
+    </row>
+    <row r="375" spans="1:16">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -7120,8 +8398,11 @@
       <c r="K375" s="5"/>
       <c r="L375" s="5"/>
       <c r="M375" s="5"/>
-    </row>
-    <row r="376" spans="1:13">
+      <c r="N375" s="5"/>
+      <c r="O375" s="5"/>
+      <c r="P375" s="5"/>
+    </row>
+    <row r="376" spans="1:16">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -7135,8 +8416,11 @@
       <c r="K376" s="5"/>
       <c r="L376" s="5"/>
       <c r="M376" s="5"/>
-    </row>
-    <row r="377" spans="1:13">
+      <c r="N376" s="5"/>
+      <c r="O376" s="5"/>
+      <c r="P376" s="5"/>
+    </row>
+    <row r="377" spans="1:16">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -7150,8 +8434,11 @@
       <c r="K377" s="5"/>
       <c r="L377" s="5"/>
       <c r="M377" s="5"/>
-    </row>
-    <row r="378" spans="1:13">
+      <c r="N377" s="5"/>
+      <c r="O377" s="5"/>
+      <c r="P377" s="5"/>
+    </row>
+    <row r="378" spans="1:16">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -7165,8 +8452,11 @@
       <c r="K378" s="5"/>
       <c r="L378" s="5"/>
       <c r="M378" s="5"/>
-    </row>
-    <row r="379" spans="1:13">
+      <c r="N378" s="5"/>
+      <c r="O378" s="5"/>
+      <c r="P378" s="5"/>
+    </row>
+    <row r="379" spans="1:16">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -7180,8 +8470,11 @@
       <c r="K379" s="5"/>
       <c r="L379" s="5"/>
       <c r="M379" s="5"/>
-    </row>
-    <row r="380" spans="1:13">
+      <c r="N379" s="5"/>
+      <c r="O379" s="5"/>
+      <c r="P379" s="5"/>
+    </row>
+    <row r="380" spans="1:16">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -7195,8 +8488,11 @@
       <c r="K380" s="5"/>
       <c r="L380" s="5"/>
       <c r="M380" s="5"/>
-    </row>
-    <row r="381" spans="1:13">
+      <c r="N380" s="5"/>
+      <c r="O380" s="5"/>
+      <c r="P380" s="5"/>
+    </row>
+    <row r="381" spans="1:16">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -7210,8 +8506,11 @@
       <c r="K381" s="5"/>
       <c r="L381" s="5"/>
       <c r="M381" s="5"/>
-    </row>
-    <row r="382" spans="1:13">
+      <c r="N381" s="5"/>
+      <c r="O381" s="5"/>
+      <c r="P381" s="5"/>
+    </row>
+    <row r="382" spans="1:16">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -7225,8 +8524,11 @@
       <c r="K382" s="5"/>
       <c r="L382" s="5"/>
       <c r="M382" s="5"/>
-    </row>
-    <row r="383" spans="1:13">
+      <c r="N382" s="5"/>
+      <c r="O382" s="5"/>
+      <c r="P382" s="5"/>
+    </row>
+    <row r="383" spans="1:16">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -7240,8 +8542,11 @@
       <c r="K383" s="5"/>
       <c r="L383" s="5"/>
       <c r="M383" s="5"/>
-    </row>
-    <row r="384" spans="1:13">
+      <c r="N383" s="5"/>
+      <c r="O383" s="5"/>
+      <c r="P383" s="5"/>
+    </row>
+    <row r="384" spans="1:16">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -7255,8 +8560,11 @@
       <c r="K384" s="5"/>
       <c r="L384" s="5"/>
       <c r="M384" s="5"/>
-    </row>
-    <row r="385" spans="1:13">
+      <c r="N384" s="5"/>
+      <c r="O384" s="5"/>
+      <c r="P384" s="5"/>
+    </row>
+    <row r="385" spans="1:16">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -7270,8 +8578,11 @@
       <c r="K385" s="5"/>
       <c r="L385" s="5"/>
       <c r="M385" s="5"/>
-    </row>
-    <row r="386" spans="1:13">
+      <c r="N385" s="5"/>
+      <c r="O385" s="5"/>
+      <c r="P385" s="5"/>
+    </row>
+    <row r="386" spans="1:16">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -7285,8 +8596,11 @@
       <c r="K386" s="5"/>
       <c r="L386" s="5"/>
       <c r="M386" s="5"/>
-    </row>
-    <row r="387" spans="1:13">
+      <c r="N386" s="5"/>
+      <c r="O386" s="5"/>
+      <c r="P386" s="5"/>
+    </row>
+    <row r="387" spans="1:16">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -7300,8 +8614,11 @@
       <c r="K387" s="5"/>
       <c r="L387" s="5"/>
       <c r="M387" s="5"/>
-    </row>
-    <row r="388" spans="1:13">
+      <c r="N387" s="5"/>
+      <c r="O387" s="5"/>
+      <c r="P387" s="5"/>
+    </row>
+    <row r="388" spans="1:16">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -7315,8 +8632,11 @@
       <c r="K388" s="5"/>
       <c r="L388" s="5"/>
       <c r="M388" s="5"/>
-    </row>
-    <row r="389" spans="1:13">
+      <c r="N388" s="5"/>
+      <c r="O388" s="5"/>
+      <c r="P388" s="5"/>
+    </row>
+    <row r="389" spans="1:16">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -7330,8 +8650,11 @@
       <c r="K389" s="5"/>
       <c r="L389" s="5"/>
       <c r="M389" s="5"/>
-    </row>
-    <row r="390" spans="1:13">
+      <c r="N389" s="5"/>
+      <c r="O389" s="5"/>
+      <c r="P389" s="5"/>
+    </row>
+    <row r="390" spans="1:16">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -7345,8 +8668,11 @@
       <c r="K390" s="5"/>
       <c r="L390" s="5"/>
       <c r="M390" s="5"/>
-    </row>
-    <row r="391" spans="1:13">
+      <c r="N390" s="5"/>
+      <c r="O390" s="5"/>
+      <c r="P390" s="5"/>
+    </row>
+    <row r="391" spans="1:16">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -7360,8 +8686,11 @@
       <c r="K391" s="5"/>
       <c r="L391" s="5"/>
       <c r="M391" s="5"/>
-    </row>
-    <row r="392" spans="1:13">
+      <c r="N391" s="5"/>
+      <c r="O391" s="5"/>
+      <c r="P391" s="5"/>
+    </row>
+    <row r="392" spans="1:16">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -7375,8 +8704,11 @@
       <c r="K392" s="5"/>
       <c r="L392" s="5"/>
       <c r="M392" s="5"/>
-    </row>
-    <row r="393" spans="1:13">
+      <c r="N392" s="5"/>
+      <c r="O392" s="5"/>
+      <c r="P392" s="5"/>
+    </row>
+    <row r="393" spans="1:16">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -7390,8 +8722,11 @@
       <c r="K393" s="5"/>
       <c r="L393" s="5"/>
       <c r="M393" s="5"/>
-    </row>
-    <row r="394" spans="1:13">
+      <c r="N393" s="5"/>
+      <c r="O393" s="5"/>
+      <c r="P393" s="5"/>
+    </row>
+    <row r="394" spans="1:16">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -7405,8 +8740,11 @@
       <c r="K394" s="5"/>
       <c r="L394" s="5"/>
       <c r="M394" s="5"/>
-    </row>
-    <row r="395" spans="1:13">
+      <c r="N394" s="5"/>
+      <c r="O394" s="5"/>
+      <c r="P394" s="5"/>
+    </row>
+    <row r="395" spans="1:16">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -7420,8 +8758,11 @@
       <c r="K395" s="5"/>
       <c r="L395" s="5"/>
       <c r="M395" s="5"/>
-    </row>
-    <row r="396" spans="1:13">
+      <c r="N395" s="5"/>
+      <c r="O395" s="5"/>
+      <c r="P395" s="5"/>
+    </row>
+    <row r="396" spans="1:16">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -7435,8 +8776,11 @@
       <c r="K396" s="5"/>
       <c r="L396" s="5"/>
       <c r="M396" s="5"/>
-    </row>
-    <row r="397" spans="1:13">
+      <c r="N396" s="5"/>
+      <c r="O396" s="5"/>
+      <c r="P396" s="5"/>
+    </row>
+    <row r="397" spans="1:16">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -7450,8 +8794,11 @@
       <c r="K397" s="5"/>
       <c r="L397" s="5"/>
       <c r="M397" s="5"/>
-    </row>
-    <row r="398" spans="1:13">
+      <c r="N397" s="5"/>
+      <c r="O397" s="5"/>
+      <c r="P397" s="5"/>
+    </row>
+    <row r="398" spans="1:16">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -7465,8 +8812,11 @@
       <c r="K398" s="5"/>
       <c r="L398" s="5"/>
       <c r="M398" s="5"/>
-    </row>
-    <row r="399" spans="1:13">
+      <c r="N398" s="5"/>
+      <c r="O398" s="5"/>
+      <c r="P398" s="5"/>
+    </row>
+    <row r="399" spans="1:16">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -7480,8 +8830,11 @@
       <c r="K399" s="5"/>
       <c r="L399" s="5"/>
       <c r="M399" s="5"/>
-    </row>
-    <row r="400" spans="1:13">
+      <c r="N399" s="5"/>
+      <c r="O399" s="5"/>
+      <c r="P399" s="5"/>
+    </row>
+    <row r="400" spans="1:16">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -7495,8 +8848,11 @@
       <c r="K400" s="5"/>
       <c r="L400" s="5"/>
       <c r="M400" s="5"/>
-    </row>
-    <row r="401" spans="1:13">
+      <c r="N400" s="5"/>
+      <c r="O400" s="5"/>
+      <c r="P400" s="5"/>
+    </row>
+    <row r="401" spans="1:16">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -7510,8 +8866,11 @@
       <c r="K401" s="5"/>
       <c r="L401" s="5"/>
       <c r="M401" s="5"/>
-    </row>
-    <row r="402" spans="1:13">
+      <c r="N401" s="5"/>
+      <c r="O401" s="5"/>
+      <c r="P401" s="5"/>
+    </row>
+    <row r="402" spans="1:16">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -7525,8 +8884,11 @@
       <c r="K402" s="5"/>
       <c r="L402" s="5"/>
       <c r="M402" s="5"/>
-    </row>
-    <row r="403" spans="1:13">
+      <c r="N402" s="5"/>
+      <c r="O402" s="5"/>
+      <c r="P402" s="5"/>
+    </row>
+    <row r="403" spans="1:16">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -7540,8 +8902,11 @@
       <c r="K403" s="5"/>
       <c r="L403" s="5"/>
       <c r="M403" s="5"/>
-    </row>
-    <row r="404" spans="1:13">
+      <c r="N403" s="5"/>
+      <c r="O403" s="5"/>
+      <c r="P403" s="5"/>
+    </row>
+    <row r="404" spans="1:16">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -7555,8 +8920,11 @@
       <c r="K404" s="5"/>
       <c r="L404" s="5"/>
       <c r="M404" s="5"/>
-    </row>
-    <row r="405" spans="1:13">
+      <c r="N404" s="5"/>
+      <c r="O404" s="5"/>
+      <c r="P404" s="5"/>
+    </row>
+    <row r="405" spans="1:16">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -7570,8 +8938,11 @@
       <c r="K405" s="5"/>
       <c r="L405" s="5"/>
       <c r="M405" s="5"/>
-    </row>
-    <row r="406" spans="1:13">
+      <c r="N405" s="5"/>
+      <c r="O405" s="5"/>
+      <c r="P405" s="5"/>
+    </row>
+    <row r="406" spans="1:16">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -7585,8 +8956,11 @@
       <c r="K406" s="5"/>
       <c r="L406" s="5"/>
       <c r="M406" s="5"/>
-    </row>
-    <row r="407" spans="1:13">
+      <c r="N406" s="5"/>
+      <c r="O406" s="5"/>
+      <c r="P406" s="5"/>
+    </row>
+    <row r="407" spans="1:16">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -7600,8 +8974,11 @@
       <c r="K407" s="5"/>
       <c r="L407" s="5"/>
       <c r="M407" s="5"/>
-    </row>
-    <row r="408" spans="1:13">
+      <c r="N407" s="5"/>
+      <c r="O407" s="5"/>
+      <c r="P407" s="5"/>
+    </row>
+    <row r="408" spans="1:16">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -7615,8 +8992,11 @@
       <c r="K408" s="5"/>
       <c r="L408" s="5"/>
       <c r="M408" s="5"/>
-    </row>
-    <row r="409" spans="1:13">
+      <c r="N408" s="5"/>
+      <c r="O408" s="5"/>
+      <c r="P408" s="5"/>
+    </row>
+    <row r="409" spans="1:16">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -7630,8 +9010,11 @@
       <c r="K409" s="5"/>
       <c r="L409" s="5"/>
       <c r="M409" s="5"/>
-    </row>
-    <row r="410" spans="1:13">
+      <c r="N409" s="5"/>
+      <c r="O409" s="5"/>
+      <c r="P409" s="5"/>
+    </row>
+    <row r="410" spans="1:16">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -7645,8 +9028,11 @@
       <c r="K410" s="5"/>
       <c r="L410" s="5"/>
       <c r="M410" s="5"/>
-    </row>
-    <row r="411" spans="1:13">
+      <c r="N410" s="5"/>
+      <c r="O410" s="5"/>
+      <c r="P410" s="5"/>
+    </row>
+    <row r="411" spans="1:16">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -7660,8 +9046,11 @@
       <c r="K411" s="5"/>
       <c r="L411" s="5"/>
       <c r="M411" s="5"/>
-    </row>
-    <row r="412" spans="1:13">
+      <c r="N411" s="5"/>
+      <c r="O411" s="5"/>
+      <c r="P411" s="5"/>
+    </row>
+    <row r="412" spans="1:16">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -7675,8 +9064,11 @@
       <c r="K412" s="5"/>
       <c r="L412" s="5"/>
       <c r="M412" s="5"/>
-    </row>
-    <row r="413" spans="1:13">
+      <c r="N412" s="5"/>
+      <c r="O412" s="5"/>
+      <c r="P412" s="5"/>
+    </row>
+    <row r="413" spans="1:16">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -7690,8 +9082,11 @@
       <c r="K413" s="5"/>
       <c r="L413" s="5"/>
       <c r="M413" s="5"/>
-    </row>
-    <row r="414" spans="1:13">
+      <c r="N413" s="5"/>
+      <c r="O413" s="5"/>
+      <c r="P413" s="5"/>
+    </row>
+    <row r="414" spans="1:16">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -7705,8 +9100,11 @@
       <c r="K414" s="5"/>
       <c r="L414" s="5"/>
       <c r="M414" s="5"/>
-    </row>
-    <row r="415" spans="1:13">
+      <c r="N414" s="5"/>
+      <c r="O414" s="5"/>
+      <c r="P414" s="5"/>
+    </row>
+    <row r="415" spans="1:16">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -7720,8 +9118,11 @@
       <c r="K415" s="5"/>
       <c r="L415" s="5"/>
       <c r="M415" s="5"/>
-    </row>
-    <row r="416" spans="1:13">
+      <c r="N415" s="5"/>
+      <c r="O415" s="5"/>
+      <c r="P415" s="5"/>
+    </row>
+    <row r="416" spans="1:16">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -7735,8 +9136,11 @@
       <c r="K416" s="5"/>
       <c r="L416" s="5"/>
       <c r="M416" s="5"/>
-    </row>
-    <row r="417" spans="1:13">
+      <c r="N416" s="5"/>
+      <c r="O416" s="5"/>
+      <c r="P416" s="5"/>
+    </row>
+    <row r="417" spans="1:16">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -7750,8 +9154,11 @@
       <c r="K417" s="5"/>
       <c r="L417" s="5"/>
       <c r="M417" s="5"/>
-    </row>
-    <row r="418" spans="1:13">
+      <c r="N417" s="5"/>
+      <c r="O417" s="5"/>
+      <c r="P417" s="5"/>
+    </row>
+    <row r="418" spans="1:16">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -7765,8 +9172,11 @@
       <c r="K418" s="5"/>
       <c r="L418" s="5"/>
       <c r="M418" s="5"/>
-    </row>
-    <row r="419" spans="1:13">
+      <c r="N418" s="5"/>
+      <c r="O418" s="5"/>
+      <c r="P418" s="5"/>
+    </row>
+    <row r="419" spans="1:16">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -7780,8 +9190,11 @@
       <c r="K419" s="5"/>
       <c r="L419" s="5"/>
       <c r="M419" s="5"/>
-    </row>
-    <row r="420" spans="1:13">
+      <c r="N419" s="5"/>
+      <c r="O419" s="5"/>
+      <c r="P419" s="5"/>
+    </row>
+    <row r="420" spans="1:16">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -7795,8 +9208,11 @@
       <c r="K420" s="5"/>
       <c r="L420" s="5"/>
       <c r="M420" s="5"/>
-    </row>
-    <row r="421" spans="1:13">
+      <c r="N420" s="5"/>
+      <c r="O420" s="5"/>
+      <c r="P420" s="5"/>
+    </row>
+    <row r="421" spans="1:16">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -7810,8 +9226,11 @@
       <c r="K421" s="5"/>
       <c r="L421" s="5"/>
       <c r="M421" s="5"/>
-    </row>
-    <row r="422" spans="1:13">
+      <c r="N421" s="5"/>
+      <c r="O421" s="5"/>
+      <c r="P421" s="5"/>
+    </row>
+    <row r="422" spans="1:16">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -7825,8 +9244,11 @@
       <c r="K422" s="5"/>
       <c r="L422" s="5"/>
       <c r="M422" s="5"/>
-    </row>
-    <row r="423" spans="1:13">
+      <c r="N422" s="5"/>
+      <c r="O422" s="5"/>
+      <c r="P422" s="5"/>
+    </row>
+    <row r="423" spans="1:16">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -7840,8 +9262,11 @@
       <c r="K423" s="5"/>
       <c r="L423" s="5"/>
       <c r="M423" s="5"/>
-    </row>
-    <row r="424" spans="1:13">
+      <c r="N423" s="5"/>
+      <c r="O423" s="5"/>
+      <c r="P423" s="5"/>
+    </row>
+    <row r="424" spans="1:16">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -7855,8 +9280,11 @@
       <c r="K424" s="5"/>
       <c r="L424" s="5"/>
       <c r="M424" s="5"/>
-    </row>
-    <row r="425" spans="1:13">
+      <c r="N424" s="5"/>
+      <c r="O424" s="5"/>
+      <c r="P424" s="5"/>
+    </row>
+    <row r="425" spans="1:16">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -7870,8 +9298,11 @@
       <c r="K425" s="5"/>
       <c r="L425" s="5"/>
       <c r="M425" s="5"/>
-    </row>
-    <row r="426" spans="1:13">
+      <c r="N425" s="5"/>
+      <c r="O425" s="5"/>
+      <c r="P425" s="5"/>
+    </row>
+    <row r="426" spans="1:16">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -7885,8 +9316,11 @@
       <c r="K426" s="5"/>
       <c r="L426" s="5"/>
       <c r="M426" s="5"/>
-    </row>
-    <row r="427" spans="1:13">
+      <c r="N426" s="5"/>
+      <c r="O426" s="5"/>
+      <c r="P426" s="5"/>
+    </row>
+    <row r="427" spans="1:16">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -7900,8 +9334,11 @@
       <c r="K427" s="5"/>
       <c r="L427" s="5"/>
       <c r="M427" s="5"/>
-    </row>
-    <row r="428" spans="1:13">
+      <c r="N427" s="5"/>
+      <c r="O427" s="5"/>
+      <c r="P427" s="5"/>
+    </row>
+    <row r="428" spans="1:16">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -7915,8 +9352,11 @@
       <c r="K428" s="5"/>
       <c r="L428" s="5"/>
       <c r="M428" s="5"/>
-    </row>
-    <row r="429" spans="1:13">
+      <c r="N428" s="5"/>
+      <c r="O428" s="5"/>
+      <c r="P428" s="5"/>
+    </row>
+    <row r="429" spans="1:16">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -7930,8 +9370,11 @@
       <c r="K429" s="5"/>
       <c r="L429" s="5"/>
       <c r="M429" s="5"/>
-    </row>
-    <row r="430" spans="1:13">
+      <c r="N429" s="5"/>
+      <c r="O429" s="5"/>
+      <c r="P429" s="5"/>
+    </row>
+    <row r="430" spans="1:16">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -7945,8 +9388,11 @@
       <c r="K430" s="5"/>
       <c r="L430" s="5"/>
       <c r="M430" s="5"/>
-    </row>
-    <row r="431" spans="1:13">
+      <c r="N430" s="5"/>
+      <c r="O430" s="5"/>
+      <c r="P430" s="5"/>
+    </row>
+    <row r="431" spans="1:16">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -7960,8 +9406,11 @@
       <c r="K431" s="5"/>
       <c r="L431" s="5"/>
       <c r="M431" s="5"/>
-    </row>
-    <row r="432" spans="1:13">
+      <c r="N431" s="5"/>
+      <c r="O431" s="5"/>
+      <c r="P431" s="5"/>
+    </row>
+    <row r="432" spans="1:16">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -7975,8 +9424,11 @@
       <c r="K432" s="5"/>
       <c r="L432" s="5"/>
       <c r="M432" s="5"/>
-    </row>
-    <row r="433" spans="1:13">
+      <c r="N432" s="5"/>
+      <c r="O432" s="5"/>
+      <c r="P432" s="5"/>
+    </row>
+    <row r="433" spans="1:16">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -7990,8 +9442,11 @@
       <c r="K433" s="5"/>
       <c r="L433" s="5"/>
       <c r="M433" s="5"/>
-    </row>
-    <row r="434" spans="1:13">
+      <c r="N433" s="5"/>
+      <c r="O433" s="5"/>
+      <c r="P433" s="5"/>
+    </row>
+    <row r="434" spans="1:16">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -8005,8 +9460,11 @@
       <c r="K434" s="5"/>
       <c r="L434" s="5"/>
       <c r="M434" s="5"/>
-    </row>
-    <row r="435" spans="1:13">
+      <c r="N434" s="5"/>
+      <c r="O434" s="5"/>
+      <c r="P434" s="5"/>
+    </row>
+    <row r="435" spans="1:16">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -8020,8 +9478,11 @@
       <c r="K435" s="5"/>
       <c r="L435" s="5"/>
       <c r="M435" s="5"/>
-    </row>
-    <row r="436" spans="1:13">
+      <c r="N435" s="5"/>
+      <c r="O435" s="5"/>
+      <c r="P435" s="5"/>
+    </row>
+    <row r="436" spans="1:16">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -8035,8 +9496,11 @@
       <c r="K436" s="5"/>
       <c r="L436" s="5"/>
       <c r="M436" s="5"/>
-    </row>
-    <row r="437" spans="1:13">
+      <c r="N436" s="5"/>
+      <c r="O436" s="5"/>
+      <c r="P436" s="5"/>
+    </row>
+    <row r="437" spans="1:16">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -8050,8 +9514,11 @@
       <c r="K437" s="5"/>
       <c r="L437" s="5"/>
       <c r="M437" s="5"/>
-    </row>
-    <row r="438" spans="1:13">
+      <c r="N437" s="5"/>
+      <c r="O437" s="5"/>
+      <c r="P437" s="5"/>
+    </row>
+    <row r="438" spans="1:16">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -8065,8 +9532,11 @@
       <c r="K438" s="5"/>
       <c r="L438" s="5"/>
       <c r="M438" s="5"/>
-    </row>
-    <row r="439" spans="1:13">
+      <c r="N438" s="5"/>
+      <c r="O438" s="5"/>
+      <c r="P438" s="5"/>
+    </row>
+    <row r="439" spans="1:16">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -8080,8 +9550,11 @@
       <c r="K439" s="5"/>
       <c r="L439" s="5"/>
       <c r="M439" s="5"/>
-    </row>
-    <row r="440" spans="1:13">
+      <c r="N439" s="5"/>
+      <c r="O439" s="5"/>
+      <c r="P439" s="5"/>
+    </row>
+    <row r="440" spans="1:16">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -8095,8 +9568,11 @@
       <c r="K440" s="5"/>
       <c r="L440" s="5"/>
       <c r="M440" s="5"/>
-    </row>
-    <row r="441" spans="1:13">
+      <c r="N440" s="5"/>
+      <c r="O440" s="5"/>
+      <c r="P440" s="5"/>
+    </row>
+    <row r="441" spans="1:16">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -8110,8 +9586,11 @@
       <c r="K441" s="5"/>
       <c r="L441" s="5"/>
       <c r="M441" s="5"/>
-    </row>
-    <row r="442" spans="1:13">
+      <c r="N441" s="5"/>
+      <c r="O441" s="5"/>
+      <c r="P441" s="5"/>
+    </row>
+    <row r="442" spans="1:16">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -8125,8 +9604,11 @@
       <c r="K442" s="5"/>
       <c r="L442" s="5"/>
       <c r="M442" s="5"/>
-    </row>
-    <row r="443" spans="1:13">
+      <c r="N442" s="5"/>
+      <c r="O442" s="5"/>
+      <c r="P442" s="5"/>
+    </row>
+    <row r="443" spans="1:16">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -8140,8 +9622,11 @@
       <c r="K443" s="5"/>
       <c r="L443" s="5"/>
       <c r="M443" s="5"/>
-    </row>
-    <row r="444" spans="1:13">
+      <c r="N443" s="5"/>
+      <c r="O443" s="5"/>
+      <c r="P443" s="5"/>
+    </row>
+    <row r="444" spans="1:16">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -8155,8 +9640,11 @@
       <c r="K444" s="5"/>
       <c r="L444" s="5"/>
       <c r="M444" s="5"/>
-    </row>
-    <row r="445" spans="1:13">
+      <c r="N444" s="5"/>
+      <c r="O444" s="5"/>
+      <c r="P444" s="5"/>
+    </row>
+    <row r="445" spans="1:16">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -8170,8 +9658,11 @@
       <c r="K445" s="5"/>
       <c r="L445" s="5"/>
       <c r="M445" s="5"/>
-    </row>
-    <row r="446" spans="1:13">
+      <c r="N445" s="5"/>
+      <c r="O445" s="5"/>
+      <c r="P445" s="5"/>
+    </row>
+    <row r="446" spans="1:16">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -8185,8 +9676,11 @@
       <c r="K446" s="5"/>
       <c r="L446" s="5"/>
       <c r="M446" s="5"/>
-    </row>
-    <row r="447" spans="1:13">
+      <c r="N446" s="5"/>
+      <c r="O446" s="5"/>
+      <c r="P446" s="5"/>
+    </row>
+    <row r="447" spans="1:16">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -8200,8 +9694,11 @@
       <c r="K447" s="5"/>
       <c r="L447" s="5"/>
       <c r="M447" s="5"/>
-    </row>
-    <row r="448" spans="1:13">
+      <c r="N447" s="5"/>
+      <c r="O447" s="5"/>
+      <c r="P447" s="5"/>
+    </row>
+    <row r="448" spans="1:16">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">
@@ -8685,7 +10182,7 @@
       <c r="A608" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I608" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -1696,7 +1696,7 @@
         <v>39</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
         <v>4</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
   <si>
     <t>编号</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>价格</t>
+  </si>
+  <si>
+    <t>是否广告购买</t>
   </si>
   <si>
     <t>攻击间隔</t>
@@ -229,6 +232,9 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>isAdBuy</t>
   </si>
   <si>
     <t>attackInterval</t>
@@ -1272,15 +1278,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T608"/>
+  <dimension ref="A1:U608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16" width="25.125" style="2" customWidth="1"/>
-    <col min="17" max="20" width="25.125" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="1" max="17" width="25.125" style="2" customWidth="1"/>
+    <col min="18" max="21" width="25.125" style="3" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:20">
+    <row r="1" ht="16.5" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1329,108 +1335,117 @@
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:20">
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:21">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:21">
       <c r="A3" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:20">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:21">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1441,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -1455,32 +1470,33 @@
       <c r="H4" s="3">
         <v>6000</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
         <v>0.5</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>2000</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>10</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
       </c>
       <c r="M4" s="3">
         <v>1</v>
       </c>
       <c r="N4" s="3">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3">
         <v>100</v>
       </c>
-      <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:20">
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:21">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1491,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -1505,32 +1521,33 @@
       <c r="H5" s="3">
         <v>7000</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
         <v>0.15</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>2000</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>3</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>0.9</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>30</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>600</v>
       </c>
-      <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:20">
+      <c r="U5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:21">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1541,7 +1558,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -1555,32 +1572,33 @@
       <c r="H6" s="3">
         <v>8000</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
         <v>0.05</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>2000</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>4</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>0.9</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>25</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>600</v>
       </c>
-      <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:20">
+      <c r="U6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:21">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1591,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -1605,32 +1623,33 @@
       <c r="H7" s="3">
         <v>9000</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
         <v>0.2</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>2000</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>5</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>0.6</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>75</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>600</v>
       </c>
-      <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:20">
+      <c r="U7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:21">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1641,7 +1660,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -1655,34 +1674,35 @@
       <c r="H8" s="3">
         <v>10000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
         <v>1</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>0.9</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8</v>
       </c>
-      <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:20">
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:21">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1693,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
@@ -1711,30 +1731,33 @@
         <v>1</v>
       </c>
       <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
         <v>4000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>0.8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3">
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3">
         <v>1</v>
       </c>
-      <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:20">
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:21">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1745,7 +1768,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -1759,32 +1782,33 @@
       <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3">
         <v>0.2</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>0.9</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:20">
+      <c r="U10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:21">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1795,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -1809,32 +1833,33 @@
       <c r="H11" s="3">
         <v>13000</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3">
         <v>0.2</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>2000</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>15</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1</v>
       </c>
       <c r="M11" s="3">
         <v>1</v>
       </c>
       <c r="N11" s="3">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
         <v>100</v>
       </c>
-      <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:20">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:21">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1855,8 +1880,9 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:20">
+      <c r="U12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:21">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1877,8 +1903,9 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:20">
+      <c r="U13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:21">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1899,8 +1926,9 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:20">
+      <c r="U14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:21">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1921,8 +1949,9 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15" s="3"/>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1939,8 +1968,9 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1957,8 +1987,9 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1975,8 +2006,9 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1993,8 +2025,9 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2011,8 +2044,9 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2029,8 +2063,9 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2047,8 +2082,9 @@
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2065,8 +2101,9 @@
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2083,8 +2120,9 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2101,8 +2139,9 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2119,8 +2158,9 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26" s="5"/>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2137,8 +2177,9 @@
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2155,8 +2196,9 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2173,8 +2215,9 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29" s="5"/>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2191,8 +2234,9 @@
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2209,8 +2253,9 @@
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31" s="5"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2227,8 +2272,9 @@
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2245,8 +2291,9 @@
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33" s="5"/>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2263,8 +2310,9 @@
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34" s="5"/>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2281,8 +2329,9 @@
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35" s="5"/>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2299,8 +2348,9 @@
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36" s="5"/>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2317,8 +2367,9 @@
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="Q37" s="5"/>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2335,8 +2386,9 @@
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="Q38" s="5"/>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2353,8 +2405,9 @@
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39" s="5"/>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2371,8 +2424,9 @@
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40" s="5"/>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2389,8 +2443,9 @@
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2407,8 +2462,9 @@
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42" s="5"/>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2425,8 +2481,9 @@
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="Q43" s="5"/>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2443,8 +2500,9 @@
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2461,8 +2519,9 @@
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45" s="5"/>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2479,8 +2538,9 @@
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46" s="5"/>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2497,8 +2557,9 @@
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="Q47" s="5"/>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2515,8 +2576,9 @@
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="Q48" s="5"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2533,8 +2595,9 @@
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="Q49" s="5"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2551,8 +2614,9 @@
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
-    </row>
-    <row r="51" spans="1:16">
+      <c r="Q50" s="5"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2569,8 +2633,9 @@
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
-    </row>
-    <row r="52" spans="1:16">
+      <c r="Q51" s="5"/>
+    </row>
+    <row r="52" spans="1:17">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2587,8 +2652,9 @@
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
-    </row>
-    <row r="53" spans="1:16">
+      <c r="Q52" s="5"/>
+    </row>
+    <row r="53" spans="1:17">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2605,8 +2671,9 @@
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53" s="5"/>
+    </row>
+    <row r="54" spans="1:17">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2623,8 +2690,9 @@
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="Q54" s="5"/>
+    </row>
+    <row r="55" spans="1:17">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2641,8 +2709,9 @@
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
-    </row>
-    <row r="56" spans="1:16">
+      <c r="Q55" s="5"/>
+    </row>
+    <row r="56" spans="1:17">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2659,8 +2728,9 @@
       <c r="N56" s="5"/>
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56" s="5"/>
+    </row>
+    <row r="57" spans="1:17">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2677,8 +2747,9 @@
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="Q57" s="5"/>
+    </row>
+    <row r="58" spans="1:17">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2695,8 +2766,9 @@
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58" s="5"/>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2713,8 +2785,9 @@
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
-    </row>
-    <row r="60" spans="1:16">
+      <c r="Q59" s="5"/>
+    </row>
+    <row r="60" spans="1:17">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2731,8 +2804,9 @@
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="Q60" s="5"/>
+    </row>
+    <row r="61" spans="1:17">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2749,8 +2823,9 @@
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="Q61" s="5"/>
+    </row>
+    <row r="62" spans="1:17">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2767,8 +2842,9 @@
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="Q62" s="5"/>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2785,8 +2861,9 @@
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="Q63" s="5"/>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2803,8 +2880,9 @@
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64" s="5"/>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2821,8 +2899,9 @@
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
-    </row>
-    <row r="66" spans="1:16">
+      <c r="Q65" s="5"/>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2839,8 +2918,9 @@
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="Q66" s="5"/>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2857,8 +2937,9 @@
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
-    </row>
-    <row r="68" spans="1:16">
+      <c r="Q67" s="5"/>
+    </row>
+    <row r="68" spans="1:17">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2875,8 +2956,9 @@
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68" s="5"/>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2893,8 +2975,9 @@
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
-    </row>
-    <row r="70" spans="1:16">
+      <c r="Q69" s="5"/>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2911,8 +2994,9 @@
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70" s="5"/>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2929,8 +3013,9 @@
       <c r="N71" s="5"/>
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="Q71" s="5"/>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2947,8 +3032,9 @@
       <c r="N72" s="5"/>
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
-    </row>
-    <row r="73" spans="1:16">
+      <c r="Q72" s="5"/>
+    </row>
+    <row r="73" spans="1:17">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2965,8 +3051,9 @@
       <c r="N73" s="5"/>
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
-    </row>
-    <row r="74" spans="1:16">
+      <c r="Q73" s="5"/>
+    </row>
+    <row r="74" spans="1:17">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2983,8 +3070,9 @@
       <c r="N74" s="5"/>
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
-    </row>
-    <row r="75" spans="1:16">
+      <c r="Q74" s="5"/>
+    </row>
+    <row r="75" spans="1:17">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3001,8 +3089,9 @@
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75" s="5"/>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3019,8 +3108,9 @@
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76" s="5"/>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3037,8 +3127,9 @@
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77" s="5"/>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3055,8 +3146,9 @@
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="Q78" s="5"/>
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3073,8 +3165,9 @@
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="Q79" s="5"/>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -3091,8 +3184,9 @@
       <c r="N80" s="5"/>
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
-    </row>
-    <row r="81" spans="1:16">
+      <c r="Q80" s="5"/>
+    </row>
+    <row r="81" spans="1:17">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -3109,8 +3203,9 @@
       <c r="N81" s="5"/>
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
-    </row>
-    <row r="82" spans="1:16">
+      <c r="Q81" s="5"/>
+    </row>
+    <row r="82" spans="1:17">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -3127,8 +3222,9 @@
       <c r="N82" s="5"/>
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="Q82" s="5"/>
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3145,8 +3241,9 @@
       <c r="N83" s="5"/>
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83" s="5"/>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -3163,8 +3260,9 @@
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
-    </row>
-    <row r="85" spans="1:16">
+      <c r="Q84" s="5"/>
+    </row>
+    <row r="85" spans="1:17">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -3181,8 +3279,9 @@
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
-    </row>
-    <row r="86" spans="1:16">
+      <c r="Q85" s="5"/>
+    </row>
+    <row r="86" spans="1:17">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -3199,8 +3298,9 @@
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
-    </row>
-    <row r="87" spans="1:16">
+      <c r="Q86" s="5"/>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -3217,8 +3317,9 @@
       <c r="N87" s="5"/>
       <c r="O87" s="5"/>
       <c r="P87" s="5"/>
-    </row>
-    <row r="88" spans="1:16">
+      <c r="Q87" s="5"/>
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -3235,8 +3336,9 @@
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
-    </row>
-    <row r="89" spans="1:16">
+      <c r="Q88" s="5"/>
+    </row>
+    <row r="89" spans="1:17">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3253,8 +3355,9 @@
       <c r="N89" s="5"/>
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
-    </row>
-    <row r="90" spans="1:16">
+      <c r="Q89" s="5"/>
+    </row>
+    <row r="90" spans="1:17">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -3271,8 +3374,9 @@
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
-    </row>
-    <row r="91" spans="1:16">
+      <c r="Q90" s="5"/>
+    </row>
+    <row r="91" spans="1:17">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -3289,8 +3393,9 @@
       <c r="N91" s="5"/>
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
-    </row>
-    <row r="92" spans="1:16">
+      <c r="Q91" s="5"/>
+    </row>
+    <row r="92" spans="1:17">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -3307,8 +3412,9 @@
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
-    </row>
-    <row r="93" spans="1:16">
+      <c r="Q92" s="5"/>
+    </row>
+    <row r="93" spans="1:17">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -3325,8 +3431,9 @@
       <c r="N93" s="5"/>
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
-    </row>
-    <row r="94" spans="1:16">
+      <c r="Q93" s="5"/>
+    </row>
+    <row r="94" spans="1:17">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -3343,8 +3450,9 @@
       <c r="N94" s="5"/>
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
-    </row>
-    <row r="95" spans="1:16">
+      <c r="Q94" s="5"/>
+    </row>
+    <row r="95" spans="1:17">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -3361,8 +3469,9 @@
       <c r="N95" s="5"/>
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
-    </row>
-    <row r="96" spans="1:16">
+      <c r="Q95" s="5"/>
+    </row>
+    <row r="96" spans="1:17">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -3379,8 +3488,9 @@
       <c r="N96" s="5"/>
       <c r="O96" s="5"/>
       <c r="P96" s="5"/>
-    </row>
-    <row r="97" spans="1:16">
+      <c r="Q96" s="5"/>
+    </row>
+    <row r="97" spans="1:17">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -3397,8 +3507,9 @@
       <c r="N97" s="5"/>
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
-    </row>
-    <row r="98" spans="1:16">
+      <c r="Q97" s="5"/>
+    </row>
+    <row r="98" spans="1:17">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -3415,8 +3526,9 @@
       <c r="N98" s="5"/>
       <c r="O98" s="5"/>
       <c r="P98" s="5"/>
-    </row>
-    <row r="99" spans="1:16">
+      <c r="Q98" s="5"/>
+    </row>
+    <row r="99" spans="1:17">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -3433,8 +3545,9 @@
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
-    </row>
-    <row r="100" spans="1:16">
+      <c r="Q99" s="5"/>
+    </row>
+    <row r="100" spans="1:17">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -3451,8 +3564,9 @@
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
-    </row>
-    <row r="101" spans="1:16">
+      <c r="Q100" s="5"/>
+    </row>
+    <row r="101" spans="1:17">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -3469,8 +3583,9 @@
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
-    </row>
-    <row r="102" spans="1:16">
+      <c r="Q101" s="5"/>
+    </row>
+    <row r="102" spans="1:17">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -3487,8 +3602,9 @@
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
-    </row>
-    <row r="103" spans="1:16">
+      <c r="Q102" s="5"/>
+    </row>
+    <row r="103" spans="1:17">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -3505,8 +3621,9 @@
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
-    </row>
-    <row r="104" spans="1:16">
+      <c r="Q103" s="5"/>
+    </row>
+    <row r="104" spans="1:17">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3523,8 +3640,9 @@
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
-    </row>
-    <row r="105" spans="1:16">
+      <c r="Q104" s="5"/>
+    </row>
+    <row r="105" spans="1:17">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -3541,8 +3659,9 @@
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
-    </row>
-    <row r="106" spans="1:16">
+      <c r="Q105" s="5"/>
+    </row>
+    <row r="106" spans="1:17">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3559,8 +3678,9 @@
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
-    </row>
-    <row r="107" spans="1:16">
+      <c r="Q106" s="5"/>
+    </row>
+    <row r="107" spans="1:17">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -3577,8 +3697,9 @@
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
-    </row>
-    <row r="108" spans="1:16">
+      <c r="Q107" s="5"/>
+    </row>
+    <row r="108" spans="1:17">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -3595,8 +3716,9 @@
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
-    </row>
-    <row r="109" spans="1:16">
+      <c r="Q108" s="5"/>
+    </row>
+    <row r="109" spans="1:17">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -3613,8 +3735,9 @@
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
-    </row>
-    <row r="110" spans="1:16">
+      <c r="Q109" s="5"/>
+    </row>
+    <row r="110" spans="1:17">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3631,8 +3754,9 @@
       <c r="N110" s="5"/>
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
-    </row>
-    <row r="111" spans="1:16">
+      <c r="Q110" s="5"/>
+    </row>
+    <row r="111" spans="1:17">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3649,8 +3773,9 @@
       <c r="N111" s="5"/>
       <c r="O111" s="5"/>
       <c r="P111" s="5"/>
-    </row>
-    <row r="112" spans="1:16">
+      <c r="Q111" s="5"/>
+    </row>
+    <row r="112" spans="1:17">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3667,8 +3792,9 @@
       <c r="N112" s="5"/>
       <c r="O112" s="5"/>
       <c r="P112" s="5"/>
-    </row>
-    <row r="113" spans="1:16">
+      <c r="Q112" s="5"/>
+    </row>
+    <row r="113" spans="1:17">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3685,8 +3811,9 @@
       <c r="N113" s="5"/>
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
-    </row>
-    <row r="114" spans="1:16">
+      <c r="Q113" s="5"/>
+    </row>
+    <row r="114" spans="1:17">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -3703,8 +3830,9 @@
       <c r="N114" s="5"/>
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
-    </row>
-    <row r="115" spans="1:16">
+      <c r="Q114" s="5"/>
+    </row>
+    <row r="115" spans="1:17">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3721,8 +3849,9 @@
       <c r="N115" s="5"/>
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
-    </row>
-    <row r="116" spans="1:16">
+      <c r="Q115" s="5"/>
+    </row>
+    <row r="116" spans="1:17">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3739,8 +3868,9 @@
       <c r="N116" s="5"/>
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
-    </row>
-    <row r="117" spans="1:16">
+      <c r="Q116" s="5"/>
+    </row>
+    <row r="117" spans="1:17">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -3757,8 +3887,9 @@
       <c r="N117" s="5"/>
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
-    </row>
-    <row r="118" spans="1:16">
+      <c r="Q117" s="5"/>
+    </row>
+    <row r="118" spans="1:17">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -3775,8 +3906,9 @@
       <c r="N118" s="5"/>
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
-    </row>
-    <row r="119" spans="1:16">
+      <c r="Q118" s="5"/>
+    </row>
+    <row r="119" spans="1:17">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -3793,8 +3925,9 @@
       <c r="N119" s="5"/>
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
-    </row>
-    <row r="120" spans="1:16">
+      <c r="Q119" s="5"/>
+    </row>
+    <row r="120" spans="1:17">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -3811,8 +3944,9 @@
       <c r="N120" s="5"/>
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
-    </row>
-    <row r="121" spans="1:16">
+      <c r="Q120" s="5"/>
+    </row>
+    <row r="121" spans="1:17">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -3829,8 +3963,9 @@
       <c r="N121" s="5"/>
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
-    </row>
-    <row r="122" spans="1:16">
+      <c r="Q121" s="5"/>
+    </row>
+    <row r="122" spans="1:17">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -3847,8 +3982,9 @@
       <c r="N122" s="5"/>
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
-    </row>
-    <row r="123" spans="1:16">
+      <c r="Q122" s="5"/>
+    </row>
+    <row r="123" spans="1:17">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -3865,8 +4001,9 @@
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
-    </row>
-    <row r="124" spans="1:16">
+      <c r="Q123" s="5"/>
+    </row>
+    <row r="124" spans="1:17">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -3883,8 +4020,9 @@
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
-    </row>
-    <row r="125" spans="1:16">
+      <c r="Q124" s="5"/>
+    </row>
+    <row r="125" spans="1:17">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -3901,8 +4039,9 @@
       <c r="N125" s="5"/>
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
-    </row>
-    <row r="126" spans="1:16">
+      <c r="Q125" s="5"/>
+    </row>
+    <row r="126" spans="1:17">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -3919,8 +4058,9 @@
       <c r="N126" s="5"/>
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
-    </row>
-    <row r="127" spans="1:16">
+      <c r="Q126" s="5"/>
+    </row>
+    <row r="127" spans="1:17">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -3937,8 +4077,9 @@
       <c r="N127" s="5"/>
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
-    </row>
-    <row r="128" spans="1:16">
+      <c r="Q127" s="5"/>
+    </row>
+    <row r="128" spans="1:17">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3955,8 +4096,9 @@
       <c r="N128" s="5"/>
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
-    </row>
-    <row r="129" spans="1:16">
+      <c r="Q128" s="5"/>
+    </row>
+    <row r="129" spans="1:17">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -3973,8 +4115,9 @@
       <c r="N129" s="5"/>
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
-    </row>
-    <row r="130" spans="1:16">
+      <c r="Q129" s="5"/>
+    </row>
+    <row r="130" spans="1:17">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -3991,8 +4134,9 @@
       <c r="N130" s="5"/>
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
-    </row>
-    <row r="131" spans="1:16">
+      <c r="Q130" s="5"/>
+    </row>
+    <row r="131" spans="1:17">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -4009,8 +4153,9 @@
       <c r="N131" s="5"/>
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
-    </row>
-    <row r="132" spans="1:16">
+      <c r="Q131" s="5"/>
+    </row>
+    <row r="132" spans="1:17">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -4027,8 +4172,9 @@
       <c r="N132" s="5"/>
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
-    </row>
-    <row r="133" spans="1:16">
+      <c r="Q132" s="5"/>
+    </row>
+    <row r="133" spans="1:17">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -4045,8 +4191,9 @@
       <c r="N133" s="5"/>
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
-    </row>
-    <row r="134" spans="1:16">
+      <c r="Q133" s="5"/>
+    </row>
+    <row r="134" spans="1:17">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -4063,8 +4210,9 @@
       <c r="N134" s="5"/>
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
-    </row>
-    <row r="135" spans="1:16">
+      <c r="Q134" s="5"/>
+    </row>
+    <row r="135" spans="1:17">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -4081,8 +4229,9 @@
       <c r="N135" s="5"/>
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
-    </row>
-    <row r="136" spans="1:16">
+      <c r="Q135" s="5"/>
+    </row>
+    <row r="136" spans="1:17">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -4099,8 +4248,9 @@
       <c r="N136" s="5"/>
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
-    </row>
-    <row r="137" spans="1:16">
+      <c r="Q136" s="5"/>
+    </row>
+    <row r="137" spans="1:17">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -4117,8 +4267,9 @@
       <c r="N137" s="5"/>
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
-    </row>
-    <row r="138" spans="1:16">
+      <c r="Q137" s="5"/>
+    </row>
+    <row r="138" spans="1:17">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -4135,8 +4286,9 @@
       <c r="N138" s="5"/>
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
-    </row>
-    <row r="139" spans="1:16">
+      <c r="Q138" s="5"/>
+    </row>
+    <row r="139" spans="1:17">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -4153,8 +4305,9 @@
       <c r="N139" s="5"/>
       <c r="O139" s="5"/>
       <c r="P139" s="5"/>
-    </row>
-    <row r="140" spans="1:16">
+      <c r="Q139" s="5"/>
+    </row>
+    <row r="140" spans="1:17">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -4171,8 +4324,9 @@
       <c r="N140" s="5"/>
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
-    </row>
-    <row r="141" spans="1:16">
+      <c r="Q140" s="5"/>
+    </row>
+    <row r="141" spans="1:17">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -4189,8 +4343,9 @@
       <c r="N141" s="5"/>
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
-    </row>
-    <row r="142" spans="1:16">
+      <c r="Q141" s="5"/>
+    </row>
+    <row r="142" spans="1:17">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -4207,8 +4362,9 @@
       <c r="N142" s="5"/>
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
-    </row>
-    <row r="143" spans="1:16">
+      <c r="Q142" s="5"/>
+    </row>
+    <row r="143" spans="1:17">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -4225,8 +4381,9 @@
       <c r="N143" s="5"/>
       <c r="O143" s="5"/>
       <c r="P143" s="5"/>
-    </row>
-    <row r="144" spans="1:16">
+      <c r="Q143" s="5"/>
+    </row>
+    <row r="144" spans="1:17">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -4243,8 +4400,9 @@
       <c r="N144" s="5"/>
       <c r="O144" s="5"/>
       <c r="P144" s="5"/>
-    </row>
-    <row r="145" spans="1:16">
+      <c r="Q144" s="5"/>
+    </row>
+    <row r="145" spans="1:17">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -4261,8 +4419,9 @@
       <c r="N145" s="5"/>
       <c r="O145" s="5"/>
       <c r="P145" s="5"/>
-    </row>
-    <row r="146" spans="1:16">
+      <c r="Q145" s="5"/>
+    </row>
+    <row r="146" spans="1:17">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -4279,8 +4438,9 @@
       <c r="N146" s="5"/>
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
-    </row>
-    <row r="147" spans="1:16">
+      <c r="Q146" s="5"/>
+    </row>
+    <row r="147" spans="1:17">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -4297,8 +4457,9 @@
       <c r="N147" s="5"/>
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
-    </row>
-    <row r="148" spans="1:16">
+      <c r="Q147" s="5"/>
+    </row>
+    <row r="148" spans="1:17">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -4315,8 +4476,9 @@
       <c r="N148" s="5"/>
       <c r="O148" s="5"/>
       <c r="P148" s="5"/>
-    </row>
-    <row r="149" spans="1:16">
+      <c r="Q148" s="5"/>
+    </row>
+    <row r="149" spans="1:17">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -4333,8 +4495,9 @@
       <c r="N149" s="5"/>
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
-    </row>
-    <row r="150" spans="1:16">
+      <c r="Q149" s="5"/>
+    </row>
+    <row r="150" spans="1:17">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -4351,8 +4514,9 @@
       <c r="N150" s="5"/>
       <c r="O150" s="5"/>
       <c r="P150" s="5"/>
-    </row>
-    <row r="151" spans="1:16">
+      <c r="Q150" s="5"/>
+    </row>
+    <row r="151" spans="1:17">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -4369,8 +4533,9 @@
       <c r="N151" s="5"/>
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
-    </row>
-    <row r="152" spans="1:16">
+      <c r="Q151" s="5"/>
+    </row>
+    <row r="152" spans="1:17">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -4387,8 +4552,9 @@
       <c r="N152" s="5"/>
       <c r="O152" s="5"/>
       <c r="P152" s="5"/>
-    </row>
-    <row r="153" spans="1:16">
+      <c r="Q152" s="5"/>
+    </row>
+    <row r="153" spans="1:17">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -4405,8 +4571,9 @@
       <c r="N153" s="5"/>
       <c r="O153" s="5"/>
       <c r="P153" s="5"/>
-    </row>
-    <row r="154" spans="1:16">
+      <c r="Q153" s="5"/>
+    </row>
+    <row r="154" spans="1:17">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -4423,8 +4590,9 @@
       <c r="N154" s="5"/>
       <c r="O154" s="5"/>
       <c r="P154" s="5"/>
-    </row>
-    <row r="155" spans="1:16">
+      <c r="Q154" s="5"/>
+    </row>
+    <row r="155" spans="1:17">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -4441,8 +4609,9 @@
       <c r="N155" s="5"/>
       <c r="O155" s="5"/>
       <c r="P155" s="5"/>
-    </row>
-    <row r="156" spans="1:16">
+      <c r="Q155" s="5"/>
+    </row>
+    <row r="156" spans="1:17">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -4459,8 +4628,9 @@
       <c r="N156" s="5"/>
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
-    </row>
-    <row r="157" spans="1:16">
+      <c r="Q156" s="5"/>
+    </row>
+    <row r="157" spans="1:17">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -4477,8 +4647,9 @@
       <c r="N157" s="5"/>
       <c r="O157" s="5"/>
       <c r="P157" s="5"/>
-    </row>
-    <row r="158" spans="1:16">
+      <c r="Q157" s="5"/>
+    </row>
+    <row r="158" spans="1:17">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -4495,8 +4666,9 @@
       <c r="N158" s="5"/>
       <c r="O158" s="5"/>
       <c r="P158" s="5"/>
-    </row>
-    <row r="159" spans="1:16">
+      <c r="Q158" s="5"/>
+    </row>
+    <row r="159" spans="1:17">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -4513,8 +4685,9 @@
       <c r="N159" s="5"/>
       <c r="O159" s="5"/>
       <c r="P159" s="5"/>
-    </row>
-    <row r="160" spans="1:16">
+      <c r="Q159" s="5"/>
+    </row>
+    <row r="160" spans="1:17">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -4531,8 +4704,9 @@
       <c r="N160" s="5"/>
       <c r="O160" s="5"/>
       <c r="P160" s="5"/>
-    </row>
-    <row r="161" spans="1:16">
+      <c r="Q160" s="5"/>
+    </row>
+    <row r="161" spans="1:17">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -4549,8 +4723,9 @@
       <c r="N161" s="5"/>
       <c r="O161" s="5"/>
       <c r="P161" s="5"/>
-    </row>
-    <row r="162" spans="1:16">
+      <c r="Q161" s="5"/>
+    </row>
+    <row r="162" spans="1:17">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -4567,8 +4742,9 @@
       <c r="N162" s="5"/>
       <c r="O162" s="5"/>
       <c r="P162" s="5"/>
-    </row>
-    <row r="163" spans="1:16">
+      <c r="Q162" s="5"/>
+    </row>
+    <row r="163" spans="1:17">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -4585,8 +4761,9 @@
       <c r="N163" s="5"/>
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
-    </row>
-    <row r="164" spans="1:16">
+      <c r="Q163" s="5"/>
+    </row>
+    <row r="164" spans="1:17">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -4603,8 +4780,9 @@
       <c r="N164" s="5"/>
       <c r="O164" s="5"/>
       <c r="P164" s="5"/>
-    </row>
-    <row r="165" spans="1:16">
+      <c r="Q164" s="5"/>
+    </row>
+    <row r="165" spans="1:17">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -4621,8 +4799,9 @@
       <c r="N165" s="5"/>
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
-    </row>
-    <row r="166" spans="1:16">
+      <c r="Q165" s="5"/>
+    </row>
+    <row r="166" spans="1:17">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -4639,8 +4818,9 @@
       <c r="N166" s="5"/>
       <c r="O166" s="5"/>
       <c r="P166" s="5"/>
-    </row>
-    <row r="167" spans="1:16">
+      <c r="Q166" s="5"/>
+    </row>
+    <row r="167" spans="1:17">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -4657,8 +4837,9 @@
       <c r="N167" s="5"/>
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
-    </row>
-    <row r="168" spans="1:16">
+      <c r="Q167" s="5"/>
+    </row>
+    <row r="168" spans="1:17">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -4675,8 +4856,9 @@
       <c r="N168" s="5"/>
       <c r="O168" s="5"/>
       <c r="P168" s="5"/>
-    </row>
-    <row r="169" spans="1:16">
+      <c r="Q168" s="5"/>
+    </row>
+    <row r="169" spans="1:17">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -4693,8 +4875,9 @@
       <c r="N169" s="5"/>
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
-    </row>
-    <row r="170" spans="1:16">
+      <c r="Q169" s="5"/>
+    </row>
+    <row r="170" spans="1:17">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -4711,8 +4894,9 @@
       <c r="N170" s="5"/>
       <c r="O170" s="5"/>
       <c r="P170" s="5"/>
-    </row>
-    <row r="171" spans="1:16">
+      <c r="Q170" s="5"/>
+    </row>
+    <row r="171" spans="1:17">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -4729,8 +4913,9 @@
       <c r="N171" s="5"/>
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
-    </row>
-    <row r="172" spans="1:16">
+      <c r="Q171" s="5"/>
+    </row>
+    <row r="172" spans="1:17">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -4747,8 +4932,9 @@
       <c r="N172" s="5"/>
       <c r="O172" s="5"/>
       <c r="P172" s="5"/>
-    </row>
-    <row r="173" spans="1:16">
+      <c r="Q172" s="5"/>
+    </row>
+    <row r="173" spans="1:17">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -4765,8 +4951,9 @@
       <c r="N173" s="5"/>
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
-    </row>
-    <row r="174" spans="1:16">
+      <c r="Q173" s="5"/>
+    </row>
+    <row r="174" spans="1:17">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -4783,8 +4970,9 @@
       <c r="N174" s="5"/>
       <c r="O174" s="5"/>
       <c r="P174" s="5"/>
-    </row>
-    <row r="175" spans="1:16">
+      <c r="Q174" s="5"/>
+    </row>
+    <row r="175" spans="1:17">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -4801,8 +4989,9 @@
       <c r="N175" s="5"/>
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
-    </row>
-    <row r="176" spans="1:16">
+      <c r="Q175" s="5"/>
+    </row>
+    <row r="176" spans="1:17">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -4819,8 +5008,9 @@
       <c r="N176" s="5"/>
       <c r="O176" s="5"/>
       <c r="P176" s="5"/>
-    </row>
-    <row r="177" spans="1:16">
+      <c r="Q176" s="5"/>
+    </row>
+    <row r="177" spans="1:17">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -4837,8 +5027,9 @@
       <c r="N177" s="5"/>
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
-    </row>
-    <row r="178" spans="1:16">
+      <c r="Q177" s="5"/>
+    </row>
+    <row r="178" spans="1:17">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -4855,8 +5046,9 @@
       <c r="N178" s="5"/>
       <c r="O178" s="5"/>
       <c r="P178" s="5"/>
-    </row>
-    <row r="179" spans="1:16">
+      <c r="Q178" s="5"/>
+    </row>
+    <row r="179" spans="1:17">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -4873,8 +5065,9 @@
       <c r="N179" s="5"/>
       <c r="O179" s="5"/>
       <c r="P179" s="5"/>
-    </row>
-    <row r="180" spans="1:16">
+      <c r="Q179" s="5"/>
+    </row>
+    <row r="180" spans="1:17">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -4891,8 +5084,9 @@
       <c r="N180" s="5"/>
       <c r="O180" s="5"/>
       <c r="P180" s="5"/>
-    </row>
-    <row r="181" spans="1:16">
+      <c r="Q180" s="5"/>
+    </row>
+    <row r="181" spans="1:17">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -4909,8 +5103,9 @@
       <c r="N181" s="5"/>
       <c r="O181" s="5"/>
       <c r="P181" s="5"/>
-    </row>
-    <row r="182" spans="1:16">
+      <c r="Q181" s="5"/>
+    </row>
+    <row r="182" spans="1:17">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -4927,8 +5122,9 @@
       <c r="N182" s="5"/>
       <c r="O182" s="5"/>
       <c r="P182" s="5"/>
-    </row>
-    <row r="183" spans="1:16">
+      <c r="Q182" s="5"/>
+    </row>
+    <row r="183" spans="1:17">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -4945,8 +5141,9 @@
       <c r="N183" s="5"/>
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
-    </row>
-    <row r="184" spans="1:16">
+      <c r="Q183" s="5"/>
+    </row>
+    <row r="184" spans="1:17">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -4963,8 +5160,9 @@
       <c r="N184" s="5"/>
       <c r="O184" s="5"/>
       <c r="P184" s="5"/>
-    </row>
-    <row r="185" spans="1:16">
+      <c r="Q184" s="5"/>
+    </row>
+    <row r="185" spans="1:17">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -4981,8 +5179,9 @@
       <c r="N185" s="5"/>
       <c r="O185" s="5"/>
       <c r="P185" s="5"/>
-    </row>
-    <row r="186" spans="1:16">
+      <c r="Q185" s="5"/>
+    </row>
+    <row r="186" spans="1:17">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -4999,8 +5198,9 @@
       <c r="N186" s="5"/>
       <c r="O186" s="5"/>
       <c r="P186" s="5"/>
-    </row>
-    <row r="187" spans="1:16">
+      <c r="Q186" s="5"/>
+    </row>
+    <row r="187" spans="1:17">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -5017,8 +5217,9 @@
       <c r="N187" s="5"/>
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
-    </row>
-    <row r="188" spans="1:16">
+      <c r="Q187" s="5"/>
+    </row>
+    <row r="188" spans="1:17">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -5035,8 +5236,9 @@
       <c r="N188" s="5"/>
       <c r="O188" s="5"/>
       <c r="P188" s="5"/>
-    </row>
-    <row r="189" spans="1:16">
+      <c r="Q188" s="5"/>
+    </row>
+    <row r="189" spans="1:17">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -5053,8 +5255,9 @@
       <c r="N189" s="5"/>
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
-    </row>
-    <row r="190" spans="1:16">
+      <c r="Q189" s="5"/>
+    </row>
+    <row r="190" spans="1:17">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -5071,8 +5274,9 @@
       <c r="N190" s="5"/>
       <c r="O190" s="5"/>
       <c r="P190" s="5"/>
-    </row>
-    <row r="191" spans="1:16">
+      <c r="Q190" s="5"/>
+    </row>
+    <row r="191" spans="1:17">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -5089,8 +5293,9 @@
       <c r="N191" s="5"/>
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
-    </row>
-    <row r="192" spans="1:16">
+      <c r="Q191" s="5"/>
+    </row>
+    <row r="192" spans="1:17">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -5107,8 +5312,9 @@
       <c r="N192" s="5"/>
       <c r="O192" s="5"/>
       <c r="P192" s="5"/>
-    </row>
-    <row r="193" spans="1:16">
+      <c r="Q192" s="5"/>
+    </row>
+    <row r="193" spans="1:17">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -5125,8 +5331,9 @@
       <c r="N193" s="5"/>
       <c r="O193" s="5"/>
       <c r="P193" s="5"/>
-    </row>
-    <row r="194" spans="1:16">
+      <c r="Q193" s="5"/>
+    </row>
+    <row r="194" spans="1:17">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -5143,8 +5350,9 @@
       <c r="N194" s="5"/>
       <c r="O194" s="5"/>
       <c r="P194" s="5"/>
-    </row>
-    <row r="195" spans="1:16">
+      <c r="Q194" s="5"/>
+    </row>
+    <row r="195" spans="1:17">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -5161,8 +5369,9 @@
       <c r="N195" s="5"/>
       <c r="O195" s="5"/>
       <c r="P195" s="5"/>
-    </row>
-    <row r="196" spans="1:16">
+      <c r="Q195" s="5"/>
+    </row>
+    <row r="196" spans="1:17">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -5179,8 +5388,9 @@
       <c r="N196" s="5"/>
       <c r="O196" s="5"/>
       <c r="P196" s="5"/>
-    </row>
-    <row r="197" spans="1:16">
+      <c r="Q196" s="5"/>
+    </row>
+    <row r="197" spans="1:17">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -5197,8 +5407,9 @@
       <c r="N197" s="5"/>
       <c r="O197" s="5"/>
       <c r="P197" s="5"/>
-    </row>
-    <row r="198" spans="1:16">
+      <c r="Q197" s="5"/>
+    </row>
+    <row r="198" spans="1:17">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -5215,8 +5426,9 @@
       <c r="N198" s="5"/>
       <c r="O198" s="5"/>
       <c r="P198" s="5"/>
-    </row>
-    <row r="199" spans="1:16">
+      <c r="Q198" s="5"/>
+    </row>
+    <row r="199" spans="1:17">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -5233,8 +5445,9 @@
       <c r="N199" s="5"/>
       <c r="O199" s="5"/>
       <c r="P199" s="5"/>
-    </row>
-    <row r="200" spans="1:16">
+      <c r="Q199" s="5"/>
+    </row>
+    <row r="200" spans="1:17">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -5251,8 +5464,9 @@
       <c r="N200" s="5"/>
       <c r="O200" s="5"/>
       <c r="P200" s="5"/>
-    </row>
-    <row r="201" spans="1:16">
+      <c r="Q200" s="5"/>
+    </row>
+    <row r="201" spans="1:17">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -5269,8 +5483,9 @@
       <c r="N201" s="5"/>
       <c r="O201" s="5"/>
       <c r="P201" s="5"/>
-    </row>
-    <row r="202" spans="1:16">
+      <c r="Q201" s="5"/>
+    </row>
+    <row r="202" spans="1:17">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -5287,8 +5502,9 @@
       <c r="N202" s="5"/>
       <c r="O202" s="5"/>
       <c r="P202" s="5"/>
-    </row>
-    <row r="203" spans="1:16">
+      <c r="Q202" s="5"/>
+    </row>
+    <row r="203" spans="1:17">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -5305,8 +5521,9 @@
       <c r="N203" s="5"/>
       <c r="O203" s="5"/>
       <c r="P203" s="5"/>
-    </row>
-    <row r="204" spans="1:16">
+      <c r="Q203" s="5"/>
+    </row>
+    <row r="204" spans="1:17">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -5323,8 +5540,9 @@
       <c r="N204" s="5"/>
       <c r="O204" s="5"/>
       <c r="P204" s="5"/>
-    </row>
-    <row r="205" spans="1:16">
+      <c r="Q204" s="5"/>
+    </row>
+    <row r="205" spans="1:17">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -5341,8 +5559,9 @@
       <c r="N205" s="5"/>
       <c r="O205" s="5"/>
       <c r="P205" s="5"/>
-    </row>
-    <row r="206" spans="1:16">
+      <c r="Q205" s="5"/>
+    </row>
+    <row r="206" spans="1:17">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -5359,8 +5578,9 @@
       <c r="N206" s="5"/>
       <c r="O206" s="5"/>
       <c r="P206" s="5"/>
-    </row>
-    <row r="207" spans="1:16">
+      <c r="Q206" s="5"/>
+    </row>
+    <row r="207" spans="1:17">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -5377,8 +5597,9 @@
       <c r="N207" s="5"/>
       <c r="O207" s="5"/>
       <c r="P207" s="5"/>
-    </row>
-    <row r="208" spans="1:16">
+      <c r="Q207" s="5"/>
+    </row>
+    <row r="208" spans="1:17">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -5395,8 +5616,9 @@
       <c r="N208" s="5"/>
       <c r="O208" s="5"/>
       <c r="P208" s="5"/>
-    </row>
-    <row r="209" spans="1:16">
+      <c r="Q208" s="5"/>
+    </row>
+    <row r="209" spans="1:17">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -5413,8 +5635,9 @@
       <c r="N209" s="5"/>
       <c r="O209" s="5"/>
       <c r="P209" s="5"/>
-    </row>
-    <row r="210" spans="1:16">
+      <c r="Q209" s="5"/>
+    </row>
+    <row r="210" spans="1:17">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -5431,8 +5654,9 @@
       <c r="N210" s="5"/>
       <c r="O210" s="5"/>
       <c r="P210" s="5"/>
-    </row>
-    <row r="211" spans="1:16">
+      <c r="Q210" s="5"/>
+    </row>
+    <row r="211" spans="1:17">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -5449,8 +5673,9 @@
       <c r="N211" s="5"/>
       <c r="O211" s="5"/>
       <c r="P211" s="5"/>
-    </row>
-    <row r="212" spans="1:16">
+      <c r="Q211" s="5"/>
+    </row>
+    <row r="212" spans="1:17">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -5467,8 +5692,9 @@
       <c r="N212" s="5"/>
       <c r="O212" s="5"/>
       <c r="P212" s="5"/>
-    </row>
-    <row r="213" spans="1:16">
+      <c r="Q212" s="5"/>
+    </row>
+    <row r="213" spans="1:17">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -5485,8 +5711,9 @@
       <c r="N213" s="5"/>
       <c r="O213" s="5"/>
       <c r="P213" s="5"/>
-    </row>
-    <row r="214" spans="1:16">
+      <c r="Q213" s="5"/>
+    </row>
+    <row r="214" spans="1:17">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -5503,8 +5730,9 @@
       <c r="N214" s="5"/>
       <c r="O214" s="5"/>
       <c r="P214" s="5"/>
-    </row>
-    <row r="215" spans="1:16">
+      <c r="Q214" s="5"/>
+    </row>
+    <row r="215" spans="1:17">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -5521,8 +5749,9 @@
       <c r="N215" s="5"/>
       <c r="O215" s="5"/>
       <c r="P215" s="5"/>
-    </row>
-    <row r="216" spans="1:16">
+      <c r="Q215" s="5"/>
+    </row>
+    <row r="216" spans="1:17">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -5539,8 +5768,9 @@
       <c r="N216" s="5"/>
       <c r="O216" s="5"/>
       <c r="P216" s="5"/>
-    </row>
-    <row r="217" spans="1:16">
+      <c r="Q216" s="5"/>
+    </row>
+    <row r="217" spans="1:17">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -5557,8 +5787,9 @@
       <c r="N217" s="5"/>
       <c r="O217" s="5"/>
       <c r="P217" s="5"/>
-    </row>
-    <row r="218" spans="1:16">
+      <c r="Q217" s="5"/>
+    </row>
+    <row r="218" spans="1:17">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -5575,8 +5806,9 @@
       <c r="N218" s="5"/>
       <c r="O218" s="5"/>
       <c r="P218" s="5"/>
-    </row>
-    <row r="219" spans="1:16">
+      <c r="Q218" s="5"/>
+    </row>
+    <row r="219" spans="1:17">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -5593,8 +5825,9 @@
       <c r="N219" s="5"/>
       <c r="O219" s="5"/>
       <c r="P219" s="5"/>
-    </row>
-    <row r="220" spans="1:16">
+      <c r="Q219" s="5"/>
+    </row>
+    <row r="220" spans="1:17">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -5611,8 +5844,9 @@
       <c r="N220" s="5"/>
       <c r="O220" s="5"/>
       <c r="P220" s="5"/>
-    </row>
-    <row r="221" spans="1:16">
+      <c r="Q220" s="5"/>
+    </row>
+    <row r="221" spans="1:17">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -5629,8 +5863,9 @@
       <c r="N221" s="5"/>
       <c r="O221" s="5"/>
       <c r="P221" s="5"/>
-    </row>
-    <row r="222" spans="1:16">
+      <c r="Q221" s="5"/>
+    </row>
+    <row r="222" spans="1:17">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -5647,8 +5882,9 @@
       <c r="N222" s="5"/>
       <c r="O222" s="5"/>
       <c r="P222" s="5"/>
-    </row>
-    <row r="223" spans="1:16">
+      <c r="Q222" s="5"/>
+    </row>
+    <row r="223" spans="1:17">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -5665,8 +5901,9 @@
       <c r="N223" s="5"/>
       <c r="O223" s="5"/>
       <c r="P223" s="5"/>
-    </row>
-    <row r="224" spans="1:16">
+      <c r="Q223" s="5"/>
+    </row>
+    <row r="224" spans="1:17">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -5683,8 +5920,9 @@
       <c r="N224" s="5"/>
       <c r="O224" s="5"/>
       <c r="P224" s="5"/>
-    </row>
-    <row r="225" spans="1:16">
+      <c r="Q224" s="5"/>
+    </row>
+    <row r="225" spans="1:17">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -5701,8 +5939,9 @@
       <c r="N225" s="5"/>
       <c r="O225" s="5"/>
       <c r="P225" s="5"/>
-    </row>
-    <row r="226" spans="1:16">
+      <c r="Q225" s="5"/>
+    </row>
+    <row r="226" spans="1:17">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -5719,8 +5958,9 @@
       <c r="N226" s="5"/>
       <c r="O226" s="5"/>
       <c r="P226" s="5"/>
-    </row>
-    <row r="227" spans="1:16">
+      <c r="Q226" s="5"/>
+    </row>
+    <row r="227" spans="1:17">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -5737,8 +5977,9 @@
       <c r="N227" s="5"/>
       <c r="O227" s="5"/>
       <c r="P227" s="5"/>
-    </row>
-    <row r="228" spans="1:16">
+      <c r="Q227" s="5"/>
+    </row>
+    <row r="228" spans="1:17">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -5755,8 +5996,9 @@
       <c r="N228" s="5"/>
       <c r="O228" s="5"/>
       <c r="P228" s="5"/>
-    </row>
-    <row r="229" spans="1:16">
+      <c r="Q228" s="5"/>
+    </row>
+    <row r="229" spans="1:17">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -5773,8 +6015,9 @@
       <c r="N229" s="5"/>
       <c r="O229" s="5"/>
       <c r="P229" s="5"/>
-    </row>
-    <row r="230" spans="1:16">
+      <c r="Q229" s="5"/>
+    </row>
+    <row r="230" spans="1:17">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -5791,8 +6034,9 @@
       <c r="N230" s="5"/>
       <c r="O230" s="5"/>
       <c r="P230" s="5"/>
-    </row>
-    <row r="231" spans="1:16">
+      <c r="Q230" s="5"/>
+    </row>
+    <row r="231" spans="1:17">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -5809,8 +6053,9 @@
       <c r="N231" s="5"/>
       <c r="O231" s="5"/>
       <c r="P231" s="5"/>
-    </row>
-    <row r="232" spans="1:16">
+      <c r="Q231" s="5"/>
+    </row>
+    <row r="232" spans="1:17">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -5827,8 +6072,9 @@
       <c r="N232" s="5"/>
       <c r="O232" s="5"/>
       <c r="P232" s="5"/>
-    </row>
-    <row r="233" spans="1:16">
+      <c r="Q232" s="5"/>
+    </row>
+    <row r="233" spans="1:17">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -5845,8 +6091,9 @@
       <c r="N233" s="5"/>
       <c r="O233" s="5"/>
       <c r="P233" s="5"/>
-    </row>
-    <row r="234" spans="1:16">
+      <c r="Q233" s="5"/>
+    </row>
+    <row r="234" spans="1:17">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -5863,8 +6110,9 @@
       <c r="N234" s="5"/>
       <c r="O234" s="5"/>
       <c r="P234" s="5"/>
-    </row>
-    <row r="235" spans="1:16">
+      <c r="Q234" s="5"/>
+    </row>
+    <row r="235" spans="1:17">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -5881,8 +6129,9 @@
       <c r="N235" s="5"/>
       <c r="O235" s="5"/>
       <c r="P235" s="5"/>
-    </row>
-    <row r="236" spans="1:16">
+      <c r="Q235" s="5"/>
+    </row>
+    <row r="236" spans="1:17">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -5899,8 +6148,9 @@
       <c r="N236" s="5"/>
       <c r="O236" s="5"/>
       <c r="P236" s="5"/>
-    </row>
-    <row r="237" spans="1:16">
+      <c r="Q236" s="5"/>
+    </row>
+    <row r="237" spans="1:17">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -5917,8 +6167,9 @@
       <c r="N237" s="5"/>
       <c r="O237" s="5"/>
       <c r="P237" s="5"/>
-    </row>
-    <row r="238" spans="1:16">
+      <c r="Q237" s="5"/>
+    </row>
+    <row r="238" spans="1:17">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -5935,8 +6186,9 @@
       <c r="N238" s="5"/>
       <c r="O238" s="5"/>
       <c r="P238" s="5"/>
-    </row>
-    <row r="239" spans="1:16">
+      <c r="Q238" s="5"/>
+    </row>
+    <row r="239" spans="1:17">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -5953,8 +6205,9 @@
       <c r="N239" s="5"/>
       <c r="O239" s="5"/>
       <c r="P239" s="5"/>
-    </row>
-    <row r="240" spans="1:16">
+      <c r="Q239" s="5"/>
+    </row>
+    <row r="240" spans="1:17">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -5971,8 +6224,9 @@
       <c r="N240" s="5"/>
       <c r="O240" s="5"/>
       <c r="P240" s="5"/>
-    </row>
-    <row r="241" spans="1:16">
+      <c r="Q240" s="5"/>
+    </row>
+    <row r="241" spans="1:17">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -5989,8 +6243,9 @@
       <c r="N241" s="5"/>
       <c r="O241" s="5"/>
       <c r="P241" s="5"/>
-    </row>
-    <row r="242" spans="1:16">
+      <c r="Q241" s="5"/>
+    </row>
+    <row r="242" spans="1:17">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -6007,8 +6262,9 @@
       <c r="N242" s="5"/>
       <c r="O242" s="5"/>
       <c r="P242" s="5"/>
-    </row>
-    <row r="243" spans="1:16">
+      <c r="Q242" s="5"/>
+    </row>
+    <row r="243" spans="1:17">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -6025,8 +6281,9 @@
       <c r="N243" s="5"/>
       <c r="O243" s="5"/>
       <c r="P243" s="5"/>
-    </row>
-    <row r="244" spans="1:16">
+      <c r="Q243" s="5"/>
+    </row>
+    <row r="244" spans="1:17">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -6043,8 +6300,9 @@
       <c r="N244" s="5"/>
       <c r="O244" s="5"/>
       <c r="P244" s="5"/>
-    </row>
-    <row r="245" spans="1:16">
+      <c r="Q244" s="5"/>
+    </row>
+    <row r="245" spans="1:17">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -6061,8 +6319,9 @@
       <c r="N245" s="5"/>
       <c r="O245" s="5"/>
       <c r="P245" s="5"/>
-    </row>
-    <row r="246" spans="1:16">
+      <c r="Q245" s="5"/>
+    </row>
+    <row r="246" spans="1:17">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -6079,8 +6338,9 @@
       <c r="N246" s="5"/>
       <c r="O246" s="5"/>
       <c r="P246" s="5"/>
-    </row>
-    <row r="247" spans="1:16">
+      <c r="Q246" s="5"/>
+    </row>
+    <row r="247" spans="1:17">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -6097,8 +6357,9 @@
       <c r="N247" s="5"/>
       <c r="O247" s="5"/>
       <c r="P247" s="5"/>
-    </row>
-    <row r="248" spans="1:16">
+      <c r="Q247" s="5"/>
+    </row>
+    <row r="248" spans="1:17">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -6115,8 +6376,9 @@
       <c r="N248" s="5"/>
       <c r="O248" s="5"/>
       <c r="P248" s="5"/>
-    </row>
-    <row r="249" spans="1:16">
+      <c r="Q248" s="5"/>
+    </row>
+    <row r="249" spans="1:17">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -6133,8 +6395,9 @@
       <c r="N249" s="5"/>
       <c r="O249" s="5"/>
       <c r="P249" s="5"/>
-    </row>
-    <row r="250" spans="1:16">
+      <c r="Q249" s="5"/>
+    </row>
+    <row r="250" spans="1:17">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -6151,8 +6414,9 @@
       <c r="N250" s="5"/>
       <c r="O250" s="5"/>
       <c r="P250" s="5"/>
-    </row>
-    <row r="251" spans="1:16">
+      <c r="Q250" s="5"/>
+    </row>
+    <row r="251" spans="1:17">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -6169,8 +6433,9 @@
       <c r="N251" s="5"/>
       <c r="O251" s="5"/>
       <c r="P251" s="5"/>
-    </row>
-    <row r="252" spans="1:16">
+      <c r="Q251" s="5"/>
+    </row>
+    <row r="252" spans="1:17">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6187,8 +6452,9 @@
       <c r="N252" s="5"/>
       <c r="O252" s="5"/>
       <c r="P252" s="5"/>
-    </row>
-    <row r="253" spans="1:16">
+      <c r="Q252" s="5"/>
+    </row>
+    <row r="253" spans="1:17">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6205,8 +6471,9 @@
       <c r="N253" s="5"/>
       <c r="O253" s="5"/>
       <c r="P253" s="5"/>
-    </row>
-    <row r="254" spans="1:16">
+      <c r="Q253" s="5"/>
+    </row>
+    <row r="254" spans="1:17">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6223,8 +6490,9 @@
       <c r="N254" s="5"/>
       <c r="O254" s="5"/>
       <c r="P254" s="5"/>
-    </row>
-    <row r="255" spans="1:16">
+      <c r="Q254" s="5"/>
+    </row>
+    <row r="255" spans="1:17">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -6241,8 +6509,9 @@
       <c r="N255" s="5"/>
       <c r="O255" s="5"/>
       <c r="P255" s="5"/>
-    </row>
-    <row r="256" spans="1:16">
+      <c r="Q255" s="5"/>
+    </row>
+    <row r="256" spans="1:17">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6259,8 +6528,9 @@
       <c r="N256" s="5"/>
       <c r="O256" s="5"/>
       <c r="P256" s="5"/>
-    </row>
-    <row r="257" spans="1:16">
+      <c r="Q256" s="5"/>
+    </row>
+    <row r="257" spans="1:17">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6277,8 +6547,9 @@
       <c r="N257" s="5"/>
       <c r="O257" s="5"/>
       <c r="P257" s="5"/>
-    </row>
-    <row r="258" spans="1:16">
+      <c r="Q257" s="5"/>
+    </row>
+    <row r="258" spans="1:17">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6295,8 +6566,9 @@
       <c r="N258" s="5"/>
       <c r="O258" s="5"/>
       <c r="P258" s="5"/>
-    </row>
-    <row r="259" spans="1:16">
+      <c r="Q258" s="5"/>
+    </row>
+    <row r="259" spans="1:17">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -6313,8 +6585,9 @@
       <c r="N259" s="5"/>
       <c r="O259" s="5"/>
       <c r="P259" s="5"/>
-    </row>
-    <row r="260" spans="1:16">
+      <c r="Q259" s="5"/>
+    </row>
+    <row r="260" spans="1:17">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -6331,8 +6604,9 @@
       <c r="N260" s="5"/>
       <c r="O260" s="5"/>
       <c r="P260" s="5"/>
-    </row>
-    <row r="261" spans="1:16">
+      <c r="Q260" s="5"/>
+    </row>
+    <row r="261" spans="1:17">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -6349,8 +6623,9 @@
       <c r="N261" s="5"/>
       <c r="O261" s="5"/>
       <c r="P261" s="5"/>
-    </row>
-    <row r="262" spans="1:16">
+      <c r="Q261" s="5"/>
+    </row>
+    <row r="262" spans="1:17">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -6367,8 +6642,9 @@
       <c r="N262" s="5"/>
       <c r="O262" s="5"/>
       <c r="P262" s="5"/>
-    </row>
-    <row r="263" spans="1:16">
+      <c r="Q262" s="5"/>
+    </row>
+    <row r="263" spans="1:17">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -6385,8 +6661,9 @@
       <c r="N263" s="5"/>
       <c r="O263" s="5"/>
       <c r="P263" s="5"/>
-    </row>
-    <row r="264" spans="1:16">
+      <c r="Q263" s="5"/>
+    </row>
+    <row r="264" spans="1:17">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -6403,8 +6680,9 @@
       <c r="N264" s="5"/>
       <c r="O264" s="5"/>
       <c r="P264" s="5"/>
-    </row>
-    <row r="265" spans="1:16">
+      <c r="Q264" s="5"/>
+    </row>
+    <row r="265" spans="1:17">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -6421,8 +6699,9 @@
       <c r="N265" s="5"/>
       <c r="O265" s="5"/>
       <c r="P265" s="5"/>
-    </row>
-    <row r="266" spans="1:16">
+      <c r="Q265" s="5"/>
+    </row>
+    <row r="266" spans="1:17">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -6439,8 +6718,9 @@
       <c r="N266" s="5"/>
       <c r="O266" s="5"/>
       <c r="P266" s="5"/>
-    </row>
-    <row r="267" spans="1:16">
+      <c r="Q266" s="5"/>
+    </row>
+    <row r="267" spans="1:17">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -6457,8 +6737,9 @@
       <c r="N267" s="5"/>
       <c r="O267" s="5"/>
       <c r="P267" s="5"/>
-    </row>
-    <row r="268" spans="1:16">
+      <c r="Q267" s="5"/>
+    </row>
+    <row r="268" spans="1:17">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -6475,8 +6756,9 @@
       <c r="N268" s="5"/>
       <c r="O268" s="5"/>
       <c r="P268" s="5"/>
-    </row>
-    <row r="269" spans="1:16">
+      <c r="Q268" s="5"/>
+    </row>
+    <row r="269" spans="1:17">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -6493,8 +6775,9 @@
       <c r="N269" s="5"/>
       <c r="O269" s="5"/>
       <c r="P269" s="5"/>
-    </row>
-    <row r="270" spans="1:16">
+      <c r="Q269" s="5"/>
+    </row>
+    <row r="270" spans="1:17">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -6511,8 +6794,9 @@
       <c r="N270" s="5"/>
       <c r="O270" s="5"/>
       <c r="P270" s="5"/>
-    </row>
-    <row r="271" spans="1:16">
+      <c r="Q270" s="5"/>
+    </row>
+    <row r="271" spans="1:17">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -6529,8 +6813,9 @@
       <c r="N271" s="5"/>
       <c r="O271" s="5"/>
       <c r="P271" s="5"/>
-    </row>
-    <row r="272" spans="1:16">
+      <c r="Q271" s="5"/>
+    </row>
+    <row r="272" spans="1:17">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -6547,8 +6832,9 @@
       <c r="N272" s="5"/>
       <c r="O272" s="5"/>
       <c r="P272" s="5"/>
-    </row>
-    <row r="273" spans="1:16">
+      <c r="Q272" s="5"/>
+    </row>
+    <row r="273" spans="1:17">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -6565,8 +6851,9 @@
       <c r="N273" s="5"/>
       <c r="O273" s="5"/>
       <c r="P273" s="5"/>
-    </row>
-    <row r="274" spans="1:16">
+      <c r="Q273" s="5"/>
+    </row>
+    <row r="274" spans="1:17">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -6583,8 +6870,9 @@
       <c r="N274" s="5"/>
       <c r="O274" s="5"/>
       <c r="P274" s="5"/>
-    </row>
-    <row r="275" spans="1:16">
+      <c r="Q274" s="5"/>
+    </row>
+    <row r="275" spans="1:17">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -6601,8 +6889,9 @@
       <c r="N275" s="5"/>
       <c r="O275" s="5"/>
       <c r="P275" s="5"/>
-    </row>
-    <row r="276" spans="1:16">
+      <c r="Q275" s="5"/>
+    </row>
+    <row r="276" spans="1:17">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -6619,8 +6908,9 @@
       <c r="N276" s="5"/>
       <c r="O276" s="5"/>
       <c r="P276" s="5"/>
-    </row>
-    <row r="277" spans="1:16">
+      <c r="Q276" s="5"/>
+    </row>
+    <row r="277" spans="1:17">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -6637,8 +6927,9 @@
       <c r="N277" s="5"/>
       <c r="O277" s="5"/>
       <c r="P277" s="5"/>
-    </row>
-    <row r="278" spans="1:16">
+      <c r="Q277" s="5"/>
+    </row>
+    <row r="278" spans="1:17">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -6655,8 +6946,9 @@
       <c r="N278" s="5"/>
       <c r="O278" s="5"/>
       <c r="P278" s="5"/>
-    </row>
-    <row r="279" spans="1:16">
+      <c r="Q278" s="5"/>
+    </row>
+    <row r="279" spans="1:17">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -6673,8 +6965,9 @@
       <c r="N279" s="5"/>
       <c r="O279" s="5"/>
       <c r="P279" s="5"/>
-    </row>
-    <row r="280" spans="1:16">
+      <c r="Q279" s="5"/>
+    </row>
+    <row r="280" spans="1:17">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -6691,8 +6984,9 @@
       <c r="N280" s="5"/>
       <c r="O280" s="5"/>
       <c r="P280" s="5"/>
-    </row>
-    <row r="281" spans="1:16">
+      <c r="Q280" s="5"/>
+    </row>
+    <row r="281" spans="1:17">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -6709,8 +7003,9 @@
       <c r="N281" s="5"/>
       <c r="O281" s="5"/>
       <c r="P281" s="5"/>
-    </row>
-    <row r="282" spans="1:16">
+      <c r="Q281" s="5"/>
+    </row>
+    <row r="282" spans="1:17">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -6727,8 +7022,9 @@
       <c r="N282" s="5"/>
       <c r="O282" s="5"/>
       <c r="P282" s="5"/>
-    </row>
-    <row r="283" spans="1:16">
+      <c r="Q282" s="5"/>
+    </row>
+    <row r="283" spans="1:17">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -6745,8 +7041,9 @@
       <c r="N283" s="5"/>
       <c r="O283" s="5"/>
       <c r="P283" s="5"/>
-    </row>
-    <row r="284" spans="1:16">
+      <c r="Q283" s="5"/>
+    </row>
+    <row r="284" spans="1:17">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -6763,8 +7060,9 @@
       <c r="N284" s="5"/>
       <c r="O284" s="5"/>
       <c r="P284" s="5"/>
-    </row>
-    <row r="285" spans="1:16">
+      <c r="Q284" s="5"/>
+    </row>
+    <row r="285" spans="1:17">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -6781,8 +7079,9 @@
       <c r="N285" s="5"/>
       <c r="O285" s="5"/>
       <c r="P285" s="5"/>
-    </row>
-    <row r="286" spans="1:16">
+      <c r="Q285" s="5"/>
+    </row>
+    <row r="286" spans="1:17">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -6799,8 +7098,9 @@
       <c r="N286" s="5"/>
       <c r="O286" s="5"/>
       <c r="P286" s="5"/>
-    </row>
-    <row r="287" spans="1:16">
+      <c r="Q286" s="5"/>
+    </row>
+    <row r="287" spans="1:17">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -6817,8 +7117,9 @@
       <c r="N287" s="5"/>
       <c r="O287" s="5"/>
       <c r="P287" s="5"/>
-    </row>
-    <row r="288" spans="1:16">
+      <c r="Q287" s="5"/>
+    </row>
+    <row r="288" spans="1:17">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -6835,8 +7136,9 @@
       <c r="N288" s="5"/>
       <c r="O288" s="5"/>
       <c r="P288" s="5"/>
-    </row>
-    <row r="289" spans="1:16">
+      <c r="Q288" s="5"/>
+    </row>
+    <row r="289" spans="1:17">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -6853,8 +7155,9 @@
       <c r="N289" s="5"/>
       <c r="O289" s="5"/>
       <c r="P289" s="5"/>
-    </row>
-    <row r="290" spans="1:16">
+      <c r="Q289" s="5"/>
+    </row>
+    <row r="290" spans="1:17">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -6871,8 +7174,9 @@
       <c r="N290" s="5"/>
       <c r="O290" s="5"/>
       <c r="P290" s="5"/>
-    </row>
-    <row r="291" spans="1:16">
+      <c r="Q290" s="5"/>
+    </row>
+    <row r="291" spans="1:17">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -6889,8 +7193,9 @@
       <c r="N291" s="5"/>
       <c r="O291" s="5"/>
       <c r="P291" s="5"/>
-    </row>
-    <row r="292" spans="1:16">
+      <c r="Q291" s="5"/>
+    </row>
+    <row r="292" spans="1:17">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -6907,8 +7212,9 @@
       <c r="N292" s="5"/>
       <c r="O292" s="5"/>
       <c r="P292" s="5"/>
-    </row>
-    <row r="293" spans="1:16">
+      <c r="Q292" s="5"/>
+    </row>
+    <row r="293" spans="1:17">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -6925,8 +7231,9 @@
       <c r="N293" s="5"/>
       <c r="O293" s="5"/>
       <c r="P293" s="5"/>
-    </row>
-    <row r="294" spans="1:16">
+      <c r="Q293" s="5"/>
+    </row>
+    <row r="294" spans="1:17">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -6943,8 +7250,9 @@
       <c r="N294" s="5"/>
       <c r="O294" s="5"/>
       <c r="P294" s="5"/>
-    </row>
-    <row r="295" spans="1:16">
+      <c r="Q294" s="5"/>
+    </row>
+    <row r="295" spans="1:17">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -6961,8 +7269,9 @@
       <c r="N295" s="5"/>
       <c r="O295" s="5"/>
       <c r="P295" s="5"/>
-    </row>
-    <row r="296" spans="1:16">
+      <c r="Q295" s="5"/>
+    </row>
+    <row r="296" spans="1:17">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -6979,8 +7288,9 @@
       <c r="N296" s="5"/>
       <c r="O296" s="5"/>
       <c r="P296" s="5"/>
-    </row>
-    <row r="297" spans="1:16">
+      <c r="Q296" s="5"/>
+    </row>
+    <row r="297" spans="1:17">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -6997,8 +7307,9 @@
       <c r="N297" s="5"/>
       <c r="O297" s="5"/>
       <c r="P297" s="5"/>
-    </row>
-    <row r="298" spans="1:16">
+      <c r="Q297" s="5"/>
+    </row>
+    <row r="298" spans="1:17">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -7015,8 +7326,9 @@
       <c r="N298" s="5"/>
       <c r="O298" s="5"/>
       <c r="P298" s="5"/>
-    </row>
-    <row r="299" spans="1:16">
+      <c r="Q298" s="5"/>
+    </row>
+    <row r="299" spans="1:17">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -7033,8 +7345,9 @@
       <c r="N299" s="5"/>
       <c r="O299" s="5"/>
       <c r="P299" s="5"/>
-    </row>
-    <row r="300" spans="1:16">
+      <c r="Q299" s="5"/>
+    </row>
+    <row r="300" spans="1:17">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -7051,8 +7364,9 @@
       <c r="N300" s="5"/>
       <c r="O300" s="5"/>
       <c r="P300" s="5"/>
-    </row>
-    <row r="301" spans="1:16">
+      <c r="Q300" s="5"/>
+    </row>
+    <row r="301" spans="1:17">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -7069,8 +7383,9 @@
       <c r="N301" s="5"/>
       <c r="O301" s="5"/>
       <c r="P301" s="5"/>
-    </row>
-    <row r="302" spans="1:16">
+      <c r="Q301" s="5"/>
+    </row>
+    <row r="302" spans="1:17">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -7087,8 +7402,9 @@
       <c r="N302" s="5"/>
       <c r="O302" s="5"/>
       <c r="P302" s="5"/>
-    </row>
-    <row r="303" spans="1:16">
+      <c r="Q302" s="5"/>
+    </row>
+    <row r="303" spans="1:17">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -7105,8 +7421,9 @@
       <c r="N303" s="5"/>
       <c r="O303" s="5"/>
       <c r="P303" s="5"/>
-    </row>
-    <row r="304" spans="1:16">
+      <c r="Q303" s="5"/>
+    </row>
+    <row r="304" spans="1:17">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -7123,8 +7440,9 @@
       <c r="N304" s="5"/>
       <c r="O304" s="5"/>
       <c r="P304" s="5"/>
-    </row>
-    <row r="305" spans="1:16">
+      <c r="Q304" s="5"/>
+    </row>
+    <row r="305" spans="1:17">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -7141,8 +7459,9 @@
       <c r="N305" s="5"/>
       <c r="O305" s="5"/>
       <c r="P305" s="5"/>
-    </row>
-    <row r="306" spans="1:16">
+      <c r="Q305" s="5"/>
+    </row>
+    <row r="306" spans="1:17">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -7159,8 +7478,9 @@
       <c r="N306" s="5"/>
       <c r="O306" s="5"/>
       <c r="P306" s="5"/>
-    </row>
-    <row r="307" spans="1:16">
+      <c r="Q306" s="5"/>
+    </row>
+    <row r="307" spans="1:17">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -7177,8 +7497,9 @@
       <c r="N307" s="5"/>
       <c r="O307" s="5"/>
       <c r="P307" s="5"/>
-    </row>
-    <row r="308" spans="1:16">
+      <c r="Q307" s="5"/>
+    </row>
+    <row r="308" spans="1:17">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -7195,8 +7516,9 @@
       <c r="N308" s="5"/>
       <c r="O308" s="5"/>
       <c r="P308" s="5"/>
-    </row>
-    <row r="309" spans="1:16">
+      <c r="Q308" s="5"/>
+    </row>
+    <row r="309" spans="1:17">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -7213,8 +7535,9 @@
       <c r="N309" s="5"/>
       <c r="O309" s="5"/>
       <c r="P309" s="5"/>
-    </row>
-    <row r="310" spans="1:16">
+      <c r="Q309" s="5"/>
+    </row>
+    <row r="310" spans="1:17">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -7231,8 +7554,9 @@
       <c r="N310" s="5"/>
       <c r="O310" s="5"/>
       <c r="P310" s="5"/>
-    </row>
-    <row r="311" spans="1:16">
+      <c r="Q310" s="5"/>
+    </row>
+    <row r="311" spans="1:17">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -7249,8 +7573,9 @@
       <c r="N311" s="5"/>
       <c r="O311" s="5"/>
       <c r="P311" s="5"/>
-    </row>
-    <row r="312" spans="1:16">
+      <c r="Q311" s="5"/>
+    </row>
+    <row r="312" spans="1:17">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -7267,8 +7592,9 @@
       <c r="N312" s="5"/>
       <c r="O312" s="5"/>
       <c r="P312" s="5"/>
-    </row>
-    <row r="313" spans="1:16">
+      <c r="Q312" s="5"/>
+    </row>
+    <row r="313" spans="1:17">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -7285,8 +7611,9 @@
       <c r="N313" s="5"/>
       <c r="O313" s="5"/>
       <c r="P313" s="5"/>
-    </row>
-    <row r="314" spans="1:16">
+      <c r="Q313" s="5"/>
+    </row>
+    <row r="314" spans="1:17">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -7303,8 +7630,9 @@
       <c r="N314" s="5"/>
       <c r="O314" s="5"/>
       <c r="P314" s="5"/>
-    </row>
-    <row r="315" spans="1:16">
+      <c r="Q314" s="5"/>
+    </row>
+    <row r="315" spans="1:17">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -7321,8 +7649,9 @@
       <c r="N315" s="5"/>
       <c r="O315" s="5"/>
       <c r="P315" s="5"/>
-    </row>
-    <row r="316" spans="1:16">
+      <c r="Q315" s="5"/>
+    </row>
+    <row r="316" spans="1:17">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -7339,8 +7668,9 @@
       <c r="N316" s="5"/>
       <c r="O316" s="5"/>
       <c r="P316" s="5"/>
-    </row>
-    <row r="317" spans="1:16">
+      <c r="Q316" s="5"/>
+    </row>
+    <row r="317" spans="1:17">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -7357,8 +7687,9 @@
       <c r="N317" s="5"/>
       <c r="O317" s="5"/>
       <c r="P317" s="5"/>
-    </row>
-    <row r="318" spans="1:16">
+      <c r="Q317" s="5"/>
+    </row>
+    <row r="318" spans="1:17">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -7375,8 +7706,9 @@
       <c r="N318" s="5"/>
       <c r="O318" s="5"/>
       <c r="P318" s="5"/>
-    </row>
-    <row r="319" spans="1:16">
+      <c r="Q318" s="5"/>
+    </row>
+    <row r="319" spans="1:17">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -7393,8 +7725,9 @@
       <c r="N319" s="5"/>
       <c r="O319" s="5"/>
       <c r="P319" s="5"/>
-    </row>
-    <row r="320" spans="1:16">
+      <c r="Q319" s="5"/>
+    </row>
+    <row r="320" spans="1:17">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -7411,8 +7744,9 @@
       <c r="N320" s="5"/>
       <c r="O320" s="5"/>
       <c r="P320" s="5"/>
-    </row>
-    <row r="321" spans="1:16">
+      <c r="Q320" s="5"/>
+    </row>
+    <row r="321" spans="1:17">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -7429,8 +7763,9 @@
       <c r="N321" s="5"/>
       <c r="O321" s="5"/>
       <c r="P321" s="5"/>
-    </row>
-    <row r="322" spans="1:16">
+      <c r="Q321" s="5"/>
+    </row>
+    <row r="322" spans="1:17">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -7447,8 +7782,9 @@
       <c r="N322" s="5"/>
       <c r="O322" s="5"/>
       <c r="P322" s="5"/>
-    </row>
-    <row r="323" spans="1:16">
+      <c r="Q322" s="5"/>
+    </row>
+    <row r="323" spans="1:17">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -7465,8 +7801,9 @@
       <c r="N323" s="5"/>
       <c r="O323" s="5"/>
       <c r="P323" s="5"/>
-    </row>
-    <row r="324" spans="1:16">
+      <c r="Q323" s="5"/>
+    </row>
+    <row r="324" spans="1:17">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -7483,8 +7820,9 @@
       <c r="N324" s="5"/>
       <c r="O324" s="5"/>
       <c r="P324" s="5"/>
-    </row>
-    <row r="325" spans="1:16">
+      <c r="Q324" s="5"/>
+    </row>
+    <row r="325" spans="1:17">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -7501,8 +7839,9 @@
       <c r="N325" s="5"/>
       <c r="O325" s="5"/>
       <c r="P325" s="5"/>
-    </row>
-    <row r="326" spans="1:16">
+      <c r="Q325" s="5"/>
+    </row>
+    <row r="326" spans="1:17">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -7519,8 +7858,9 @@
       <c r="N326" s="5"/>
       <c r="O326" s="5"/>
       <c r="P326" s="5"/>
-    </row>
-    <row r="327" spans="1:16">
+      <c r="Q326" s="5"/>
+    </row>
+    <row r="327" spans="1:17">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -7537,8 +7877,9 @@
       <c r="N327" s="5"/>
       <c r="O327" s="5"/>
       <c r="P327" s="5"/>
-    </row>
-    <row r="328" spans="1:16">
+      <c r="Q327" s="5"/>
+    </row>
+    <row r="328" spans="1:17">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -7555,8 +7896,9 @@
       <c r="N328" s="5"/>
       <c r="O328" s="5"/>
       <c r="P328" s="5"/>
-    </row>
-    <row r="329" spans="1:16">
+      <c r="Q328" s="5"/>
+    </row>
+    <row r="329" spans="1:17">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -7573,8 +7915,9 @@
       <c r="N329" s="5"/>
       <c r="O329" s="5"/>
       <c r="P329" s="5"/>
-    </row>
-    <row r="330" spans="1:16">
+      <c r="Q329" s="5"/>
+    </row>
+    <row r="330" spans="1:17">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -7591,8 +7934,9 @@
       <c r="N330" s="5"/>
       <c r="O330" s="5"/>
       <c r="P330" s="5"/>
-    </row>
-    <row r="331" spans="1:16">
+      <c r="Q330" s="5"/>
+    </row>
+    <row r="331" spans="1:17">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -7609,8 +7953,9 @@
       <c r="N331" s="5"/>
       <c r="O331" s="5"/>
       <c r="P331" s="5"/>
-    </row>
-    <row r="332" spans="1:16">
+      <c r="Q331" s="5"/>
+    </row>
+    <row r="332" spans="1:17">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -7627,8 +7972,9 @@
       <c r="N332" s="5"/>
       <c r="O332" s="5"/>
       <c r="P332" s="5"/>
-    </row>
-    <row r="333" spans="1:16">
+      <c r="Q332" s="5"/>
+    </row>
+    <row r="333" spans="1:17">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -7645,8 +7991,9 @@
       <c r="N333" s="5"/>
       <c r="O333" s="5"/>
       <c r="P333" s="5"/>
-    </row>
-    <row r="334" spans="1:16">
+      <c r="Q333" s="5"/>
+    </row>
+    <row r="334" spans="1:17">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -7663,8 +8010,9 @@
       <c r="N334" s="5"/>
       <c r="O334" s="5"/>
       <c r="P334" s="5"/>
-    </row>
-    <row r="335" spans="1:16">
+      <c r="Q334" s="5"/>
+    </row>
+    <row r="335" spans="1:17">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -7681,8 +8029,9 @@
       <c r="N335" s="5"/>
       <c r="O335" s="5"/>
       <c r="P335" s="5"/>
-    </row>
-    <row r="336" spans="1:16">
+      <c r="Q335" s="5"/>
+    </row>
+    <row r="336" spans="1:17">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -7699,8 +8048,9 @@
       <c r="N336" s="5"/>
       <c r="O336" s="5"/>
       <c r="P336" s="5"/>
-    </row>
-    <row r="337" spans="1:16">
+      <c r="Q336" s="5"/>
+    </row>
+    <row r="337" spans="1:17">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -7717,8 +8067,9 @@
       <c r="N337" s="5"/>
       <c r="O337" s="5"/>
       <c r="P337" s="5"/>
-    </row>
-    <row r="338" spans="1:16">
+      <c r="Q337" s="5"/>
+    </row>
+    <row r="338" spans="1:17">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -7735,8 +8086,9 @@
       <c r="N338" s="5"/>
       <c r="O338" s="5"/>
       <c r="P338" s="5"/>
-    </row>
-    <row r="339" spans="1:16">
+      <c r="Q338" s="5"/>
+    </row>
+    <row r="339" spans="1:17">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -7753,8 +8105,9 @@
       <c r="N339" s="5"/>
       <c r="O339" s="5"/>
       <c r="P339" s="5"/>
-    </row>
-    <row r="340" spans="1:16">
+      <c r="Q339" s="5"/>
+    </row>
+    <row r="340" spans="1:17">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -7771,8 +8124,9 @@
       <c r="N340" s="5"/>
       <c r="O340" s="5"/>
       <c r="P340" s="5"/>
-    </row>
-    <row r="341" spans="1:16">
+      <c r="Q340" s="5"/>
+    </row>
+    <row r="341" spans="1:17">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -7789,8 +8143,9 @@
       <c r="N341" s="5"/>
       <c r="O341" s="5"/>
       <c r="P341" s="5"/>
-    </row>
-    <row r="342" spans="1:16">
+      <c r="Q341" s="5"/>
+    </row>
+    <row r="342" spans="1:17">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -7807,8 +8162,9 @@
       <c r="N342" s="5"/>
       <c r="O342" s="5"/>
       <c r="P342" s="5"/>
-    </row>
-    <row r="343" spans="1:16">
+      <c r="Q342" s="5"/>
+    </row>
+    <row r="343" spans="1:17">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -7825,8 +8181,9 @@
       <c r="N343" s="5"/>
       <c r="O343" s="5"/>
       <c r="P343" s="5"/>
-    </row>
-    <row r="344" spans="1:16">
+      <c r="Q343" s="5"/>
+    </row>
+    <row r="344" spans="1:17">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -7843,8 +8200,9 @@
       <c r="N344" s="5"/>
       <c r="O344" s="5"/>
       <c r="P344" s="5"/>
-    </row>
-    <row r="345" spans="1:16">
+      <c r="Q344" s="5"/>
+    </row>
+    <row r="345" spans="1:17">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -7861,8 +8219,9 @@
       <c r="N345" s="5"/>
       <c r="O345" s="5"/>
       <c r="P345" s="5"/>
-    </row>
-    <row r="346" spans="1:16">
+      <c r="Q345" s="5"/>
+    </row>
+    <row r="346" spans="1:17">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -7879,8 +8238,9 @@
       <c r="N346" s="5"/>
       <c r="O346" s="5"/>
       <c r="P346" s="5"/>
-    </row>
-    <row r="347" spans="1:16">
+      <c r="Q346" s="5"/>
+    </row>
+    <row r="347" spans="1:17">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -7897,8 +8257,9 @@
       <c r="N347" s="5"/>
       <c r="O347" s="5"/>
       <c r="P347" s="5"/>
-    </row>
-    <row r="348" spans="1:16">
+      <c r="Q347" s="5"/>
+    </row>
+    <row r="348" spans="1:17">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -7915,8 +8276,9 @@
       <c r="N348" s="5"/>
       <c r="O348" s="5"/>
       <c r="P348" s="5"/>
-    </row>
-    <row r="349" spans="1:16">
+      <c r="Q348" s="5"/>
+    </row>
+    <row r="349" spans="1:17">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -7933,8 +8295,9 @@
       <c r="N349" s="5"/>
       <c r="O349" s="5"/>
       <c r="P349" s="5"/>
-    </row>
-    <row r="350" spans="1:16">
+      <c r="Q349" s="5"/>
+    </row>
+    <row r="350" spans="1:17">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -7951,8 +8314,9 @@
       <c r="N350" s="5"/>
       <c r="O350" s="5"/>
       <c r="P350" s="5"/>
-    </row>
-    <row r="351" spans="1:16">
+      <c r="Q350" s="5"/>
+    </row>
+    <row r="351" spans="1:17">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -7969,8 +8333,9 @@
       <c r="N351" s="5"/>
       <c r="O351" s="5"/>
       <c r="P351" s="5"/>
-    </row>
-    <row r="352" spans="1:16">
+      <c r="Q351" s="5"/>
+    </row>
+    <row r="352" spans="1:17">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -7987,8 +8352,9 @@
       <c r="N352" s="5"/>
       <c r="O352" s="5"/>
       <c r="P352" s="5"/>
-    </row>
-    <row r="353" spans="1:16">
+      <c r="Q352" s="5"/>
+    </row>
+    <row r="353" spans="1:17">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -8005,8 +8371,9 @@
       <c r="N353" s="5"/>
       <c r="O353" s="5"/>
       <c r="P353" s="5"/>
-    </row>
-    <row r="354" spans="1:16">
+      <c r="Q353" s="5"/>
+    </row>
+    <row r="354" spans="1:17">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -8023,8 +8390,9 @@
       <c r="N354" s="5"/>
       <c r="O354" s="5"/>
       <c r="P354" s="5"/>
-    </row>
-    <row r="355" spans="1:16">
+      <c r="Q354" s="5"/>
+    </row>
+    <row r="355" spans="1:17">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -8041,8 +8409,9 @@
       <c r="N355" s="5"/>
       <c r="O355" s="5"/>
       <c r="P355" s="5"/>
-    </row>
-    <row r="356" spans="1:16">
+      <c r="Q355" s="5"/>
+    </row>
+    <row r="356" spans="1:17">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -8059,8 +8428,9 @@
       <c r="N356" s="5"/>
       <c r="O356" s="5"/>
       <c r="P356" s="5"/>
-    </row>
-    <row r="357" spans="1:16">
+      <c r="Q356" s="5"/>
+    </row>
+    <row r="357" spans="1:17">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -8077,8 +8447,9 @@
       <c r="N357" s="5"/>
       <c r="O357" s="5"/>
       <c r="P357" s="5"/>
-    </row>
-    <row r="358" spans="1:16">
+      <c r="Q357" s="5"/>
+    </row>
+    <row r="358" spans="1:17">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -8095,8 +8466,9 @@
       <c r="N358" s="5"/>
       <c r="O358" s="5"/>
       <c r="P358" s="5"/>
-    </row>
-    <row r="359" spans="1:16">
+      <c r="Q358" s="5"/>
+    </row>
+    <row r="359" spans="1:17">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -8113,8 +8485,9 @@
       <c r="N359" s="5"/>
       <c r="O359" s="5"/>
       <c r="P359" s="5"/>
-    </row>
-    <row r="360" spans="1:16">
+      <c r="Q359" s="5"/>
+    </row>
+    <row r="360" spans="1:17">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -8131,8 +8504,9 @@
       <c r="N360" s="5"/>
       <c r="O360" s="5"/>
       <c r="P360" s="5"/>
-    </row>
-    <row r="361" spans="1:16">
+      <c r="Q360" s="5"/>
+    </row>
+    <row r="361" spans="1:17">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -8149,8 +8523,9 @@
       <c r="N361" s="5"/>
       <c r="O361" s="5"/>
       <c r="P361" s="5"/>
-    </row>
-    <row r="362" spans="1:16">
+      <c r="Q361" s="5"/>
+    </row>
+    <row r="362" spans="1:17">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -8167,8 +8542,9 @@
       <c r="N362" s="5"/>
       <c r="O362" s="5"/>
       <c r="P362" s="5"/>
-    </row>
-    <row r="363" spans="1:16">
+      <c r="Q362" s="5"/>
+    </row>
+    <row r="363" spans="1:17">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -8185,8 +8561,9 @@
       <c r="N363" s="5"/>
       <c r="O363" s="5"/>
       <c r="P363" s="5"/>
-    </row>
-    <row r="364" spans="1:16">
+      <c r="Q363" s="5"/>
+    </row>
+    <row r="364" spans="1:17">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -8203,8 +8580,9 @@
       <c r="N364" s="5"/>
       <c r="O364" s="5"/>
       <c r="P364" s="5"/>
-    </row>
-    <row r="365" spans="1:16">
+      <c r="Q364" s="5"/>
+    </row>
+    <row r="365" spans="1:17">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -8221,8 +8599,9 @@
       <c r="N365" s="5"/>
       <c r="O365" s="5"/>
       <c r="P365" s="5"/>
-    </row>
-    <row r="366" spans="1:16">
+      <c r="Q365" s="5"/>
+    </row>
+    <row r="366" spans="1:17">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -8239,8 +8618,9 @@
       <c r="N366" s="5"/>
       <c r="O366" s="5"/>
       <c r="P366" s="5"/>
-    </row>
-    <row r="367" spans="1:16">
+      <c r="Q366" s="5"/>
+    </row>
+    <row r="367" spans="1:17">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -8257,8 +8637,9 @@
       <c r="N367" s="5"/>
       <c r="O367" s="5"/>
       <c r="P367" s="5"/>
-    </row>
-    <row r="368" spans="1:16">
+      <c r="Q367" s="5"/>
+    </row>
+    <row r="368" spans="1:17">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -8275,8 +8656,9 @@
       <c r="N368" s="5"/>
       <c r="O368" s="5"/>
       <c r="P368" s="5"/>
-    </row>
-    <row r="369" spans="1:16">
+      <c r="Q368" s="5"/>
+    </row>
+    <row r="369" spans="1:17">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -8293,8 +8675,9 @@
       <c r="N369" s="5"/>
       <c r="O369" s="5"/>
       <c r="P369" s="5"/>
-    </row>
-    <row r="370" spans="1:16">
+      <c r="Q369" s="5"/>
+    </row>
+    <row r="370" spans="1:17">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -8311,8 +8694,9 @@
       <c r="N370" s="5"/>
       <c r="O370" s="5"/>
       <c r="P370" s="5"/>
-    </row>
-    <row r="371" spans="1:16">
+      <c r="Q370" s="5"/>
+    </row>
+    <row r="371" spans="1:17">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -8329,8 +8713,9 @@
       <c r="N371" s="5"/>
       <c r="O371" s="5"/>
       <c r="P371" s="5"/>
-    </row>
-    <row r="372" spans="1:16">
+      <c r="Q371" s="5"/>
+    </row>
+    <row r="372" spans="1:17">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -8347,8 +8732,9 @@
       <c r="N372" s="5"/>
       <c r="O372" s="5"/>
       <c r="P372" s="5"/>
-    </row>
-    <row r="373" spans="1:16">
+      <c r="Q372" s="5"/>
+    </row>
+    <row r="373" spans="1:17">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -8365,8 +8751,9 @@
       <c r="N373" s="5"/>
       <c r="O373" s="5"/>
       <c r="P373" s="5"/>
-    </row>
-    <row r="374" spans="1:16">
+      <c r="Q373" s="5"/>
+    </row>
+    <row r="374" spans="1:17">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -8383,8 +8770,9 @@
       <c r="N374" s="5"/>
       <c r="O374" s="5"/>
       <c r="P374" s="5"/>
-    </row>
-    <row r="375" spans="1:16">
+      <c r="Q374" s="5"/>
+    </row>
+    <row r="375" spans="1:17">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -8401,8 +8789,9 @@
       <c r="N375" s="5"/>
       <c r="O375" s="5"/>
       <c r="P375" s="5"/>
-    </row>
-    <row r="376" spans="1:16">
+      <c r="Q375" s="5"/>
+    </row>
+    <row r="376" spans="1:17">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -8419,8 +8808,9 @@
       <c r="N376" s="5"/>
       <c r="O376" s="5"/>
       <c r="P376" s="5"/>
-    </row>
-    <row r="377" spans="1:16">
+      <c r="Q376" s="5"/>
+    </row>
+    <row r="377" spans="1:17">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -8437,8 +8827,9 @@
       <c r="N377" s="5"/>
       <c r="O377" s="5"/>
       <c r="P377" s="5"/>
-    </row>
-    <row r="378" spans="1:16">
+      <c r="Q377" s="5"/>
+    </row>
+    <row r="378" spans="1:17">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -8455,8 +8846,9 @@
       <c r="N378" s="5"/>
       <c r="O378" s="5"/>
       <c r="P378" s="5"/>
-    </row>
-    <row r="379" spans="1:16">
+      <c r="Q378" s="5"/>
+    </row>
+    <row r="379" spans="1:17">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -8473,8 +8865,9 @@
       <c r="N379" s="5"/>
       <c r="O379" s="5"/>
       <c r="P379" s="5"/>
-    </row>
-    <row r="380" spans="1:16">
+      <c r="Q379" s="5"/>
+    </row>
+    <row r="380" spans="1:17">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -8491,8 +8884,9 @@
       <c r="N380" s="5"/>
       <c r="O380" s="5"/>
       <c r="P380" s="5"/>
-    </row>
-    <row r="381" spans="1:16">
+      <c r="Q380" s="5"/>
+    </row>
+    <row r="381" spans="1:17">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -8509,8 +8903,9 @@
       <c r="N381" s="5"/>
       <c r="O381" s="5"/>
       <c r="P381" s="5"/>
-    </row>
-    <row r="382" spans="1:16">
+      <c r="Q381" s="5"/>
+    </row>
+    <row r="382" spans="1:17">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -8527,8 +8922,9 @@
       <c r="N382" s="5"/>
       <c r="O382" s="5"/>
       <c r="P382" s="5"/>
-    </row>
-    <row r="383" spans="1:16">
+      <c r="Q382" s="5"/>
+    </row>
+    <row r="383" spans="1:17">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -8545,8 +8941,9 @@
       <c r="N383" s="5"/>
       <c r="O383" s="5"/>
       <c r="P383" s="5"/>
-    </row>
-    <row r="384" spans="1:16">
+      <c r="Q383" s="5"/>
+    </row>
+    <row r="384" spans="1:17">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -8563,8 +8960,9 @@
       <c r="N384" s="5"/>
       <c r="O384" s="5"/>
       <c r="P384" s="5"/>
-    </row>
-    <row r="385" spans="1:16">
+      <c r="Q384" s="5"/>
+    </row>
+    <row r="385" spans="1:17">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -8581,8 +8979,9 @@
       <c r="N385" s="5"/>
       <c r="O385" s="5"/>
       <c r="P385" s="5"/>
-    </row>
-    <row r="386" spans="1:16">
+      <c r="Q385" s="5"/>
+    </row>
+    <row r="386" spans="1:17">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -8599,8 +8998,9 @@
       <c r="N386" s="5"/>
       <c r="O386" s="5"/>
       <c r="P386" s="5"/>
-    </row>
-    <row r="387" spans="1:16">
+      <c r="Q386" s="5"/>
+    </row>
+    <row r="387" spans="1:17">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -8617,8 +9017,9 @@
       <c r="N387" s="5"/>
       <c r="O387" s="5"/>
       <c r="P387" s="5"/>
-    </row>
-    <row r="388" spans="1:16">
+      <c r="Q387" s="5"/>
+    </row>
+    <row r="388" spans="1:17">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -8635,8 +9036,9 @@
       <c r="N388" s="5"/>
       <c r="O388" s="5"/>
       <c r="P388" s="5"/>
-    </row>
-    <row r="389" spans="1:16">
+      <c r="Q388" s="5"/>
+    </row>
+    <row r="389" spans="1:17">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -8653,8 +9055,9 @@
       <c r="N389" s="5"/>
       <c r="O389" s="5"/>
       <c r="P389" s="5"/>
-    </row>
-    <row r="390" spans="1:16">
+      <c r="Q389" s="5"/>
+    </row>
+    <row r="390" spans="1:17">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -8671,8 +9074,9 @@
       <c r="N390" s="5"/>
       <c r="O390" s="5"/>
       <c r="P390" s="5"/>
-    </row>
-    <row r="391" spans="1:16">
+      <c r="Q390" s="5"/>
+    </row>
+    <row r="391" spans="1:17">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -8689,8 +9093,9 @@
       <c r="N391" s="5"/>
       <c r="O391" s="5"/>
       <c r="P391" s="5"/>
-    </row>
-    <row r="392" spans="1:16">
+      <c r="Q391" s="5"/>
+    </row>
+    <row r="392" spans="1:17">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -8707,8 +9112,9 @@
       <c r="N392" s="5"/>
       <c r="O392" s="5"/>
       <c r="P392" s="5"/>
-    </row>
-    <row r="393" spans="1:16">
+      <c r="Q392" s="5"/>
+    </row>
+    <row r="393" spans="1:17">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -8725,8 +9131,9 @@
       <c r="N393" s="5"/>
       <c r="O393" s="5"/>
       <c r="P393" s="5"/>
-    </row>
-    <row r="394" spans="1:16">
+      <c r="Q393" s="5"/>
+    </row>
+    <row r="394" spans="1:17">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -8743,8 +9150,9 @@
       <c r="N394" s="5"/>
       <c r="O394" s="5"/>
       <c r="P394" s="5"/>
-    </row>
-    <row r="395" spans="1:16">
+      <c r="Q394" s="5"/>
+    </row>
+    <row r="395" spans="1:17">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -8761,8 +9169,9 @@
       <c r="N395" s="5"/>
       <c r="O395" s="5"/>
       <c r="P395" s="5"/>
-    </row>
-    <row r="396" spans="1:16">
+      <c r="Q395" s="5"/>
+    </row>
+    <row r="396" spans="1:17">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -8779,8 +9188,9 @@
       <c r="N396" s="5"/>
       <c r="O396" s="5"/>
       <c r="P396" s="5"/>
-    </row>
-    <row r="397" spans="1:16">
+      <c r="Q396" s="5"/>
+    </row>
+    <row r="397" spans="1:17">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -8797,8 +9207,9 @@
       <c r="N397" s="5"/>
       <c r="O397" s="5"/>
       <c r="P397" s="5"/>
-    </row>
-    <row r="398" spans="1:16">
+      <c r="Q397" s="5"/>
+    </row>
+    <row r="398" spans="1:17">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -8815,8 +9226,9 @@
       <c r="N398" s="5"/>
       <c r="O398" s="5"/>
       <c r="P398" s="5"/>
-    </row>
-    <row r="399" spans="1:16">
+      <c r="Q398" s="5"/>
+    </row>
+    <row r="399" spans="1:17">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -8833,8 +9245,9 @@
       <c r="N399" s="5"/>
       <c r="O399" s="5"/>
       <c r="P399" s="5"/>
-    </row>
-    <row r="400" spans="1:16">
+      <c r="Q399" s="5"/>
+    </row>
+    <row r="400" spans="1:17">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -8851,8 +9264,9 @@
       <c r="N400" s="5"/>
       <c r="O400" s="5"/>
       <c r="P400" s="5"/>
-    </row>
-    <row r="401" spans="1:16">
+      <c r="Q400" s="5"/>
+    </row>
+    <row r="401" spans="1:17">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -8869,8 +9283,9 @@
       <c r="N401" s="5"/>
       <c r="O401" s="5"/>
       <c r="P401" s="5"/>
-    </row>
-    <row r="402" spans="1:16">
+      <c r="Q401" s="5"/>
+    </row>
+    <row r="402" spans="1:17">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -8887,8 +9302,9 @@
       <c r="N402" s="5"/>
       <c r="O402" s="5"/>
       <c r="P402" s="5"/>
-    </row>
-    <row r="403" spans="1:16">
+      <c r="Q402" s="5"/>
+    </row>
+    <row r="403" spans="1:17">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -8905,8 +9321,9 @@
       <c r="N403" s="5"/>
       <c r="O403" s="5"/>
       <c r="P403" s="5"/>
-    </row>
-    <row r="404" spans="1:16">
+      <c r="Q403" s="5"/>
+    </row>
+    <row r="404" spans="1:17">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -8923,8 +9340,9 @@
       <c r="N404" s="5"/>
       <c r="O404" s="5"/>
       <c r="P404" s="5"/>
-    </row>
-    <row r="405" spans="1:16">
+      <c r="Q404" s="5"/>
+    </row>
+    <row r="405" spans="1:17">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -8941,8 +9359,9 @@
       <c r="N405" s="5"/>
       <c r="O405" s="5"/>
       <c r="P405" s="5"/>
-    </row>
-    <row r="406" spans="1:16">
+      <c r="Q405" s="5"/>
+    </row>
+    <row r="406" spans="1:17">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -8959,8 +9378,9 @@
       <c r="N406" s="5"/>
       <c r="O406" s="5"/>
       <c r="P406" s="5"/>
-    </row>
-    <row r="407" spans="1:16">
+      <c r="Q406" s="5"/>
+    </row>
+    <row r="407" spans="1:17">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -8977,8 +9397,9 @@
       <c r="N407" s="5"/>
       <c r="O407" s="5"/>
       <c r="P407" s="5"/>
-    </row>
-    <row r="408" spans="1:16">
+      <c r="Q407" s="5"/>
+    </row>
+    <row r="408" spans="1:17">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -8995,8 +9416,9 @@
       <c r="N408" s="5"/>
       <c r="O408" s="5"/>
       <c r="P408" s="5"/>
-    </row>
-    <row r="409" spans="1:16">
+      <c r="Q408" s="5"/>
+    </row>
+    <row r="409" spans="1:17">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9013,8 +9435,9 @@
       <c r="N409" s="5"/>
       <c r="O409" s="5"/>
       <c r="P409" s="5"/>
-    </row>
-    <row r="410" spans="1:16">
+      <c r="Q409" s="5"/>
+    </row>
+    <row r="410" spans="1:17">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9031,8 +9454,9 @@
       <c r="N410" s="5"/>
       <c r="O410" s="5"/>
       <c r="P410" s="5"/>
-    </row>
-    <row r="411" spans="1:16">
+      <c r="Q410" s="5"/>
+    </row>
+    <row r="411" spans="1:17">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9049,8 +9473,9 @@
       <c r="N411" s="5"/>
       <c r="O411" s="5"/>
       <c r="P411" s="5"/>
-    </row>
-    <row r="412" spans="1:16">
+      <c r="Q411" s="5"/>
+    </row>
+    <row r="412" spans="1:17">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -9067,8 +9492,9 @@
       <c r="N412" s="5"/>
       <c r="O412" s="5"/>
       <c r="P412" s="5"/>
-    </row>
-    <row r="413" spans="1:16">
+      <c r="Q412" s="5"/>
+    </row>
+    <row r="413" spans="1:17">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -9085,8 +9511,9 @@
       <c r="N413" s="5"/>
       <c r="O413" s="5"/>
       <c r="P413" s="5"/>
-    </row>
-    <row r="414" spans="1:16">
+      <c r="Q413" s="5"/>
+    </row>
+    <row r="414" spans="1:17">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -9103,8 +9530,9 @@
       <c r="N414" s="5"/>
       <c r="O414" s="5"/>
       <c r="P414" s="5"/>
-    </row>
-    <row r="415" spans="1:16">
+      <c r="Q414" s="5"/>
+    </row>
+    <row r="415" spans="1:17">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -9121,8 +9549,9 @@
       <c r="N415" s="5"/>
       <c r="O415" s="5"/>
       <c r="P415" s="5"/>
-    </row>
-    <row r="416" spans="1:16">
+      <c r="Q415" s="5"/>
+    </row>
+    <row r="416" spans="1:17">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -9139,8 +9568,9 @@
       <c r="N416" s="5"/>
       <c r="O416" s="5"/>
       <c r="P416" s="5"/>
-    </row>
-    <row r="417" spans="1:16">
+      <c r="Q416" s="5"/>
+    </row>
+    <row r="417" spans="1:17">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -9157,8 +9587,9 @@
       <c r="N417" s="5"/>
       <c r="O417" s="5"/>
       <c r="P417" s="5"/>
-    </row>
-    <row r="418" spans="1:16">
+      <c r="Q417" s="5"/>
+    </row>
+    <row r="418" spans="1:17">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -9175,8 +9606,9 @@
       <c r="N418" s="5"/>
       <c r="O418" s="5"/>
       <c r="P418" s="5"/>
-    </row>
-    <row r="419" spans="1:16">
+      <c r="Q418" s="5"/>
+    </row>
+    <row r="419" spans="1:17">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -9193,8 +9625,9 @@
       <c r="N419" s="5"/>
       <c r="O419" s="5"/>
       <c r="P419" s="5"/>
-    </row>
-    <row r="420" spans="1:16">
+      <c r="Q419" s="5"/>
+    </row>
+    <row r="420" spans="1:17">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -9211,8 +9644,9 @@
       <c r="N420" s="5"/>
       <c r="O420" s="5"/>
       <c r="P420" s="5"/>
-    </row>
-    <row r="421" spans="1:16">
+      <c r="Q420" s="5"/>
+    </row>
+    <row r="421" spans="1:17">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -9229,8 +9663,9 @@
       <c r="N421" s="5"/>
       <c r="O421" s="5"/>
       <c r="P421" s="5"/>
-    </row>
-    <row r="422" spans="1:16">
+      <c r="Q421" s="5"/>
+    </row>
+    <row r="422" spans="1:17">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -9247,8 +9682,9 @@
       <c r="N422" s="5"/>
       <c r="O422" s="5"/>
       <c r="P422" s="5"/>
-    </row>
-    <row r="423" spans="1:16">
+      <c r="Q422" s="5"/>
+    </row>
+    <row r="423" spans="1:17">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -9265,8 +9701,9 @@
       <c r="N423" s="5"/>
       <c r="O423" s="5"/>
       <c r="P423" s="5"/>
-    </row>
-    <row r="424" spans="1:16">
+      <c r="Q423" s="5"/>
+    </row>
+    <row r="424" spans="1:17">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -9283,8 +9720,9 @@
       <c r="N424" s="5"/>
       <c r="O424" s="5"/>
       <c r="P424" s="5"/>
-    </row>
-    <row r="425" spans="1:16">
+      <c r="Q424" s="5"/>
+    </row>
+    <row r="425" spans="1:17">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -9301,8 +9739,9 @@
       <c r="N425" s="5"/>
       <c r="O425" s="5"/>
       <c r="P425" s="5"/>
-    </row>
-    <row r="426" spans="1:16">
+      <c r="Q425" s="5"/>
+    </row>
+    <row r="426" spans="1:17">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -9319,8 +9758,9 @@
       <c r="N426" s="5"/>
       <c r="O426" s="5"/>
       <c r="P426" s="5"/>
-    </row>
-    <row r="427" spans="1:16">
+      <c r="Q426" s="5"/>
+    </row>
+    <row r="427" spans="1:17">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -9337,8 +9777,9 @@
       <c r="N427" s="5"/>
       <c r="O427" s="5"/>
       <c r="P427" s="5"/>
-    </row>
-    <row r="428" spans="1:16">
+      <c r="Q427" s="5"/>
+    </row>
+    <row r="428" spans="1:17">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -9355,8 +9796,9 @@
       <c r="N428" s="5"/>
       <c r="O428" s="5"/>
       <c r="P428" s="5"/>
-    </row>
-    <row r="429" spans="1:16">
+      <c r="Q428" s="5"/>
+    </row>
+    <row r="429" spans="1:17">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -9373,8 +9815,9 @@
       <c r="N429" s="5"/>
       <c r="O429" s="5"/>
       <c r="P429" s="5"/>
-    </row>
-    <row r="430" spans="1:16">
+      <c r="Q429" s="5"/>
+    </row>
+    <row r="430" spans="1:17">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -9391,8 +9834,9 @@
       <c r="N430" s="5"/>
       <c r="O430" s="5"/>
       <c r="P430" s="5"/>
-    </row>
-    <row r="431" spans="1:16">
+      <c r="Q430" s="5"/>
+    </row>
+    <row r="431" spans="1:17">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -9409,8 +9853,9 @@
       <c r="N431" s="5"/>
       <c r="O431" s="5"/>
       <c r="P431" s="5"/>
-    </row>
-    <row r="432" spans="1:16">
+      <c r="Q431" s="5"/>
+    </row>
+    <row r="432" spans="1:17">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -9427,8 +9872,9 @@
       <c r="N432" s="5"/>
       <c r="O432" s="5"/>
       <c r="P432" s="5"/>
-    </row>
-    <row r="433" spans="1:16">
+      <c r="Q432" s="5"/>
+    </row>
+    <row r="433" spans="1:17">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -9445,8 +9891,9 @@
       <c r="N433" s="5"/>
       <c r="O433" s="5"/>
       <c r="P433" s="5"/>
-    </row>
-    <row r="434" spans="1:16">
+      <c r="Q433" s="5"/>
+    </row>
+    <row r="434" spans="1:17">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -9463,8 +9910,9 @@
       <c r="N434" s="5"/>
       <c r="O434" s="5"/>
       <c r="P434" s="5"/>
-    </row>
-    <row r="435" spans="1:16">
+      <c r="Q434" s="5"/>
+    </row>
+    <row r="435" spans="1:17">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -9481,8 +9929,9 @@
       <c r="N435" s="5"/>
       <c r="O435" s="5"/>
       <c r="P435" s="5"/>
-    </row>
-    <row r="436" spans="1:16">
+      <c r="Q435" s="5"/>
+    </row>
+    <row r="436" spans="1:17">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -9499,8 +9948,9 @@
       <c r="N436" s="5"/>
       <c r="O436" s="5"/>
       <c r="P436" s="5"/>
-    </row>
-    <row r="437" spans="1:16">
+      <c r="Q436" s="5"/>
+    </row>
+    <row r="437" spans="1:17">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -9517,8 +9967,9 @@
       <c r="N437" s="5"/>
       <c r="O437" s="5"/>
       <c r="P437" s="5"/>
-    </row>
-    <row r="438" spans="1:16">
+      <c r="Q437" s="5"/>
+    </row>
+    <row r="438" spans="1:17">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -9535,8 +9986,9 @@
       <c r="N438" s="5"/>
       <c r="O438" s="5"/>
       <c r="P438" s="5"/>
-    </row>
-    <row r="439" spans="1:16">
+      <c r="Q438" s="5"/>
+    </row>
+    <row r="439" spans="1:17">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -9553,8 +10005,9 @@
       <c r="N439" s="5"/>
       <c r="O439" s="5"/>
       <c r="P439" s="5"/>
-    </row>
-    <row r="440" spans="1:16">
+      <c r="Q439" s="5"/>
+    </row>
+    <row r="440" spans="1:17">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -9571,8 +10024,9 @@
       <c r="N440" s="5"/>
       <c r="O440" s="5"/>
       <c r="P440" s="5"/>
-    </row>
-    <row r="441" spans="1:16">
+      <c r="Q440" s="5"/>
+    </row>
+    <row r="441" spans="1:17">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -9589,8 +10043,9 @@
       <c r="N441" s="5"/>
       <c r="O441" s="5"/>
       <c r="P441" s="5"/>
-    </row>
-    <row r="442" spans="1:16">
+      <c r="Q441" s="5"/>
+    </row>
+    <row r="442" spans="1:17">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -9607,8 +10062,9 @@
       <c r="N442" s="5"/>
       <c r="O442" s="5"/>
       <c r="P442" s="5"/>
-    </row>
-    <row r="443" spans="1:16">
+      <c r="Q442" s="5"/>
+    </row>
+    <row r="443" spans="1:17">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -9625,8 +10081,9 @@
       <c r="N443" s="5"/>
       <c r="O443" s="5"/>
       <c r="P443" s="5"/>
-    </row>
-    <row r="444" spans="1:16">
+      <c r="Q443" s="5"/>
+    </row>
+    <row r="444" spans="1:17">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -9643,8 +10100,9 @@
       <c r="N444" s="5"/>
       <c r="O444" s="5"/>
       <c r="P444" s="5"/>
-    </row>
-    <row r="445" spans="1:16">
+      <c r="Q444" s="5"/>
+    </row>
+    <row r="445" spans="1:17">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -9661,8 +10119,9 @@
       <c r="N445" s="5"/>
       <c r="O445" s="5"/>
       <c r="P445" s="5"/>
-    </row>
-    <row r="446" spans="1:16">
+      <c r="Q445" s="5"/>
+    </row>
+    <row r="446" spans="1:17">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -9679,8 +10138,9 @@
       <c r="N446" s="5"/>
       <c r="O446" s="5"/>
       <c r="P446" s="5"/>
-    </row>
-    <row r="447" spans="1:16">
+      <c r="Q446" s="5"/>
+    </row>
+    <row r="447" spans="1:17">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -9697,8 +10157,9 @@
       <c r="N447" s="5"/>
       <c r="O447" s="5"/>
       <c r="P447" s="5"/>
-    </row>
-    <row r="448" spans="1:16">
+      <c r="Q447" s="5"/>
+    </row>
+    <row r="448" spans="1:17">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">
@@ -10182,7 +10643,7 @@
       <c r="A608" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J608" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>编号</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>是否广告购买</t>
+  </si>
+  <si>
+    <t>火力值</t>
   </si>
   <si>
     <t>攻击间隔</t>
@@ -235,6 +238,9 @@
   </si>
   <si>
     <t>isAdBuy</t>
+  </si>
+  <si>
+    <t>firepower</t>
   </si>
   <si>
     <t>attackInterval</t>
@@ -1278,15 +1284,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U608"/>
+  <dimension ref="A1:V608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="17" width="25.125" style="2" customWidth="1"/>
-    <col min="18" max="21" width="25.125" style="3" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="2"/>
+    <col min="1" max="18" width="25.125" style="2" customWidth="1"/>
+    <col min="19" max="22" width="25.125" style="3" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:21">
+    <row r="1" ht="16.5" spans="1:22">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1338,114 +1344,121 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:21">
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:22">
       <c r="A2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:21">
+        <v>34</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:22">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>35</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:21">
+        <v>37</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:22">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1456,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -1472,31 +1485,34 @@
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
+        <v>100</v>
+      </c>
+      <c r="K4" s="3">
         <v>0.5</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>2000</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>10</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1</v>
       </c>
       <c r="N4" s="3">
         <v>1</v>
       </c>
       <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
         <v>100</v>
       </c>
-      <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:21">
+      <c r="V4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:22">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1507,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -1523,31 +1539,34 @@
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
+        <v>200</v>
+      </c>
+      <c r="K5" s="3">
         <v>0.15</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>2000</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>3</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>0.9</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>30</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="3">
         <v>600</v>
       </c>
-      <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:21">
+      <c r="V5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:22">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1558,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -1574,31 +1593,34 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
+        <v>300</v>
+      </c>
+      <c r="K6" s="3">
         <v>0.05</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>2000</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>4</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>0.9</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>25</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>600</v>
       </c>
-      <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:21">
+      <c r="V6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:22">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1609,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -1625,31 +1647,34 @@
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
+        <v>400</v>
+      </c>
+      <c r="K7" s="3">
         <v>0.2</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>2000</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>5</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>0.6</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>75</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>600</v>
       </c>
-      <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:21">
+      <c r="V7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:22">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1660,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -1676,33 +1701,36 @@
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3">
+        <v>500</v>
+      </c>
+      <c r="K8" s="3">
         <v>1</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>0.9</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8</v>
       </c>
-      <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:21">
+      <c r="V8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:22">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1713,7 +1741,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
@@ -1731,33 +1759,36 @@
         <v>1</v>
       </c>
       <c r="J9" s="3">
+        <v>600</v>
+      </c>
+      <c r="K9" s="3">
         <v>1</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>0.8</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3">
         <v>1</v>
       </c>
-      <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:21">
+      <c r="V9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:22">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1768,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -1784,31 +1815,34 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
+        <v>700</v>
+      </c>
+      <c r="K10" s="3">
         <v>0.2</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>0.9</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:21">
+      <c r="V10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:22">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1819,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -1835,31 +1869,34 @@
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
+        <v>800</v>
+      </c>
+      <c r="K11" s="3">
         <v>0.2</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>2000</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>15</v>
-      </c>
-      <c r="M11" s="3">
-        <v>1</v>
       </c>
       <c r="N11" s="3">
         <v>1</v>
       </c>
       <c r="O11" s="3">
+        <v>1</v>
+      </c>
+      <c r="P11" s="3">
         <v>100</v>
       </c>
-      <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:21">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1881,8 +1918,9 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:21">
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1904,8 +1942,9 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:21">
+      <c r="V13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1927,8 +1966,9 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:21">
+      <c r="V14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1950,8 +1990,9 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
-    </row>
-    <row r="16" spans="1:21">
+      <c r="V15" s="3"/>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1969,8 +2010,9 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="5"/>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1988,8 +2030,9 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="5"/>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2007,8 +2050,9 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="5"/>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2026,8 +2070,9 @@
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="5"/>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2045,8 +2090,9 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="5"/>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2064,8 +2110,9 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="5"/>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2083,8 +2130,9 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" s="5"/>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2102,8 +2150,9 @@
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2121,8 +2170,9 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24" s="5"/>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2140,8 +2190,9 @@
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25" s="5"/>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2159,8 +2210,9 @@
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26" s="5"/>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2178,8 +2230,9 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" s="5"/>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2197,8 +2250,9 @@
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" s="5"/>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2216,8 +2270,9 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" s="5"/>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2235,8 +2290,9 @@
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30" s="5"/>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2254,8 +2310,9 @@
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31" s="5"/>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2273,8 +2330,9 @@
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="R32" s="5"/>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2292,8 +2350,9 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="R33" s="5"/>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2311,8 +2370,9 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="R34" s="5"/>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2330,8 +2390,9 @@
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
-    </row>
-    <row r="36" spans="1:17">
+      <c r="R35" s="5"/>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2349,8 +2410,9 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
-    </row>
-    <row r="37" spans="1:17">
+      <c r="R36" s="5"/>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2368,8 +2430,9 @@
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
-    </row>
-    <row r="38" spans="1:17">
+      <c r="R37" s="5"/>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2387,8 +2450,9 @@
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="R38" s="5"/>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2406,8 +2470,9 @@
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="R39" s="5"/>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2425,8 +2490,9 @@
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="R40" s="5"/>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2444,8 +2510,9 @@
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="R41" s="5"/>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2463,8 +2530,9 @@
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="R42" s="5"/>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2482,8 +2550,9 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="R43" s="5"/>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2501,8 +2570,9 @@
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="R44" s="5"/>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2520,8 +2590,9 @@
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="R45" s="5"/>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2539,8 +2610,9 @@
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="R46" s="5"/>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2558,8 +2630,9 @@
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="R47" s="5"/>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2577,8 +2650,9 @@
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="R48" s="5"/>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2596,8 +2670,9 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
-    </row>
-    <row r="50" spans="1:17">
+      <c r="R49" s="5"/>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2615,8 +2690,9 @@
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
-    </row>
-    <row r="51" spans="1:17">
+      <c r="R50" s="5"/>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2634,8 +2710,9 @@
       <c r="O51" s="5"/>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
-    </row>
-    <row r="52" spans="1:17">
+      <c r="R51" s="5"/>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2653,8 +2730,9 @@
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
-    </row>
-    <row r="53" spans="1:17">
+      <c r="R52" s="5"/>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2672,8 +2750,9 @@
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
-    </row>
-    <row r="54" spans="1:17">
+      <c r="R53" s="5"/>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2691,8 +2770,9 @@
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
-    </row>
-    <row r="55" spans="1:17">
+      <c r="R54" s="5"/>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2710,8 +2790,9 @@
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
-    </row>
-    <row r="56" spans="1:17">
+      <c r="R55" s="5"/>
+    </row>
+    <row r="56" spans="1:18">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2729,8 +2810,9 @@
       <c r="O56" s="5"/>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
-    </row>
-    <row r="57" spans="1:17">
+      <c r="R56" s="5"/>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2748,8 +2830,9 @@
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
       <c r="Q57" s="5"/>
-    </row>
-    <row r="58" spans="1:17">
+      <c r="R57" s="5"/>
+    </row>
+    <row r="58" spans="1:18">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2767,8 +2850,9 @@
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
-    </row>
-    <row r="59" spans="1:17">
+      <c r="R58" s="5"/>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2786,8 +2870,9 @@
       <c r="O59" s="5"/>
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
-    </row>
-    <row r="60" spans="1:17">
+      <c r="R59" s="5"/>
+    </row>
+    <row r="60" spans="1:18">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2805,8 +2890,9 @@
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
-    </row>
-    <row r="61" spans="1:17">
+      <c r="R60" s="5"/>
+    </row>
+    <row r="61" spans="1:18">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2824,8 +2910,9 @@
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
       <c r="Q61" s="5"/>
-    </row>
-    <row r="62" spans="1:17">
+      <c r="R61" s="5"/>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2843,8 +2930,9 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
       <c r="Q62" s="5"/>
-    </row>
-    <row r="63" spans="1:17">
+      <c r="R62" s="5"/>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2862,8 +2950,9 @@
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
-    </row>
-    <row r="64" spans="1:17">
+      <c r="R63" s="5"/>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2881,8 +2970,9 @@
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
-    </row>
-    <row r="65" spans="1:17">
+      <c r="R64" s="5"/>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2900,8 +2990,9 @@
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
-    </row>
-    <row r="66" spans="1:17">
+      <c r="R65" s="5"/>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2919,8 +3010,9 @@
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
       <c r="Q66" s="5"/>
-    </row>
-    <row r="67" spans="1:17">
+      <c r="R66" s="5"/>
+    </row>
+    <row r="67" spans="1:18">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2938,8 +3030,9 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
-    </row>
-    <row r="68" spans="1:17">
+      <c r="R67" s="5"/>
+    </row>
+    <row r="68" spans="1:18">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2957,8 +3050,9 @@
       <c r="O68" s="5"/>
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
-    </row>
-    <row r="69" spans="1:17">
+      <c r="R68" s="5"/>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2976,8 +3070,9 @@
       <c r="O69" s="5"/>
       <c r="P69" s="5"/>
       <c r="Q69" s="5"/>
-    </row>
-    <row r="70" spans="1:17">
+      <c r="R69" s="5"/>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2995,8 +3090,9 @@
       <c r="O70" s="5"/>
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
-    </row>
-    <row r="71" spans="1:17">
+      <c r="R70" s="5"/>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -3014,8 +3110,9 @@
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
-    </row>
-    <row r="72" spans="1:17">
+      <c r="R71" s="5"/>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3033,8 +3130,9 @@
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
-    </row>
-    <row r="73" spans="1:17">
+      <c r="R72" s="5"/>
+    </row>
+    <row r="73" spans="1:18">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -3052,8 +3150,9 @@
       <c r="O73" s="5"/>
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
-    </row>
-    <row r="74" spans="1:17">
+      <c r="R73" s="5"/>
+    </row>
+    <row r="74" spans="1:18">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3071,8 +3170,9 @@
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
-    </row>
-    <row r="75" spans="1:17">
+      <c r="R74" s="5"/>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3090,8 +3190,9 @@
       <c r="O75" s="5"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-    </row>
-    <row r="76" spans="1:17">
+      <c r="R75" s="5"/>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3109,8 +3210,9 @@
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
-    </row>
-    <row r="77" spans="1:17">
+      <c r="R76" s="5"/>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3128,8 +3230,9 @@
       <c r="O77" s="5"/>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
-    </row>
-    <row r="78" spans="1:17">
+      <c r="R77" s="5"/>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3147,8 +3250,9 @@
       <c r="O78" s="5"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-    </row>
-    <row r="79" spans="1:17">
+      <c r="R78" s="5"/>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3166,8 +3270,9 @@
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
-    </row>
-    <row r="80" spans="1:17">
+      <c r="R79" s="5"/>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -3185,8 +3290,9 @@
       <c r="O80" s="5"/>
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
-    </row>
-    <row r="81" spans="1:17">
+      <c r="R80" s="5"/>
+    </row>
+    <row r="81" spans="1:18">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -3204,8 +3310,9 @@
       <c r="O81" s="5"/>
       <c r="P81" s="5"/>
       <c r="Q81" s="5"/>
-    </row>
-    <row r="82" spans="1:17">
+      <c r="R81" s="5"/>
+    </row>
+    <row r="82" spans="1:18">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -3223,8 +3330,9 @@
       <c r="O82" s="5"/>
       <c r="P82" s="5"/>
       <c r="Q82" s="5"/>
-    </row>
-    <row r="83" spans="1:17">
+      <c r="R82" s="5"/>
+    </row>
+    <row r="83" spans="1:18">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3242,8 +3350,9 @@
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
-    </row>
-    <row r="84" spans="1:17">
+      <c r="R83" s="5"/>
+    </row>
+    <row r="84" spans="1:18">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -3261,8 +3370,9 @@
       <c r="O84" s="5"/>
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
-    </row>
-    <row r="85" spans="1:17">
+      <c r="R84" s="5"/>
+    </row>
+    <row r="85" spans="1:18">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -3280,8 +3390,9 @@
       <c r="O85" s="5"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
-    </row>
-    <row r="86" spans="1:17">
+      <c r="R85" s="5"/>
+    </row>
+    <row r="86" spans="1:18">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -3299,8 +3410,9 @@
       <c r="O86" s="5"/>
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
-    </row>
-    <row r="87" spans="1:17">
+      <c r="R86" s="5"/>
+    </row>
+    <row r="87" spans="1:18">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -3318,8 +3430,9 @@
       <c r="O87" s="5"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
-    </row>
-    <row r="88" spans="1:17">
+      <c r="R87" s="5"/>
+    </row>
+    <row r="88" spans="1:18">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -3337,8 +3450,9 @@
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
-    </row>
-    <row r="89" spans="1:17">
+      <c r="R88" s="5"/>
+    </row>
+    <row r="89" spans="1:18">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3356,8 +3470,9 @@
       <c r="O89" s="5"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
-    </row>
-    <row r="90" spans="1:17">
+      <c r="R89" s="5"/>
+    </row>
+    <row r="90" spans="1:18">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -3375,8 +3490,9 @@
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
-    </row>
-    <row r="91" spans="1:17">
+      <c r="R90" s="5"/>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -3394,8 +3510,9 @@
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
-    </row>
-    <row r="92" spans="1:17">
+      <c r="R91" s="5"/>
+    </row>
+    <row r="92" spans="1:18">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -3413,8 +3530,9 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
-    </row>
-    <row r="93" spans="1:17">
+      <c r="R92" s="5"/>
+    </row>
+    <row r="93" spans="1:18">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -3432,8 +3550,9 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
       <c r="Q93" s="5"/>
-    </row>
-    <row r="94" spans="1:17">
+      <c r="R93" s="5"/>
+    </row>
+    <row r="94" spans="1:18">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -3451,8 +3570,9 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
-    </row>
-    <row r="95" spans="1:17">
+      <c r="R94" s="5"/>
+    </row>
+    <row r="95" spans="1:18">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -3470,8 +3590,9 @@
       <c r="O95" s="5"/>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
-    </row>
-    <row r="96" spans="1:17">
+      <c r="R95" s="5"/>
+    </row>
+    <row r="96" spans="1:18">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -3489,8 +3610,9 @@
       <c r="O96" s="5"/>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
-    </row>
-    <row r="97" spans="1:17">
+      <c r="R96" s="5"/>
+    </row>
+    <row r="97" spans="1:18">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -3508,8 +3630,9 @@
       <c r="O97" s="5"/>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
-    </row>
-    <row r="98" spans="1:17">
+      <c r="R97" s="5"/>
+    </row>
+    <row r="98" spans="1:18">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -3527,8 +3650,9 @@
       <c r="O98" s="5"/>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
-    </row>
-    <row r="99" spans="1:17">
+      <c r="R98" s="5"/>
+    </row>
+    <row r="99" spans="1:18">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -3546,8 +3670,9 @@
       <c r="O99" s="5"/>
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
-    </row>
-    <row r="100" spans="1:17">
+      <c r="R99" s="5"/>
+    </row>
+    <row r="100" spans="1:18">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -3565,8 +3690,9 @@
       <c r="O100" s="5"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-    </row>
-    <row r="101" spans="1:17">
+      <c r="R100" s="5"/>
+    </row>
+    <row r="101" spans="1:18">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -3584,8 +3710,9 @@
       <c r="O101" s="5"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-    </row>
-    <row r="102" spans="1:17">
+      <c r="R101" s="5"/>
+    </row>
+    <row r="102" spans="1:18">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -3603,8 +3730,9 @@
       <c r="O102" s="5"/>
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
-    </row>
-    <row r="103" spans="1:17">
+      <c r="R102" s="5"/>
+    </row>
+    <row r="103" spans="1:18">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -3622,8 +3750,9 @@
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
-    </row>
-    <row r="104" spans="1:17">
+      <c r="R103" s="5"/>
+    </row>
+    <row r="104" spans="1:18">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3641,8 +3770,9 @@
       <c r="O104" s="5"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-    </row>
-    <row r="105" spans="1:17">
+      <c r="R104" s="5"/>
+    </row>
+    <row r="105" spans="1:18">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -3660,8 +3790,9 @@
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-    </row>
-    <row r="106" spans="1:17">
+      <c r="R105" s="5"/>
+    </row>
+    <row r="106" spans="1:18">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3679,8 +3810,9 @@
       <c r="O106" s="5"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
-    </row>
-    <row r="107" spans="1:17">
+      <c r="R106" s="5"/>
+    </row>
+    <row r="107" spans="1:18">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -3698,8 +3830,9 @@
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
-    </row>
-    <row r="108" spans="1:17">
+      <c r="R107" s="5"/>
+    </row>
+    <row r="108" spans="1:18">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -3717,8 +3850,9 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
       <c r="Q108" s="5"/>
-    </row>
-    <row r="109" spans="1:17">
+      <c r="R108" s="5"/>
+    </row>
+    <row r="109" spans="1:18">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -3736,8 +3870,9 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
       <c r="Q109" s="5"/>
-    </row>
-    <row r="110" spans="1:17">
+      <c r="R109" s="5"/>
+    </row>
+    <row r="110" spans="1:18">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3755,8 +3890,9 @@
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
       <c r="Q110" s="5"/>
-    </row>
-    <row r="111" spans="1:17">
+      <c r="R110" s="5"/>
+    </row>
+    <row r="111" spans="1:18">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3774,8 +3910,9 @@
       <c r="O111" s="5"/>
       <c r="P111" s="5"/>
       <c r="Q111" s="5"/>
-    </row>
-    <row r="112" spans="1:17">
+      <c r="R111" s="5"/>
+    </row>
+    <row r="112" spans="1:18">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3793,8 +3930,9 @@
       <c r="O112" s="5"/>
       <c r="P112" s="5"/>
       <c r="Q112" s="5"/>
-    </row>
-    <row r="113" spans="1:17">
+      <c r="R112" s="5"/>
+    </row>
+    <row r="113" spans="1:18">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3812,8 +3950,9 @@
       <c r="O113" s="5"/>
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
-    </row>
-    <row r="114" spans="1:17">
+      <c r="R113" s="5"/>
+    </row>
+    <row r="114" spans="1:18">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -3831,8 +3970,9 @@
       <c r="O114" s="5"/>
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
-    </row>
-    <row r="115" spans="1:17">
+      <c r="R114" s="5"/>
+    </row>
+    <row r="115" spans="1:18">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3850,8 +3990,9 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
       <c r="Q115" s="5"/>
-    </row>
-    <row r="116" spans="1:17">
+      <c r="R115" s="5"/>
+    </row>
+    <row r="116" spans="1:18">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3869,8 +4010,9 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
       <c r="Q116" s="5"/>
-    </row>
-    <row r="117" spans="1:17">
+      <c r="R116" s="5"/>
+    </row>
+    <row r="117" spans="1:18">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -3888,8 +4030,9 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
       <c r="Q117" s="5"/>
-    </row>
-    <row r="118" spans="1:17">
+      <c r="R117" s="5"/>
+    </row>
+    <row r="118" spans="1:18">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -3907,8 +4050,9 @@
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
       <c r="Q118" s="5"/>
-    </row>
-    <row r="119" spans="1:17">
+      <c r="R118" s="5"/>
+    </row>
+    <row r="119" spans="1:18">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -3926,8 +4070,9 @@
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
-    </row>
-    <row r="120" spans="1:17">
+      <c r="R119" s="5"/>
+    </row>
+    <row r="120" spans="1:18">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -3945,8 +4090,9 @@
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-    </row>
-    <row r="121" spans="1:17">
+      <c r="R120" s="5"/>
+    </row>
+    <row r="121" spans="1:18">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -3964,8 +4110,9 @@
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
-    </row>
-    <row r="122" spans="1:17">
+      <c r="R121" s="5"/>
+    </row>
+    <row r="122" spans="1:18">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -3983,8 +4130,9 @@
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
-    </row>
-    <row r="123" spans="1:17">
+      <c r="R122" s="5"/>
+    </row>
+    <row r="123" spans="1:18">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -4002,8 +4150,9 @@
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
       <c r="Q123" s="5"/>
-    </row>
-    <row r="124" spans="1:17">
+      <c r="R123" s="5"/>
+    </row>
+    <row r="124" spans="1:18">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -4021,8 +4170,9 @@
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
-    </row>
-    <row r="125" spans="1:17">
+      <c r="R124" s="5"/>
+    </row>
+    <row r="125" spans="1:18">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -4040,8 +4190,9 @@
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
-    </row>
-    <row r="126" spans="1:17">
+      <c r="R125" s="5"/>
+    </row>
+    <row r="126" spans="1:18">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -4059,8 +4210,9 @@
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
       <c r="Q126" s="5"/>
-    </row>
-    <row r="127" spans="1:17">
+      <c r="R126" s="5"/>
+    </row>
+    <row r="127" spans="1:18">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -4078,8 +4230,9 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
       <c r="Q127" s="5"/>
-    </row>
-    <row r="128" spans="1:17">
+      <c r="R127" s="5"/>
+    </row>
+    <row r="128" spans="1:18">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -4097,8 +4250,9 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
       <c r="Q128" s="5"/>
-    </row>
-    <row r="129" spans="1:17">
+      <c r="R128" s="5"/>
+    </row>
+    <row r="129" spans="1:18">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -4116,8 +4270,9 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
-    </row>
-    <row r="130" spans="1:17">
+      <c r="R129" s="5"/>
+    </row>
+    <row r="130" spans="1:18">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -4135,8 +4290,9 @@
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
-    </row>
-    <row r="131" spans="1:17">
+      <c r="R130" s="5"/>
+    </row>
+    <row r="131" spans="1:18">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -4154,8 +4310,9 @@
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
       <c r="Q131" s="5"/>
-    </row>
-    <row r="132" spans="1:17">
+      <c r="R131" s="5"/>
+    </row>
+    <row r="132" spans="1:18">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -4173,8 +4330,9 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
       <c r="Q132" s="5"/>
-    </row>
-    <row r="133" spans="1:17">
+      <c r="R132" s="5"/>
+    </row>
+    <row r="133" spans="1:18">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -4192,8 +4350,9 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
-    </row>
-    <row r="134" spans="1:17">
+      <c r="R133" s="5"/>
+    </row>
+    <row r="134" spans="1:18">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -4211,8 +4370,9 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
-    </row>
-    <row r="135" spans="1:17">
+      <c r="R134" s="5"/>
+    </row>
+    <row r="135" spans="1:18">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -4230,8 +4390,9 @@
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
       <c r="Q135" s="5"/>
-    </row>
-    <row r="136" spans="1:17">
+      <c r="R135" s="5"/>
+    </row>
+    <row r="136" spans="1:18">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -4249,8 +4410,9 @@
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
       <c r="Q136" s="5"/>
-    </row>
-    <row r="137" spans="1:17">
+      <c r="R136" s="5"/>
+    </row>
+    <row r="137" spans="1:18">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -4268,8 +4430,9 @@
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
-    </row>
-    <row r="138" spans="1:17">
+      <c r="R137" s="5"/>
+    </row>
+    <row r="138" spans="1:18">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -4287,8 +4450,9 @@
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
       <c r="Q138" s="5"/>
-    </row>
-    <row r="139" spans="1:17">
+      <c r="R138" s="5"/>
+    </row>
+    <row r="139" spans="1:18">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -4306,8 +4470,9 @@
       <c r="O139" s="5"/>
       <c r="P139" s="5"/>
       <c r="Q139" s="5"/>
-    </row>
-    <row r="140" spans="1:17">
+      <c r="R139" s="5"/>
+    </row>
+    <row r="140" spans="1:18">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -4325,8 +4490,9 @@
       <c r="O140" s="5"/>
       <c r="P140" s="5"/>
       <c r="Q140" s="5"/>
-    </row>
-    <row r="141" spans="1:17">
+      <c r="R140" s="5"/>
+    </row>
+    <row r="141" spans="1:18">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -4344,8 +4510,9 @@
       <c r="O141" s="5"/>
       <c r="P141" s="5"/>
       <c r="Q141" s="5"/>
-    </row>
-    <row r="142" spans="1:17">
+      <c r="R141" s="5"/>
+    </row>
+    <row r="142" spans="1:18">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -4363,8 +4530,9 @@
       <c r="O142" s="5"/>
       <c r="P142" s="5"/>
       <c r="Q142" s="5"/>
-    </row>
-    <row r="143" spans="1:17">
+      <c r="R142" s="5"/>
+    </row>
+    <row r="143" spans="1:18">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -4382,8 +4550,9 @@
       <c r="O143" s="5"/>
       <c r="P143" s="5"/>
       <c r="Q143" s="5"/>
-    </row>
-    <row r="144" spans="1:17">
+      <c r="R143" s="5"/>
+    </row>
+    <row r="144" spans="1:18">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -4401,8 +4570,9 @@
       <c r="O144" s="5"/>
       <c r="P144" s="5"/>
       <c r="Q144" s="5"/>
-    </row>
-    <row r="145" spans="1:17">
+      <c r="R144" s="5"/>
+    </row>
+    <row r="145" spans="1:18">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -4420,8 +4590,9 @@
       <c r="O145" s="5"/>
       <c r="P145" s="5"/>
       <c r="Q145" s="5"/>
-    </row>
-    <row r="146" spans="1:17">
+      <c r="R145" s="5"/>
+    </row>
+    <row r="146" spans="1:18">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -4439,8 +4610,9 @@
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
       <c r="Q146" s="5"/>
-    </row>
-    <row r="147" spans="1:17">
+      <c r="R146" s="5"/>
+    </row>
+    <row r="147" spans="1:18">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -4458,8 +4630,9 @@
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
       <c r="Q147" s="5"/>
-    </row>
-    <row r="148" spans="1:17">
+      <c r="R147" s="5"/>
+    </row>
+    <row r="148" spans="1:18">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -4477,8 +4650,9 @@
       <c r="O148" s="5"/>
       <c r="P148" s="5"/>
       <c r="Q148" s="5"/>
-    </row>
-    <row r="149" spans="1:17">
+      <c r="R148" s="5"/>
+    </row>
+    <row r="149" spans="1:18">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -4496,8 +4670,9 @@
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
       <c r="Q149" s="5"/>
-    </row>
-    <row r="150" spans="1:17">
+      <c r="R149" s="5"/>
+    </row>
+    <row r="150" spans="1:18">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -4515,8 +4690,9 @@
       <c r="O150" s="5"/>
       <c r="P150" s="5"/>
       <c r="Q150" s="5"/>
-    </row>
-    <row r="151" spans="1:17">
+      <c r="R150" s="5"/>
+    </row>
+    <row r="151" spans="1:18">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -4534,8 +4710,9 @@
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
       <c r="Q151" s="5"/>
-    </row>
-    <row r="152" spans="1:17">
+      <c r="R151" s="5"/>
+    </row>
+    <row r="152" spans="1:18">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -4553,8 +4730,9 @@
       <c r="O152" s="5"/>
       <c r="P152" s="5"/>
       <c r="Q152" s="5"/>
-    </row>
-    <row r="153" spans="1:17">
+      <c r="R152" s="5"/>
+    </row>
+    <row r="153" spans="1:18">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -4572,8 +4750,9 @@
       <c r="O153" s="5"/>
       <c r="P153" s="5"/>
       <c r="Q153" s="5"/>
-    </row>
-    <row r="154" spans="1:17">
+      <c r="R153" s="5"/>
+    </row>
+    <row r="154" spans="1:18">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -4591,8 +4770,9 @@
       <c r="O154" s="5"/>
       <c r="P154" s="5"/>
       <c r="Q154" s="5"/>
-    </row>
-    <row r="155" spans="1:17">
+      <c r="R154" s="5"/>
+    </row>
+    <row r="155" spans="1:18">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -4610,8 +4790,9 @@
       <c r="O155" s="5"/>
       <c r="P155" s="5"/>
       <c r="Q155" s="5"/>
-    </row>
-    <row r="156" spans="1:17">
+      <c r="R155" s="5"/>
+    </row>
+    <row r="156" spans="1:18">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -4629,8 +4810,9 @@
       <c r="O156" s="5"/>
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
-    </row>
-    <row r="157" spans="1:17">
+      <c r="R156" s="5"/>
+    </row>
+    <row r="157" spans="1:18">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -4648,8 +4830,9 @@
       <c r="O157" s="5"/>
       <c r="P157" s="5"/>
       <c r="Q157" s="5"/>
-    </row>
-    <row r="158" spans="1:17">
+      <c r="R157" s="5"/>
+    </row>
+    <row r="158" spans="1:18">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -4667,8 +4850,9 @@
       <c r="O158" s="5"/>
       <c r="P158" s="5"/>
       <c r="Q158" s="5"/>
-    </row>
-    <row r="159" spans="1:17">
+      <c r="R158" s="5"/>
+    </row>
+    <row r="159" spans="1:18">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -4686,8 +4870,9 @@
       <c r="O159" s="5"/>
       <c r="P159" s="5"/>
       <c r="Q159" s="5"/>
-    </row>
-    <row r="160" spans="1:17">
+      <c r="R159" s="5"/>
+    </row>
+    <row r="160" spans="1:18">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -4705,8 +4890,9 @@
       <c r="O160" s="5"/>
       <c r="P160" s="5"/>
       <c r="Q160" s="5"/>
-    </row>
-    <row r="161" spans="1:17">
+      <c r="R160" s="5"/>
+    </row>
+    <row r="161" spans="1:18">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -4724,8 +4910,9 @@
       <c r="O161" s="5"/>
       <c r="P161" s="5"/>
       <c r="Q161" s="5"/>
-    </row>
-    <row r="162" spans="1:17">
+      <c r="R161" s="5"/>
+    </row>
+    <row r="162" spans="1:18">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -4743,8 +4930,9 @@
       <c r="O162" s="5"/>
       <c r="P162" s="5"/>
       <c r="Q162" s="5"/>
-    </row>
-    <row r="163" spans="1:17">
+      <c r="R162" s="5"/>
+    </row>
+    <row r="163" spans="1:18">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -4762,8 +4950,9 @@
       <c r="O163" s="5"/>
       <c r="P163" s="5"/>
       <c r="Q163" s="5"/>
-    </row>
-    <row r="164" spans="1:17">
+      <c r="R163" s="5"/>
+    </row>
+    <row r="164" spans="1:18">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -4781,8 +4970,9 @@
       <c r="O164" s="5"/>
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
-    </row>
-    <row r="165" spans="1:17">
+      <c r="R164" s="5"/>
+    </row>
+    <row r="165" spans="1:18">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -4800,8 +4990,9 @@
       <c r="O165" s="5"/>
       <c r="P165" s="5"/>
       <c r="Q165" s="5"/>
-    </row>
-    <row r="166" spans="1:17">
+      <c r="R165" s="5"/>
+    </row>
+    <row r="166" spans="1:18">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -4819,8 +5010,9 @@
       <c r="O166" s="5"/>
       <c r="P166" s="5"/>
       <c r="Q166" s="5"/>
-    </row>
-    <row r="167" spans="1:17">
+      <c r="R166" s="5"/>
+    </row>
+    <row r="167" spans="1:18">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -4838,8 +5030,9 @@
       <c r="O167" s="5"/>
       <c r="P167" s="5"/>
       <c r="Q167" s="5"/>
-    </row>
-    <row r="168" spans="1:17">
+      <c r="R167" s="5"/>
+    </row>
+    <row r="168" spans="1:18">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -4857,8 +5050,9 @@
       <c r="O168" s="5"/>
       <c r="P168" s="5"/>
       <c r="Q168" s="5"/>
-    </row>
-    <row r="169" spans="1:17">
+      <c r="R168" s="5"/>
+    </row>
+    <row r="169" spans="1:18">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -4876,8 +5070,9 @@
       <c r="O169" s="5"/>
       <c r="P169" s="5"/>
       <c r="Q169" s="5"/>
-    </row>
-    <row r="170" spans="1:17">
+      <c r="R169" s="5"/>
+    </row>
+    <row r="170" spans="1:18">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -4895,8 +5090,9 @@
       <c r="O170" s="5"/>
       <c r="P170" s="5"/>
       <c r="Q170" s="5"/>
-    </row>
-    <row r="171" spans="1:17">
+      <c r="R170" s="5"/>
+    </row>
+    <row r="171" spans="1:18">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -4914,8 +5110,9 @@
       <c r="O171" s="5"/>
       <c r="P171" s="5"/>
       <c r="Q171" s="5"/>
-    </row>
-    <row r="172" spans="1:17">
+      <c r="R171" s="5"/>
+    </row>
+    <row r="172" spans="1:18">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -4933,8 +5130,9 @@
       <c r="O172" s="5"/>
       <c r="P172" s="5"/>
       <c r="Q172" s="5"/>
-    </row>
-    <row r="173" spans="1:17">
+      <c r="R172" s="5"/>
+    </row>
+    <row r="173" spans="1:18">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -4952,8 +5150,9 @@
       <c r="O173" s="5"/>
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>
-    </row>
-    <row r="174" spans="1:17">
+      <c r="R173" s="5"/>
+    </row>
+    <row r="174" spans="1:18">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -4971,8 +5170,9 @@
       <c r="O174" s="5"/>
       <c r="P174" s="5"/>
       <c r="Q174" s="5"/>
-    </row>
-    <row r="175" spans="1:17">
+      <c r="R174" s="5"/>
+    </row>
+    <row r="175" spans="1:18">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -4990,8 +5190,9 @@
       <c r="O175" s="5"/>
       <c r="P175" s="5"/>
       <c r="Q175" s="5"/>
-    </row>
-    <row r="176" spans="1:17">
+      <c r="R175" s="5"/>
+    </row>
+    <row r="176" spans="1:18">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -5009,8 +5210,9 @@
       <c r="O176" s="5"/>
       <c r="P176" s="5"/>
       <c r="Q176" s="5"/>
-    </row>
-    <row r="177" spans="1:17">
+      <c r="R176" s="5"/>
+    </row>
+    <row r="177" spans="1:18">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -5028,8 +5230,9 @@
       <c r="O177" s="5"/>
       <c r="P177" s="5"/>
       <c r="Q177" s="5"/>
-    </row>
-    <row r="178" spans="1:17">
+      <c r="R177" s="5"/>
+    </row>
+    <row r="178" spans="1:18">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -5047,8 +5250,9 @@
       <c r="O178" s="5"/>
       <c r="P178" s="5"/>
       <c r="Q178" s="5"/>
-    </row>
-    <row r="179" spans="1:17">
+      <c r="R178" s="5"/>
+    </row>
+    <row r="179" spans="1:18">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -5066,8 +5270,9 @@
       <c r="O179" s="5"/>
       <c r="P179" s="5"/>
       <c r="Q179" s="5"/>
-    </row>
-    <row r="180" spans="1:17">
+      <c r="R179" s="5"/>
+    </row>
+    <row r="180" spans="1:18">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -5085,8 +5290,9 @@
       <c r="O180" s="5"/>
       <c r="P180" s="5"/>
       <c r="Q180" s="5"/>
-    </row>
-    <row r="181" spans="1:17">
+      <c r="R180" s="5"/>
+    </row>
+    <row r="181" spans="1:18">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -5104,8 +5310,9 @@
       <c r="O181" s="5"/>
       <c r="P181" s="5"/>
       <c r="Q181" s="5"/>
-    </row>
-    <row r="182" spans="1:17">
+      <c r="R181" s="5"/>
+    </row>
+    <row r="182" spans="1:18">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -5123,8 +5330,9 @@
       <c r="O182" s="5"/>
       <c r="P182" s="5"/>
       <c r="Q182" s="5"/>
-    </row>
-    <row r="183" spans="1:17">
+      <c r="R182" s="5"/>
+    </row>
+    <row r="183" spans="1:18">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -5142,8 +5350,9 @@
       <c r="O183" s="5"/>
       <c r="P183" s="5"/>
       <c r="Q183" s="5"/>
-    </row>
-    <row r="184" spans="1:17">
+      <c r="R183" s="5"/>
+    </row>
+    <row r="184" spans="1:18">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -5161,8 +5370,9 @@
       <c r="O184" s="5"/>
       <c r="P184" s="5"/>
       <c r="Q184" s="5"/>
-    </row>
-    <row r="185" spans="1:17">
+      <c r="R184" s="5"/>
+    </row>
+    <row r="185" spans="1:18">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -5180,8 +5390,9 @@
       <c r="O185" s="5"/>
       <c r="P185" s="5"/>
       <c r="Q185" s="5"/>
-    </row>
-    <row r="186" spans="1:17">
+      <c r="R185" s="5"/>
+    </row>
+    <row r="186" spans="1:18">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -5199,8 +5410,9 @@
       <c r="O186" s="5"/>
       <c r="P186" s="5"/>
       <c r="Q186" s="5"/>
-    </row>
-    <row r="187" spans="1:17">
+      <c r="R186" s="5"/>
+    </row>
+    <row r="187" spans="1:18">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -5218,8 +5430,9 @@
       <c r="O187" s="5"/>
       <c r="P187" s="5"/>
       <c r="Q187" s="5"/>
-    </row>
-    <row r="188" spans="1:17">
+      <c r="R187" s="5"/>
+    </row>
+    <row r="188" spans="1:18">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -5237,8 +5450,9 @@
       <c r="O188" s="5"/>
       <c r="P188" s="5"/>
       <c r="Q188" s="5"/>
-    </row>
-    <row r="189" spans="1:17">
+      <c r="R188" s="5"/>
+    </row>
+    <row r="189" spans="1:18">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -5256,8 +5470,9 @@
       <c r="O189" s="5"/>
       <c r="P189" s="5"/>
       <c r="Q189" s="5"/>
-    </row>
-    <row r="190" spans="1:17">
+      <c r="R189" s="5"/>
+    </row>
+    <row r="190" spans="1:18">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -5275,8 +5490,9 @@
       <c r="O190" s="5"/>
       <c r="P190" s="5"/>
       <c r="Q190" s="5"/>
-    </row>
-    <row r="191" spans="1:17">
+      <c r="R190" s="5"/>
+    </row>
+    <row r="191" spans="1:18">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -5294,8 +5510,9 @@
       <c r="O191" s="5"/>
       <c r="P191" s="5"/>
       <c r="Q191" s="5"/>
-    </row>
-    <row r="192" spans="1:17">
+      <c r="R191" s="5"/>
+    </row>
+    <row r="192" spans="1:18">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -5313,8 +5530,9 @@
       <c r="O192" s="5"/>
       <c r="P192" s="5"/>
       <c r="Q192" s="5"/>
-    </row>
-    <row r="193" spans="1:17">
+      <c r="R192" s="5"/>
+    </row>
+    <row r="193" spans="1:18">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -5332,8 +5550,9 @@
       <c r="O193" s="5"/>
       <c r="P193" s="5"/>
       <c r="Q193" s="5"/>
-    </row>
-    <row r="194" spans="1:17">
+      <c r="R193" s="5"/>
+    </row>
+    <row r="194" spans="1:18">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -5351,8 +5570,9 @@
       <c r="O194" s="5"/>
       <c r="P194" s="5"/>
       <c r="Q194" s="5"/>
-    </row>
-    <row r="195" spans="1:17">
+      <c r="R194" s="5"/>
+    </row>
+    <row r="195" spans="1:18">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -5370,8 +5590,9 @@
       <c r="O195" s="5"/>
       <c r="P195" s="5"/>
       <c r="Q195" s="5"/>
-    </row>
-    <row r="196" spans="1:17">
+      <c r="R195" s="5"/>
+    </row>
+    <row r="196" spans="1:18">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -5389,8 +5610,9 @@
       <c r="O196" s="5"/>
       <c r="P196" s="5"/>
       <c r="Q196" s="5"/>
-    </row>
-    <row r="197" spans="1:17">
+      <c r="R196" s="5"/>
+    </row>
+    <row r="197" spans="1:18">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -5408,8 +5630,9 @@
       <c r="O197" s="5"/>
       <c r="P197" s="5"/>
       <c r="Q197" s="5"/>
-    </row>
-    <row r="198" spans="1:17">
+      <c r="R197" s="5"/>
+    </row>
+    <row r="198" spans="1:18">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -5427,8 +5650,9 @@
       <c r="O198" s="5"/>
       <c r="P198" s="5"/>
       <c r="Q198" s="5"/>
-    </row>
-    <row r="199" spans="1:17">
+      <c r="R198" s="5"/>
+    </row>
+    <row r="199" spans="1:18">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -5446,8 +5670,9 @@
       <c r="O199" s="5"/>
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
-    </row>
-    <row r="200" spans="1:17">
+      <c r="R199" s="5"/>
+    </row>
+    <row r="200" spans="1:18">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -5465,8 +5690,9 @@
       <c r="O200" s="5"/>
       <c r="P200" s="5"/>
       <c r="Q200" s="5"/>
-    </row>
-    <row r="201" spans="1:17">
+      <c r="R200" s="5"/>
+    </row>
+    <row r="201" spans="1:18">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -5484,8 +5710,9 @@
       <c r="O201" s="5"/>
       <c r="P201" s="5"/>
       <c r="Q201" s="5"/>
-    </row>
-    <row r="202" spans="1:17">
+      <c r="R201" s="5"/>
+    </row>
+    <row r="202" spans="1:18">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -5503,8 +5730,9 @@
       <c r="O202" s="5"/>
       <c r="P202" s="5"/>
       <c r="Q202" s="5"/>
-    </row>
-    <row r="203" spans="1:17">
+      <c r="R202" s="5"/>
+    </row>
+    <row r="203" spans="1:18">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -5522,8 +5750,9 @@
       <c r="O203" s="5"/>
       <c r="P203" s="5"/>
       <c r="Q203" s="5"/>
-    </row>
-    <row r="204" spans="1:17">
+      <c r="R203" s="5"/>
+    </row>
+    <row r="204" spans="1:18">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -5541,8 +5770,9 @@
       <c r="O204" s="5"/>
       <c r="P204" s="5"/>
       <c r="Q204" s="5"/>
-    </row>
-    <row r="205" spans="1:17">
+      <c r="R204" s="5"/>
+    </row>
+    <row r="205" spans="1:18">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -5560,8 +5790,9 @@
       <c r="O205" s="5"/>
       <c r="P205" s="5"/>
       <c r="Q205" s="5"/>
-    </row>
-    <row r="206" spans="1:17">
+      <c r="R205" s="5"/>
+    </row>
+    <row r="206" spans="1:18">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -5579,8 +5810,9 @@
       <c r="O206" s="5"/>
       <c r="P206" s="5"/>
       <c r="Q206" s="5"/>
-    </row>
-    <row r="207" spans="1:17">
+      <c r="R206" s="5"/>
+    </row>
+    <row r="207" spans="1:18">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -5598,8 +5830,9 @@
       <c r="O207" s="5"/>
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
-    </row>
-    <row r="208" spans="1:17">
+      <c r="R207" s="5"/>
+    </row>
+    <row r="208" spans="1:18">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -5617,8 +5850,9 @@
       <c r="O208" s="5"/>
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
-    </row>
-    <row r="209" spans="1:17">
+      <c r="R208" s="5"/>
+    </row>
+    <row r="209" spans="1:18">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -5636,8 +5870,9 @@
       <c r="O209" s="5"/>
       <c r="P209" s="5"/>
       <c r="Q209" s="5"/>
-    </row>
-    <row r="210" spans="1:17">
+      <c r="R209" s="5"/>
+    </row>
+    <row r="210" spans="1:18">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -5655,8 +5890,9 @@
       <c r="O210" s="5"/>
       <c r="P210" s="5"/>
       <c r="Q210" s="5"/>
-    </row>
-    <row r="211" spans="1:17">
+      <c r="R210" s="5"/>
+    </row>
+    <row r="211" spans="1:18">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -5674,8 +5910,9 @@
       <c r="O211" s="5"/>
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
-    </row>
-    <row r="212" spans="1:17">
+      <c r="R211" s="5"/>
+    </row>
+    <row r="212" spans="1:18">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -5693,8 +5930,9 @@
       <c r="O212" s="5"/>
       <c r="P212" s="5"/>
       <c r="Q212" s="5"/>
-    </row>
-    <row r="213" spans="1:17">
+      <c r="R212" s="5"/>
+    </row>
+    <row r="213" spans="1:18">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -5712,8 +5950,9 @@
       <c r="O213" s="5"/>
       <c r="P213" s="5"/>
       <c r="Q213" s="5"/>
-    </row>
-    <row r="214" spans="1:17">
+      <c r="R213" s="5"/>
+    </row>
+    <row r="214" spans="1:18">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -5731,8 +5970,9 @@
       <c r="O214" s="5"/>
       <c r="P214" s="5"/>
       <c r="Q214" s="5"/>
-    </row>
-    <row r="215" spans="1:17">
+      <c r="R214" s="5"/>
+    </row>
+    <row r="215" spans="1:18">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -5750,8 +5990,9 @@
       <c r="O215" s="5"/>
       <c r="P215" s="5"/>
       <c r="Q215" s="5"/>
-    </row>
-    <row r="216" spans="1:17">
+      <c r="R215" s="5"/>
+    </row>
+    <row r="216" spans="1:18">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -5769,8 +6010,9 @@
       <c r="O216" s="5"/>
       <c r="P216" s="5"/>
       <c r="Q216" s="5"/>
-    </row>
-    <row r="217" spans="1:17">
+      <c r="R216" s="5"/>
+    </row>
+    <row r="217" spans="1:18">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -5788,8 +6030,9 @@
       <c r="O217" s="5"/>
       <c r="P217" s="5"/>
       <c r="Q217" s="5"/>
-    </row>
-    <row r="218" spans="1:17">
+      <c r="R217" s="5"/>
+    </row>
+    <row r="218" spans="1:18">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -5807,8 +6050,9 @@
       <c r="O218" s="5"/>
       <c r="P218" s="5"/>
       <c r="Q218" s="5"/>
-    </row>
-    <row r="219" spans="1:17">
+      <c r="R218" s="5"/>
+    </row>
+    <row r="219" spans="1:18">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -5826,8 +6070,9 @@
       <c r="O219" s="5"/>
       <c r="P219" s="5"/>
       <c r="Q219" s="5"/>
-    </row>
-    <row r="220" spans="1:17">
+      <c r="R219" s="5"/>
+    </row>
+    <row r="220" spans="1:18">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -5845,8 +6090,9 @@
       <c r="O220" s="5"/>
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
-    </row>
-    <row r="221" spans="1:17">
+      <c r="R220" s="5"/>
+    </row>
+    <row r="221" spans="1:18">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -5864,8 +6110,9 @@
       <c r="O221" s="5"/>
       <c r="P221" s="5"/>
       <c r="Q221" s="5"/>
-    </row>
-    <row r="222" spans="1:17">
+      <c r="R221" s="5"/>
+    </row>
+    <row r="222" spans="1:18">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -5883,8 +6130,9 @@
       <c r="O222" s="5"/>
       <c r="P222" s="5"/>
       <c r="Q222" s="5"/>
-    </row>
-    <row r="223" spans="1:17">
+      <c r="R222" s="5"/>
+    </row>
+    <row r="223" spans="1:18">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -5902,8 +6150,9 @@
       <c r="O223" s="5"/>
       <c r="P223" s="5"/>
       <c r="Q223" s="5"/>
-    </row>
-    <row r="224" spans="1:17">
+      <c r="R223" s="5"/>
+    </row>
+    <row r="224" spans="1:18">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -5921,8 +6170,9 @@
       <c r="O224" s="5"/>
       <c r="P224" s="5"/>
       <c r="Q224" s="5"/>
-    </row>
-    <row r="225" spans="1:17">
+      <c r="R224" s="5"/>
+    </row>
+    <row r="225" spans="1:18">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -5940,8 +6190,9 @@
       <c r="O225" s="5"/>
       <c r="P225" s="5"/>
       <c r="Q225" s="5"/>
-    </row>
-    <row r="226" spans="1:17">
+      <c r="R225" s="5"/>
+    </row>
+    <row r="226" spans="1:18">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -5959,8 +6210,9 @@
       <c r="O226" s="5"/>
       <c r="P226" s="5"/>
       <c r="Q226" s="5"/>
-    </row>
-    <row r="227" spans="1:17">
+      <c r="R226" s="5"/>
+    </row>
+    <row r="227" spans="1:18">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -5978,8 +6230,9 @@
       <c r="O227" s="5"/>
       <c r="P227" s="5"/>
       <c r="Q227" s="5"/>
-    </row>
-    <row r="228" spans="1:17">
+      <c r="R227" s="5"/>
+    </row>
+    <row r="228" spans="1:18">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -5997,8 +6250,9 @@
       <c r="O228" s="5"/>
       <c r="P228" s="5"/>
       <c r="Q228" s="5"/>
-    </row>
-    <row r="229" spans="1:17">
+      <c r="R228" s="5"/>
+    </row>
+    <row r="229" spans="1:18">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -6016,8 +6270,9 @@
       <c r="O229" s="5"/>
       <c r="P229" s="5"/>
       <c r="Q229" s="5"/>
-    </row>
-    <row r="230" spans="1:17">
+      <c r="R229" s="5"/>
+    </row>
+    <row r="230" spans="1:18">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -6035,8 +6290,9 @@
       <c r="O230" s="5"/>
       <c r="P230" s="5"/>
       <c r="Q230" s="5"/>
-    </row>
-    <row r="231" spans="1:17">
+      <c r="R230" s="5"/>
+    </row>
+    <row r="231" spans="1:18">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -6054,8 +6310,9 @@
       <c r="O231" s="5"/>
       <c r="P231" s="5"/>
       <c r="Q231" s="5"/>
-    </row>
-    <row r="232" spans="1:17">
+      <c r="R231" s="5"/>
+    </row>
+    <row r="232" spans="1:18">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -6073,8 +6330,9 @@
       <c r="O232" s="5"/>
       <c r="P232" s="5"/>
       <c r="Q232" s="5"/>
-    </row>
-    <row r="233" spans="1:17">
+      <c r="R232" s="5"/>
+    </row>
+    <row r="233" spans="1:18">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -6092,8 +6350,9 @@
       <c r="O233" s="5"/>
       <c r="P233" s="5"/>
       <c r="Q233" s="5"/>
-    </row>
-    <row r="234" spans="1:17">
+      <c r="R233" s="5"/>
+    </row>
+    <row r="234" spans="1:18">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -6111,8 +6370,9 @@
       <c r="O234" s="5"/>
       <c r="P234" s="5"/>
       <c r="Q234" s="5"/>
-    </row>
-    <row r="235" spans="1:17">
+      <c r="R234" s="5"/>
+    </row>
+    <row r="235" spans="1:18">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -6130,8 +6390,9 @@
       <c r="O235" s="5"/>
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
-    </row>
-    <row r="236" spans="1:17">
+      <c r="R235" s="5"/>
+    </row>
+    <row r="236" spans="1:18">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -6149,8 +6410,9 @@
       <c r="O236" s="5"/>
       <c r="P236" s="5"/>
       <c r="Q236" s="5"/>
-    </row>
-    <row r="237" spans="1:17">
+      <c r="R236" s="5"/>
+    </row>
+    <row r="237" spans="1:18">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -6168,8 +6430,9 @@
       <c r="O237" s="5"/>
       <c r="P237" s="5"/>
       <c r="Q237" s="5"/>
-    </row>
-    <row r="238" spans="1:17">
+      <c r="R237" s="5"/>
+    </row>
+    <row r="238" spans="1:18">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -6187,8 +6450,9 @@
       <c r="O238" s="5"/>
       <c r="P238" s="5"/>
       <c r="Q238" s="5"/>
-    </row>
-    <row r="239" spans="1:17">
+      <c r="R238" s="5"/>
+    </row>
+    <row r="239" spans="1:18">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -6206,8 +6470,9 @@
       <c r="O239" s="5"/>
       <c r="P239" s="5"/>
       <c r="Q239" s="5"/>
-    </row>
-    <row r="240" spans="1:17">
+      <c r="R239" s="5"/>
+    </row>
+    <row r="240" spans="1:18">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -6225,8 +6490,9 @@
       <c r="O240" s="5"/>
       <c r="P240" s="5"/>
       <c r="Q240" s="5"/>
-    </row>
-    <row r="241" spans="1:17">
+      <c r="R240" s="5"/>
+    </row>
+    <row r="241" spans="1:18">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -6244,8 +6510,9 @@
       <c r="O241" s="5"/>
       <c r="P241" s="5"/>
       <c r="Q241" s="5"/>
-    </row>
-    <row r="242" spans="1:17">
+      <c r="R241" s="5"/>
+    </row>
+    <row r="242" spans="1:18">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -6263,8 +6530,9 @@
       <c r="O242" s="5"/>
       <c r="P242" s="5"/>
       <c r="Q242" s="5"/>
-    </row>
-    <row r="243" spans="1:17">
+      <c r="R242" s="5"/>
+    </row>
+    <row r="243" spans="1:18">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -6282,8 +6550,9 @@
       <c r="O243" s="5"/>
       <c r="P243" s="5"/>
       <c r="Q243" s="5"/>
-    </row>
-    <row r="244" spans="1:17">
+      <c r="R243" s="5"/>
+    </row>
+    <row r="244" spans="1:18">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -6301,8 +6570,9 @@
       <c r="O244" s="5"/>
       <c r="P244" s="5"/>
       <c r="Q244" s="5"/>
-    </row>
-    <row r="245" spans="1:17">
+      <c r="R244" s="5"/>
+    </row>
+    <row r="245" spans="1:18">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -6320,8 +6590,9 @@
       <c r="O245" s="5"/>
       <c r="P245" s="5"/>
       <c r="Q245" s="5"/>
-    </row>
-    <row r="246" spans="1:17">
+      <c r="R245" s="5"/>
+    </row>
+    <row r="246" spans="1:18">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -6339,8 +6610,9 @@
       <c r="O246" s="5"/>
       <c r="P246" s="5"/>
       <c r="Q246" s="5"/>
-    </row>
-    <row r="247" spans="1:17">
+      <c r="R246" s="5"/>
+    </row>
+    <row r="247" spans="1:18">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -6358,8 +6630,9 @@
       <c r="O247" s="5"/>
       <c r="P247" s="5"/>
       <c r="Q247" s="5"/>
-    </row>
-    <row r="248" spans="1:17">
+      <c r="R247" s="5"/>
+    </row>
+    <row r="248" spans="1:18">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -6377,8 +6650,9 @@
       <c r="O248" s="5"/>
       <c r="P248" s="5"/>
       <c r="Q248" s="5"/>
-    </row>
-    <row r="249" spans="1:17">
+      <c r="R248" s="5"/>
+    </row>
+    <row r="249" spans="1:18">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -6396,8 +6670,9 @@
       <c r="O249" s="5"/>
       <c r="P249" s="5"/>
       <c r="Q249" s="5"/>
-    </row>
-    <row r="250" spans="1:17">
+      <c r="R249" s="5"/>
+    </row>
+    <row r="250" spans="1:18">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -6415,8 +6690,9 @@
       <c r="O250" s="5"/>
       <c r="P250" s="5"/>
       <c r="Q250" s="5"/>
-    </row>
-    <row r="251" spans="1:17">
+      <c r="R250" s="5"/>
+    </row>
+    <row r="251" spans="1:18">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -6434,8 +6710,9 @@
       <c r="O251" s="5"/>
       <c r="P251" s="5"/>
       <c r="Q251" s="5"/>
-    </row>
-    <row r="252" spans="1:17">
+      <c r="R251" s="5"/>
+    </row>
+    <row r="252" spans="1:18">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6453,8 +6730,9 @@
       <c r="O252" s="5"/>
       <c r="P252" s="5"/>
       <c r="Q252" s="5"/>
-    </row>
-    <row r="253" spans="1:17">
+      <c r="R252" s="5"/>
+    </row>
+    <row r="253" spans="1:18">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6472,8 +6750,9 @@
       <c r="O253" s="5"/>
       <c r="P253" s="5"/>
       <c r="Q253" s="5"/>
-    </row>
-    <row r="254" spans="1:17">
+      <c r="R253" s="5"/>
+    </row>
+    <row r="254" spans="1:18">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6491,8 +6770,9 @@
       <c r="O254" s="5"/>
       <c r="P254" s="5"/>
       <c r="Q254" s="5"/>
-    </row>
-    <row r="255" spans="1:17">
+      <c r="R254" s="5"/>
+    </row>
+    <row r="255" spans="1:18">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -6510,8 +6790,9 @@
       <c r="O255" s="5"/>
       <c r="P255" s="5"/>
       <c r="Q255" s="5"/>
-    </row>
-    <row r="256" spans="1:17">
+      <c r="R255" s="5"/>
+    </row>
+    <row r="256" spans="1:18">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6529,8 +6810,9 @@
       <c r="O256" s="5"/>
       <c r="P256" s="5"/>
       <c r="Q256" s="5"/>
-    </row>
-    <row r="257" spans="1:17">
+      <c r="R256" s="5"/>
+    </row>
+    <row r="257" spans="1:18">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6548,8 +6830,9 @@
       <c r="O257" s="5"/>
       <c r="P257" s="5"/>
       <c r="Q257" s="5"/>
-    </row>
-    <row r="258" spans="1:17">
+      <c r="R257" s="5"/>
+    </row>
+    <row r="258" spans="1:18">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6567,8 +6850,9 @@
       <c r="O258" s="5"/>
       <c r="P258" s="5"/>
       <c r="Q258" s="5"/>
-    </row>
-    <row r="259" spans="1:17">
+      <c r="R258" s="5"/>
+    </row>
+    <row r="259" spans="1:18">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -6586,8 +6870,9 @@
       <c r="O259" s="5"/>
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
-    </row>
-    <row r="260" spans="1:17">
+      <c r="R259" s="5"/>
+    </row>
+    <row r="260" spans="1:18">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -6605,8 +6890,9 @@
       <c r="O260" s="5"/>
       <c r="P260" s="5"/>
       <c r="Q260" s="5"/>
-    </row>
-    <row r="261" spans="1:17">
+      <c r="R260" s="5"/>
+    </row>
+    <row r="261" spans="1:18">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -6624,8 +6910,9 @@
       <c r="O261" s="5"/>
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
-    </row>
-    <row r="262" spans="1:17">
+      <c r="R261" s="5"/>
+    </row>
+    <row r="262" spans="1:18">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -6643,8 +6930,9 @@
       <c r="O262" s="5"/>
       <c r="P262" s="5"/>
       <c r="Q262" s="5"/>
-    </row>
-    <row r="263" spans="1:17">
+      <c r="R262" s="5"/>
+    </row>
+    <row r="263" spans="1:18">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -6662,8 +6950,9 @@
       <c r="O263" s="5"/>
       <c r="P263" s="5"/>
       <c r="Q263" s="5"/>
-    </row>
-    <row r="264" spans="1:17">
+      <c r="R263" s="5"/>
+    </row>
+    <row r="264" spans="1:18">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -6681,8 +6970,9 @@
       <c r="O264" s="5"/>
       <c r="P264" s="5"/>
       <c r="Q264" s="5"/>
-    </row>
-    <row r="265" spans="1:17">
+      <c r="R264" s="5"/>
+    </row>
+    <row r="265" spans="1:18">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -6700,8 +6990,9 @@
       <c r="O265" s="5"/>
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
-    </row>
-    <row r="266" spans="1:17">
+      <c r="R265" s="5"/>
+    </row>
+    <row r="266" spans="1:18">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -6719,8 +7010,9 @@
       <c r="O266" s="5"/>
       <c r="P266" s="5"/>
       <c r="Q266" s="5"/>
-    </row>
-    <row r="267" spans="1:17">
+      <c r="R266" s="5"/>
+    </row>
+    <row r="267" spans="1:18">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -6738,8 +7030,9 @@
       <c r="O267" s="5"/>
       <c r="P267" s="5"/>
       <c r="Q267" s="5"/>
-    </row>
-    <row r="268" spans="1:17">
+      <c r="R267" s="5"/>
+    </row>
+    <row r="268" spans="1:18">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -6757,8 +7050,9 @@
       <c r="O268" s="5"/>
       <c r="P268" s="5"/>
       <c r="Q268" s="5"/>
-    </row>
-    <row r="269" spans="1:17">
+      <c r="R268" s="5"/>
+    </row>
+    <row r="269" spans="1:18">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -6776,8 +7070,9 @@
       <c r="O269" s="5"/>
       <c r="P269" s="5"/>
       <c r="Q269" s="5"/>
-    </row>
-    <row r="270" spans="1:17">
+      <c r="R269" s="5"/>
+    </row>
+    <row r="270" spans="1:18">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -6795,8 +7090,9 @@
       <c r="O270" s="5"/>
       <c r="P270" s="5"/>
       <c r="Q270" s="5"/>
-    </row>
-    <row r="271" spans="1:17">
+      <c r="R270" s="5"/>
+    </row>
+    <row r="271" spans="1:18">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -6814,8 +7110,9 @@
       <c r="O271" s="5"/>
       <c r="P271" s="5"/>
       <c r="Q271" s="5"/>
-    </row>
-    <row r="272" spans="1:17">
+      <c r="R271" s="5"/>
+    </row>
+    <row r="272" spans="1:18">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -6833,8 +7130,9 @@
       <c r="O272" s="5"/>
       <c r="P272" s="5"/>
       <c r="Q272" s="5"/>
-    </row>
-    <row r="273" spans="1:17">
+      <c r="R272" s="5"/>
+    </row>
+    <row r="273" spans="1:18">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -6852,8 +7150,9 @@
       <c r="O273" s="5"/>
       <c r="P273" s="5"/>
       <c r="Q273" s="5"/>
-    </row>
-    <row r="274" spans="1:17">
+      <c r="R273" s="5"/>
+    </row>
+    <row r="274" spans="1:18">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -6871,8 +7170,9 @@
       <c r="O274" s="5"/>
       <c r="P274" s="5"/>
       <c r="Q274" s="5"/>
-    </row>
-    <row r="275" spans="1:17">
+      <c r="R274" s="5"/>
+    </row>
+    <row r="275" spans="1:18">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -6890,8 +7190,9 @@
       <c r="O275" s="5"/>
       <c r="P275" s="5"/>
       <c r="Q275" s="5"/>
-    </row>
-    <row r="276" spans="1:17">
+      <c r="R275" s="5"/>
+    </row>
+    <row r="276" spans="1:18">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -6909,8 +7210,9 @@
       <c r="O276" s="5"/>
       <c r="P276" s="5"/>
       <c r="Q276" s="5"/>
-    </row>
-    <row r="277" spans="1:17">
+      <c r="R276" s="5"/>
+    </row>
+    <row r="277" spans="1:18">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -6928,8 +7230,9 @@
       <c r="O277" s="5"/>
       <c r="P277" s="5"/>
       <c r="Q277" s="5"/>
-    </row>
-    <row r="278" spans="1:17">
+      <c r="R277" s="5"/>
+    </row>
+    <row r="278" spans="1:18">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -6947,8 +7250,9 @@
       <c r="O278" s="5"/>
       <c r="P278" s="5"/>
       <c r="Q278" s="5"/>
-    </row>
-    <row r="279" spans="1:17">
+      <c r="R278" s="5"/>
+    </row>
+    <row r="279" spans="1:18">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -6966,8 +7270,9 @@
       <c r="O279" s="5"/>
       <c r="P279" s="5"/>
       <c r="Q279" s="5"/>
-    </row>
-    <row r="280" spans="1:17">
+      <c r="R279" s="5"/>
+    </row>
+    <row r="280" spans="1:18">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -6985,8 +7290,9 @@
       <c r="O280" s="5"/>
       <c r="P280" s="5"/>
       <c r="Q280" s="5"/>
-    </row>
-    <row r="281" spans="1:17">
+      <c r="R280" s="5"/>
+    </row>
+    <row r="281" spans="1:18">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -7004,8 +7310,9 @@
       <c r="O281" s="5"/>
       <c r="P281" s="5"/>
       <c r="Q281" s="5"/>
-    </row>
-    <row r="282" spans="1:17">
+      <c r="R281" s="5"/>
+    </row>
+    <row r="282" spans="1:18">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -7023,8 +7330,9 @@
       <c r="O282" s="5"/>
       <c r="P282" s="5"/>
       <c r="Q282" s="5"/>
-    </row>
-    <row r="283" spans="1:17">
+      <c r="R282" s="5"/>
+    </row>
+    <row r="283" spans="1:18">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -7042,8 +7350,9 @@
       <c r="O283" s="5"/>
       <c r="P283" s="5"/>
       <c r="Q283" s="5"/>
-    </row>
-    <row r="284" spans="1:17">
+      <c r="R283" s="5"/>
+    </row>
+    <row r="284" spans="1:18">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -7061,8 +7370,9 @@
       <c r="O284" s="5"/>
       <c r="P284" s="5"/>
       <c r="Q284" s="5"/>
-    </row>
-    <row r="285" spans="1:17">
+      <c r="R284" s="5"/>
+    </row>
+    <row r="285" spans="1:18">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -7080,8 +7390,9 @@
       <c r="O285" s="5"/>
       <c r="P285" s="5"/>
       <c r="Q285" s="5"/>
-    </row>
-    <row r="286" spans="1:17">
+      <c r="R285" s="5"/>
+    </row>
+    <row r="286" spans="1:18">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -7099,8 +7410,9 @@
       <c r="O286" s="5"/>
       <c r="P286" s="5"/>
       <c r="Q286" s="5"/>
-    </row>
-    <row r="287" spans="1:17">
+      <c r="R286" s="5"/>
+    </row>
+    <row r="287" spans="1:18">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -7118,8 +7430,9 @@
       <c r="O287" s="5"/>
       <c r="P287" s="5"/>
       <c r="Q287" s="5"/>
-    </row>
-    <row r="288" spans="1:17">
+      <c r="R287" s="5"/>
+    </row>
+    <row r="288" spans="1:18">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -7137,8 +7450,9 @@
       <c r="O288" s="5"/>
       <c r="P288" s="5"/>
       <c r="Q288" s="5"/>
-    </row>
-    <row r="289" spans="1:17">
+      <c r="R288" s="5"/>
+    </row>
+    <row r="289" spans="1:18">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -7156,8 +7470,9 @@
       <c r="O289" s="5"/>
       <c r="P289" s="5"/>
       <c r="Q289" s="5"/>
-    </row>
-    <row r="290" spans="1:17">
+      <c r="R289" s="5"/>
+    </row>
+    <row r="290" spans="1:18">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -7175,8 +7490,9 @@
       <c r="O290" s="5"/>
       <c r="P290" s="5"/>
       <c r="Q290" s="5"/>
-    </row>
-    <row r="291" spans="1:17">
+      <c r="R290" s="5"/>
+    </row>
+    <row r="291" spans="1:18">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -7194,8 +7510,9 @@
       <c r="O291" s="5"/>
       <c r="P291" s="5"/>
       <c r="Q291" s="5"/>
-    </row>
-    <row r="292" spans="1:17">
+      <c r="R291" s="5"/>
+    </row>
+    <row r="292" spans="1:18">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -7213,8 +7530,9 @@
       <c r="O292" s="5"/>
       <c r="P292" s="5"/>
       <c r="Q292" s="5"/>
-    </row>
-    <row r="293" spans="1:17">
+      <c r="R292" s="5"/>
+    </row>
+    <row r="293" spans="1:18">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -7232,8 +7550,9 @@
       <c r="O293" s="5"/>
       <c r="P293" s="5"/>
       <c r="Q293" s="5"/>
-    </row>
-    <row r="294" spans="1:17">
+      <c r="R293" s="5"/>
+    </row>
+    <row r="294" spans="1:18">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -7251,8 +7570,9 @@
       <c r="O294" s="5"/>
       <c r="P294" s="5"/>
       <c r="Q294" s="5"/>
-    </row>
-    <row r="295" spans="1:17">
+      <c r="R294" s="5"/>
+    </row>
+    <row r="295" spans="1:18">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -7270,8 +7590,9 @@
       <c r="O295" s="5"/>
       <c r="P295" s="5"/>
       <c r="Q295" s="5"/>
-    </row>
-    <row r="296" spans="1:17">
+      <c r="R295" s="5"/>
+    </row>
+    <row r="296" spans="1:18">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -7289,8 +7610,9 @@
       <c r="O296" s="5"/>
       <c r="P296" s="5"/>
       <c r="Q296" s="5"/>
-    </row>
-    <row r="297" spans="1:17">
+      <c r="R296" s="5"/>
+    </row>
+    <row r="297" spans="1:18">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -7308,8 +7630,9 @@
       <c r="O297" s="5"/>
       <c r="P297" s="5"/>
       <c r="Q297" s="5"/>
-    </row>
-    <row r="298" spans="1:17">
+      <c r="R297" s="5"/>
+    </row>
+    <row r="298" spans="1:18">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -7327,8 +7650,9 @@
       <c r="O298" s="5"/>
       <c r="P298" s="5"/>
       <c r="Q298" s="5"/>
-    </row>
-    <row r="299" spans="1:17">
+      <c r="R298" s="5"/>
+    </row>
+    <row r="299" spans="1:18">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -7346,8 +7670,9 @@
       <c r="O299" s="5"/>
       <c r="P299" s="5"/>
       <c r="Q299" s="5"/>
-    </row>
-    <row r="300" spans="1:17">
+      <c r="R299" s="5"/>
+    </row>
+    <row r="300" spans="1:18">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -7365,8 +7690,9 @@
       <c r="O300" s="5"/>
       <c r="P300" s="5"/>
       <c r="Q300" s="5"/>
-    </row>
-    <row r="301" spans="1:17">
+      <c r="R300" s="5"/>
+    </row>
+    <row r="301" spans="1:18">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -7384,8 +7710,9 @@
       <c r="O301" s="5"/>
       <c r="P301" s="5"/>
       <c r="Q301" s="5"/>
-    </row>
-    <row r="302" spans="1:17">
+      <c r="R301" s="5"/>
+    </row>
+    <row r="302" spans="1:18">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -7403,8 +7730,9 @@
       <c r="O302" s="5"/>
       <c r="P302" s="5"/>
       <c r="Q302" s="5"/>
-    </row>
-    <row r="303" spans="1:17">
+      <c r="R302" s="5"/>
+    </row>
+    <row r="303" spans="1:18">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -7422,8 +7750,9 @@
       <c r="O303" s="5"/>
       <c r="P303" s="5"/>
       <c r="Q303" s="5"/>
-    </row>
-    <row r="304" spans="1:17">
+      <c r="R303" s="5"/>
+    </row>
+    <row r="304" spans="1:18">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -7441,8 +7770,9 @@
       <c r="O304" s="5"/>
       <c r="P304" s="5"/>
       <c r="Q304" s="5"/>
-    </row>
-    <row r="305" spans="1:17">
+      <c r="R304" s="5"/>
+    </row>
+    <row r="305" spans="1:18">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -7460,8 +7790,9 @@
       <c r="O305" s="5"/>
       <c r="P305" s="5"/>
       <c r="Q305" s="5"/>
-    </row>
-    <row r="306" spans="1:17">
+      <c r="R305" s="5"/>
+    </row>
+    <row r="306" spans="1:18">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -7479,8 +7810,9 @@
       <c r="O306" s="5"/>
       <c r="P306" s="5"/>
       <c r="Q306" s="5"/>
-    </row>
-    <row r="307" spans="1:17">
+      <c r="R306" s="5"/>
+    </row>
+    <row r="307" spans="1:18">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -7498,8 +7830,9 @@
       <c r="O307" s="5"/>
       <c r="P307" s="5"/>
       <c r="Q307" s="5"/>
-    </row>
-    <row r="308" spans="1:17">
+      <c r="R307" s="5"/>
+    </row>
+    <row r="308" spans="1:18">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -7517,8 +7850,9 @@
       <c r="O308" s="5"/>
       <c r="P308" s="5"/>
       <c r="Q308" s="5"/>
-    </row>
-    <row r="309" spans="1:17">
+      <c r="R308" s="5"/>
+    </row>
+    <row r="309" spans="1:18">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -7536,8 +7870,9 @@
       <c r="O309" s="5"/>
       <c r="P309" s="5"/>
       <c r="Q309" s="5"/>
-    </row>
-    <row r="310" spans="1:17">
+      <c r="R309" s="5"/>
+    </row>
+    <row r="310" spans="1:18">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -7555,8 +7890,9 @@
       <c r="O310" s="5"/>
       <c r="P310" s="5"/>
       <c r="Q310" s="5"/>
-    </row>
-    <row r="311" spans="1:17">
+      <c r="R310" s="5"/>
+    </row>
+    <row r="311" spans="1:18">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -7574,8 +7910,9 @@
       <c r="O311" s="5"/>
       <c r="P311" s="5"/>
       <c r="Q311" s="5"/>
-    </row>
-    <row r="312" spans="1:17">
+      <c r="R311" s="5"/>
+    </row>
+    <row r="312" spans="1:18">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -7593,8 +7930,9 @@
       <c r="O312" s="5"/>
       <c r="P312" s="5"/>
       <c r="Q312" s="5"/>
-    </row>
-    <row r="313" spans="1:17">
+      <c r="R312" s="5"/>
+    </row>
+    <row r="313" spans="1:18">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -7612,8 +7950,9 @@
       <c r="O313" s="5"/>
       <c r="P313" s="5"/>
       <c r="Q313" s="5"/>
-    </row>
-    <row r="314" spans="1:17">
+      <c r="R313" s="5"/>
+    </row>
+    <row r="314" spans="1:18">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -7631,8 +7970,9 @@
       <c r="O314" s="5"/>
       <c r="P314" s="5"/>
       <c r="Q314" s="5"/>
-    </row>
-    <row r="315" spans="1:17">
+      <c r="R314" s="5"/>
+    </row>
+    <row r="315" spans="1:18">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -7650,8 +7990,9 @@
       <c r="O315" s="5"/>
       <c r="P315" s="5"/>
       <c r="Q315" s="5"/>
-    </row>
-    <row r="316" spans="1:17">
+      <c r="R315" s="5"/>
+    </row>
+    <row r="316" spans="1:18">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -7669,8 +8010,9 @@
       <c r="O316" s="5"/>
       <c r="P316" s="5"/>
       <c r="Q316" s="5"/>
-    </row>
-    <row r="317" spans="1:17">
+      <c r="R316" s="5"/>
+    </row>
+    <row r="317" spans="1:18">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -7688,8 +8030,9 @@
       <c r="O317" s="5"/>
       <c r="P317" s="5"/>
       <c r="Q317" s="5"/>
-    </row>
-    <row r="318" spans="1:17">
+      <c r="R317" s="5"/>
+    </row>
+    <row r="318" spans="1:18">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -7707,8 +8050,9 @@
       <c r="O318" s="5"/>
       <c r="P318" s="5"/>
       <c r="Q318" s="5"/>
-    </row>
-    <row r="319" spans="1:17">
+      <c r="R318" s="5"/>
+    </row>
+    <row r="319" spans="1:18">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -7726,8 +8070,9 @@
       <c r="O319" s="5"/>
       <c r="P319" s="5"/>
       <c r="Q319" s="5"/>
-    </row>
-    <row r="320" spans="1:17">
+      <c r="R319" s="5"/>
+    </row>
+    <row r="320" spans="1:18">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -7745,8 +8090,9 @@
       <c r="O320" s="5"/>
       <c r="P320" s="5"/>
       <c r="Q320" s="5"/>
-    </row>
-    <row r="321" spans="1:17">
+      <c r="R320" s="5"/>
+    </row>
+    <row r="321" spans="1:18">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -7764,8 +8110,9 @@
       <c r="O321" s="5"/>
       <c r="P321" s="5"/>
       <c r="Q321" s="5"/>
-    </row>
-    <row r="322" spans="1:17">
+      <c r="R321" s="5"/>
+    </row>
+    <row r="322" spans="1:18">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -7783,8 +8130,9 @@
       <c r="O322" s="5"/>
       <c r="P322" s="5"/>
       <c r="Q322" s="5"/>
-    </row>
-    <row r="323" spans="1:17">
+      <c r="R322" s="5"/>
+    </row>
+    <row r="323" spans="1:18">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -7802,8 +8150,9 @@
       <c r="O323" s="5"/>
       <c r="P323" s="5"/>
       <c r="Q323" s="5"/>
-    </row>
-    <row r="324" spans="1:17">
+      <c r="R323" s="5"/>
+    </row>
+    <row r="324" spans="1:18">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -7821,8 +8170,9 @@
       <c r="O324" s="5"/>
       <c r="P324" s="5"/>
       <c r="Q324" s="5"/>
-    </row>
-    <row r="325" spans="1:17">
+      <c r="R324" s="5"/>
+    </row>
+    <row r="325" spans="1:18">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -7840,8 +8190,9 @@
       <c r="O325" s="5"/>
       <c r="P325" s="5"/>
       <c r="Q325" s="5"/>
-    </row>
-    <row r="326" spans="1:17">
+      <c r="R325" s="5"/>
+    </row>
+    <row r="326" spans="1:18">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -7859,8 +8210,9 @@
       <c r="O326" s="5"/>
       <c r="P326" s="5"/>
       <c r="Q326" s="5"/>
-    </row>
-    <row r="327" spans="1:17">
+      <c r="R326" s="5"/>
+    </row>
+    <row r="327" spans="1:18">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -7878,8 +8230,9 @@
       <c r="O327" s="5"/>
       <c r="P327" s="5"/>
       <c r="Q327" s="5"/>
-    </row>
-    <row r="328" spans="1:17">
+      <c r="R327" s="5"/>
+    </row>
+    <row r="328" spans="1:18">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -7897,8 +8250,9 @@
       <c r="O328" s="5"/>
       <c r="P328" s="5"/>
       <c r="Q328" s="5"/>
-    </row>
-    <row r="329" spans="1:17">
+      <c r="R328" s="5"/>
+    </row>
+    <row r="329" spans="1:18">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -7916,8 +8270,9 @@
       <c r="O329" s="5"/>
       <c r="P329" s="5"/>
       <c r="Q329" s="5"/>
-    </row>
-    <row r="330" spans="1:17">
+      <c r="R329" s="5"/>
+    </row>
+    <row r="330" spans="1:18">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -7935,8 +8290,9 @@
       <c r="O330" s="5"/>
       <c r="P330" s="5"/>
       <c r="Q330" s="5"/>
-    </row>
-    <row r="331" spans="1:17">
+      <c r="R330" s="5"/>
+    </row>
+    <row r="331" spans="1:18">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -7954,8 +8310,9 @@
       <c r="O331" s="5"/>
       <c r="P331" s="5"/>
       <c r="Q331" s="5"/>
-    </row>
-    <row r="332" spans="1:17">
+      <c r="R331" s="5"/>
+    </row>
+    <row r="332" spans="1:18">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -7973,8 +8330,9 @@
       <c r="O332" s="5"/>
       <c r="P332" s="5"/>
       <c r="Q332" s="5"/>
-    </row>
-    <row r="333" spans="1:17">
+      <c r="R332" s="5"/>
+    </row>
+    <row r="333" spans="1:18">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -7992,8 +8350,9 @@
       <c r="O333" s="5"/>
       <c r="P333" s="5"/>
       <c r="Q333" s="5"/>
-    </row>
-    <row r="334" spans="1:17">
+      <c r="R333" s="5"/>
+    </row>
+    <row r="334" spans="1:18">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -8011,8 +8370,9 @@
       <c r="O334" s="5"/>
       <c r="P334" s="5"/>
       <c r="Q334" s="5"/>
-    </row>
-    <row r="335" spans="1:17">
+      <c r="R334" s="5"/>
+    </row>
+    <row r="335" spans="1:18">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -8030,8 +8390,9 @@
       <c r="O335" s="5"/>
       <c r="P335" s="5"/>
       <c r="Q335" s="5"/>
-    </row>
-    <row r="336" spans="1:17">
+      <c r="R335" s="5"/>
+    </row>
+    <row r="336" spans="1:18">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -8049,8 +8410,9 @@
       <c r="O336" s="5"/>
       <c r="P336" s="5"/>
       <c r="Q336" s="5"/>
-    </row>
-    <row r="337" spans="1:17">
+      <c r="R336" s="5"/>
+    </row>
+    <row r="337" spans="1:18">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -8068,8 +8430,9 @@
       <c r="O337" s="5"/>
       <c r="P337" s="5"/>
       <c r="Q337" s="5"/>
-    </row>
-    <row r="338" spans="1:17">
+      <c r="R337" s="5"/>
+    </row>
+    <row r="338" spans="1:18">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -8087,8 +8450,9 @@
       <c r="O338" s="5"/>
       <c r="P338" s="5"/>
       <c r="Q338" s="5"/>
-    </row>
-    <row r="339" spans="1:17">
+      <c r="R338" s="5"/>
+    </row>
+    <row r="339" spans="1:18">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -8106,8 +8470,9 @@
       <c r="O339" s="5"/>
       <c r="P339" s="5"/>
       <c r="Q339" s="5"/>
-    </row>
-    <row r="340" spans="1:17">
+      <c r="R339" s="5"/>
+    </row>
+    <row r="340" spans="1:18">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -8125,8 +8490,9 @@
       <c r="O340" s="5"/>
       <c r="P340" s="5"/>
       <c r="Q340" s="5"/>
-    </row>
-    <row r="341" spans="1:17">
+      <c r="R340" s="5"/>
+    </row>
+    <row r="341" spans="1:18">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8144,8 +8510,9 @@
       <c r="O341" s="5"/>
       <c r="P341" s="5"/>
       <c r="Q341" s="5"/>
-    </row>
-    <row r="342" spans="1:17">
+      <c r="R341" s="5"/>
+    </row>
+    <row r="342" spans="1:18">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -8163,8 +8530,9 @@
       <c r="O342" s="5"/>
       <c r="P342" s="5"/>
       <c r="Q342" s="5"/>
-    </row>
-    <row r="343" spans="1:17">
+      <c r="R342" s="5"/>
+    </row>
+    <row r="343" spans="1:18">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -8182,8 +8550,9 @@
       <c r="O343" s="5"/>
       <c r="P343" s="5"/>
       <c r="Q343" s="5"/>
-    </row>
-    <row r="344" spans="1:17">
+      <c r="R343" s="5"/>
+    </row>
+    <row r="344" spans="1:18">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -8201,8 +8570,9 @@
       <c r="O344" s="5"/>
       <c r="P344" s="5"/>
       <c r="Q344" s="5"/>
-    </row>
-    <row r="345" spans="1:17">
+      <c r="R344" s="5"/>
+    </row>
+    <row r="345" spans="1:18">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -8220,8 +8590,9 @@
       <c r="O345" s="5"/>
       <c r="P345" s="5"/>
       <c r="Q345" s="5"/>
-    </row>
-    <row r="346" spans="1:17">
+      <c r="R345" s="5"/>
+    </row>
+    <row r="346" spans="1:18">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -8239,8 +8610,9 @@
       <c r="O346" s="5"/>
       <c r="P346" s="5"/>
       <c r="Q346" s="5"/>
-    </row>
-    <row r="347" spans="1:17">
+      <c r="R346" s="5"/>
+    </row>
+    <row r="347" spans="1:18">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -8258,8 +8630,9 @@
       <c r="O347" s="5"/>
       <c r="P347" s="5"/>
       <c r="Q347" s="5"/>
-    </row>
-    <row r="348" spans="1:17">
+      <c r="R347" s="5"/>
+    </row>
+    <row r="348" spans="1:18">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -8277,8 +8650,9 @@
       <c r="O348" s="5"/>
       <c r="P348" s="5"/>
       <c r="Q348" s="5"/>
-    </row>
-    <row r="349" spans="1:17">
+      <c r="R348" s="5"/>
+    </row>
+    <row r="349" spans="1:18">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -8296,8 +8670,9 @@
       <c r="O349" s="5"/>
       <c r="P349" s="5"/>
       <c r="Q349" s="5"/>
-    </row>
-    <row r="350" spans="1:17">
+      <c r="R349" s="5"/>
+    </row>
+    <row r="350" spans="1:18">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -8315,8 +8690,9 @@
       <c r="O350" s="5"/>
       <c r="P350" s="5"/>
       <c r="Q350" s="5"/>
-    </row>
-    <row r="351" spans="1:17">
+      <c r="R350" s="5"/>
+    </row>
+    <row r="351" spans="1:18">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -8334,8 +8710,9 @@
       <c r="O351" s="5"/>
       <c r="P351" s="5"/>
       <c r="Q351" s="5"/>
-    </row>
-    <row r="352" spans="1:17">
+      <c r="R351" s="5"/>
+    </row>
+    <row r="352" spans="1:18">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -8353,8 +8730,9 @@
       <c r="O352" s="5"/>
       <c r="P352" s="5"/>
       <c r="Q352" s="5"/>
-    </row>
-    <row r="353" spans="1:17">
+      <c r="R352" s="5"/>
+    </row>
+    <row r="353" spans="1:18">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -8372,8 +8750,9 @@
       <c r="O353" s="5"/>
       <c r="P353" s="5"/>
       <c r="Q353" s="5"/>
-    </row>
-    <row r="354" spans="1:17">
+      <c r="R353" s="5"/>
+    </row>
+    <row r="354" spans="1:18">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -8391,8 +8770,9 @@
       <c r="O354" s="5"/>
       <c r="P354" s="5"/>
       <c r="Q354" s="5"/>
-    </row>
-    <row r="355" spans="1:17">
+      <c r="R354" s="5"/>
+    </row>
+    <row r="355" spans="1:18">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -8410,8 +8790,9 @@
       <c r="O355" s="5"/>
       <c r="P355" s="5"/>
       <c r="Q355" s="5"/>
-    </row>
-    <row r="356" spans="1:17">
+      <c r="R355" s="5"/>
+    </row>
+    <row r="356" spans="1:18">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -8429,8 +8810,9 @@
       <c r="O356" s="5"/>
       <c r="P356" s="5"/>
       <c r="Q356" s="5"/>
-    </row>
-    <row r="357" spans="1:17">
+      <c r="R356" s="5"/>
+    </row>
+    <row r="357" spans="1:18">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -8448,8 +8830,9 @@
       <c r="O357" s="5"/>
       <c r="P357" s="5"/>
       <c r="Q357" s="5"/>
-    </row>
-    <row r="358" spans="1:17">
+      <c r="R357" s="5"/>
+    </row>
+    <row r="358" spans="1:18">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -8467,8 +8850,9 @@
       <c r="O358" s="5"/>
       <c r="P358" s="5"/>
       <c r="Q358" s="5"/>
-    </row>
-    <row r="359" spans="1:17">
+      <c r="R358" s="5"/>
+    </row>
+    <row r="359" spans="1:18">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -8486,8 +8870,9 @@
       <c r="O359" s="5"/>
       <c r="P359" s="5"/>
       <c r="Q359" s="5"/>
-    </row>
-    <row r="360" spans="1:17">
+      <c r="R359" s="5"/>
+    </row>
+    <row r="360" spans="1:18">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -8505,8 +8890,9 @@
       <c r="O360" s="5"/>
       <c r="P360" s="5"/>
       <c r="Q360" s="5"/>
-    </row>
-    <row r="361" spans="1:17">
+      <c r="R360" s="5"/>
+    </row>
+    <row r="361" spans="1:18">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -8524,8 +8910,9 @@
       <c r="O361" s="5"/>
       <c r="P361" s="5"/>
       <c r="Q361" s="5"/>
-    </row>
-    <row r="362" spans="1:17">
+      <c r="R361" s="5"/>
+    </row>
+    <row r="362" spans="1:18">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -8543,8 +8930,9 @@
       <c r="O362" s="5"/>
       <c r="P362" s="5"/>
       <c r="Q362" s="5"/>
-    </row>
-    <row r="363" spans="1:17">
+      <c r="R362" s="5"/>
+    </row>
+    <row r="363" spans="1:18">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -8562,8 +8950,9 @@
       <c r="O363" s="5"/>
       <c r="P363" s="5"/>
       <c r="Q363" s="5"/>
-    </row>
-    <row r="364" spans="1:17">
+      <c r="R363" s="5"/>
+    </row>
+    <row r="364" spans="1:18">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -8581,8 +8970,9 @@
       <c r="O364" s="5"/>
       <c r="P364" s="5"/>
       <c r="Q364" s="5"/>
-    </row>
-    <row r="365" spans="1:17">
+      <c r="R364" s="5"/>
+    </row>
+    <row r="365" spans="1:18">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -8600,8 +8990,9 @@
       <c r="O365" s="5"/>
       <c r="P365" s="5"/>
       <c r="Q365" s="5"/>
-    </row>
-    <row r="366" spans="1:17">
+      <c r="R365" s="5"/>
+    </row>
+    <row r="366" spans="1:18">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -8619,8 +9010,9 @@
       <c r="O366" s="5"/>
       <c r="P366" s="5"/>
       <c r="Q366" s="5"/>
-    </row>
-    <row r="367" spans="1:17">
+      <c r="R366" s="5"/>
+    </row>
+    <row r="367" spans="1:18">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -8638,8 +9030,9 @@
       <c r="O367" s="5"/>
       <c r="P367" s="5"/>
       <c r="Q367" s="5"/>
-    </row>
-    <row r="368" spans="1:17">
+      <c r="R367" s="5"/>
+    </row>
+    <row r="368" spans="1:18">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -8657,8 +9050,9 @@
       <c r="O368" s="5"/>
       <c r="P368" s="5"/>
       <c r="Q368" s="5"/>
-    </row>
-    <row r="369" spans="1:17">
+      <c r="R368" s="5"/>
+    </row>
+    <row r="369" spans="1:18">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -8676,8 +9070,9 @@
       <c r="O369" s="5"/>
       <c r="P369" s="5"/>
       <c r="Q369" s="5"/>
-    </row>
-    <row r="370" spans="1:17">
+      <c r="R369" s="5"/>
+    </row>
+    <row r="370" spans="1:18">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -8695,8 +9090,9 @@
       <c r="O370" s="5"/>
       <c r="P370" s="5"/>
       <c r="Q370" s="5"/>
-    </row>
-    <row r="371" spans="1:17">
+      <c r="R370" s="5"/>
+    </row>
+    <row r="371" spans="1:18">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -8714,8 +9110,9 @@
       <c r="O371" s="5"/>
       <c r="P371" s="5"/>
       <c r="Q371" s="5"/>
-    </row>
-    <row r="372" spans="1:17">
+      <c r="R371" s="5"/>
+    </row>
+    <row r="372" spans="1:18">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -8733,8 +9130,9 @@
       <c r="O372" s="5"/>
       <c r="P372" s="5"/>
       <c r="Q372" s="5"/>
-    </row>
-    <row r="373" spans="1:17">
+      <c r="R372" s="5"/>
+    </row>
+    <row r="373" spans="1:18">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -8752,8 +9150,9 @@
       <c r="O373" s="5"/>
       <c r="P373" s="5"/>
       <c r="Q373" s="5"/>
-    </row>
-    <row r="374" spans="1:17">
+      <c r="R373" s="5"/>
+    </row>
+    <row r="374" spans="1:18">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -8771,8 +9170,9 @@
       <c r="O374" s="5"/>
       <c r="P374" s="5"/>
       <c r="Q374" s="5"/>
-    </row>
-    <row r="375" spans="1:17">
+      <c r="R374" s="5"/>
+    </row>
+    <row r="375" spans="1:18">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -8790,8 +9190,9 @@
       <c r="O375" s="5"/>
       <c r="P375" s="5"/>
       <c r="Q375" s="5"/>
-    </row>
-    <row r="376" spans="1:17">
+      <c r="R375" s="5"/>
+    </row>
+    <row r="376" spans="1:18">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -8809,8 +9210,9 @@
       <c r="O376" s="5"/>
       <c r="P376" s="5"/>
       <c r="Q376" s="5"/>
-    </row>
-    <row r="377" spans="1:17">
+      <c r="R376" s="5"/>
+    </row>
+    <row r="377" spans="1:18">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -8828,8 +9230,9 @@
       <c r="O377" s="5"/>
       <c r="P377" s="5"/>
       <c r="Q377" s="5"/>
-    </row>
-    <row r="378" spans="1:17">
+      <c r="R377" s="5"/>
+    </row>
+    <row r="378" spans="1:18">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -8847,8 +9250,9 @@
       <c r="O378" s="5"/>
       <c r="P378" s="5"/>
       <c r="Q378" s="5"/>
-    </row>
-    <row r="379" spans="1:17">
+      <c r="R378" s="5"/>
+    </row>
+    <row r="379" spans="1:18">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -8866,8 +9270,9 @@
       <c r="O379" s="5"/>
       <c r="P379" s="5"/>
       <c r="Q379" s="5"/>
-    </row>
-    <row r="380" spans="1:17">
+      <c r="R379" s="5"/>
+    </row>
+    <row r="380" spans="1:18">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -8885,8 +9290,9 @@
       <c r="O380" s="5"/>
       <c r="P380" s="5"/>
       <c r="Q380" s="5"/>
-    </row>
-    <row r="381" spans="1:17">
+      <c r="R380" s="5"/>
+    </row>
+    <row r="381" spans="1:18">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -8904,8 +9310,9 @@
       <c r="O381" s="5"/>
       <c r="P381" s="5"/>
       <c r="Q381" s="5"/>
-    </row>
-    <row r="382" spans="1:17">
+      <c r="R381" s="5"/>
+    </row>
+    <row r="382" spans="1:18">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -8923,8 +9330,9 @@
       <c r="O382" s="5"/>
       <c r="P382" s="5"/>
       <c r="Q382" s="5"/>
-    </row>
-    <row r="383" spans="1:17">
+      <c r="R382" s="5"/>
+    </row>
+    <row r="383" spans="1:18">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -8942,8 +9350,9 @@
       <c r="O383" s="5"/>
       <c r="P383" s="5"/>
       <c r="Q383" s="5"/>
-    </row>
-    <row r="384" spans="1:17">
+      <c r="R383" s="5"/>
+    </row>
+    <row r="384" spans="1:18">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -8961,8 +9370,9 @@
       <c r="O384" s="5"/>
       <c r="P384" s="5"/>
       <c r="Q384" s="5"/>
-    </row>
-    <row r="385" spans="1:17">
+      <c r="R384" s="5"/>
+    </row>
+    <row r="385" spans="1:18">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -8980,8 +9390,9 @@
       <c r="O385" s="5"/>
       <c r="P385" s="5"/>
       <c r="Q385" s="5"/>
-    </row>
-    <row r="386" spans="1:17">
+      <c r="R385" s="5"/>
+    </row>
+    <row r="386" spans="1:18">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -8999,8 +9410,9 @@
       <c r="O386" s="5"/>
       <c r="P386" s="5"/>
       <c r="Q386" s="5"/>
-    </row>
-    <row r="387" spans="1:17">
+      <c r="R386" s="5"/>
+    </row>
+    <row r="387" spans="1:18">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -9018,8 +9430,9 @@
       <c r="O387" s="5"/>
       <c r="P387" s="5"/>
       <c r="Q387" s="5"/>
-    </row>
-    <row r="388" spans="1:17">
+      <c r="R387" s="5"/>
+    </row>
+    <row r="388" spans="1:18">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -9037,8 +9450,9 @@
       <c r="O388" s="5"/>
       <c r="P388" s="5"/>
       <c r="Q388" s="5"/>
-    </row>
-    <row r="389" spans="1:17">
+      <c r="R388" s="5"/>
+    </row>
+    <row r="389" spans="1:18">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -9056,8 +9470,9 @@
       <c r="O389" s="5"/>
       <c r="P389" s="5"/>
       <c r="Q389" s="5"/>
-    </row>
-    <row r="390" spans="1:17">
+      <c r="R389" s="5"/>
+    </row>
+    <row r="390" spans="1:18">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -9075,8 +9490,9 @@
       <c r="O390" s="5"/>
       <c r="P390" s="5"/>
       <c r="Q390" s="5"/>
-    </row>
-    <row r="391" spans="1:17">
+      <c r="R390" s="5"/>
+    </row>
+    <row r="391" spans="1:18">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -9094,8 +9510,9 @@
       <c r="O391" s="5"/>
       <c r="P391" s="5"/>
       <c r="Q391" s="5"/>
-    </row>
-    <row r="392" spans="1:17">
+      <c r="R391" s="5"/>
+    </row>
+    <row r="392" spans="1:18">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -9113,8 +9530,9 @@
       <c r="O392" s="5"/>
       <c r="P392" s="5"/>
       <c r="Q392" s="5"/>
-    </row>
-    <row r="393" spans="1:17">
+      <c r="R392" s="5"/>
+    </row>
+    <row r="393" spans="1:18">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -9132,8 +9550,9 @@
       <c r="O393" s="5"/>
       <c r="P393" s="5"/>
       <c r="Q393" s="5"/>
-    </row>
-    <row r="394" spans="1:17">
+      <c r="R393" s="5"/>
+    </row>
+    <row r="394" spans="1:18">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -9151,8 +9570,9 @@
       <c r="O394" s="5"/>
       <c r="P394" s="5"/>
       <c r="Q394" s="5"/>
-    </row>
-    <row r="395" spans="1:17">
+      <c r="R394" s="5"/>
+    </row>
+    <row r="395" spans="1:18">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -9170,8 +9590,9 @@
       <c r="O395" s="5"/>
       <c r="P395" s="5"/>
       <c r="Q395" s="5"/>
-    </row>
-    <row r="396" spans="1:17">
+      <c r="R395" s="5"/>
+    </row>
+    <row r="396" spans="1:18">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -9189,8 +9610,9 @@
       <c r="O396" s="5"/>
       <c r="P396" s="5"/>
       <c r="Q396" s="5"/>
-    </row>
-    <row r="397" spans="1:17">
+      <c r="R396" s="5"/>
+    </row>
+    <row r="397" spans="1:18">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -9208,8 +9630,9 @@
       <c r="O397" s="5"/>
       <c r="P397" s="5"/>
       <c r="Q397" s="5"/>
-    </row>
-    <row r="398" spans="1:17">
+      <c r="R397" s="5"/>
+    </row>
+    <row r="398" spans="1:18">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -9227,8 +9650,9 @@
       <c r="O398" s="5"/>
       <c r="P398" s="5"/>
       <c r="Q398" s="5"/>
-    </row>
-    <row r="399" spans="1:17">
+      <c r="R398" s="5"/>
+    </row>
+    <row r="399" spans="1:18">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -9246,8 +9670,9 @@
       <c r="O399" s="5"/>
       <c r="P399" s="5"/>
       <c r="Q399" s="5"/>
-    </row>
-    <row r="400" spans="1:17">
+      <c r="R399" s="5"/>
+    </row>
+    <row r="400" spans="1:18">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -9265,8 +9690,9 @@
       <c r="O400" s="5"/>
       <c r="P400" s="5"/>
       <c r="Q400" s="5"/>
-    </row>
-    <row r="401" spans="1:17">
+      <c r="R400" s="5"/>
+    </row>
+    <row r="401" spans="1:18">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -9284,8 +9710,9 @@
       <c r="O401" s="5"/>
       <c r="P401" s="5"/>
       <c r="Q401" s="5"/>
-    </row>
-    <row r="402" spans="1:17">
+      <c r="R401" s="5"/>
+    </row>
+    <row r="402" spans="1:18">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -9303,8 +9730,9 @@
       <c r="O402" s="5"/>
       <c r="P402" s="5"/>
       <c r="Q402" s="5"/>
-    </row>
-    <row r="403" spans="1:17">
+      <c r="R402" s="5"/>
+    </row>
+    <row r="403" spans="1:18">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -9322,8 +9750,9 @@
       <c r="O403" s="5"/>
       <c r="P403" s="5"/>
       <c r="Q403" s="5"/>
-    </row>
-    <row r="404" spans="1:17">
+      <c r="R403" s="5"/>
+    </row>
+    <row r="404" spans="1:18">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -9341,8 +9770,9 @@
       <c r="O404" s="5"/>
       <c r="P404" s="5"/>
       <c r="Q404" s="5"/>
-    </row>
-    <row r="405" spans="1:17">
+      <c r="R404" s="5"/>
+    </row>
+    <row r="405" spans="1:18">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -9360,8 +9790,9 @@
       <c r="O405" s="5"/>
       <c r="P405" s="5"/>
       <c r="Q405" s="5"/>
-    </row>
-    <row r="406" spans="1:17">
+      <c r="R405" s="5"/>
+    </row>
+    <row r="406" spans="1:18">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -9379,8 +9810,9 @@
       <c r="O406" s="5"/>
       <c r="P406" s="5"/>
       <c r="Q406" s="5"/>
-    </row>
-    <row r="407" spans="1:17">
+      <c r="R406" s="5"/>
+    </row>
+    <row r="407" spans="1:18">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -9398,8 +9830,9 @@
       <c r="O407" s="5"/>
       <c r="P407" s="5"/>
       <c r="Q407" s="5"/>
-    </row>
-    <row r="408" spans="1:17">
+      <c r="R407" s="5"/>
+    </row>
+    <row r="408" spans="1:18">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -9417,8 +9850,9 @@
       <c r="O408" s="5"/>
       <c r="P408" s="5"/>
       <c r="Q408" s="5"/>
-    </row>
-    <row r="409" spans="1:17">
+      <c r="R408" s="5"/>
+    </row>
+    <row r="409" spans="1:18">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9436,8 +9870,9 @@
       <c r="O409" s="5"/>
       <c r="P409" s="5"/>
       <c r="Q409" s="5"/>
-    </row>
-    <row r="410" spans="1:17">
+      <c r="R409" s="5"/>
+    </row>
+    <row r="410" spans="1:18">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9455,8 +9890,9 @@
       <c r="O410" s="5"/>
       <c r="P410" s="5"/>
       <c r="Q410" s="5"/>
-    </row>
-    <row r="411" spans="1:17">
+      <c r="R410" s="5"/>
+    </row>
+    <row r="411" spans="1:18">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9474,8 +9910,9 @@
       <c r="O411" s="5"/>
       <c r="P411" s="5"/>
       <c r="Q411" s="5"/>
-    </row>
-    <row r="412" spans="1:17">
+      <c r="R411" s="5"/>
+    </row>
+    <row r="412" spans="1:18">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -9493,8 +9930,9 @@
       <c r="O412" s="5"/>
       <c r="P412" s="5"/>
       <c r="Q412" s="5"/>
-    </row>
-    <row r="413" spans="1:17">
+      <c r="R412" s="5"/>
+    </row>
+    <row r="413" spans="1:18">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -9512,8 +9950,9 @@
       <c r="O413" s="5"/>
       <c r="P413" s="5"/>
       <c r="Q413" s="5"/>
-    </row>
-    <row r="414" spans="1:17">
+      <c r="R413" s="5"/>
+    </row>
+    <row r="414" spans="1:18">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -9531,8 +9970,9 @@
       <c r="O414" s="5"/>
       <c r="P414" s="5"/>
       <c r="Q414" s="5"/>
-    </row>
-    <row r="415" spans="1:17">
+      <c r="R414" s="5"/>
+    </row>
+    <row r="415" spans="1:18">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -9550,8 +9990,9 @@
       <c r="O415" s="5"/>
       <c r="P415" s="5"/>
       <c r="Q415" s="5"/>
-    </row>
-    <row r="416" spans="1:17">
+      <c r="R415" s="5"/>
+    </row>
+    <row r="416" spans="1:18">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -9569,8 +10010,9 @@
       <c r="O416" s="5"/>
       <c r="P416" s="5"/>
       <c r="Q416" s="5"/>
-    </row>
-    <row r="417" spans="1:17">
+      <c r="R416" s="5"/>
+    </row>
+    <row r="417" spans="1:18">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -9588,8 +10030,9 @@
       <c r="O417" s="5"/>
       <c r="P417" s="5"/>
       <c r="Q417" s="5"/>
-    </row>
-    <row r="418" spans="1:17">
+      <c r="R417" s="5"/>
+    </row>
+    <row r="418" spans="1:18">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -9607,8 +10050,9 @@
       <c r="O418" s="5"/>
       <c r="P418" s="5"/>
       <c r="Q418" s="5"/>
-    </row>
-    <row r="419" spans="1:17">
+      <c r="R418" s="5"/>
+    </row>
+    <row r="419" spans="1:18">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -9626,8 +10070,9 @@
       <c r="O419" s="5"/>
       <c r="P419" s="5"/>
       <c r="Q419" s="5"/>
-    </row>
-    <row r="420" spans="1:17">
+      <c r="R419" s="5"/>
+    </row>
+    <row r="420" spans="1:18">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -9645,8 +10090,9 @@
       <c r="O420" s="5"/>
       <c r="P420" s="5"/>
       <c r="Q420" s="5"/>
-    </row>
-    <row r="421" spans="1:17">
+      <c r="R420" s="5"/>
+    </row>
+    <row r="421" spans="1:18">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -9664,8 +10110,9 @@
       <c r="O421" s="5"/>
       <c r="P421" s="5"/>
       <c r="Q421" s="5"/>
-    </row>
-    <row r="422" spans="1:17">
+      <c r="R421" s="5"/>
+    </row>
+    <row r="422" spans="1:18">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -9683,8 +10130,9 @@
       <c r="O422" s="5"/>
       <c r="P422" s="5"/>
       <c r="Q422" s="5"/>
-    </row>
-    <row r="423" spans="1:17">
+      <c r="R422" s="5"/>
+    </row>
+    <row r="423" spans="1:18">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -9702,8 +10150,9 @@
       <c r="O423" s="5"/>
       <c r="P423" s="5"/>
       <c r="Q423" s="5"/>
-    </row>
-    <row r="424" spans="1:17">
+      <c r="R423" s="5"/>
+    </row>
+    <row r="424" spans="1:18">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -9721,8 +10170,9 @@
       <c r="O424" s="5"/>
       <c r="P424" s="5"/>
       <c r="Q424" s="5"/>
-    </row>
-    <row r="425" spans="1:17">
+      <c r="R424" s="5"/>
+    </row>
+    <row r="425" spans="1:18">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -9740,8 +10190,9 @@
       <c r="O425" s="5"/>
       <c r="P425" s="5"/>
       <c r="Q425" s="5"/>
-    </row>
-    <row r="426" spans="1:17">
+      <c r="R425" s="5"/>
+    </row>
+    <row r="426" spans="1:18">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -9759,8 +10210,9 @@
       <c r="O426" s="5"/>
       <c r="P426" s="5"/>
       <c r="Q426" s="5"/>
-    </row>
-    <row r="427" spans="1:17">
+      <c r="R426" s="5"/>
+    </row>
+    <row r="427" spans="1:18">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -9778,8 +10230,9 @@
       <c r="O427" s="5"/>
       <c r="P427" s="5"/>
       <c r="Q427" s="5"/>
-    </row>
-    <row r="428" spans="1:17">
+      <c r="R427" s="5"/>
+    </row>
+    <row r="428" spans="1:18">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -9797,8 +10250,9 @@
       <c r="O428" s="5"/>
       <c r="P428" s="5"/>
       <c r="Q428" s="5"/>
-    </row>
-    <row r="429" spans="1:17">
+      <c r="R428" s="5"/>
+    </row>
+    <row r="429" spans="1:18">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -9816,8 +10270,9 @@
       <c r="O429" s="5"/>
       <c r="P429" s="5"/>
       <c r="Q429" s="5"/>
-    </row>
-    <row r="430" spans="1:17">
+      <c r="R429" s="5"/>
+    </row>
+    <row r="430" spans="1:18">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -9835,8 +10290,9 @@
       <c r="O430" s="5"/>
       <c r="P430" s="5"/>
       <c r="Q430" s="5"/>
-    </row>
-    <row r="431" spans="1:17">
+      <c r="R430" s="5"/>
+    </row>
+    <row r="431" spans="1:18">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -9854,8 +10310,9 @@
       <c r="O431" s="5"/>
       <c r="P431" s="5"/>
       <c r="Q431" s="5"/>
-    </row>
-    <row r="432" spans="1:17">
+      <c r="R431" s="5"/>
+    </row>
+    <row r="432" spans="1:18">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -9873,8 +10330,9 @@
       <c r="O432" s="5"/>
       <c r="P432" s="5"/>
       <c r="Q432" s="5"/>
-    </row>
-    <row r="433" spans="1:17">
+      <c r="R432" s="5"/>
+    </row>
+    <row r="433" spans="1:18">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -9892,8 +10350,9 @@
       <c r="O433" s="5"/>
       <c r="P433" s="5"/>
       <c r="Q433" s="5"/>
-    </row>
-    <row r="434" spans="1:17">
+      <c r="R433" s="5"/>
+    </row>
+    <row r="434" spans="1:18">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -9911,8 +10370,9 @@
       <c r="O434" s="5"/>
       <c r="P434" s="5"/>
       <c r="Q434" s="5"/>
-    </row>
-    <row r="435" spans="1:17">
+      <c r="R434" s="5"/>
+    </row>
+    <row r="435" spans="1:18">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -9930,8 +10390,9 @@
       <c r="O435" s="5"/>
       <c r="P435" s="5"/>
       <c r="Q435" s="5"/>
-    </row>
-    <row r="436" spans="1:17">
+      <c r="R435" s="5"/>
+    </row>
+    <row r="436" spans="1:18">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -9949,8 +10410,9 @@
       <c r="O436" s="5"/>
       <c r="P436" s="5"/>
       <c r="Q436" s="5"/>
-    </row>
-    <row r="437" spans="1:17">
+      <c r="R436" s="5"/>
+    </row>
+    <row r="437" spans="1:18">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -9968,8 +10430,9 @@
       <c r="O437" s="5"/>
       <c r="P437" s="5"/>
       <c r="Q437" s="5"/>
-    </row>
-    <row r="438" spans="1:17">
+      <c r="R437" s="5"/>
+    </row>
+    <row r="438" spans="1:18">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -9987,8 +10450,9 @@
       <c r="O438" s="5"/>
       <c r="P438" s="5"/>
       <c r="Q438" s="5"/>
-    </row>
-    <row r="439" spans="1:17">
+      <c r="R438" s="5"/>
+    </row>
+    <row r="439" spans="1:18">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -10006,8 +10470,9 @@
       <c r="O439" s="5"/>
       <c r="P439" s="5"/>
       <c r="Q439" s="5"/>
-    </row>
-    <row r="440" spans="1:17">
+      <c r="R439" s="5"/>
+    </row>
+    <row r="440" spans="1:18">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -10025,8 +10490,9 @@
       <c r="O440" s="5"/>
       <c r="P440" s="5"/>
       <c r="Q440" s="5"/>
-    </row>
-    <row r="441" spans="1:17">
+      <c r="R440" s="5"/>
+    </row>
+    <row r="441" spans="1:18">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -10044,8 +10510,9 @@
       <c r="O441" s="5"/>
       <c r="P441" s="5"/>
       <c r="Q441" s="5"/>
-    </row>
-    <row r="442" spans="1:17">
+      <c r="R441" s="5"/>
+    </row>
+    <row r="442" spans="1:18">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -10063,8 +10530,9 @@
       <c r="O442" s="5"/>
       <c r="P442" s="5"/>
       <c r="Q442" s="5"/>
-    </row>
-    <row r="443" spans="1:17">
+      <c r="R442" s="5"/>
+    </row>
+    <row r="443" spans="1:18">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -10082,8 +10550,9 @@
       <c r="O443" s="5"/>
       <c r="P443" s="5"/>
       <c r="Q443" s="5"/>
-    </row>
-    <row r="444" spans="1:17">
+      <c r="R443" s="5"/>
+    </row>
+    <row r="444" spans="1:18">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -10101,8 +10570,9 @@
       <c r="O444" s="5"/>
       <c r="P444" s="5"/>
       <c r="Q444" s="5"/>
-    </row>
-    <row r="445" spans="1:17">
+      <c r="R444" s="5"/>
+    </row>
+    <row r="445" spans="1:18">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -10120,8 +10590,9 @@
       <c r="O445" s="5"/>
       <c r="P445" s="5"/>
       <c r="Q445" s="5"/>
-    </row>
-    <row r="446" spans="1:17">
+      <c r="R445" s="5"/>
+    </row>
+    <row r="446" spans="1:18">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -10139,8 +10610,9 @@
       <c r="O446" s="5"/>
       <c r="P446" s="5"/>
       <c r="Q446" s="5"/>
-    </row>
-    <row r="447" spans="1:17">
+      <c r="R446" s="5"/>
+    </row>
+    <row r="447" spans="1:18">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -10158,8 +10630,9 @@
       <c r="O447" s="5"/>
       <c r="P447" s="5"/>
       <c r="Q447" s="5"/>
-    </row>
-    <row r="448" spans="1:17">
+      <c r="R447" s="5"/>
+    </row>
+    <row r="448" spans="1:18">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">
@@ -10643,7 +11116,7 @@
       <c r="A608" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K608" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>编号</t>
   </si>
@@ -240,7 +240,7 @@
     <t>isAdBuy</t>
   </si>
   <si>
-    <t>firepower</t>
+    <t>firePower</t>
   </si>
   <si>
     <t>attackInterval</t>
@@ -1432,7 +1432,9 @@
       <c r="I3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="K3" s="4" t="s">
         <v>37</v>
       </c>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -1712,7 +1712,7 @@
         <v>2000</v>
       </c>
       <c r="M8" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0.9</v>
@@ -1810,7 +1810,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>12000</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,8 +98,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0：普通
-1：超武</t>
+0：绿
+1：蓝
+2：紫
+3：金
+4：红</t>
         </r>
       </text>
     </comment>
@@ -121,11 +124,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0：绿
-1：蓝
-2：紫
-3：金
-4：红</t>
+0：普通
+1：超武</t>
         </r>
       </text>
     </comment>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>编号</t>
   </si>
@@ -171,10 +171,10 @@
     <t>名称</t>
   </si>
   <si>
-    <t>种类</t>
+    <t>品质</t>
   </si>
   <si>
-    <t>品质</t>
+    <t>种类</t>
   </si>
   <si>
     <t>货币类型</t>
@@ -225,10 +225,10 @@
     <t>name</t>
   </si>
   <si>
-    <t>kinds</t>
+    <t>quality</t>
   </si>
   <si>
-    <t>quality</t>
+    <t>kinds</t>
   </si>
   <si>
     <t>currencyType</t>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>刀2</t>
+  </si>
+  <si>
+    <t>刀3</t>
+  </si>
+  <si>
+    <t>狙击枪2</t>
   </si>
 </sst>
 </file>
@@ -1528,10 +1534,10 @@
         <v>39</v>
       </c>
       <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
         <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -1582,10 +1588,10 @@
         <v>40</v>
       </c>
       <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
         <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -1636,10 +1642,10 @@
         <v>41</v>
       </c>
       <c r="E7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
         <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -1746,10 +1752,10 @@
         <v>43</v>
       </c>
       <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
         <v>1</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -1804,10 +1810,10 @@
         <v>44</v>
       </c>
       <c r="E10" s="3">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
         <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>4</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -1858,10 +1864,10 @@
         <v>45</v>
       </c>
       <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
         <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <v>4</v>
       </c>
       <c r="G11" s="3">
         <v>1</v>
@@ -1899,22 +1905,52 @@
       <c r="V11" s="3"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>12000</v>
+      </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="J12" s="3">
+        <v>800</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>15</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3">
+        <v>100</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -1923,24 +1959,56 @@
       <c r="V12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>14000</v>
+      </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+      <c r="J13" s="3">
+        <v>600</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M13" s="3">
+        <v>7</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="O13" s="3">
+        <v>5</v>
+      </c>
+      <c r="P13" s="3">
+        <v>500</v>
+      </c>
       <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
+      <c r="R13" s="3">
+        <v>1</v>
+      </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -1505,7 +1505,7 @@
         <v>10</v>
       </c>
       <c r="N4" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O4" s="3">
         <v>1</v>
@@ -1559,7 +1559,7 @@
         <v>3</v>
       </c>
       <c r="N5" s="3">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="O5" s="3">
         <v>30</v>
@@ -1613,7 +1613,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="3">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="O6" s="3">
         <v>25</v>
@@ -1667,7 +1667,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="3">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="O7" s="3">
         <v>75</v>
@@ -1721,7 +1721,7 @@
         <v>3</v>
       </c>
       <c r="N8" s="3">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="O8" s="3">
         <v>5</v>
@@ -1779,7 +1779,7 @@
         <v>7</v>
       </c>
       <c r="N9" s="3">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="O9" s="3">
         <v>5</v>
@@ -1835,7 +1835,7 @@
         <v>8</v>
       </c>
       <c r="N10" s="3">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="O10" s="3">
         <v>8</v>
@@ -1889,7 +1889,7 @@
         <v>15</v>
       </c>
       <c r="N11" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O11" s="3">
         <v>1</v>
@@ -1943,7 +1943,7 @@
         <v>15</v>
       </c>
       <c r="N12" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O12" s="3">
         <v>1</v>
@@ -1997,7 +1997,7 @@
         <v>7</v>
       </c>
       <c r="N13" s="3">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="O13" s="3">
         <v>5</v>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>编号</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>是否广告购买</t>
+  </si>
+  <si>
+    <t>是否加入商店</t>
   </si>
   <si>
     <t>火力值</t>
@@ -238,6 +241,9 @@
   </si>
   <si>
     <t>isAdBuy</t>
+  </si>
+  <si>
+    <t>isStore</t>
   </si>
   <si>
     <t>firePower</t>
@@ -301,6 +307,15 @@
   </si>
   <si>
     <t>狙击枪2</t>
+  </si>
+  <si>
+    <t>步枪2</t>
+  </si>
+  <si>
+    <t>步枪3</t>
+  </si>
+  <si>
+    <t>步枪4</t>
   </si>
 </sst>
 </file>
@@ -1290,15 +1305,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V608"/>
+  <dimension ref="A1:W608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="18" width="25.125" style="2" customWidth="1"/>
-    <col min="19" max="22" width="25.125" style="3" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="2"/>
+    <col min="1" max="19" width="25.125" style="2" customWidth="1"/>
+    <col min="20" max="23" width="25.125" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:22">
+    <row r="1" ht="16.5" spans="1:23">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1353,120 +1368,129 @@
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:22">
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:23">
       <c r="A2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:22">
+        <v>36</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:23">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:22">
+        <v>39</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:23">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1477,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -1492,35 +1516,36 @@
         <v>6000</v>
       </c>
       <c r="I4" s="3"/>
-      <c r="J4" s="3">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3">
         <v>100</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>0.5</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>2000</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="3">
         <v>100</v>
       </c>
-      <c r="O4" s="3">
+      <c r="P4" s="3">
         <v>1</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>100</v>
       </c>
-      <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:22">
+      <c r="W4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:23">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1531,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
@@ -1547,34 +1572,37 @@
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
         <v>200</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>0.15</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>2000</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>3</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>90</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="3">
         <v>30</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>600</v>
       </c>
-      <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:22">
+      <c r="W5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:23">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1585,7 +1613,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
@@ -1601,34 +1629,37 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
         <v>300</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>0.05</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>2000</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>4</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>90</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>25</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>600</v>
       </c>
-      <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:22">
+      <c r="W6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:23">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1639,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3">
         <v>3</v>
@@ -1655,34 +1686,37 @@
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
         <v>400</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>0.2</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>2000</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>5</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>60</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>75</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>600</v>
       </c>
-      <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:22">
+      <c r="W7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:23">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1693,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -1709,36 +1743,39 @@
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>90</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8</v>
       </c>
-      <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:22">
+      <c r="W8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:23">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1749,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3">
         <v>4</v>
@@ -1767,36 +1804,39 @@
         <v>1</v>
       </c>
       <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>80</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3">
+      <c r="R9" s="3"/>
+      <c r="S9" s="3">
         <v>1</v>
       </c>
-      <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:22">
+      <c r="W9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:23">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1807,7 +1847,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3">
         <v>4</v>
@@ -1823,34 +1863,37 @@
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>0.2</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>90</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>600</v>
       </c>
-      <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:22">
+      <c r="W10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:23">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1861,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3">
         <v>4</v>
@@ -1877,34 +1920,37 @@
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3">
         <v>800</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>0.2</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>2000</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>15</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>100</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>1</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>100</v>
       </c>
-      <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:22">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:23">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -1915,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3">
         <v>3</v>
@@ -1931,34 +1977,37 @@
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>0.2</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:22">
+      <c r="W12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:23">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -1969,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3">
         <v>3</v>
@@ -1985,104 +2034,204 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3">
         <v>600</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>1</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>4000</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>7</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>80</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <v>5</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>500</v>
       </c>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3">
+      <c r="R13" s="3"/>
+      <c r="S13" s="3">
         <v>1</v>
       </c>
-      <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:22">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="W13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:23">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7000</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
+      <c r="K14" s="3">
+        <v>200</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>90</v>
+      </c>
+      <c r="P14" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>600</v>
+      </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:22">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="W14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:23">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>7000</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
+      <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
+        <v>90</v>
+      </c>
+      <c r="P15" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>600</v>
+      </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="W15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:23">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
+        <v>200</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M16" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3</v>
+      </c>
+      <c r="O16" s="3">
+        <v>90</v>
+      </c>
+      <c r="P16" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>600</v>
+      </c>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2101,8 +2250,9 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2121,8 +2271,9 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2141,8 +2292,9 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2161,8 +2313,9 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2181,8 +2334,9 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2201,8 +2355,9 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2221,8 +2376,9 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2241,8 +2397,9 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2261,8 +2418,9 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2281,8 +2439,9 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="S26" s="5"/>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2301,8 +2460,9 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2321,8 +2481,9 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2341,8 +2502,9 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2361,8 +2523,9 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2381,8 +2544,9 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="S31" s="5"/>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2401,8 +2565,9 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="S32" s="5"/>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2421,8 +2586,9 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="S33" s="5"/>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2441,8 +2607,9 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="S34" s="5"/>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2461,8 +2628,9 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="S35" s="5"/>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2481,8 +2649,9 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="S36" s="5"/>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2501,8 +2670,9 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="S37" s="5"/>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2521,8 +2691,9 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="S38" s="5"/>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2541,8 +2712,9 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="S39" s="5"/>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2561,8 +2733,9 @@
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="S40" s="5"/>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2581,8 +2754,9 @@
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="S41" s="5"/>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2601,8 +2775,9 @@
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="S42" s="5"/>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2621,8 +2796,9 @@
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="S43" s="5"/>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2641,8 +2817,9 @@
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="S44" s="5"/>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2661,8 +2838,9 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="S45" s="5"/>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2681,8 +2859,9 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="S46" s="5"/>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2701,8 +2880,9 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="S47" s="5"/>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2721,8 +2901,9 @@
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="S48" s="5"/>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2741,8 +2922,9 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
-    </row>
-    <row r="50" spans="1:18">
+      <c r="S49" s="5"/>
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2761,8 +2943,9 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="S50" s="5"/>
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2781,8 +2964,9 @@
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51" s="5"/>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2801,8 +2985,9 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52" s="5"/>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2821,8 +3006,9 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="S53" s="5"/>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2841,8 +3027,9 @@
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="S54" s="5"/>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2861,8 +3048,9 @@
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="S55" s="5"/>
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2881,8 +3069,9 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="S56" s="5"/>
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2901,8 +3090,9 @@
       <c r="P57" s="5"/>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="S57" s="5"/>
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2921,8 +3111,9 @@
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="S58" s="5"/>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2941,8 +3132,9 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
       <c r="R59" s="5"/>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="S59" s="5"/>
+    </row>
+    <row r="60" spans="1:19">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2961,8 +3153,9 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="S60" s="5"/>
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2981,8 +3174,9 @@
       <c r="P61" s="5"/>
       <c r="Q61" s="5"/>
       <c r="R61" s="5"/>
-    </row>
-    <row r="62" spans="1:18">
+      <c r="S61" s="5"/>
+    </row>
+    <row r="62" spans="1:19">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -3001,8 +3195,9 @@
       <c r="P62" s="5"/>
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
-    </row>
-    <row r="63" spans="1:18">
+      <c r="S62" s="5"/>
+    </row>
+    <row r="63" spans="1:19">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -3021,8 +3216,9 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
-    </row>
-    <row r="64" spans="1:18">
+      <c r="S63" s="5"/>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -3041,8 +3237,9 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
-    </row>
-    <row r="65" spans="1:18">
+      <c r="S64" s="5"/>
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -3061,8 +3258,9 @@
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
-    </row>
-    <row r="66" spans="1:18">
+      <c r="S65" s="5"/>
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -3081,8 +3279,9 @@
       <c r="P66" s="5"/>
       <c r="Q66" s="5"/>
       <c r="R66" s="5"/>
-    </row>
-    <row r="67" spans="1:18">
+      <c r="S66" s="5"/>
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -3101,8 +3300,9 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
       <c r="R67" s="5"/>
-    </row>
-    <row r="68" spans="1:18">
+      <c r="S67" s="5"/>
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -3121,8 +3321,9 @@
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
       <c r="R68" s="5"/>
-    </row>
-    <row r="69" spans="1:18">
+      <c r="S68" s="5"/>
+    </row>
+    <row r="69" spans="1:19">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3141,8 +3342,9 @@
       <c r="P69" s="5"/>
       <c r="Q69" s="5"/>
       <c r="R69" s="5"/>
-    </row>
-    <row r="70" spans="1:18">
+      <c r="S69" s="5"/>
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -3161,8 +3363,9 @@
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
       <c r="R70" s="5"/>
-    </row>
-    <row r="71" spans="1:18">
+      <c r="S70" s="5"/>
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -3181,8 +3384,9 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
       <c r="R71" s="5"/>
-    </row>
-    <row r="72" spans="1:18">
+      <c r="S71" s="5"/>
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3201,8 +3405,9 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
-    </row>
-    <row r="73" spans="1:18">
+      <c r="S72" s="5"/>
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -3221,8 +3426,9 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
       <c r="R73" s="5"/>
-    </row>
-    <row r="74" spans="1:18">
+      <c r="S73" s="5"/>
+    </row>
+    <row r="74" spans="1:19">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3241,8 +3447,9 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
       <c r="R74" s="5"/>
-    </row>
-    <row r="75" spans="1:18">
+      <c r="S74" s="5"/>
+    </row>
+    <row r="75" spans="1:19">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3261,8 +3468,9 @@
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
       <c r="R75" s="5"/>
-    </row>
-    <row r="76" spans="1:18">
+      <c r="S75" s="5"/>
+    </row>
+    <row r="76" spans="1:19">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3281,8 +3489,9 @@
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
       <c r="R76" s="5"/>
-    </row>
-    <row r="77" spans="1:18">
+      <c r="S76" s="5"/>
+    </row>
+    <row r="77" spans="1:19">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3301,8 +3510,9 @@
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
       <c r="R77" s="5"/>
-    </row>
-    <row r="78" spans="1:18">
+      <c r="S77" s="5"/>
+    </row>
+    <row r="78" spans="1:19">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3321,8 +3531,9 @@
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
       <c r="R78" s="5"/>
-    </row>
-    <row r="79" spans="1:18">
+      <c r="S78" s="5"/>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3341,8 +3552,9 @@
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
       <c r="R79" s="5"/>
-    </row>
-    <row r="80" spans="1:18">
+      <c r="S79" s="5"/>
+    </row>
+    <row r="80" spans="1:19">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -3361,8 +3573,9 @@
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
       <c r="R80" s="5"/>
-    </row>
-    <row r="81" spans="1:18">
+      <c r="S80" s="5"/>
+    </row>
+    <row r="81" spans="1:19">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -3381,8 +3594,9 @@
       <c r="P81" s="5"/>
       <c r="Q81" s="5"/>
       <c r="R81" s="5"/>
-    </row>
-    <row r="82" spans="1:18">
+      <c r="S81" s="5"/>
+    </row>
+    <row r="82" spans="1:19">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -3401,8 +3615,9 @@
       <c r="P82" s="5"/>
       <c r="Q82" s="5"/>
       <c r="R82" s="5"/>
-    </row>
-    <row r="83" spans="1:18">
+      <c r="S82" s="5"/>
+    </row>
+    <row r="83" spans="1:19">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3421,8 +3636,9 @@
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
       <c r="R83" s="5"/>
-    </row>
-    <row r="84" spans="1:18">
+      <c r="S83" s="5"/>
+    </row>
+    <row r="84" spans="1:19">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -3441,8 +3657,9 @@
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
       <c r="R84" s="5"/>
-    </row>
-    <row r="85" spans="1:18">
+      <c r="S84" s="5"/>
+    </row>
+    <row r="85" spans="1:19">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -3461,8 +3678,9 @@
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
       <c r="R85" s="5"/>
-    </row>
-    <row r="86" spans="1:18">
+      <c r="S85" s="5"/>
+    </row>
+    <row r="86" spans="1:19">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -3481,8 +3699,9 @@
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
       <c r="R86" s="5"/>
-    </row>
-    <row r="87" spans="1:18">
+      <c r="S86" s="5"/>
+    </row>
+    <row r="87" spans="1:19">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -3501,8 +3720,9 @@
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
       <c r="R87" s="5"/>
-    </row>
-    <row r="88" spans="1:18">
+      <c r="S87" s="5"/>
+    </row>
+    <row r="88" spans="1:19">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -3521,8 +3741,9 @@
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
       <c r="R88" s="5"/>
-    </row>
-    <row r="89" spans="1:18">
+      <c r="S88" s="5"/>
+    </row>
+    <row r="89" spans="1:19">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3541,8 +3762,9 @@
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
       <c r="R89" s="5"/>
-    </row>
-    <row r="90" spans="1:18">
+      <c r="S89" s="5"/>
+    </row>
+    <row r="90" spans="1:19">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -3561,8 +3783,9 @@
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
       <c r="R90" s="5"/>
-    </row>
-    <row r="91" spans="1:18">
+      <c r="S90" s="5"/>
+    </row>
+    <row r="91" spans="1:19">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -3581,8 +3804,9 @@
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
       <c r="R91" s="5"/>
-    </row>
-    <row r="92" spans="1:18">
+      <c r="S91" s="5"/>
+    </row>
+    <row r="92" spans="1:19">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -3601,8 +3825,9 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
       <c r="R92" s="5"/>
-    </row>
-    <row r="93" spans="1:18">
+      <c r="S92" s="5"/>
+    </row>
+    <row r="93" spans="1:19">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -3621,8 +3846,9 @@
       <c r="P93" s="5"/>
       <c r="Q93" s="5"/>
       <c r="R93" s="5"/>
-    </row>
-    <row r="94" spans="1:18">
+      <c r="S93" s="5"/>
+    </row>
+    <row r="94" spans="1:19">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -3641,8 +3867,9 @@
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
       <c r="R94" s="5"/>
-    </row>
-    <row r="95" spans="1:18">
+      <c r="S94" s="5"/>
+    </row>
+    <row r="95" spans="1:19">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -3661,8 +3888,9 @@
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
       <c r="R95" s="5"/>
-    </row>
-    <row r="96" spans="1:18">
+      <c r="S95" s="5"/>
+    </row>
+    <row r="96" spans="1:19">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -3681,8 +3909,9 @@
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
       <c r="R96" s="5"/>
-    </row>
-    <row r="97" spans="1:18">
+      <c r="S96" s="5"/>
+    </row>
+    <row r="97" spans="1:19">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -3701,8 +3930,9 @@
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
       <c r="R97" s="5"/>
-    </row>
-    <row r="98" spans="1:18">
+      <c r="S97" s="5"/>
+    </row>
+    <row r="98" spans="1:19">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -3721,8 +3951,9 @@
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
       <c r="R98" s="5"/>
-    </row>
-    <row r="99" spans="1:18">
+      <c r="S98" s="5"/>
+    </row>
+    <row r="99" spans="1:19">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -3741,8 +3972,9 @@
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
       <c r="R99" s="5"/>
-    </row>
-    <row r="100" spans="1:18">
+      <c r="S99" s="5"/>
+    </row>
+    <row r="100" spans="1:19">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -3761,8 +3993,9 @@
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
       <c r="R100" s="5"/>
-    </row>
-    <row r="101" spans="1:18">
+      <c r="S100" s="5"/>
+    </row>
+    <row r="101" spans="1:19">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -3781,8 +4014,9 @@
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
       <c r="R101" s="5"/>
-    </row>
-    <row r="102" spans="1:18">
+      <c r="S101" s="5"/>
+    </row>
+    <row r="102" spans="1:19">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -3801,8 +4035,9 @@
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
       <c r="R102" s="5"/>
-    </row>
-    <row r="103" spans="1:18">
+      <c r="S102" s="5"/>
+    </row>
+    <row r="103" spans="1:19">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -3821,8 +4056,9 @@
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
       <c r="R103" s="5"/>
-    </row>
-    <row r="104" spans="1:18">
+      <c r="S103" s="5"/>
+    </row>
+    <row r="104" spans="1:19">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3841,8 +4077,9 @@
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
       <c r="R104" s="5"/>
-    </row>
-    <row r="105" spans="1:18">
+      <c r="S104" s="5"/>
+    </row>
+    <row r="105" spans="1:19">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -3861,8 +4098,9 @@
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
       <c r="R105" s="5"/>
-    </row>
-    <row r="106" spans="1:18">
+      <c r="S105" s="5"/>
+    </row>
+    <row r="106" spans="1:19">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3881,8 +4119,9 @@
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
       <c r="R106" s="5"/>
-    </row>
-    <row r="107" spans="1:18">
+      <c r="S106" s="5"/>
+    </row>
+    <row r="107" spans="1:19">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -3901,8 +4140,9 @@
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
       <c r="R107" s="5"/>
-    </row>
-    <row r="108" spans="1:18">
+      <c r="S107" s="5"/>
+    </row>
+    <row r="108" spans="1:19">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -3921,8 +4161,9 @@
       <c r="P108" s="5"/>
       <c r="Q108" s="5"/>
       <c r="R108" s="5"/>
-    </row>
-    <row r="109" spans="1:18">
+      <c r="S108" s="5"/>
+    </row>
+    <row r="109" spans="1:19">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -3941,8 +4182,9 @@
       <c r="P109" s="5"/>
       <c r="Q109" s="5"/>
       <c r="R109" s="5"/>
-    </row>
-    <row r="110" spans="1:18">
+      <c r="S109" s="5"/>
+    </row>
+    <row r="110" spans="1:19">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3961,8 +4203,9 @@
       <c r="P110" s="5"/>
       <c r="Q110" s="5"/>
       <c r="R110" s="5"/>
-    </row>
-    <row r="111" spans="1:18">
+      <c r="S110" s="5"/>
+    </row>
+    <row r="111" spans="1:19">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3981,8 +4224,9 @@
       <c r="P111" s="5"/>
       <c r="Q111" s="5"/>
       <c r="R111" s="5"/>
-    </row>
-    <row r="112" spans="1:18">
+      <c r="S111" s="5"/>
+    </row>
+    <row r="112" spans="1:19">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -4001,8 +4245,9 @@
       <c r="P112" s="5"/>
       <c r="Q112" s="5"/>
       <c r="R112" s="5"/>
-    </row>
-    <row r="113" spans="1:18">
+      <c r="S112" s="5"/>
+    </row>
+    <row r="113" spans="1:19">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -4021,8 +4266,9 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
       <c r="R113" s="5"/>
-    </row>
-    <row r="114" spans="1:18">
+      <c r="S113" s="5"/>
+    </row>
+    <row r="114" spans="1:19">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -4041,8 +4287,9 @@
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
       <c r="R114" s="5"/>
-    </row>
-    <row r="115" spans="1:18">
+      <c r="S114" s="5"/>
+    </row>
+    <row r="115" spans="1:19">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -4061,8 +4308,9 @@
       <c r="P115" s="5"/>
       <c r="Q115" s="5"/>
       <c r="R115" s="5"/>
-    </row>
-    <row r="116" spans="1:18">
+      <c r="S115" s="5"/>
+    </row>
+    <row r="116" spans="1:19">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -4081,8 +4329,9 @@
       <c r="P116" s="5"/>
       <c r="Q116" s="5"/>
       <c r="R116" s="5"/>
-    </row>
-    <row r="117" spans="1:18">
+      <c r="S116" s="5"/>
+    </row>
+    <row r="117" spans="1:19">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -4101,8 +4350,9 @@
       <c r="P117" s="5"/>
       <c r="Q117" s="5"/>
       <c r="R117" s="5"/>
-    </row>
-    <row r="118" spans="1:18">
+      <c r="S117" s="5"/>
+    </row>
+    <row r="118" spans="1:19">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -4121,8 +4371,9 @@
       <c r="P118" s="5"/>
       <c r="Q118" s="5"/>
       <c r="R118" s="5"/>
-    </row>
-    <row r="119" spans="1:18">
+      <c r="S118" s="5"/>
+    </row>
+    <row r="119" spans="1:19">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -4141,8 +4392,9 @@
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
       <c r="R119" s="5"/>
-    </row>
-    <row r="120" spans="1:18">
+      <c r="S119" s="5"/>
+    </row>
+    <row r="120" spans="1:19">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -4161,8 +4413,9 @@
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
       <c r="R120" s="5"/>
-    </row>
-    <row r="121" spans="1:18">
+      <c r="S120" s="5"/>
+    </row>
+    <row r="121" spans="1:19">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -4181,8 +4434,9 @@
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
       <c r="R121" s="5"/>
-    </row>
-    <row r="122" spans="1:18">
+      <c r="S121" s="5"/>
+    </row>
+    <row r="122" spans="1:19">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -4201,8 +4455,9 @@
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
       <c r="R122" s="5"/>
-    </row>
-    <row r="123" spans="1:18">
+      <c r="S122" s="5"/>
+    </row>
+    <row r="123" spans="1:19">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -4221,8 +4476,9 @@
       <c r="P123" s="5"/>
       <c r="Q123" s="5"/>
       <c r="R123" s="5"/>
-    </row>
-    <row r="124" spans="1:18">
+      <c r="S123" s="5"/>
+    </row>
+    <row r="124" spans="1:19">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -4241,8 +4497,9 @@
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
       <c r="R124" s="5"/>
-    </row>
-    <row r="125" spans="1:18">
+      <c r="S124" s="5"/>
+    </row>
+    <row r="125" spans="1:19">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -4261,8 +4518,9 @@
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
       <c r="R125" s="5"/>
-    </row>
-    <row r="126" spans="1:18">
+      <c r="S125" s="5"/>
+    </row>
+    <row r="126" spans="1:19">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -4281,8 +4539,9 @@
       <c r="P126" s="5"/>
       <c r="Q126" s="5"/>
       <c r="R126" s="5"/>
-    </row>
-    <row r="127" spans="1:18">
+      <c r="S126" s="5"/>
+    </row>
+    <row r="127" spans="1:19">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -4301,8 +4560,9 @@
       <c r="P127" s="5"/>
       <c r="Q127" s="5"/>
       <c r="R127" s="5"/>
-    </row>
-    <row r="128" spans="1:18">
+      <c r="S127" s="5"/>
+    </row>
+    <row r="128" spans="1:19">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -4321,8 +4581,9 @@
       <c r="P128" s="5"/>
       <c r="Q128" s="5"/>
       <c r="R128" s="5"/>
-    </row>
-    <row r="129" spans="1:18">
+      <c r="S128" s="5"/>
+    </row>
+    <row r="129" spans="1:19">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -4341,8 +4602,9 @@
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
       <c r="R129" s="5"/>
-    </row>
-    <row r="130" spans="1:18">
+      <c r="S129" s="5"/>
+    </row>
+    <row r="130" spans="1:19">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -4361,8 +4623,9 @@
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
       <c r="R130" s="5"/>
-    </row>
-    <row r="131" spans="1:18">
+      <c r="S130" s="5"/>
+    </row>
+    <row r="131" spans="1:19">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -4381,8 +4644,9 @@
       <c r="P131" s="5"/>
       <c r="Q131" s="5"/>
       <c r="R131" s="5"/>
-    </row>
-    <row r="132" spans="1:18">
+      <c r="S131" s="5"/>
+    </row>
+    <row r="132" spans="1:19">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -4401,8 +4665,9 @@
       <c r="P132" s="5"/>
       <c r="Q132" s="5"/>
       <c r="R132" s="5"/>
-    </row>
-    <row r="133" spans="1:18">
+      <c r="S132" s="5"/>
+    </row>
+    <row r="133" spans="1:19">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -4421,8 +4686,9 @@
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
       <c r="R133" s="5"/>
-    </row>
-    <row r="134" spans="1:18">
+      <c r="S133" s="5"/>
+    </row>
+    <row r="134" spans="1:19">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -4441,8 +4707,9 @@
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
       <c r="R134" s="5"/>
-    </row>
-    <row r="135" spans="1:18">
+      <c r="S134" s="5"/>
+    </row>
+    <row r="135" spans="1:19">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -4461,8 +4728,9 @@
       <c r="P135" s="5"/>
       <c r="Q135" s="5"/>
       <c r="R135" s="5"/>
-    </row>
-    <row r="136" spans="1:18">
+      <c r="S135" s="5"/>
+    </row>
+    <row r="136" spans="1:19">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -4481,8 +4749,9 @@
       <c r="P136" s="5"/>
       <c r="Q136" s="5"/>
       <c r="R136" s="5"/>
-    </row>
-    <row r="137" spans="1:18">
+      <c r="S136" s="5"/>
+    </row>
+    <row r="137" spans="1:19">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -4501,8 +4770,9 @@
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
       <c r="R137" s="5"/>
-    </row>
-    <row r="138" spans="1:18">
+      <c r="S137" s="5"/>
+    </row>
+    <row r="138" spans="1:19">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -4521,8 +4791,9 @@
       <c r="P138" s="5"/>
       <c r="Q138" s="5"/>
       <c r="R138" s="5"/>
-    </row>
-    <row r="139" spans="1:18">
+      <c r="S138" s="5"/>
+    </row>
+    <row r="139" spans="1:19">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -4541,8 +4812,9 @@
       <c r="P139" s="5"/>
       <c r="Q139" s="5"/>
       <c r="R139" s="5"/>
-    </row>
-    <row r="140" spans="1:18">
+      <c r="S139" s="5"/>
+    </row>
+    <row r="140" spans="1:19">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -4561,8 +4833,9 @@
       <c r="P140" s="5"/>
       <c r="Q140" s="5"/>
       <c r="R140" s="5"/>
-    </row>
-    <row r="141" spans="1:18">
+      <c r="S140" s="5"/>
+    </row>
+    <row r="141" spans="1:19">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -4581,8 +4854,9 @@
       <c r="P141" s="5"/>
       <c r="Q141" s="5"/>
       <c r="R141" s="5"/>
-    </row>
-    <row r="142" spans="1:18">
+      <c r="S141" s="5"/>
+    </row>
+    <row r="142" spans="1:19">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -4601,8 +4875,9 @@
       <c r="P142" s="5"/>
       <c r="Q142" s="5"/>
       <c r="R142" s="5"/>
-    </row>
-    <row r="143" spans="1:18">
+      <c r="S142" s="5"/>
+    </row>
+    <row r="143" spans="1:19">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -4621,8 +4896,9 @@
       <c r="P143" s="5"/>
       <c r="Q143" s="5"/>
       <c r="R143" s="5"/>
-    </row>
-    <row r="144" spans="1:18">
+      <c r="S143" s="5"/>
+    </row>
+    <row r="144" spans="1:19">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -4641,8 +4917,9 @@
       <c r="P144" s="5"/>
       <c r="Q144" s="5"/>
       <c r="R144" s="5"/>
-    </row>
-    <row r="145" spans="1:18">
+      <c r="S144" s="5"/>
+    </row>
+    <row r="145" spans="1:19">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -4661,8 +4938,9 @@
       <c r="P145" s="5"/>
       <c r="Q145" s="5"/>
       <c r="R145" s="5"/>
-    </row>
-    <row r="146" spans="1:18">
+      <c r="S145" s="5"/>
+    </row>
+    <row r="146" spans="1:19">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -4681,8 +4959,9 @@
       <c r="P146" s="5"/>
       <c r="Q146" s="5"/>
       <c r="R146" s="5"/>
-    </row>
-    <row r="147" spans="1:18">
+      <c r="S146" s="5"/>
+    </row>
+    <row r="147" spans="1:19">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -4701,8 +4980,9 @@
       <c r="P147" s="5"/>
       <c r="Q147" s="5"/>
       <c r="R147" s="5"/>
-    </row>
-    <row r="148" spans="1:18">
+      <c r="S147" s="5"/>
+    </row>
+    <row r="148" spans="1:19">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -4721,8 +5001,9 @@
       <c r="P148" s="5"/>
       <c r="Q148" s="5"/>
       <c r="R148" s="5"/>
-    </row>
-    <row r="149" spans="1:18">
+      <c r="S148" s="5"/>
+    </row>
+    <row r="149" spans="1:19">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -4741,8 +5022,9 @@
       <c r="P149" s="5"/>
       <c r="Q149" s="5"/>
       <c r="R149" s="5"/>
-    </row>
-    <row r="150" spans="1:18">
+      <c r="S149" s="5"/>
+    </row>
+    <row r="150" spans="1:19">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -4761,8 +5043,9 @@
       <c r="P150" s="5"/>
       <c r="Q150" s="5"/>
       <c r="R150" s="5"/>
-    </row>
-    <row r="151" spans="1:18">
+      <c r="S150" s="5"/>
+    </row>
+    <row r="151" spans="1:19">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -4781,8 +5064,9 @@
       <c r="P151" s="5"/>
       <c r="Q151" s="5"/>
       <c r="R151" s="5"/>
-    </row>
-    <row r="152" spans="1:18">
+      <c r="S151" s="5"/>
+    </row>
+    <row r="152" spans="1:19">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -4801,8 +5085,9 @@
       <c r="P152" s="5"/>
       <c r="Q152" s="5"/>
       <c r="R152" s="5"/>
-    </row>
-    <row r="153" spans="1:18">
+      <c r="S152" s="5"/>
+    </row>
+    <row r="153" spans="1:19">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -4821,8 +5106,9 @@
       <c r="P153" s="5"/>
       <c r="Q153" s="5"/>
       <c r="R153" s="5"/>
-    </row>
-    <row r="154" spans="1:18">
+      <c r="S153" s="5"/>
+    </row>
+    <row r="154" spans="1:19">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -4841,8 +5127,9 @@
       <c r="P154" s="5"/>
       <c r="Q154" s="5"/>
       <c r="R154" s="5"/>
-    </row>
-    <row r="155" spans="1:18">
+      <c r="S154" s="5"/>
+    </row>
+    <row r="155" spans="1:19">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -4861,8 +5148,9 @@
       <c r="P155" s="5"/>
       <c r="Q155" s="5"/>
       <c r="R155" s="5"/>
-    </row>
-    <row r="156" spans="1:18">
+      <c r="S155" s="5"/>
+    </row>
+    <row r="156" spans="1:19">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -4881,8 +5169,9 @@
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
       <c r="R156" s="5"/>
-    </row>
-    <row r="157" spans="1:18">
+      <c r="S156" s="5"/>
+    </row>
+    <row r="157" spans="1:19">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -4901,8 +5190,9 @@
       <c r="P157" s="5"/>
       <c r="Q157" s="5"/>
       <c r="R157" s="5"/>
-    </row>
-    <row r="158" spans="1:18">
+      <c r="S157" s="5"/>
+    </row>
+    <row r="158" spans="1:19">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -4921,8 +5211,9 @@
       <c r="P158" s="5"/>
       <c r="Q158" s="5"/>
       <c r="R158" s="5"/>
-    </row>
-    <row r="159" spans="1:18">
+      <c r="S158" s="5"/>
+    </row>
+    <row r="159" spans="1:19">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -4941,8 +5232,9 @@
       <c r="P159" s="5"/>
       <c r="Q159" s="5"/>
       <c r="R159" s="5"/>
-    </row>
-    <row r="160" spans="1:18">
+      <c r="S159" s="5"/>
+    </row>
+    <row r="160" spans="1:19">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -4961,8 +5253,9 @@
       <c r="P160" s="5"/>
       <c r="Q160" s="5"/>
       <c r="R160" s="5"/>
-    </row>
-    <row r="161" spans="1:18">
+      <c r="S160" s="5"/>
+    </row>
+    <row r="161" spans="1:19">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -4981,8 +5274,9 @@
       <c r="P161" s="5"/>
       <c r="Q161" s="5"/>
       <c r="R161" s="5"/>
-    </row>
-    <row r="162" spans="1:18">
+      <c r="S161" s="5"/>
+    </row>
+    <row r="162" spans="1:19">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -5001,8 +5295,9 @@
       <c r="P162" s="5"/>
       <c r="Q162" s="5"/>
       <c r="R162" s="5"/>
-    </row>
-    <row r="163" spans="1:18">
+      <c r="S162" s="5"/>
+    </row>
+    <row r="163" spans="1:19">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -5021,8 +5316,9 @@
       <c r="P163" s="5"/>
       <c r="Q163" s="5"/>
       <c r="R163" s="5"/>
-    </row>
-    <row r="164" spans="1:18">
+      <c r="S163" s="5"/>
+    </row>
+    <row r="164" spans="1:19">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -5041,8 +5337,9 @@
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
       <c r="R164" s="5"/>
-    </row>
-    <row r="165" spans="1:18">
+      <c r="S164" s="5"/>
+    </row>
+    <row r="165" spans="1:19">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -5061,8 +5358,9 @@
       <c r="P165" s="5"/>
       <c r="Q165" s="5"/>
       <c r="R165" s="5"/>
-    </row>
-    <row r="166" spans="1:18">
+      <c r="S165" s="5"/>
+    </row>
+    <row r="166" spans="1:19">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -5081,8 +5379,9 @@
       <c r="P166" s="5"/>
       <c r="Q166" s="5"/>
       <c r="R166" s="5"/>
-    </row>
-    <row r="167" spans="1:18">
+      <c r="S166" s="5"/>
+    </row>
+    <row r="167" spans="1:19">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -5101,8 +5400,9 @@
       <c r="P167" s="5"/>
       <c r="Q167" s="5"/>
       <c r="R167" s="5"/>
-    </row>
-    <row r="168" spans="1:18">
+      <c r="S167" s="5"/>
+    </row>
+    <row r="168" spans="1:19">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -5121,8 +5421,9 @@
       <c r="P168" s="5"/>
       <c r="Q168" s="5"/>
       <c r="R168" s="5"/>
-    </row>
-    <row r="169" spans="1:18">
+      <c r="S168" s="5"/>
+    </row>
+    <row r="169" spans="1:19">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -5141,8 +5442,9 @@
       <c r="P169" s="5"/>
       <c r="Q169" s="5"/>
       <c r="R169" s="5"/>
-    </row>
-    <row r="170" spans="1:18">
+      <c r="S169" s="5"/>
+    </row>
+    <row r="170" spans="1:19">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -5161,8 +5463,9 @@
       <c r="P170" s="5"/>
       <c r="Q170" s="5"/>
       <c r="R170" s="5"/>
-    </row>
-    <row r="171" spans="1:18">
+      <c r="S170" s="5"/>
+    </row>
+    <row r="171" spans="1:19">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -5181,8 +5484,9 @@
       <c r="P171" s="5"/>
       <c r="Q171" s="5"/>
       <c r="R171" s="5"/>
-    </row>
-    <row r="172" spans="1:18">
+      <c r="S171" s="5"/>
+    </row>
+    <row r="172" spans="1:19">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -5201,8 +5505,9 @@
       <c r="P172" s="5"/>
       <c r="Q172" s="5"/>
       <c r="R172" s="5"/>
-    </row>
-    <row r="173" spans="1:18">
+      <c r="S172" s="5"/>
+    </row>
+    <row r="173" spans="1:19">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -5221,8 +5526,9 @@
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>
       <c r="R173" s="5"/>
-    </row>
-    <row r="174" spans="1:18">
+      <c r="S173" s="5"/>
+    </row>
+    <row r="174" spans="1:19">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -5241,8 +5547,9 @@
       <c r="P174" s="5"/>
       <c r="Q174" s="5"/>
       <c r="R174" s="5"/>
-    </row>
-    <row r="175" spans="1:18">
+      <c r="S174" s="5"/>
+    </row>
+    <row r="175" spans="1:19">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -5261,8 +5568,9 @@
       <c r="P175" s="5"/>
       <c r="Q175" s="5"/>
       <c r="R175" s="5"/>
-    </row>
-    <row r="176" spans="1:18">
+      <c r="S175" s="5"/>
+    </row>
+    <row r="176" spans="1:19">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -5281,8 +5589,9 @@
       <c r="P176" s="5"/>
       <c r="Q176" s="5"/>
       <c r="R176" s="5"/>
-    </row>
-    <row r="177" spans="1:18">
+      <c r="S176" s="5"/>
+    </row>
+    <row r="177" spans="1:19">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -5301,8 +5610,9 @@
       <c r="P177" s="5"/>
       <c r="Q177" s="5"/>
       <c r="R177" s="5"/>
-    </row>
-    <row r="178" spans="1:18">
+      <c r="S177" s="5"/>
+    </row>
+    <row r="178" spans="1:19">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -5321,8 +5631,9 @@
       <c r="P178" s="5"/>
       <c r="Q178" s="5"/>
       <c r="R178" s="5"/>
-    </row>
-    <row r="179" spans="1:18">
+      <c r="S178" s="5"/>
+    </row>
+    <row r="179" spans="1:19">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -5341,8 +5652,9 @@
       <c r="P179" s="5"/>
       <c r="Q179" s="5"/>
       <c r="R179" s="5"/>
-    </row>
-    <row r="180" spans="1:18">
+      <c r="S179" s="5"/>
+    </row>
+    <row r="180" spans="1:19">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -5361,8 +5673,9 @@
       <c r="P180" s="5"/>
       <c r="Q180" s="5"/>
       <c r="R180" s="5"/>
-    </row>
-    <row r="181" spans="1:18">
+      <c r="S180" s="5"/>
+    </row>
+    <row r="181" spans="1:19">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -5381,8 +5694,9 @@
       <c r="P181" s="5"/>
       <c r="Q181" s="5"/>
       <c r="R181" s="5"/>
-    </row>
-    <row r="182" spans="1:18">
+      <c r="S181" s="5"/>
+    </row>
+    <row r="182" spans="1:19">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -5401,8 +5715,9 @@
       <c r="P182" s="5"/>
       <c r="Q182" s="5"/>
       <c r="R182" s="5"/>
-    </row>
-    <row r="183" spans="1:18">
+      <c r="S182" s="5"/>
+    </row>
+    <row r="183" spans="1:19">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -5421,8 +5736,9 @@
       <c r="P183" s="5"/>
       <c r="Q183" s="5"/>
       <c r="R183" s="5"/>
-    </row>
-    <row r="184" spans="1:18">
+      <c r="S183" s="5"/>
+    </row>
+    <row r="184" spans="1:19">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -5441,8 +5757,9 @@
       <c r="P184" s="5"/>
       <c r="Q184" s="5"/>
       <c r="R184" s="5"/>
-    </row>
-    <row r="185" spans="1:18">
+      <c r="S184" s="5"/>
+    </row>
+    <row r="185" spans="1:19">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -5461,8 +5778,9 @@
       <c r="P185" s="5"/>
       <c r="Q185" s="5"/>
       <c r="R185" s="5"/>
-    </row>
-    <row r="186" spans="1:18">
+      <c r="S185" s="5"/>
+    </row>
+    <row r="186" spans="1:19">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -5481,8 +5799,9 @@
       <c r="P186" s="5"/>
       <c r="Q186" s="5"/>
       <c r="R186" s="5"/>
-    </row>
-    <row r="187" spans="1:18">
+      <c r="S186" s="5"/>
+    </row>
+    <row r="187" spans="1:19">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -5501,8 +5820,9 @@
       <c r="P187" s="5"/>
       <c r="Q187" s="5"/>
       <c r="R187" s="5"/>
-    </row>
-    <row r="188" spans="1:18">
+      <c r="S187" s="5"/>
+    </row>
+    <row r="188" spans="1:19">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -5521,8 +5841,9 @@
       <c r="P188" s="5"/>
       <c r="Q188" s="5"/>
       <c r="R188" s="5"/>
-    </row>
-    <row r="189" spans="1:18">
+      <c r="S188" s="5"/>
+    </row>
+    <row r="189" spans="1:19">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -5541,8 +5862,9 @@
       <c r="P189" s="5"/>
       <c r="Q189" s="5"/>
       <c r="R189" s="5"/>
-    </row>
-    <row r="190" spans="1:18">
+      <c r="S189" s="5"/>
+    </row>
+    <row r="190" spans="1:19">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -5561,8 +5883,9 @@
       <c r="P190" s="5"/>
       <c r="Q190" s="5"/>
       <c r="R190" s="5"/>
-    </row>
-    <row r="191" spans="1:18">
+      <c r="S190" s="5"/>
+    </row>
+    <row r="191" spans="1:19">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -5581,8 +5904,9 @@
       <c r="P191" s="5"/>
       <c r="Q191" s="5"/>
       <c r="R191" s="5"/>
-    </row>
-    <row r="192" spans="1:18">
+      <c r="S191" s="5"/>
+    </row>
+    <row r="192" spans="1:19">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -5601,8 +5925,9 @@
       <c r="P192" s="5"/>
       <c r="Q192" s="5"/>
       <c r="R192" s="5"/>
-    </row>
-    <row r="193" spans="1:18">
+      <c r="S192" s="5"/>
+    </row>
+    <row r="193" spans="1:19">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -5621,8 +5946,9 @@
       <c r="P193" s="5"/>
       <c r="Q193" s="5"/>
       <c r="R193" s="5"/>
-    </row>
-    <row r="194" spans="1:18">
+      <c r="S193" s="5"/>
+    </row>
+    <row r="194" spans="1:19">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -5641,8 +5967,9 @@
       <c r="P194" s="5"/>
       <c r="Q194" s="5"/>
       <c r="R194" s="5"/>
-    </row>
-    <row r="195" spans="1:18">
+      <c r="S194" s="5"/>
+    </row>
+    <row r="195" spans="1:19">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -5661,8 +5988,9 @@
       <c r="P195" s="5"/>
       <c r="Q195" s="5"/>
       <c r="R195" s="5"/>
-    </row>
-    <row r="196" spans="1:18">
+      <c r="S195" s="5"/>
+    </row>
+    <row r="196" spans="1:19">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -5681,8 +6009,9 @@
       <c r="P196" s="5"/>
       <c r="Q196" s="5"/>
       <c r="R196" s="5"/>
-    </row>
-    <row r="197" spans="1:18">
+      <c r="S196" s="5"/>
+    </row>
+    <row r="197" spans="1:19">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -5701,8 +6030,9 @@
       <c r="P197" s="5"/>
       <c r="Q197" s="5"/>
       <c r="R197" s="5"/>
-    </row>
-    <row r="198" spans="1:18">
+      <c r="S197" s="5"/>
+    </row>
+    <row r="198" spans="1:19">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -5721,8 +6051,9 @@
       <c r="P198" s="5"/>
       <c r="Q198" s="5"/>
       <c r="R198" s="5"/>
-    </row>
-    <row r="199" spans="1:18">
+      <c r="S198" s="5"/>
+    </row>
+    <row r="199" spans="1:19">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -5741,8 +6072,9 @@
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
       <c r="R199" s="5"/>
-    </row>
-    <row r="200" spans="1:18">
+      <c r="S199" s="5"/>
+    </row>
+    <row r="200" spans="1:19">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -5761,8 +6093,9 @@
       <c r="P200" s="5"/>
       <c r="Q200" s="5"/>
       <c r="R200" s="5"/>
-    </row>
-    <row r="201" spans="1:18">
+      <c r="S200" s="5"/>
+    </row>
+    <row r="201" spans="1:19">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -5781,8 +6114,9 @@
       <c r="P201" s="5"/>
       <c r="Q201" s="5"/>
       <c r="R201" s="5"/>
-    </row>
-    <row r="202" spans="1:18">
+      <c r="S201" s="5"/>
+    </row>
+    <row r="202" spans="1:19">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -5801,8 +6135,9 @@
       <c r="P202" s="5"/>
       <c r="Q202" s="5"/>
       <c r="R202" s="5"/>
-    </row>
-    <row r="203" spans="1:18">
+      <c r="S202" s="5"/>
+    </row>
+    <row r="203" spans="1:19">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -5821,8 +6156,9 @@
       <c r="P203" s="5"/>
       <c r="Q203" s="5"/>
       <c r="R203" s="5"/>
-    </row>
-    <row r="204" spans="1:18">
+      <c r="S203" s="5"/>
+    </row>
+    <row r="204" spans="1:19">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -5841,8 +6177,9 @@
       <c r="P204" s="5"/>
       <c r="Q204" s="5"/>
       <c r="R204" s="5"/>
-    </row>
-    <row r="205" spans="1:18">
+      <c r="S204" s="5"/>
+    </row>
+    <row r="205" spans="1:19">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -5861,8 +6198,9 @@
       <c r="P205" s="5"/>
       <c r="Q205" s="5"/>
       <c r="R205" s="5"/>
-    </row>
-    <row r="206" spans="1:18">
+      <c r="S205" s="5"/>
+    </row>
+    <row r="206" spans="1:19">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -5881,8 +6219,9 @@
       <c r="P206" s="5"/>
       <c r="Q206" s="5"/>
       <c r="R206" s="5"/>
-    </row>
-    <row r="207" spans="1:18">
+      <c r="S206" s="5"/>
+    </row>
+    <row r="207" spans="1:19">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -5901,8 +6240,9 @@
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
       <c r="R207" s="5"/>
-    </row>
-    <row r="208" spans="1:18">
+      <c r="S207" s="5"/>
+    </row>
+    <row r="208" spans="1:19">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -5921,8 +6261,9 @@
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
       <c r="R208" s="5"/>
-    </row>
-    <row r="209" spans="1:18">
+      <c r="S208" s="5"/>
+    </row>
+    <row r="209" spans="1:19">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -5941,8 +6282,9 @@
       <c r="P209" s="5"/>
       <c r="Q209" s="5"/>
       <c r="R209" s="5"/>
-    </row>
-    <row r="210" spans="1:18">
+      <c r="S209" s="5"/>
+    </row>
+    <row r="210" spans="1:19">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -5961,8 +6303,9 @@
       <c r="P210" s="5"/>
       <c r="Q210" s="5"/>
       <c r="R210" s="5"/>
-    </row>
-    <row r="211" spans="1:18">
+      <c r="S210" s="5"/>
+    </row>
+    <row r="211" spans="1:19">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -5981,8 +6324,9 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
       <c r="R211" s="5"/>
-    </row>
-    <row r="212" spans="1:18">
+      <c r="S211" s="5"/>
+    </row>
+    <row r="212" spans="1:19">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -6001,8 +6345,9 @@
       <c r="P212" s="5"/>
       <c r="Q212" s="5"/>
       <c r="R212" s="5"/>
-    </row>
-    <row r="213" spans="1:18">
+      <c r="S212" s="5"/>
+    </row>
+    <row r="213" spans="1:19">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -6021,8 +6366,9 @@
       <c r="P213" s="5"/>
       <c r="Q213" s="5"/>
       <c r="R213" s="5"/>
-    </row>
-    <row r="214" spans="1:18">
+      <c r="S213" s="5"/>
+    </row>
+    <row r="214" spans="1:19">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -6041,8 +6387,9 @@
       <c r="P214" s="5"/>
       <c r="Q214" s="5"/>
       <c r="R214" s="5"/>
-    </row>
-    <row r="215" spans="1:18">
+      <c r="S214" s="5"/>
+    </row>
+    <row r="215" spans="1:19">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -6061,8 +6408,9 @@
       <c r="P215" s="5"/>
       <c r="Q215" s="5"/>
       <c r="R215" s="5"/>
-    </row>
-    <row r="216" spans="1:18">
+      <c r="S215" s="5"/>
+    </row>
+    <row r="216" spans="1:19">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -6081,8 +6429,9 @@
       <c r="P216" s="5"/>
       <c r="Q216" s="5"/>
       <c r="R216" s="5"/>
-    </row>
-    <row r="217" spans="1:18">
+      <c r="S216" s="5"/>
+    </row>
+    <row r="217" spans="1:19">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -6101,8 +6450,9 @@
       <c r="P217" s="5"/>
       <c r="Q217" s="5"/>
       <c r="R217" s="5"/>
-    </row>
-    <row r="218" spans="1:18">
+      <c r="S217" s="5"/>
+    </row>
+    <row r="218" spans="1:19">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -6121,8 +6471,9 @@
       <c r="P218" s="5"/>
       <c r="Q218" s="5"/>
       <c r="R218" s="5"/>
-    </row>
-    <row r="219" spans="1:18">
+      <c r="S218" s="5"/>
+    </row>
+    <row r="219" spans="1:19">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -6141,8 +6492,9 @@
       <c r="P219" s="5"/>
       <c r="Q219" s="5"/>
       <c r="R219" s="5"/>
-    </row>
-    <row r="220" spans="1:18">
+      <c r="S219" s="5"/>
+    </row>
+    <row r="220" spans="1:19">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -6161,8 +6513,9 @@
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
       <c r="R220" s="5"/>
-    </row>
-    <row r="221" spans="1:18">
+      <c r="S220" s="5"/>
+    </row>
+    <row r="221" spans="1:19">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -6181,8 +6534,9 @@
       <c r="P221" s="5"/>
       <c r="Q221" s="5"/>
       <c r="R221" s="5"/>
-    </row>
-    <row r="222" spans="1:18">
+      <c r="S221" s="5"/>
+    </row>
+    <row r="222" spans="1:19">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -6201,8 +6555,9 @@
       <c r="P222" s="5"/>
       <c r="Q222" s="5"/>
       <c r="R222" s="5"/>
-    </row>
-    <row r="223" spans="1:18">
+      <c r="S222" s="5"/>
+    </row>
+    <row r="223" spans="1:19">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -6221,8 +6576,9 @@
       <c r="P223" s="5"/>
       <c r="Q223" s="5"/>
       <c r="R223" s="5"/>
-    </row>
-    <row r="224" spans="1:18">
+      <c r="S223" s="5"/>
+    </row>
+    <row r="224" spans="1:19">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -6241,8 +6597,9 @@
       <c r="P224" s="5"/>
       <c r="Q224" s="5"/>
       <c r="R224" s="5"/>
-    </row>
-    <row r="225" spans="1:18">
+      <c r="S224" s="5"/>
+    </row>
+    <row r="225" spans="1:19">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -6261,8 +6618,9 @@
       <c r="P225" s="5"/>
       <c r="Q225" s="5"/>
       <c r="R225" s="5"/>
-    </row>
-    <row r="226" spans="1:18">
+      <c r="S225" s="5"/>
+    </row>
+    <row r="226" spans="1:19">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -6281,8 +6639,9 @@
       <c r="P226" s="5"/>
       <c r="Q226" s="5"/>
       <c r="R226" s="5"/>
-    </row>
-    <row r="227" spans="1:18">
+      <c r="S226" s="5"/>
+    </row>
+    <row r="227" spans="1:19">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -6301,8 +6660,9 @@
       <c r="P227" s="5"/>
       <c r="Q227" s="5"/>
       <c r="R227" s="5"/>
-    </row>
-    <row r="228" spans="1:18">
+      <c r="S227" s="5"/>
+    </row>
+    <row r="228" spans="1:19">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -6321,8 +6681,9 @@
       <c r="P228" s="5"/>
       <c r="Q228" s="5"/>
       <c r="R228" s="5"/>
-    </row>
-    <row r="229" spans="1:18">
+      <c r="S228" s="5"/>
+    </row>
+    <row r="229" spans="1:19">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -6341,8 +6702,9 @@
       <c r="P229" s="5"/>
       <c r="Q229" s="5"/>
       <c r="R229" s="5"/>
-    </row>
-    <row r="230" spans="1:18">
+      <c r="S229" s="5"/>
+    </row>
+    <row r="230" spans="1:19">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -6361,8 +6723,9 @@
       <c r="P230" s="5"/>
       <c r="Q230" s="5"/>
       <c r="R230" s="5"/>
-    </row>
-    <row r="231" spans="1:18">
+      <c r="S230" s="5"/>
+    </row>
+    <row r="231" spans="1:19">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -6381,8 +6744,9 @@
       <c r="P231" s="5"/>
       <c r="Q231" s="5"/>
       <c r="R231" s="5"/>
-    </row>
-    <row r="232" spans="1:18">
+      <c r="S231" s="5"/>
+    </row>
+    <row r="232" spans="1:19">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -6401,8 +6765,9 @@
       <c r="P232" s="5"/>
       <c r="Q232" s="5"/>
       <c r="R232" s="5"/>
-    </row>
-    <row r="233" spans="1:18">
+      <c r="S232" s="5"/>
+    </row>
+    <row r="233" spans="1:19">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -6421,8 +6786,9 @@
       <c r="P233" s="5"/>
       <c r="Q233" s="5"/>
       <c r="R233" s="5"/>
-    </row>
-    <row r="234" spans="1:18">
+      <c r="S233" s="5"/>
+    </row>
+    <row r="234" spans="1:19">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -6441,8 +6807,9 @@
       <c r="P234" s="5"/>
       <c r="Q234" s="5"/>
       <c r="R234" s="5"/>
-    </row>
-    <row r="235" spans="1:18">
+      <c r="S234" s="5"/>
+    </row>
+    <row r="235" spans="1:19">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -6461,8 +6828,9 @@
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
       <c r="R235" s="5"/>
-    </row>
-    <row r="236" spans="1:18">
+      <c r="S235" s="5"/>
+    </row>
+    <row r="236" spans="1:19">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -6481,8 +6849,9 @@
       <c r="P236" s="5"/>
       <c r="Q236" s="5"/>
       <c r="R236" s="5"/>
-    </row>
-    <row r="237" spans="1:18">
+      <c r="S236" s="5"/>
+    </row>
+    <row r="237" spans="1:19">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -6501,8 +6870,9 @@
       <c r="P237" s="5"/>
       <c r="Q237" s="5"/>
       <c r="R237" s="5"/>
-    </row>
-    <row r="238" spans="1:18">
+      <c r="S237" s="5"/>
+    </row>
+    <row r="238" spans="1:19">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -6521,8 +6891,9 @@
       <c r="P238" s="5"/>
       <c r="Q238" s="5"/>
       <c r="R238" s="5"/>
-    </row>
-    <row r="239" spans="1:18">
+      <c r="S238" s="5"/>
+    </row>
+    <row r="239" spans="1:19">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -6541,8 +6912,9 @@
       <c r="P239" s="5"/>
       <c r="Q239" s="5"/>
       <c r="R239" s="5"/>
-    </row>
-    <row r="240" spans="1:18">
+      <c r="S239" s="5"/>
+    </row>
+    <row r="240" spans="1:19">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -6561,8 +6933,9 @@
       <c r="P240" s="5"/>
       <c r="Q240" s="5"/>
       <c r="R240" s="5"/>
-    </row>
-    <row r="241" spans="1:18">
+      <c r="S240" s="5"/>
+    </row>
+    <row r="241" spans="1:19">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -6581,8 +6954,9 @@
       <c r="P241" s="5"/>
       <c r="Q241" s="5"/>
       <c r="R241" s="5"/>
-    </row>
-    <row r="242" spans="1:18">
+      <c r="S241" s="5"/>
+    </row>
+    <row r="242" spans="1:19">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -6601,8 +6975,9 @@
       <c r="P242" s="5"/>
       <c r="Q242" s="5"/>
       <c r="R242" s="5"/>
-    </row>
-    <row r="243" spans="1:18">
+      <c r="S242" s="5"/>
+    </row>
+    <row r="243" spans="1:19">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -6621,8 +6996,9 @@
       <c r="P243" s="5"/>
       <c r="Q243" s="5"/>
       <c r="R243" s="5"/>
-    </row>
-    <row r="244" spans="1:18">
+      <c r="S243" s="5"/>
+    </row>
+    <row r="244" spans="1:19">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -6641,8 +7017,9 @@
       <c r="P244" s="5"/>
       <c r="Q244" s="5"/>
       <c r="R244" s="5"/>
-    </row>
-    <row r="245" spans="1:18">
+      <c r="S244" s="5"/>
+    </row>
+    <row r="245" spans="1:19">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -6661,8 +7038,9 @@
       <c r="P245" s="5"/>
       <c r="Q245" s="5"/>
       <c r="R245" s="5"/>
-    </row>
-    <row r="246" spans="1:18">
+      <c r="S245" s="5"/>
+    </row>
+    <row r="246" spans="1:19">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -6681,8 +7059,9 @@
       <c r="P246" s="5"/>
       <c r="Q246" s="5"/>
       <c r="R246" s="5"/>
-    </row>
-    <row r="247" spans="1:18">
+      <c r="S246" s="5"/>
+    </row>
+    <row r="247" spans="1:19">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -6701,8 +7080,9 @@
       <c r="P247" s="5"/>
       <c r="Q247" s="5"/>
       <c r="R247" s="5"/>
-    </row>
-    <row r="248" spans="1:18">
+      <c r="S247" s="5"/>
+    </row>
+    <row r="248" spans="1:19">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -6721,8 +7101,9 @@
       <c r="P248" s="5"/>
       <c r="Q248" s="5"/>
       <c r="R248" s="5"/>
-    </row>
-    <row r="249" spans="1:18">
+      <c r="S248" s="5"/>
+    </row>
+    <row r="249" spans="1:19">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -6741,8 +7122,9 @@
       <c r="P249" s="5"/>
       <c r="Q249" s="5"/>
       <c r="R249" s="5"/>
-    </row>
-    <row r="250" spans="1:18">
+      <c r="S249" s="5"/>
+    </row>
+    <row r="250" spans="1:19">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -6761,8 +7143,9 @@
       <c r="P250" s="5"/>
       <c r="Q250" s="5"/>
       <c r="R250" s="5"/>
-    </row>
-    <row r="251" spans="1:18">
+      <c r="S250" s="5"/>
+    </row>
+    <row r="251" spans="1:19">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -6781,8 +7164,9 @@
       <c r="P251" s="5"/>
       <c r="Q251" s="5"/>
       <c r="R251" s="5"/>
-    </row>
-    <row r="252" spans="1:18">
+      <c r="S251" s="5"/>
+    </row>
+    <row r="252" spans="1:19">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6801,8 +7185,9 @@
       <c r="P252" s="5"/>
       <c r="Q252" s="5"/>
       <c r="R252" s="5"/>
-    </row>
-    <row r="253" spans="1:18">
+      <c r="S252" s="5"/>
+    </row>
+    <row r="253" spans="1:19">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6821,8 +7206,9 @@
       <c r="P253" s="5"/>
       <c r="Q253" s="5"/>
       <c r="R253" s="5"/>
-    </row>
-    <row r="254" spans="1:18">
+      <c r="S253" s="5"/>
+    </row>
+    <row r="254" spans="1:19">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6841,8 +7227,9 @@
       <c r="P254" s="5"/>
       <c r="Q254" s="5"/>
       <c r="R254" s="5"/>
-    </row>
-    <row r="255" spans="1:18">
+      <c r="S254" s="5"/>
+    </row>
+    <row r="255" spans="1:19">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -6861,8 +7248,9 @@
       <c r="P255" s="5"/>
       <c r="Q255" s="5"/>
       <c r="R255" s="5"/>
-    </row>
-    <row r="256" spans="1:18">
+      <c r="S255" s="5"/>
+    </row>
+    <row r="256" spans="1:19">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6881,8 +7269,9 @@
       <c r="P256" s="5"/>
       <c r="Q256" s="5"/>
       <c r="R256" s="5"/>
-    </row>
-    <row r="257" spans="1:18">
+      <c r="S256" s="5"/>
+    </row>
+    <row r="257" spans="1:19">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6901,8 +7290,9 @@
       <c r="P257" s="5"/>
       <c r="Q257" s="5"/>
       <c r="R257" s="5"/>
-    </row>
-    <row r="258" spans="1:18">
+      <c r="S257" s="5"/>
+    </row>
+    <row r="258" spans="1:19">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6921,8 +7311,9 @@
       <c r="P258" s="5"/>
       <c r="Q258" s="5"/>
       <c r="R258" s="5"/>
-    </row>
-    <row r="259" spans="1:18">
+      <c r="S258" s="5"/>
+    </row>
+    <row r="259" spans="1:19">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -6941,8 +7332,9 @@
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
       <c r="R259" s="5"/>
-    </row>
-    <row r="260" spans="1:18">
+      <c r="S259" s="5"/>
+    </row>
+    <row r="260" spans="1:19">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -6961,8 +7353,9 @@
       <c r="P260" s="5"/>
       <c r="Q260" s="5"/>
       <c r="R260" s="5"/>
-    </row>
-    <row r="261" spans="1:18">
+      <c r="S260" s="5"/>
+    </row>
+    <row r="261" spans="1:19">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -6981,8 +7374,9 @@
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
       <c r="R261" s="5"/>
-    </row>
-    <row r="262" spans="1:18">
+      <c r="S261" s="5"/>
+    </row>
+    <row r="262" spans="1:19">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -7001,8 +7395,9 @@
       <c r="P262" s="5"/>
       <c r="Q262" s="5"/>
       <c r="R262" s="5"/>
-    </row>
-    <row r="263" spans="1:18">
+      <c r="S262" s="5"/>
+    </row>
+    <row r="263" spans="1:19">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -7021,8 +7416,9 @@
       <c r="P263" s="5"/>
       <c r="Q263" s="5"/>
       <c r="R263" s="5"/>
-    </row>
-    <row r="264" spans="1:18">
+      <c r="S263" s="5"/>
+    </row>
+    <row r="264" spans="1:19">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -7041,8 +7437,9 @@
       <c r="P264" s="5"/>
       <c r="Q264" s="5"/>
       <c r="R264" s="5"/>
-    </row>
-    <row r="265" spans="1:18">
+      <c r="S264" s="5"/>
+    </row>
+    <row r="265" spans="1:19">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -7061,8 +7458,9 @@
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
       <c r="R265" s="5"/>
-    </row>
-    <row r="266" spans="1:18">
+      <c r="S265" s="5"/>
+    </row>
+    <row r="266" spans="1:19">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -7081,8 +7479,9 @@
       <c r="P266" s="5"/>
       <c r="Q266" s="5"/>
       <c r="R266" s="5"/>
-    </row>
-    <row r="267" spans="1:18">
+      <c r="S266" s="5"/>
+    </row>
+    <row r="267" spans="1:19">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -7101,8 +7500,9 @@
       <c r="P267" s="5"/>
       <c r="Q267" s="5"/>
       <c r="R267" s="5"/>
-    </row>
-    <row r="268" spans="1:18">
+      <c r="S267" s="5"/>
+    </row>
+    <row r="268" spans="1:19">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -7121,8 +7521,9 @@
       <c r="P268" s="5"/>
       <c r="Q268" s="5"/>
       <c r="R268" s="5"/>
-    </row>
-    <row r="269" spans="1:18">
+      <c r="S268" s="5"/>
+    </row>
+    <row r="269" spans="1:19">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -7141,8 +7542,9 @@
       <c r="P269" s="5"/>
       <c r="Q269" s="5"/>
       <c r="R269" s="5"/>
-    </row>
-    <row r="270" spans="1:18">
+      <c r="S269" s="5"/>
+    </row>
+    <row r="270" spans="1:19">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7161,8 +7563,9 @@
       <c r="P270" s="5"/>
       <c r="Q270" s="5"/>
       <c r="R270" s="5"/>
-    </row>
-    <row r="271" spans="1:18">
+      <c r="S270" s="5"/>
+    </row>
+    <row r="271" spans="1:19">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7181,8 +7584,9 @@
       <c r="P271" s="5"/>
       <c r="Q271" s="5"/>
       <c r="R271" s="5"/>
-    </row>
-    <row r="272" spans="1:18">
+      <c r="S271" s="5"/>
+    </row>
+    <row r="272" spans="1:19">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7201,8 +7605,9 @@
       <c r="P272" s="5"/>
       <c r="Q272" s="5"/>
       <c r="R272" s="5"/>
-    </row>
-    <row r="273" spans="1:18">
+      <c r="S272" s="5"/>
+    </row>
+    <row r="273" spans="1:19">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -7221,8 +7626,9 @@
       <c r="P273" s="5"/>
       <c r="Q273" s="5"/>
       <c r="R273" s="5"/>
-    </row>
-    <row r="274" spans="1:18">
+      <c r="S273" s="5"/>
+    </row>
+    <row r="274" spans="1:19">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -7241,8 +7647,9 @@
       <c r="P274" s="5"/>
       <c r="Q274" s="5"/>
       <c r="R274" s="5"/>
-    </row>
-    <row r="275" spans="1:18">
+      <c r="S274" s="5"/>
+    </row>
+    <row r="275" spans="1:19">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -7261,8 +7668,9 @@
       <c r="P275" s="5"/>
       <c r="Q275" s="5"/>
       <c r="R275" s="5"/>
-    </row>
-    <row r="276" spans="1:18">
+      <c r="S275" s="5"/>
+    </row>
+    <row r="276" spans="1:19">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -7281,8 +7689,9 @@
       <c r="P276" s="5"/>
       <c r="Q276" s="5"/>
       <c r="R276" s="5"/>
-    </row>
-    <row r="277" spans="1:18">
+      <c r="S276" s="5"/>
+    </row>
+    <row r="277" spans="1:19">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -7301,8 +7710,9 @@
       <c r="P277" s="5"/>
       <c r="Q277" s="5"/>
       <c r="R277" s="5"/>
-    </row>
-    <row r="278" spans="1:18">
+      <c r="S277" s="5"/>
+    </row>
+    <row r="278" spans="1:19">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -7321,8 +7731,9 @@
       <c r="P278" s="5"/>
       <c r="Q278" s="5"/>
       <c r="R278" s="5"/>
-    </row>
-    <row r="279" spans="1:18">
+      <c r="S278" s="5"/>
+    </row>
+    <row r="279" spans="1:19">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -7341,8 +7752,9 @@
       <c r="P279" s="5"/>
       <c r="Q279" s="5"/>
       <c r="R279" s="5"/>
-    </row>
-    <row r="280" spans="1:18">
+      <c r="S279" s="5"/>
+    </row>
+    <row r="280" spans="1:19">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -7361,8 +7773,9 @@
       <c r="P280" s="5"/>
       <c r="Q280" s="5"/>
       <c r="R280" s="5"/>
-    </row>
-    <row r="281" spans="1:18">
+      <c r="S280" s="5"/>
+    </row>
+    <row r="281" spans="1:19">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -7381,8 +7794,9 @@
       <c r="P281" s="5"/>
       <c r="Q281" s="5"/>
       <c r="R281" s="5"/>
-    </row>
-    <row r="282" spans="1:18">
+      <c r="S281" s="5"/>
+    </row>
+    <row r="282" spans="1:19">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -7401,8 +7815,9 @@
       <c r="P282" s="5"/>
       <c r="Q282" s="5"/>
       <c r="R282" s="5"/>
-    </row>
-    <row r="283" spans="1:18">
+      <c r="S282" s="5"/>
+    </row>
+    <row r="283" spans="1:19">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -7421,8 +7836,9 @@
       <c r="P283" s="5"/>
       <c r="Q283" s="5"/>
       <c r="R283" s="5"/>
-    </row>
-    <row r="284" spans="1:18">
+      <c r="S283" s="5"/>
+    </row>
+    <row r="284" spans="1:19">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -7441,8 +7857,9 @@
       <c r="P284" s="5"/>
       <c r="Q284" s="5"/>
       <c r="R284" s="5"/>
-    </row>
-    <row r="285" spans="1:18">
+      <c r="S284" s="5"/>
+    </row>
+    <row r="285" spans="1:19">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -7461,8 +7878,9 @@
       <c r="P285" s="5"/>
       <c r="Q285" s="5"/>
       <c r="R285" s="5"/>
-    </row>
-    <row r="286" spans="1:18">
+      <c r="S285" s="5"/>
+    </row>
+    <row r="286" spans="1:19">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -7481,8 +7899,9 @@
       <c r="P286" s="5"/>
       <c r="Q286" s="5"/>
       <c r="R286" s="5"/>
-    </row>
-    <row r="287" spans="1:18">
+      <c r="S286" s="5"/>
+    </row>
+    <row r="287" spans="1:19">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -7501,8 +7920,9 @@
       <c r="P287" s="5"/>
       <c r="Q287" s="5"/>
       <c r="R287" s="5"/>
-    </row>
-    <row r="288" spans="1:18">
+      <c r="S287" s="5"/>
+    </row>
+    <row r="288" spans="1:19">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -7521,8 +7941,9 @@
       <c r="P288" s="5"/>
       <c r="Q288" s="5"/>
       <c r="R288" s="5"/>
-    </row>
-    <row r="289" spans="1:18">
+      <c r="S288" s="5"/>
+    </row>
+    <row r="289" spans="1:19">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -7541,8 +7962,9 @@
       <c r="P289" s="5"/>
       <c r="Q289" s="5"/>
       <c r="R289" s="5"/>
-    </row>
-    <row r="290" spans="1:18">
+      <c r="S289" s="5"/>
+    </row>
+    <row r="290" spans="1:19">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -7561,8 +7983,9 @@
       <c r="P290" s="5"/>
       <c r="Q290" s="5"/>
       <c r="R290" s="5"/>
-    </row>
-    <row r="291" spans="1:18">
+      <c r="S290" s="5"/>
+    </row>
+    <row r="291" spans="1:19">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -7581,8 +8004,9 @@
       <c r="P291" s="5"/>
       <c r="Q291" s="5"/>
       <c r="R291" s="5"/>
-    </row>
-    <row r="292" spans="1:18">
+      <c r="S291" s="5"/>
+    </row>
+    <row r="292" spans="1:19">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -7601,8 +8025,9 @@
       <c r="P292" s="5"/>
       <c r="Q292" s="5"/>
       <c r="R292" s="5"/>
-    </row>
-    <row r="293" spans="1:18">
+      <c r="S292" s="5"/>
+    </row>
+    <row r="293" spans="1:19">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -7621,8 +8046,9 @@
       <c r="P293" s="5"/>
       <c r="Q293" s="5"/>
       <c r="R293" s="5"/>
-    </row>
-    <row r="294" spans="1:18">
+      <c r="S293" s="5"/>
+    </row>
+    <row r="294" spans="1:19">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -7641,8 +8067,9 @@
       <c r="P294" s="5"/>
       <c r="Q294" s="5"/>
       <c r="R294" s="5"/>
-    </row>
-    <row r="295" spans="1:18">
+      <c r="S294" s="5"/>
+    </row>
+    <row r="295" spans="1:19">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -7661,8 +8088,9 @@
       <c r="P295" s="5"/>
       <c r="Q295" s="5"/>
       <c r="R295" s="5"/>
-    </row>
-    <row r="296" spans="1:18">
+      <c r="S295" s="5"/>
+    </row>
+    <row r="296" spans="1:19">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -7681,8 +8109,9 @@
       <c r="P296" s="5"/>
       <c r="Q296" s="5"/>
       <c r="R296" s="5"/>
-    </row>
-    <row r="297" spans="1:18">
+      <c r="S296" s="5"/>
+    </row>
+    <row r="297" spans="1:19">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -7701,8 +8130,9 @@
       <c r="P297" s="5"/>
       <c r="Q297" s="5"/>
       <c r="R297" s="5"/>
-    </row>
-    <row r="298" spans="1:18">
+      <c r="S297" s="5"/>
+    </row>
+    <row r="298" spans="1:19">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -7721,8 +8151,9 @@
       <c r="P298" s="5"/>
       <c r="Q298" s="5"/>
       <c r="R298" s="5"/>
-    </row>
-    <row r="299" spans="1:18">
+      <c r="S298" s="5"/>
+    </row>
+    <row r="299" spans="1:19">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -7741,8 +8172,9 @@
       <c r="P299" s="5"/>
       <c r="Q299" s="5"/>
       <c r="R299" s="5"/>
-    </row>
-    <row r="300" spans="1:18">
+      <c r="S299" s="5"/>
+    </row>
+    <row r="300" spans="1:19">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -7761,8 +8193,9 @@
       <c r="P300" s="5"/>
       <c r="Q300" s="5"/>
       <c r="R300" s="5"/>
-    </row>
-    <row r="301" spans="1:18">
+      <c r="S300" s="5"/>
+    </row>
+    <row r="301" spans="1:19">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -7781,8 +8214,9 @@
       <c r="P301" s="5"/>
       <c r="Q301" s="5"/>
       <c r="R301" s="5"/>
-    </row>
-    <row r="302" spans="1:18">
+      <c r="S301" s="5"/>
+    </row>
+    <row r="302" spans="1:19">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -7801,8 +8235,9 @@
       <c r="P302" s="5"/>
       <c r="Q302" s="5"/>
       <c r="R302" s="5"/>
-    </row>
-    <row r="303" spans="1:18">
+      <c r="S302" s="5"/>
+    </row>
+    <row r="303" spans="1:19">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -7821,8 +8256,9 @@
       <c r="P303" s="5"/>
       <c r="Q303" s="5"/>
       <c r="R303" s="5"/>
-    </row>
-    <row r="304" spans="1:18">
+      <c r="S303" s="5"/>
+    </row>
+    <row r="304" spans="1:19">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -7841,8 +8277,9 @@
       <c r="P304" s="5"/>
       <c r="Q304" s="5"/>
       <c r="R304" s="5"/>
-    </row>
-    <row r="305" spans="1:18">
+      <c r="S304" s="5"/>
+    </row>
+    <row r="305" spans="1:19">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -7861,8 +8298,9 @@
       <c r="P305" s="5"/>
       <c r="Q305" s="5"/>
       <c r="R305" s="5"/>
-    </row>
-    <row r="306" spans="1:18">
+      <c r="S305" s="5"/>
+    </row>
+    <row r="306" spans="1:19">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -7881,8 +8319,9 @@
       <c r="P306" s="5"/>
       <c r="Q306" s="5"/>
       <c r="R306" s="5"/>
-    </row>
-    <row r="307" spans="1:18">
+      <c r="S306" s="5"/>
+    </row>
+    <row r="307" spans="1:19">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -7901,8 +8340,9 @@
       <c r="P307" s="5"/>
       <c r="Q307" s="5"/>
       <c r="R307" s="5"/>
-    </row>
-    <row r="308" spans="1:18">
+      <c r="S307" s="5"/>
+    </row>
+    <row r="308" spans="1:19">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -7921,8 +8361,9 @@
       <c r="P308" s="5"/>
       <c r="Q308" s="5"/>
       <c r="R308" s="5"/>
-    </row>
-    <row r="309" spans="1:18">
+      <c r="S308" s="5"/>
+    </row>
+    <row r="309" spans="1:19">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -7941,8 +8382,9 @@
       <c r="P309" s="5"/>
       <c r="Q309" s="5"/>
       <c r="R309" s="5"/>
-    </row>
-    <row r="310" spans="1:18">
+      <c r="S309" s="5"/>
+    </row>
+    <row r="310" spans="1:19">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -7961,8 +8403,9 @@
       <c r="P310" s="5"/>
       <c r="Q310" s="5"/>
       <c r="R310" s="5"/>
-    </row>
-    <row r="311" spans="1:18">
+      <c r="S310" s="5"/>
+    </row>
+    <row r="311" spans="1:19">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -7981,8 +8424,9 @@
       <c r="P311" s="5"/>
       <c r="Q311" s="5"/>
       <c r="R311" s="5"/>
-    </row>
-    <row r="312" spans="1:18">
+      <c r="S311" s="5"/>
+    </row>
+    <row r="312" spans="1:19">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -8001,8 +8445,9 @@
       <c r="P312" s="5"/>
       <c r="Q312" s="5"/>
       <c r="R312" s="5"/>
-    </row>
-    <row r="313" spans="1:18">
+      <c r="S312" s="5"/>
+    </row>
+    <row r="313" spans="1:19">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -8021,8 +8466,9 @@
       <c r="P313" s="5"/>
       <c r="Q313" s="5"/>
       <c r="R313" s="5"/>
-    </row>
-    <row r="314" spans="1:18">
+      <c r="S313" s="5"/>
+    </row>
+    <row r="314" spans="1:19">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -8041,8 +8487,9 @@
       <c r="P314" s="5"/>
       <c r="Q314" s="5"/>
       <c r="R314" s="5"/>
-    </row>
-    <row r="315" spans="1:18">
+      <c r="S314" s="5"/>
+    </row>
+    <row r="315" spans="1:19">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -8061,8 +8508,9 @@
       <c r="P315" s="5"/>
       <c r="Q315" s="5"/>
       <c r="R315" s="5"/>
-    </row>
-    <row r="316" spans="1:18">
+      <c r="S315" s="5"/>
+    </row>
+    <row r="316" spans="1:19">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -8081,8 +8529,9 @@
       <c r="P316" s="5"/>
       <c r="Q316" s="5"/>
       <c r="R316" s="5"/>
-    </row>
-    <row r="317" spans="1:18">
+      <c r="S316" s="5"/>
+    </row>
+    <row r="317" spans="1:19">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -8101,8 +8550,9 @@
       <c r="P317" s="5"/>
       <c r="Q317" s="5"/>
       <c r="R317" s="5"/>
-    </row>
-    <row r="318" spans="1:18">
+      <c r="S317" s="5"/>
+    </row>
+    <row r="318" spans="1:19">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -8121,8 +8571,9 @@
       <c r="P318" s="5"/>
       <c r="Q318" s="5"/>
       <c r="R318" s="5"/>
-    </row>
-    <row r="319" spans="1:18">
+      <c r="S318" s="5"/>
+    </row>
+    <row r="319" spans="1:19">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -8141,8 +8592,9 @@
       <c r="P319" s="5"/>
       <c r="Q319" s="5"/>
       <c r="R319" s="5"/>
-    </row>
-    <row r="320" spans="1:18">
+      <c r="S319" s="5"/>
+    </row>
+    <row r="320" spans="1:19">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -8161,8 +8613,9 @@
       <c r="P320" s="5"/>
       <c r="Q320" s="5"/>
       <c r="R320" s="5"/>
-    </row>
-    <row r="321" spans="1:18">
+      <c r="S320" s="5"/>
+    </row>
+    <row r="321" spans="1:19">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -8181,8 +8634,9 @@
       <c r="P321" s="5"/>
       <c r="Q321" s="5"/>
       <c r="R321" s="5"/>
-    </row>
-    <row r="322" spans="1:18">
+      <c r="S321" s="5"/>
+    </row>
+    <row r="322" spans="1:19">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -8201,8 +8655,9 @@
       <c r="P322" s="5"/>
       <c r="Q322" s="5"/>
       <c r="R322" s="5"/>
-    </row>
-    <row r="323" spans="1:18">
+      <c r="S322" s="5"/>
+    </row>
+    <row r="323" spans="1:19">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -8221,8 +8676,9 @@
       <c r="P323" s="5"/>
       <c r="Q323" s="5"/>
       <c r="R323" s="5"/>
-    </row>
-    <row r="324" spans="1:18">
+      <c r="S323" s="5"/>
+    </row>
+    <row r="324" spans="1:19">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -8241,8 +8697,9 @@
       <c r="P324" s="5"/>
       <c r="Q324" s="5"/>
       <c r="R324" s="5"/>
-    </row>
-    <row r="325" spans="1:18">
+      <c r="S324" s="5"/>
+    </row>
+    <row r="325" spans="1:19">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -8261,8 +8718,9 @@
       <c r="P325" s="5"/>
       <c r="Q325" s="5"/>
       <c r="R325" s="5"/>
-    </row>
-    <row r="326" spans="1:18">
+      <c r="S325" s="5"/>
+    </row>
+    <row r="326" spans="1:19">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -8281,8 +8739,9 @@
       <c r="P326" s="5"/>
       <c r="Q326" s="5"/>
       <c r="R326" s="5"/>
-    </row>
-    <row r="327" spans="1:18">
+      <c r="S326" s="5"/>
+    </row>
+    <row r="327" spans="1:19">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -8301,8 +8760,9 @@
       <c r="P327" s="5"/>
       <c r="Q327" s="5"/>
       <c r="R327" s="5"/>
-    </row>
-    <row r="328" spans="1:18">
+      <c r="S327" s="5"/>
+    </row>
+    <row r="328" spans="1:19">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -8321,8 +8781,9 @@
       <c r="P328" s="5"/>
       <c r="Q328" s="5"/>
       <c r="R328" s="5"/>
-    </row>
-    <row r="329" spans="1:18">
+      <c r="S328" s="5"/>
+    </row>
+    <row r="329" spans="1:19">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -8341,8 +8802,9 @@
       <c r="P329" s="5"/>
       <c r="Q329" s="5"/>
       <c r="R329" s="5"/>
-    </row>
-    <row r="330" spans="1:18">
+      <c r="S329" s="5"/>
+    </row>
+    <row r="330" spans="1:19">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -8361,8 +8823,9 @@
       <c r="P330" s="5"/>
       <c r="Q330" s="5"/>
       <c r="R330" s="5"/>
-    </row>
-    <row r="331" spans="1:18">
+      <c r="S330" s="5"/>
+    </row>
+    <row r="331" spans="1:19">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -8381,8 +8844,9 @@
       <c r="P331" s="5"/>
       <c r="Q331" s="5"/>
       <c r="R331" s="5"/>
-    </row>
-    <row r="332" spans="1:18">
+      <c r="S331" s="5"/>
+    </row>
+    <row r="332" spans="1:19">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -8401,8 +8865,9 @@
       <c r="P332" s="5"/>
       <c r="Q332" s="5"/>
       <c r="R332" s="5"/>
-    </row>
-    <row r="333" spans="1:18">
+      <c r="S332" s="5"/>
+    </row>
+    <row r="333" spans="1:19">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -8421,8 +8886,9 @@
       <c r="P333" s="5"/>
       <c r="Q333" s="5"/>
       <c r="R333" s="5"/>
-    </row>
-    <row r="334" spans="1:18">
+      <c r="S333" s="5"/>
+    </row>
+    <row r="334" spans="1:19">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -8441,8 +8907,9 @@
       <c r="P334" s="5"/>
       <c r="Q334" s="5"/>
       <c r="R334" s="5"/>
-    </row>
-    <row r="335" spans="1:18">
+      <c r="S334" s="5"/>
+    </row>
+    <row r="335" spans="1:19">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -8461,8 +8928,9 @@
       <c r="P335" s="5"/>
       <c r="Q335" s="5"/>
       <c r="R335" s="5"/>
-    </row>
-    <row r="336" spans="1:18">
+      <c r="S335" s="5"/>
+    </row>
+    <row r="336" spans="1:19">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -8481,8 +8949,9 @@
       <c r="P336" s="5"/>
       <c r="Q336" s="5"/>
       <c r="R336" s="5"/>
-    </row>
-    <row r="337" spans="1:18">
+      <c r="S336" s="5"/>
+    </row>
+    <row r="337" spans="1:19">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -8501,8 +8970,9 @@
       <c r="P337" s="5"/>
       <c r="Q337" s="5"/>
       <c r="R337" s="5"/>
-    </row>
-    <row r="338" spans="1:18">
+      <c r="S337" s="5"/>
+    </row>
+    <row r="338" spans="1:19">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -8521,8 +8991,9 @@
       <c r="P338" s="5"/>
       <c r="Q338" s="5"/>
       <c r="R338" s="5"/>
-    </row>
-    <row r="339" spans="1:18">
+      <c r="S338" s="5"/>
+    </row>
+    <row r="339" spans="1:19">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -8541,8 +9012,9 @@
       <c r="P339" s="5"/>
       <c r="Q339" s="5"/>
       <c r="R339" s="5"/>
-    </row>
-    <row r="340" spans="1:18">
+      <c r="S339" s="5"/>
+    </row>
+    <row r="340" spans="1:19">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -8561,8 +9033,9 @@
       <c r="P340" s="5"/>
       <c r="Q340" s="5"/>
       <c r="R340" s="5"/>
-    </row>
-    <row r="341" spans="1:18">
+      <c r="S340" s="5"/>
+    </row>
+    <row r="341" spans="1:19">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8581,8 +9054,9 @@
       <c r="P341" s="5"/>
       <c r="Q341" s="5"/>
       <c r="R341" s="5"/>
-    </row>
-    <row r="342" spans="1:18">
+      <c r="S341" s="5"/>
+    </row>
+    <row r="342" spans="1:19">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -8601,8 +9075,9 @@
       <c r="P342" s="5"/>
       <c r="Q342" s="5"/>
       <c r="R342" s="5"/>
-    </row>
-    <row r="343" spans="1:18">
+      <c r="S342" s="5"/>
+    </row>
+    <row r="343" spans="1:19">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -8621,8 +9096,9 @@
       <c r="P343" s="5"/>
       <c r="Q343" s="5"/>
       <c r="R343" s="5"/>
-    </row>
-    <row r="344" spans="1:18">
+      <c r="S343" s="5"/>
+    </row>
+    <row r="344" spans="1:19">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -8641,8 +9117,9 @@
       <c r="P344" s="5"/>
       <c r="Q344" s="5"/>
       <c r="R344" s="5"/>
-    </row>
-    <row r="345" spans="1:18">
+      <c r="S344" s="5"/>
+    </row>
+    <row r="345" spans="1:19">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -8661,8 +9138,9 @@
       <c r="P345" s="5"/>
       <c r="Q345" s="5"/>
       <c r="R345" s="5"/>
-    </row>
-    <row r="346" spans="1:18">
+      <c r="S345" s="5"/>
+    </row>
+    <row r="346" spans="1:19">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -8681,8 +9159,9 @@
       <c r="P346" s="5"/>
       <c r="Q346" s="5"/>
       <c r="R346" s="5"/>
-    </row>
-    <row r="347" spans="1:18">
+      <c r="S346" s="5"/>
+    </row>
+    <row r="347" spans="1:19">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -8701,8 +9180,9 @@
       <c r="P347" s="5"/>
       <c r="Q347" s="5"/>
       <c r="R347" s="5"/>
-    </row>
-    <row r="348" spans="1:18">
+      <c r="S347" s="5"/>
+    </row>
+    <row r="348" spans="1:19">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -8721,8 +9201,9 @@
       <c r="P348" s="5"/>
       <c r="Q348" s="5"/>
       <c r="R348" s="5"/>
-    </row>
-    <row r="349" spans="1:18">
+      <c r="S348" s="5"/>
+    </row>
+    <row r="349" spans="1:19">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -8741,8 +9222,9 @@
       <c r="P349" s="5"/>
       <c r="Q349" s="5"/>
       <c r="R349" s="5"/>
-    </row>
-    <row r="350" spans="1:18">
+      <c r="S349" s="5"/>
+    </row>
+    <row r="350" spans="1:19">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -8761,8 +9243,9 @@
       <c r="P350" s="5"/>
       <c r="Q350" s="5"/>
       <c r="R350" s="5"/>
-    </row>
-    <row r="351" spans="1:18">
+      <c r="S350" s="5"/>
+    </row>
+    <row r="351" spans="1:19">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -8781,8 +9264,9 @@
       <c r="P351" s="5"/>
       <c r="Q351" s="5"/>
       <c r="R351" s="5"/>
-    </row>
-    <row r="352" spans="1:18">
+      <c r="S351" s="5"/>
+    </row>
+    <row r="352" spans="1:19">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -8801,8 +9285,9 @@
       <c r="P352" s="5"/>
       <c r="Q352" s="5"/>
       <c r="R352" s="5"/>
-    </row>
-    <row r="353" spans="1:18">
+      <c r="S352" s="5"/>
+    </row>
+    <row r="353" spans="1:19">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -8821,8 +9306,9 @@
       <c r="P353" s="5"/>
       <c r="Q353" s="5"/>
       <c r="R353" s="5"/>
-    </row>
-    <row r="354" spans="1:18">
+      <c r="S353" s="5"/>
+    </row>
+    <row r="354" spans="1:19">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -8841,8 +9327,9 @@
       <c r="P354" s="5"/>
       <c r="Q354" s="5"/>
       <c r="R354" s="5"/>
-    </row>
-    <row r="355" spans="1:18">
+      <c r="S354" s="5"/>
+    </row>
+    <row r="355" spans="1:19">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -8861,8 +9348,9 @@
       <c r="P355" s="5"/>
       <c r="Q355" s="5"/>
       <c r="R355" s="5"/>
-    </row>
-    <row r="356" spans="1:18">
+      <c r="S355" s="5"/>
+    </row>
+    <row r="356" spans="1:19">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -8881,8 +9369,9 @@
       <c r="P356" s="5"/>
       <c r="Q356" s="5"/>
       <c r="R356" s="5"/>
-    </row>
-    <row r="357" spans="1:18">
+      <c r="S356" s="5"/>
+    </row>
+    <row r="357" spans="1:19">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -8901,8 +9390,9 @@
       <c r="P357" s="5"/>
       <c r="Q357" s="5"/>
       <c r="R357" s="5"/>
-    </row>
-    <row r="358" spans="1:18">
+      <c r="S357" s="5"/>
+    </row>
+    <row r="358" spans="1:19">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -8921,8 +9411,9 @@
       <c r="P358" s="5"/>
       <c r="Q358" s="5"/>
       <c r="R358" s="5"/>
-    </row>
-    <row r="359" spans="1:18">
+      <c r="S358" s="5"/>
+    </row>
+    <row r="359" spans="1:19">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -8941,8 +9432,9 @@
       <c r="P359" s="5"/>
       <c r="Q359" s="5"/>
       <c r="R359" s="5"/>
-    </row>
-    <row r="360" spans="1:18">
+      <c r="S359" s="5"/>
+    </row>
+    <row r="360" spans="1:19">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -8961,8 +9453,9 @@
       <c r="P360" s="5"/>
       <c r="Q360" s="5"/>
       <c r="R360" s="5"/>
-    </row>
-    <row r="361" spans="1:18">
+      <c r="S360" s="5"/>
+    </row>
+    <row r="361" spans="1:19">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -8981,8 +9474,9 @@
       <c r="P361" s="5"/>
       <c r="Q361" s="5"/>
       <c r="R361" s="5"/>
-    </row>
-    <row r="362" spans="1:18">
+      <c r="S361" s="5"/>
+    </row>
+    <row r="362" spans="1:19">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -9001,8 +9495,9 @@
       <c r="P362" s="5"/>
       <c r="Q362" s="5"/>
       <c r="R362" s="5"/>
-    </row>
-    <row r="363" spans="1:18">
+      <c r="S362" s="5"/>
+    </row>
+    <row r="363" spans="1:19">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -9021,8 +9516,9 @@
       <c r="P363" s="5"/>
       <c r="Q363" s="5"/>
       <c r="R363" s="5"/>
-    </row>
-    <row r="364" spans="1:18">
+      <c r="S363" s="5"/>
+    </row>
+    <row r="364" spans="1:19">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -9041,8 +9537,9 @@
       <c r="P364" s="5"/>
       <c r="Q364" s="5"/>
       <c r="R364" s="5"/>
-    </row>
-    <row r="365" spans="1:18">
+      <c r="S364" s="5"/>
+    </row>
+    <row r="365" spans="1:19">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -9061,8 +9558,9 @@
       <c r="P365" s="5"/>
       <c r="Q365" s="5"/>
       <c r="R365" s="5"/>
-    </row>
-    <row r="366" spans="1:18">
+      <c r="S365" s="5"/>
+    </row>
+    <row r="366" spans="1:19">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -9081,8 +9579,9 @@
       <c r="P366" s="5"/>
       <c r="Q366" s="5"/>
       <c r="R366" s="5"/>
-    </row>
-    <row r="367" spans="1:18">
+      <c r="S366" s="5"/>
+    </row>
+    <row r="367" spans="1:19">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -9101,8 +9600,9 @@
       <c r="P367" s="5"/>
       <c r="Q367" s="5"/>
       <c r="R367" s="5"/>
-    </row>
-    <row r="368" spans="1:18">
+      <c r="S367" s="5"/>
+    </row>
+    <row r="368" spans="1:19">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -9121,8 +9621,9 @@
       <c r="P368" s="5"/>
       <c r="Q368" s="5"/>
       <c r="R368" s="5"/>
-    </row>
-    <row r="369" spans="1:18">
+      <c r="S368" s="5"/>
+    </row>
+    <row r="369" spans="1:19">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -9141,8 +9642,9 @@
       <c r="P369" s="5"/>
       <c r="Q369" s="5"/>
       <c r="R369" s="5"/>
-    </row>
-    <row r="370" spans="1:18">
+      <c r="S369" s="5"/>
+    </row>
+    <row r="370" spans="1:19">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -9161,8 +9663,9 @@
       <c r="P370" s="5"/>
       <c r="Q370" s="5"/>
       <c r="R370" s="5"/>
-    </row>
-    <row r="371" spans="1:18">
+      <c r="S370" s="5"/>
+    </row>
+    <row r="371" spans="1:19">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -9181,8 +9684,9 @@
       <c r="P371" s="5"/>
       <c r="Q371" s="5"/>
       <c r="R371" s="5"/>
-    </row>
-    <row r="372" spans="1:18">
+      <c r="S371" s="5"/>
+    </row>
+    <row r="372" spans="1:19">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -9201,8 +9705,9 @@
       <c r="P372" s="5"/>
       <c r="Q372" s="5"/>
       <c r="R372" s="5"/>
-    </row>
-    <row r="373" spans="1:18">
+      <c r="S372" s="5"/>
+    </row>
+    <row r="373" spans="1:19">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -9221,8 +9726,9 @@
       <c r="P373" s="5"/>
       <c r="Q373" s="5"/>
       <c r="R373" s="5"/>
-    </row>
-    <row r="374" spans="1:18">
+      <c r="S373" s="5"/>
+    </row>
+    <row r="374" spans="1:19">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -9241,8 +9747,9 @@
       <c r="P374" s="5"/>
       <c r="Q374" s="5"/>
       <c r="R374" s="5"/>
-    </row>
-    <row r="375" spans="1:18">
+      <c r="S374" s="5"/>
+    </row>
+    <row r="375" spans="1:19">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -9261,8 +9768,9 @@
       <c r="P375" s="5"/>
       <c r="Q375" s="5"/>
       <c r="R375" s="5"/>
-    </row>
-    <row r="376" spans="1:18">
+      <c r="S375" s="5"/>
+    </row>
+    <row r="376" spans="1:19">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -9281,8 +9789,9 @@
       <c r="P376" s="5"/>
       <c r="Q376" s="5"/>
       <c r="R376" s="5"/>
-    </row>
-    <row r="377" spans="1:18">
+      <c r="S376" s="5"/>
+    </row>
+    <row r="377" spans="1:19">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -9301,8 +9810,9 @@
       <c r="P377" s="5"/>
       <c r="Q377" s="5"/>
       <c r="R377" s="5"/>
-    </row>
-    <row r="378" spans="1:18">
+      <c r="S377" s="5"/>
+    </row>
+    <row r="378" spans="1:19">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -9321,8 +9831,9 @@
       <c r="P378" s="5"/>
       <c r="Q378" s="5"/>
       <c r="R378" s="5"/>
-    </row>
-    <row r="379" spans="1:18">
+      <c r="S378" s="5"/>
+    </row>
+    <row r="379" spans="1:19">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -9341,8 +9852,9 @@
       <c r="P379" s="5"/>
       <c r="Q379" s="5"/>
       <c r="R379" s="5"/>
-    </row>
-    <row r="380" spans="1:18">
+      <c r="S379" s="5"/>
+    </row>
+    <row r="380" spans="1:19">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -9361,8 +9873,9 @@
       <c r="P380" s="5"/>
       <c r="Q380" s="5"/>
       <c r="R380" s="5"/>
-    </row>
-    <row r="381" spans="1:18">
+      <c r="S380" s="5"/>
+    </row>
+    <row r="381" spans="1:19">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -9381,8 +9894,9 @@
       <c r="P381" s="5"/>
       <c r="Q381" s="5"/>
       <c r="R381" s="5"/>
-    </row>
-    <row r="382" spans="1:18">
+      <c r="S381" s="5"/>
+    </row>
+    <row r="382" spans="1:19">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -9401,8 +9915,9 @@
       <c r="P382" s="5"/>
       <c r="Q382" s="5"/>
       <c r="R382" s="5"/>
-    </row>
-    <row r="383" spans="1:18">
+      <c r="S382" s="5"/>
+    </row>
+    <row r="383" spans="1:19">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -9421,8 +9936,9 @@
       <c r="P383" s="5"/>
       <c r="Q383" s="5"/>
       <c r="R383" s="5"/>
-    </row>
-    <row r="384" spans="1:18">
+      <c r="S383" s="5"/>
+    </row>
+    <row r="384" spans="1:19">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -9441,8 +9957,9 @@
       <c r="P384" s="5"/>
       <c r="Q384" s="5"/>
       <c r="R384" s="5"/>
-    </row>
-    <row r="385" spans="1:18">
+      <c r="S384" s="5"/>
+    </row>
+    <row r="385" spans="1:19">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -9461,8 +9978,9 @@
       <c r="P385" s="5"/>
       <c r="Q385" s="5"/>
       <c r="R385" s="5"/>
-    </row>
-    <row r="386" spans="1:18">
+      <c r="S385" s="5"/>
+    </row>
+    <row r="386" spans="1:19">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -9481,8 +9999,9 @@
       <c r="P386" s="5"/>
       <c r="Q386" s="5"/>
       <c r="R386" s="5"/>
-    </row>
-    <row r="387" spans="1:18">
+      <c r="S386" s="5"/>
+    </row>
+    <row r="387" spans="1:19">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -9501,8 +10020,9 @@
       <c r="P387" s="5"/>
       <c r="Q387" s="5"/>
       <c r="R387" s="5"/>
-    </row>
-    <row r="388" spans="1:18">
+      <c r="S387" s="5"/>
+    </row>
+    <row r="388" spans="1:19">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -9521,8 +10041,9 @@
       <c r="P388" s="5"/>
       <c r="Q388" s="5"/>
       <c r="R388" s="5"/>
-    </row>
-    <row r="389" spans="1:18">
+      <c r="S388" s="5"/>
+    </row>
+    <row r="389" spans="1:19">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -9541,8 +10062,9 @@
       <c r="P389" s="5"/>
       <c r="Q389" s="5"/>
       <c r="R389" s="5"/>
-    </row>
-    <row r="390" spans="1:18">
+      <c r="S389" s="5"/>
+    </row>
+    <row r="390" spans="1:19">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -9561,8 +10083,9 @@
       <c r="P390" s="5"/>
       <c r="Q390" s="5"/>
       <c r="R390" s="5"/>
-    </row>
-    <row r="391" spans="1:18">
+      <c r="S390" s="5"/>
+    </row>
+    <row r="391" spans="1:19">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -9581,8 +10104,9 @@
       <c r="P391" s="5"/>
       <c r="Q391" s="5"/>
       <c r="R391" s="5"/>
-    </row>
-    <row r="392" spans="1:18">
+      <c r="S391" s="5"/>
+    </row>
+    <row r="392" spans="1:19">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -9601,8 +10125,9 @@
       <c r="P392" s="5"/>
       <c r="Q392" s="5"/>
       <c r="R392" s="5"/>
-    </row>
-    <row r="393" spans="1:18">
+      <c r="S392" s="5"/>
+    </row>
+    <row r="393" spans="1:19">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -9621,8 +10146,9 @@
       <c r="P393" s="5"/>
       <c r="Q393" s="5"/>
       <c r="R393" s="5"/>
-    </row>
-    <row r="394" spans="1:18">
+      <c r="S393" s="5"/>
+    </row>
+    <row r="394" spans="1:19">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -9641,8 +10167,9 @@
       <c r="P394" s="5"/>
       <c r="Q394" s="5"/>
       <c r="R394" s="5"/>
-    </row>
-    <row r="395" spans="1:18">
+      <c r="S394" s="5"/>
+    </row>
+    <row r="395" spans="1:19">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -9661,8 +10188,9 @@
       <c r="P395" s="5"/>
       <c r="Q395" s="5"/>
       <c r="R395" s="5"/>
-    </row>
-    <row r="396" spans="1:18">
+      <c r="S395" s="5"/>
+    </row>
+    <row r="396" spans="1:19">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -9681,8 +10209,9 @@
       <c r="P396" s="5"/>
       <c r="Q396" s="5"/>
       <c r="R396" s="5"/>
-    </row>
-    <row r="397" spans="1:18">
+      <c r="S396" s="5"/>
+    </row>
+    <row r="397" spans="1:19">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -9701,8 +10230,9 @@
       <c r="P397" s="5"/>
       <c r="Q397" s="5"/>
       <c r="R397" s="5"/>
-    </row>
-    <row r="398" spans="1:18">
+      <c r="S397" s="5"/>
+    </row>
+    <row r="398" spans="1:19">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -9721,8 +10251,9 @@
       <c r="P398" s="5"/>
       <c r="Q398" s="5"/>
       <c r="R398" s="5"/>
-    </row>
-    <row r="399" spans="1:18">
+      <c r="S398" s="5"/>
+    </row>
+    <row r="399" spans="1:19">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -9741,8 +10272,9 @@
       <c r="P399" s="5"/>
       <c r="Q399" s="5"/>
       <c r="R399" s="5"/>
-    </row>
-    <row r="400" spans="1:18">
+      <c r="S399" s="5"/>
+    </row>
+    <row r="400" spans="1:19">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -9761,8 +10293,9 @@
       <c r="P400" s="5"/>
       <c r="Q400" s="5"/>
       <c r="R400" s="5"/>
-    </row>
-    <row r="401" spans="1:18">
+      <c r="S400" s="5"/>
+    </row>
+    <row r="401" spans="1:19">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -9781,8 +10314,9 @@
       <c r="P401" s="5"/>
       <c r="Q401" s="5"/>
       <c r="R401" s="5"/>
-    </row>
-    <row r="402" spans="1:18">
+      <c r="S401" s="5"/>
+    </row>
+    <row r="402" spans="1:19">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -9801,8 +10335,9 @@
       <c r="P402" s="5"/>
       <c r="Q402" s="5"/>
       <c r="R402" s="5"/>
-    </row>
-    <row r="403" spans="1:18">
+      <c r="S402" s="5"/>
+    </row>
+    <row r="403" spans="1:19">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -9821,8 +10356,9 @@
       <c r="P403" s="5"/>
       <c r="Q403" s="5"/>
       <c r="R403" s="5"/>
-    </row>
-    <row r="404" spans="1:18">
+      <c r="S403" s="5"/>
+    </row>
+    <row r="404" spans="1:19">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -9841,8 +10377,9 @@
       <c r="P404" s="5"/>
       <c r="Q404" s="5"/>
       <c r="R404" s="5"/>
-    </row>
-    <row r="405" spans="1:18">
+      <c r="S404" s="5"/>
+    </row>
+    <row r="405" spans="1:19">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -9861,8 +10398,9 @@
       <c r="P405" s="5"/>
       <c r="Q405" s="5"/>
       <c r="R405" s="5"/>
-    </row>
-    <row r="406" spans="1:18">
+      <c r="S405" s="5"/>
+    </row>
+    <row r="406" spans="1:19">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -9881,8 +10419,9 @@
       <c r="P406" s="5"/>
       <c r="Q406" s="5"/>
       <c r="R406" s="5"/>
-    </row>
-    <row r="407" spans="1:18">
+      <c r="S406" s="5"/>
+    </row>
+    <row r="407" spans="1:19">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -9901,8 +10440,9 @@
       <c r="P407" s="5"/>
       <c r="Q407" s="5"/>
       <c r="R407" s="5"/>
-    </row>
-    <row r="408" spans="1:18">
+      <c r="S407" s="5"/>
+    </row>
+    <row r="408" spans="1:19">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -9921,8 +10461,9 @@
       <c r="P408" s="5"/>
       <c r="Q408" s="5"/>
       <c r="R408" s="5"/>
-    </row>
-    <row r="409" spans="1:18">
+      <c r="S408" s="5"/>
+    </row>
+    <row r="409" spans="1:19">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9941,8 +10482,9 @@
       <c r="P409" s="5"/>
       <c r="Q409" s="5"/>
       <c r="R409" s="5"/>
-    </row>
-    <row r="410" spans="1:18">
+      <c r="S409" s="5"/>
+    </row>
+    <row r="410" spans="1:19">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9961,8 +10503,9 @@
       <c r="P410" s="5"/>
       <c r="Q410" s="5"/>
       <c r="R410" s="5"/>
-    </row>
-    <row r="411" spans="1:18">
+      <c r="S410" s="5"/>
+    </row>
+    <row r="411" spans="1:19">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9981,8 +10524,9 @@
       <c r="P411" s="5"/>
       <c r="Q411" s="5"/>
       <c r="R411" s="5"/>
-    </row>
-    <row r="412" spans="1:18">
+      <c r="S411" s="5"/>
+    </row>
+    <row r="412" spans="1:19">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -10001,8 +10545,9 @@
       <c r="P412" s="5"/>
       <c r="Q412" s="5"/>
       <c r="R412" s="5"/>
-    </row>
-    <row r="413" spans="1:18">
+      <c r="S412" s="5"/>
+    </row>
+    <row r="413" spans="1:19">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -10021,8 +10566,9 @@
       <c r="P413" s="5"/>
       <c r="Q413" s="5"/>
       <c r="R413" s="5"/>
-    </row>
-    <row r="414" spans="1:18">
+      <c r="S413" s="5"/>
+    </row>
+    <row r="414" spans="1:19">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -10041,8 +10587,9 @@
       <c r="P414" s="5"/>
       <c r="Q414" s="5"/>
       <c r="R414" s="5"/>
-    </row>
-    <row r="415" spans="1:18">
+      <c r="S414" s="5"/>
+    </row>
+    <row r="415" spans="1:19">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -10061,8 +10608,9 @@
       <c r="P415" s="5"/>
       <c r="Q415" s="5"/>
       <c r="R415" s="5"/>
-    </row>
-    <row r="416" spans="1:18">
+      <c r="S415" s="5"/>
+    </row>
+    <row r="416" spans="1:19">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -10081,8 +10629,9 @@
       <c r="P416" s="5"/>
       <c r="Q416" s="5"/>
       <c r="R416" s="5"/>
-    </row>
-    <row r="417" spans="1:18">
+      <c r="S416" s="5"/>
+    </row>
+    <row r="417" spans="1:19">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -10101,8 +10650,9 @@
       <c r="P417" s="5"/>
       <c r="Q417" s="5"/>
       <c r="R417" s="5"/>
-    </row>
-    <row r="418" spans="1:18">
+      <c r="S417" s="5"/>
+    </row>
+    <row r="418" spans="1:19">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -10121,8 +10671,9 @@
       <c r="P418" s="5"/>
       <c r="Q418" s="5"/>
       <c r="R418" s="5"/>
-    </row>
-    <row r="419" spans="1:18">
+      <c r="S418" s="5"/>
+    </row>
+    <row r="419" spans="1:19">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -10141,8 +10692,9 @@
       <c r="P419" s="5"/>
       <c r="Q419" s="5"/>
       <c r="R419" s="5"/>
-    </row>
-    <row r="420" spans="1:18">
+      <c r="S419" s="5"/>
+    </row>
+    <row r="420" spans="1:19">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -10161,8 +10713,9 @@
       <c r="P420" s="5"/>
       <c r="Q420" s="5"/>
       <c r="R420" s="5"/>
-    </row>
-    <row r="421" spans="1:18">
+      <c r="S420" s="5"/>
+    </row>
+    <row r="421" spans="1:19">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -10181,8 +10734,9 @@
       <c r="P421" s="5"/>
       <c r="Q421" s="5"/>
       <c r="R421" s="5"/>
-    </row>
-    <row r="422" spans="1:18">
+      <c r="S421" s="5"/>
+    </row>
+    <row r="422" spans="1:19">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -10201,8 +10755,9 @@
       <c r="P422" s="5"/>
       <c r="Q422" s="5"/>
       <c r="R422" s="5"/>
-    </row>
-    <row r="423" spans="1:18">
+      <c r="S422" s="5"/>
+    </row>
+    <row r="423" spans="1:19">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -10221,8 +10776,9 @@
       <c r="P423" s="5"/>
       <c r="Q423" s="5"/>
       <c r="R423" s="5"/>
-    </row>
-    <row r="424" spans="1:18">
+      <c r="S423" s="5"/>
+    </row>
+    <row r="424" spans="1:19">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -10241,8 +10797,9 @@
       <c r="P424" s="5"/>
       <c r="Q424" s="5"/>
       <c r="R424" s="5"/>
-    </row>
-    <row r="425" spans="1:18">
+      <c r="S424" s="5"/>
+    </row>
+    <row r="425" spans="1:19">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -10261,8 +10818,9 @@
       <c r="P425" s="5"/>
       <c r="Q425" s="5"/>
       <c r="R425" s="5"/>
-    </row>
-    <row r="426" spans="1:18">
+      <c r="S425" s="5"/>
+    </row>
+    <row r="426" spans="1:19">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -10281,8 +10839,9 @@
       <c r="P426" s="5"/>
       <c r="Q426" s="5"/>
       <c r="R426" s="5"/>
-    </row>
-    <row r="427" spans="1:18">
+      <c r="S426" s="5"/>
+    </row>
+    <row r="427" spans="1:19">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -10301,8 +10860,9 @@
       <c r="P427" s="5"/>
       <c r="Q427" s="5"/>
       <c r="R427" s="5"/>
-    </row>
-    <row r="428" spans="1:18">
+      <c r="S427" s="5"/>
+    </row>
+    <row r="428" spans="1:19">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -10321,8 +10881,9 @@
       <c r="P428" s="5"/>
       <c r="Q428" s="5"/>
       <c r="R428" s="5"/>
-    </row>
-    <row r="429" spans="1:18">
+      <c r="S428" s="5"/>
+    </row>
+    <row r="429" spans="1:19">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -10341,8 +10902,9 @@
       <c r="P429" s="5"/>
       <c r="Q429" s="5"/>
       <c r="R429" s="5"/>
-    </row>
-    <row r="430" spans="1:18">
+      <c r="S429" s="5"/>
+    </row>
+    <row r="430" spans="1:19">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -10361,8 +10923,9 @@
       <c r="P430" s="5"/>
       <c r="Q430" s="5"/>
       <c r="R430" s="5"/>
-    </row>
-    <row r="431" spans="1:18">
+      <c r="S430" s="5"/>
+    </row>
+    <row r="431" spans="1:19">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -10381,8 +10944,9 @@
       <c r="P431" s="5"/>
       <c r="Q431" s="5"/>
       <c r="R431" s="5"/>
-    </row>
-    <row r="432" spans="1:18">
+      <c r="S431" s="5"/>
+    </row>
+    <row r="432" spans="1:19">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -10401,8 +10965,9 @@
       <c r="P432" s="5"/>
       <c r="Q432" s="5"/>
       <c r="R432" s="5"/>
-    </row>
-    <row r="433" spans="1:18">
+      <c r="S432" s="5"/>
+    </row>
+    <row r="433" spans="1:19">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -10421,8 +10986,9 @@
       <c r="P433" s="5"/>
       <c r="Q433" s="5"/>
       <c r="R433" s="5"/>
-    </row>
-    <row r="434" spans="1:18">
+      <c r="S433" s="5"/>
+    </row>
+    <row r="434" spans="1:19">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -10441,8 +11007,9 @@
       <c r="P434" s="5"/>
       <c r="Q434" s="5"/>
       <c r="R434" s="5"/>
-    </row>
-    <row r="435" spans="1:18">
+      <c r="S434" s="5"/>
+    </row>
+    <row r="435" spans="1:19">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -10461,8 +11028,9 @@
       <c r="P435" s="5"/>
       <c r="Q435" s="5"/>
       <c r="R435" s="5"/>
-    </row>
-    <row r="436" spans="1:18">
+      <c r="S435" s="5"/>
+    </row>
+    <row r="436" spans="1:19">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -10481,8 +11049,9 @@
       <c r="P436" s="5"/>
       <c r="Q436" s="5"/>
       <c r="R436" s="5"/>
-    </row>
-    <row r="437" spans="1:18">
+      <c r="S436" s="5"/>
+    </row>
+    <row r="437" spans="1:19">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -10501,8 +11070,9 @@
       <c r="P437" s="5"/>
       <c r="Q437" s="5"/>
       <c r="R437" s="5"/>
-    </row>
-    <row r="438" spans="1:18">
+      <c r="S437" s="5"/>
+    </row>
+    <row r="438" spans="1:19">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -10521,8 +11091,9 @@
       <c r="P438" s="5"/>
       <c r="Q438" s="5"/>
       <c r="R438" s="5"/>
-    </row>
-    <row r="439" spans="1:18">
+      <c r="S438" s="5"/>
+    </row>
+    <row r="439" spans="1:19">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -10541,8 +11112,9 @@
       <c r="P439" s="5"/>
       <c r="Q439" s="5"/>
       <c r="R439" s="5"/>
-    </row>
-    <row r="440" spans="1:18">
+      <c r="S439" s="5"/>
+    </row>
+    <row r="440" spans="1:19">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -10561,8 +11133,9 @@
       <c r="P440" s="5"/>
       <c r="Q440" s="5"/>
       <c r="R440" s="5"/>
-    </row>
-    <row r="441" spans="1:18">
+      <c r="S440" s="5"/>
+    </row>
+    <row r="441" spans="1:19">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -10581,8 +11154,9 @@
       <c r="P441" s="5"/>
       <c r="Q441" s="5"/>
       <c r="R441" s="5"/>
-    </row>
-    <row r="442" spans="1:18">
+      <c r="S441" s="5"/>
+    </row>
+    <row r="442" spans="1:19">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -10601,8 +11175,9 @@
       <c r="P442" s="5"/>
       <c r="Q442" s="5"/>
       <c r="R442" s="5"/>
-    </row>
-    <row r="443" spans="1:18">
+      <c r="S442" s="5"/>
+    </row>
+    <row r="443" spans="1:19">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -10621,8 +11196,9 @@
       <c r="P443" s="5"/>
       <c r="Q443" s="5"/>
       <c r="R443" s="5"/>
-    </row>
-    <row r="444" spans="1:18">
+      <c r="S443" s="5"/>
+    </row>
+    <row r="444" spans="1:19">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -10641,8 +11217,9 @@
       <c r="P444" s="5"/>
       <c r="Q444" s="5"/>
       <c r="R444" s="5"/>
-    </row>
-    <row r="445" spans="1:18">
+      <c r="S444" s="5"/>
+    </row>
+    <row r="445" spans="1:19">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -10661,8 +11238,9 @@
       <c r="P445" s="5"/>
       <c r="Q445" s="5"/>
       <c r="R445" s="5"/>
-    </row>
-    <row r="446" spans="1:18">
+      <c r="S445" s="5"/>
+    </row>
+    <row r="446" spans="1:19">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -10681,8 +11259,9 @@
       <c r="P446" s="5"/>
       <c r="Q446" s="5"/>
       <c r="R446" s="5"/>
-    </row>
-    <row r="447" spans="1:18">
+      <c r="S446" s="5"/>
+    </row>
+    <row r="447" spans="1:19">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -10701,8 +11280,9 @@
       <c r="P447" s="5"/>
       <c r="Q447" s="5"/>
       <c r="R447" s="5"/>
-    </row>
-    <row r="448" spans="1:18">
+      <c r="S447" s="5"/>
+    </row>
+    <row r="448" spans="1:19">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">
@@ -11186,7 +11766,7 @@
       <c r="A608" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L608" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>编号</t>
   </si>
@@ -273,10 +273,10 @@
     <t>chargeTime</t>
   </si>
   <si>
-    <t>string</t>
+    <t>int</t>
   </si>
   <si>
-    <t>int</t>
+    <t>string</t>
   </si>
   <si>
     <t>刀1</t>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>步枪4</t>
+  </si>
+  <si>
+    <t>霰弹枪2</t>
   </si>
 </sst>
 </file>
@@ -1436,58 +1439,58 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:23">
@@ -2231,28 +2234,64 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
     </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-    </row>
-    <row r="18" spans="1:19">
+    <row r="17" s="1" customFormat="1" spans="1:23">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3">
+        <v>500</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3">
+        <v>90</v>
+      </c>
+      <c r="P17" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>200</v>
+      </c>
+      <c r="R17" s="3">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2273,7 +2312,7 @@
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:23">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2294,7 +2333,7 @@
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:23">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2315,7 +2354,7 @@
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:23">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2336,7 +2375,7 @@
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:23">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2357,7 +2396,7 @@
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:23">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2378,7 +2417,7 @@
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:23">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2399,7 +2438,7 @@
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:23">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2420,7 +2459,7 @@
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:23">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2441,7 +2480,7 @@
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:23">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2462,7 +2501,7 @@
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:23">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2483,7 +2522,7 @@
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:23">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2504,7 +2543,7 @@
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:23">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2525,7 +2564,7 @@
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:23">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2546,7 +2585,7 @@
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:23">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>

--- a/excel/weapons.xlsx
+++ b/excel/weapons.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$609</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -125,7 +125,8 @@
           </rPr>
           <t xml:space="preserve">
 0：普通
-1：超武</t>
+1：超武
+2：boss专武</t>
         </r>
       </text>
     </comment>
@@ -157,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>编号</t>
   </si>
@@ -214,6 +215,9 @@
   </si>
   <si>
     <t>蓄力时间（狙击枪）</t>
+  </si>
+  <si>
+    <t>换弹时间</t>
   </si>
   <si>
     <t>id</t>
@@ -273,52 +277,79 @@
     <t>chargeTime</t>
   </si>
   <si>
+    <t>reloadTime</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>刀1</t>
+    <t>军用匕首</t>
   </si>
   <si>
-    <t>步枪1</t>
+    <t>左轮</t>
   </si>
   <si>
-    <t>冲锋枪1</t>
+    <t>UZI</t>
   </si>
   <si>
-    <t>机枪1</t>
+    <t>武士长刀</t>
   </si>
   <si>
-    <t>霰弹枪1</t>
+    <t>M4A1</t>
   </si>
   <si>
-    <t>狙击枪1</t>
+    <t>M870</t>
   </si>
   <si>
-    <t>手枪1</t>
+    <t>AWM</t>
   </si>
   <si>
-    <t>刀2</t>
+    <t>沙漠之鹰</t>
   </si>
   <si>
-    <t>刀3</t>
+    <t>M249</t>
   </si>
   <si>
-    <t>狙击枪2</t>
+    <t>AK47</t>
   </si>
   <si>
-    <t>步枪2</t>
+    <t>Viktor</t>
   </si>
   <si>
-    <t>步枪3</t>
+    <t>AA-12</t>
   </si>
   <si>
-    <t>步枪4</t>
+    <t>MG3</t>
   </si>
   <si>
-    <t>霰弹枪2</t>
+    <t>Barrett</t>
+  </si>
+  <si>
+    <t>焚天狱斩</t>
+  </si>
+  <si>
+    <t>无尽炼狱</t>
+  </si>
+  <si>
+    <t>苍龙极镜</t>
+  </si>
+  <si>
+    <t>极寒风暴</t>
+  </si>
+  <si>
+    <t>沧渊逐浪</t>
+  </si>
+  <si>
+    <t>赤阳焚空</t>
+  </si>
+  <si>
+    <t>杠铃</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -1308,15 +1339,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W608"/>
+  <dimension ref="A1:X609"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="19" width="25.125" style="2" customWidth="1"/>
-    <col min="20" max="23" width="25.125" style="3" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="2"/>
+    <col min="20" max="24" width="25.125" style="3" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:23">
+    <row r="1" ht="16.5" spans="1:24">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1374,126 +1405,135 @@
       <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:23">
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:24">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:23">
+        <v>38</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:24">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:23">
+        <v>40</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:24">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1504,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -1516,12 +1556,12 @@
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3">
         <v>0.5</v>
@@ -1539,16 +1579,19 @@
         <v>1</v>
       </c>
       <c r="Q4" s="3">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:23">
+      <c r="X4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:24">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1556,13 +1599,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
@@ -1571,41 +1614,44 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
         <v>1</v>
       </c>
       <c r="K5" s="3">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="L5" s="3">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="3">
         <v>2000</v>
       </c>
       <c r="N5" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O5" s="3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P5" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="3">
         <v>600</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:23">
+      <c r="X5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:24">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1616,10 +1662,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -1628,26 +1674,26 @@
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
         <v>1</v>
       </c>
       <c r="K6" s="3">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="L6" s="3">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="M6" s="3">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="N6" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O6" s="3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P6" s="3">
         <v>25</v>
@@ -1657,12 +1703,15 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:23">
+      <c r="X6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:24">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1670,13 +1719,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
@@ -1685,41 +1734,44 @@
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>9000</v>
+        <v>29999</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
         <v>1</v>
       </c>
       <c r="K7" s="3">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="L7" s="3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M7" s="3">
         <v>2000</v>
       </c>
       <c r="N7" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O7" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="P7" s="3">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="3">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:23">
+      <c r="X7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:24">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1727,13 +1779,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -1742,43 +1794,44 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>10000</v>
+        <v>58888</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3">
         <v>1</v>
       </c>
       <c r="K8" s="3">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="L8" s="3">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="M8" s="3">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N8" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O8" s="3">
         <v>90</v>
       </c>
       <c r="P8" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="3">
-        <v>200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>8</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:23">
+      <c r="X8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:24">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1786,60 +1839,61 @@
         <v>5</v>
       </c>
       <c r="C9" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>11000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
+        <v>109899</v>
+      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="3">
         <v>1</v>
       </c>
       <c r="K9" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N9" s="3">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
+        <v>85</v>
+      </c>
+      <c r="P9" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>200</v>
+      </c>
+      <c r="R9" s="3">
+        <v>10</v>
+      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3">
         <v>1</v>
       </c>
-      <c r="M9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="N9" s="3">
-        <v>7</v>
-      </c>
-      <c r="O9" s="3">
-        <v>80</v>
-      </c>
-      <c r="P9" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>500</v>
-      </c>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3">
-        <v>1</v>
-      </c>
-      <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:23">
+      <c r="X9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:24">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1847,13 +1901,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -1862,41 +1916,44 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>12000</v>
+        <v>201500</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
         <v>1</v>
       </c>
       <c r="K10" s="3">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="L10" s="3">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M10" s="3">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="N10" s="3">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="O10" s="3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P10" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:23">
+      <c r="X10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:24">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1904,56 +1961,61 @@
         <v>7</v>
       </c>
       <c r="C11" s="3">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3">
-        <v>4</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
       <c r="G11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>13000</v>
+        <v>369999</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
         <v>1</v>
       </c>
       <c r="K11" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="L11" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M11" s="3">
         <v>2000</v>
       </c>
       <c r="N11" s="3">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O11" s="3">
         <v>100</v>
       </c>
       <c r="P11" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>600</v>
+      </c>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="T11" s="3">
         <v>1</v>
       </c>
-      <c r="Q11" s="3">
-        <v>100</v>
-      </c>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:23">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:24">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -1961,13 +2023,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -1976,41 +2038,44 @@
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>12000</v>
+        <v>596900</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
         <v>1</v>
       </c>
       <c r="K12" s="3">
-        <v>800</v>
+        <v>299</v>
       </c>
       <c r="L12" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M12" s="3">
         <v>2000</v>
       </c>
       <c r="N12" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O12" s="3">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="P12" s="3">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="Q12" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="T12" s="3">
+        <v>2</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:23">
+      <c r="X12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:24">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -2018,13 +2083,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2033,43 +2098,44 @@
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>14000</v>
+        <v>989999</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
         <v>1</v>
       </c>
       <c r="K13" s="3">
+        <v>405</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="M13" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N13" s="3">
+        <v>20</v>
+      </c>
+      <c r="O13" s="3">
+        <v>90</v>
+      </c>
+      <c r="P13" s="3">
+        <v>35</v>
+      </c>
+      <c r="Q13" s="3">
         <v>600</v>
       </c>
-      <c r="L13" s="3">
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3">
         <v>1</v>
       </c>
-      <c r="M13" s="3">
-        <v>4000</v>
-      </c>
-      <c r="N13" s="3">
-        <v>7</v>
-      </c>
-      <c r="O13" s="3">
-        <v>80</v>
-      </c>
-      <c r="P13" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>500</v>
-      </c>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3">
-        <v>1</v>
-      </c>
-      <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:23">
+      <c r="X13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:24">
       <c r="A14" s="3">
         <v>10</v>
       </c>
@@ -2077,13 +2143,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -2092,39 +2158,44 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>7000</v>
+        <v>1589600</v>
       </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>1</v>
+      </c>
       <c r="K14" s="3">
-        <v>200</v>
+        <v>566</v>
       </c>
       <c r="L14" s="3">
-        <v>0.15</v>
+        <v>0.07</v>
       </c>
       <c r="M14" s="3">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="N14" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O14" s="3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P14" s="3">
         <v>30</v>
       </c>
       <c r="Q14" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
+      <c r="T14" s="3">
+        <v>1</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:23">
+      <c r="X14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:24">
       <c r="A15" s="3">
         <v>11</v>
       </c>
@@ -2132,13 +2203,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -2147,39 +2218,46 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>7000</v>
+        <v>3960000</v>
       </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
       <c r="K15" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="L15" s="3">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="M15" s="3">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N15" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O15" s="3">
         <v>90</v>
       </c>
       <c r="P15" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="3">
-        <v>600</v>
-      </c>
-      <c r="R15" s="3"/>
+        <v>200</v>
+      </c>
+      <c r="R15" s="3">
+        <v>10</v>
+      </c>
       <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="T15" s="3">
+        <v>1</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:23">
+      <c r="X15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:24">
       <c r="A16" s="3">
         <v>12</v>
       </c>
@@ -2187,13 +2265,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
@@ -2202,39 +2280,44 @@
         <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>7000</v>
+        <v>7959000</v>
       </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
       <c r="K16" s="3">
-        <v>200</v>
+        <v>850</v>
       </c>
       <c r="L16" s="3">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="M16" s="3">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N16" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O16" s="3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P16" s="3">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q16" s="3">
         <v>600</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
+      <c r="T16" s="3">
+        <v>2</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:23">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:24">
       <c r="A17" s="3">
         <v>13</v>
       </c>
@@ -2242,13 +2325,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E17" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
@@ -2257,188 +2340,446 @@
         <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>10000</v>
+        <v>9999999</v>
       </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>1</v>
+      </c>
       <c r="K17" s="3">
-        <v>500</v>
+        <v>999</v>
       </c>
       <c r="L17" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="M17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>200</v>
+      </c>
+      <c r="O17" s="3">
+        <v>85</v>
+      </c>
+      <c r="P17" s="3">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>800</v>
+      </c>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="T17" s="3">
         <v>1</v>
       </c>
-      <c r="M17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3">
-        <v>90</v>
-      </c>
-      <c r="P17" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>200</v>
-      </c>
-      <c r="R17" s="3">
-        <v>8</v>
-      </c>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
+      <c r="X17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:24">
+      <c r="A18" s="3">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
+        <v>14</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1188</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>105</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>200</v>
+      </c>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5">
+        <v>3</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="5">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>200</v>
+      </c>
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5">
+        <v>1299</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="M19" s="5">
+        <v>3000</v>
+      </c>
+      <c r="N19" s="5">
+        <v>15</v>
+      </c>
+      <c r="O19" s="5">
+        <v>80</v>
+      </c>
+      <c r="P19" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>650</v>
+      </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20" s="3">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="5">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5">
+        <v>999</v>
+      </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1999</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="M20" s="5">
+        <v>4000</v>
+      </c>
+      <c r="N20" s="5">
+        <v>300</v>
+      </c>
+      <c r="O20" s="5">
+        <v>85</v>
+      </c>
+      <c r="P20" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>850</v>
+      </c>
       <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-    </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="S20" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21" s="3">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>500</v>
+      </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
+      <c r="J21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1360</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="M21" s="5">
+        <v>3000</v>
+      </c>
+      <c r="N21" s="5">
+        <v>22</v>
+      </c>
+      <c r="O21" s="5">
+        <v>90</v>
+      </c>
+      <c r="P21" s="5">
+        <v>40</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>650</v>
+      </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
-    </row>
-    <row r="22" spans="1:23">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="T21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3">
+        <v>18</v>
+      </c>
+      <c r="C22" s="5">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="5">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
+        <v>699</v>
+      </c>
       <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
+      <c r="J22" s="3">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1599</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M22" s="5">
+        <v>3000</v>
+      </c>
+      <c r="N22" s="5">
+        <v>14</v>
+      </c>
+      <c r="O22" s="5">
+        <v>90</v>
+      </c>
+      <c r="P22" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>200</v>
+      </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
-    </row>
-    <row r="23" spans="1:23">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="T22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>19</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="5">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
+        <v>499</v>
+      </c>
       <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
+      <c r="J23" s="3">
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1321</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="M23" s="5">
+        <v>3000</v>
+      </c>
+      <c r="N23" s="5">
+        <v>13</v>
+      </c>
+      <c r="O23" s="5">
+        <v>100</v>
+      </c>
+      <c r="P23" s="5">
+        <v>40</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>500</v>
+      </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
-    </row>
-    <row r="24" spans="1:23">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="T23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="5">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="5">
+        <v>4</v>
+      </c>
+      <c r="F24" s="5">
+        <v>2</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5">
+        <v>100</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
+      <c r="K24" s="5">
+        <v>1000</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="5">
+        <v>2000</v>
+      </c>
+      <c r="N24" s="5">
+        <v>70</v>
+      </c>
+      <c r="O24" s="5">
+        <v>100</v>
+      </c>
+      <c r="P24" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>150</v>
+      </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="T24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2459,7 +2800,7 @@
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2480,7 +2821,7 @@
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2501,7 +2842,7 @@
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2509,7 +2850,9 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="H28" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -2522,7 +2865,7 @@
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2543,7 +2886,7 @@
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2564,7 +2907,7 @@
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2585,7 +2928,7 @@
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -11323,6 +11666,24 @@
     </row>
     <row r="448" spans="1:19">
       <c r="A448" s="5"/>
+      <c r="B448" s="5"/>
+      <c r="C448" s="5"/>
+      <c r="D448" s="5"/>
+      <c r="E448" s="5"/>
+      <c r="F448" s="5"/>
+      <c r="G448" s="5"/>
+      <c r="H448" s="5"/>
+      <c r="I448" s="5"/>
+      <c r="J448" s="5"/>
+      <c r="K448" s="5"/>
+      <c r="L448" s="5"/>
+      <c r="M448" s="5"/>
+      <c r="N448" s="5"/>
+      <c r="O448" s="5"/>
+      <c r="P448" s="5"/>
+      <c r="Q448" s="5"/>
+      <c r="R448" s="5"/>
+      <c r="S448" s="5"/>
     </row>
     <row r="449" spans="1:1">
       <c r="A449" s="5"/>
@@ -11804,8 +12165,11 @@
     <row r="608" spans="1:1">
       <c r="A608" s="5"/>
     </row>
+    <row r="609" spans="1:1">
+      <c r="A609" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L609" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
